--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1004"/>
+  <dimension ref="A1:J504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8585,7526 +8585,26 @@
       <c r="I502" s="7" t="n"/>
       <c r="J502" s="4" t="n"/>
     </row>
-    <row r="503" ht="22" customHeight="1">
-      <c r="A503" s="3">
-        <f>IF(C503="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B503" s="3" t="n"/>
-      <c r="C503" s="3" t="n"/>
-      <c r="D503" s="4" t="n"/>
-      <c r="E503" s="4" t="n"/>
-      <c r="F503" s="5" t="n"/>
-      <c r="G503" s="6" t="n"/>
-      <c r="H503" s="4" t="n"/>
-      <c r="I503" s="7" t="n"/>
-      <c r="J503" s="4" t="n"/>
-    </row>
-    <row r="504" ht="22" customHeight="1">
-      <c r="A504" s="3">
-        <f>IF(C504="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B504" s="3" t="n"/>
-      <c r="C504" s="3" t="n"/>
-      <c r="D504" s="4" t="n"/>
-      <c r="E504" s="4" t="n"/>
-      <c r="F504" s="5" t="n"/>
-      <c r="G504" s="6" t="n"/>
-      <c r="H504" s="4" t="n"/>
-      <c r="I504" s="7" t="n"/>
-      <c r="J504" s="4" t="n"/>
-    </row>
-    <row r="505" ht="22" customHeight="1">
-      <c r="A505" s="3">
-        <f>IF(C505="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B505" s="3" t="n"/>
-      <c r="C505" s="3" t="n"/>
-      <c r="D505" s="4" t="n"/>
-      <c r="E505" s="4" t="n"/>
-      <c r="F505" s="5" t="n"/>
-      <c r="G505" s="6" t="n"/>
-      <c r="H505" s="4" t="n"/>
-      <c r="I505" s="7" t="n"/>
-      <c r="J505" s="4" t="n"/>
-    </row>
-    <row r="506" ht="22" customHeight="1">
-      <c r="A506" s="3">
-        <f>IF(C506="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B506" s="3" t="n"/>
-      <c r="C506" s="3" t="n"/>
-      <c r="D506" s="4" t="n"/>
-      <c r="E506" s="4" t="n"/>
-      <c r="F506" s="5" t="n"/>
-      <c r="G506" s="6" t="n"/>
-      <c r="H506" s="4" t="n"/>
-      <c r="I506" s="7" t="n"/>
-      <c r="J506" s="4" t="n"/>
-    </row>
-    <row r="507" ht="22" customHeight="1">
-      <c r="A507" s="3">
-        <f>IF(C507="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B507" s="3" t="n"/>
-      <c r="C507" s="3" t="n"/>
-      <c r="D507" s="4" t="n"/>
-      <c r="E507" s="4" t="n"/>
-      <c r="F507" s="5" t="n"/>
-      <c r="G507" s="6" t="n"/>
-      <c r="H507" s="4" t="n"/>
-      <c r="I507" s="7" t="n"/>
-      <c r="J507" s="4" t="n"/>
-    </row>
-    <row r="508" ht="22" customHeight="1">
-      <c r="A508" s="3">
-        <f>IF(C508="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B508" s="3" t="n"/>
-      <c r="C508" s="3" t="n"/>
-      <c r="D508" s="4" t="n"/>
-      <c r="E508" s="4" t="n"/>
-      <c r="F508" s="5" t="n"/>
-      <c r="G508" s="6" t="n"/>
-      <c r="H508" s="4" t="n"/>
-      <c r="I508" s="7" t="n"/>
-      <c r="J508" s="4" t="n"/>
-    </row>
-    <row r="509" ht="22" customHeight="1">
-      <c r="A509" s="3">
-        <f>IF(C509="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B509" s="3" t="n"/>
-      <c r="C509" s="3" t="n"/>
-      <c r="D509" s="4" t="n"/>
-      <c r="E509" s="4" t="n"/>
-      <c r="F509" s="5" t="n"/>
-      <c r="G509" s="6" t="n"/>
-      <c r="H509" s="4" t="n"/>
-      <c r="I509" s="7" t="n"/>
-      <c r="J509" s="4" t="n"/>
-    </row>
-    <row r="510" ht="22" customHeight="1">
-      <c r="A510" s="3">
-        <f>IF(C510="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B510" s="3" t="n"/>
-      <c r="C510" s="3" t="n"/>
-      <c r="D510" s="4" t="n"/>
-      <c r="E510" s="4" t="n"/>
-      <c r="F510" s="5" t="n"/>
-      <c r="G510" s="6" t="n"/>
-      <c r="H510" s="4" t="n"/>
-      <c r="I510" s="7" t="n"/>
-      <c r="J510" s="4" t="n"/>
-    </row>
-    <row r="511" ht="22" customHeight="1">
-      <c r="A511" s="3">
-        <f>IF(C511="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B511" s="3" t="n"/>
-      <c r="C511" s="3" t="n"/>
-      <c r="D511" s="4" t="n"/>
-      <c r="E511" s="4" t="n"/>
-      <c r="F511" s="5" t="n"/>
-      <c r="G511" s="6" t="n"/>
-      <c r="H511" s="4" t="n"/>
-      <c r="I511" s="7" t="n"/>
-      <c r="J511" s="4" t="n"/>
-    </row>
-    <row r="512" ht="22" customHeight="1">
-      <c r="A512" s="3">
-        <f>IF(C512="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B512" s="3" t="n"/>
-      <c r="C512" s="3" t="n"/>
-      <c r="D512" s="4" t="n"/>
-      <c r="E512" s="4" t="n"/>
-      <c r="F512" s="5" t="n"/>
-      <c r="G512" s="6" t="n"/>
-      <c r="H512" s="4" t="n"/>
-      <c r="I512" s="7" t="n"/>
-      <c r="J512" s="4" t="n"/>
-    </row>
-    <row r="513" ht="22" customHeight="1">
-      <c r="A513" s="3">
-        <f>IF(C513="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B513" s="3" t="n"/>
-      <c r="C513" s="3" t="n"/>
-      <c r="D513" s="4" t="n"/>
-      <c r="E513" s="4" t="n"/>
-      <c r="F513" s="5" t="n"/>
-      <c r="G513" s="6" t="n"/>
-      <c r="H513" s="4" t="n"/>
-      <c r="I513" s="7" t="n"/>
-      <c r="J513" s="4" t="n"/>
-    </row>
-    <row r="514" ht="22" customHeight="1">
-      <c r="A514" s="3">
-        <f>IF(C514="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B514" s="3" t="n"/>
-      <c r="C514" s="3" t="n"/>
-      <c r="D514" s="4" t="n"/>
-      <c r="E514" s="4" t="n"/>
-      <c r="F514" s="5" t="n"/>
-      <c r="G514" s="6" t="n"/>
-      <c r="H514" s="4" t="n"/>
-      <c r="I514" s="7" t="n"/>
-      <c r="J514" s="4" t="n"/>
-    </row>
-    <row r="515" ht="22" customHeight="1">
-      <c r="A515" s="3">
-        <f>IF(C515="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B515" s="3" t="n"/>
-      <c r="C515" s="3" t="n"/>
-      <c r="D515" s="4" t="n"/>
-      <c r="E515" s="4" t="n"/>
-      <c r="F515" s="5" t="n"/>
-      <c r="G515" s="6" t="n"/>
-      <c r="H515" s="4" t="n"/>
-      <c r="I515" s="7" t="n"/>
-      <c r="J515" s="4" t="n"/>
-    </row>
-    <row r="516" ht="22" customHeight="1">
-      <c r="A516" s="3">
-        <f>IF(C516="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B516" s="3" t="n"/>
-      <c r="C516" s="3" t="n"/>
-      <c r="D516" s="4" t="n"/>
-      <c r="E516" s="4" t="n"/>
-      <c r="F516" s="5" t="n"/>
-      <c r="G516" s="6" t="n"/>
-      <c r="H516" s="4" t="n"/>
-      <c r="I516" s="7" t="n"/>
-      <c r="J516" s="4" t="n"/>
-    </row>
-    <row r="517" ht="22" customHeight="1">
-      <c r="A517" s="3">
-        <f>IF(C517="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B517" s="3" t="n"/>
-      <c r="C517" s="3" t="n"/>
-      <c r="D517" s="4" t="n"/>
-      <c r="E517" s="4" t="n"/>
-      <c r="F517" s="5" t="n"/>
-      <c r="G517" s="6" t="n"/>
-      <c r="H517" s="4" t="n"/>
-      <c r="I517" s="7" t="n"/>
-      <c r="J517" s="4" t="n"/>
-    </row>
-    <row r="518" ht="22" customHeight="1">
-      <c r="A518" s="3">
-        <f>IF(C518="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B518" s="3" t="n"/>
-      <c r="C518" s="3" t="n"/>
-      <c r="D518" s="4" t="n"/>
-      <c r="E518" s="4" t="n"/>
-      <c r="F518" s="5" t="n"/>
-      <c r="G518" s="6" t="n"/>
-      <c r="H518" s="4" t="n"/>
-      <c r="I518" s="7" t="n"/>
-      <c r="J518" s="4" t="n"/>
-    </row>
-    <row r="519" ht="22" customHeight="1">
-      <c r="A519" s="3">
-        <f>IF(C519="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B519" s="3" t="n"/>
-      <c r="C519" s="3" t="n"/>
-      <c r="D519" s="4" t="n"/>
-      <c r="E519" s="4" t="n"/>
-      <c r="F519" s="5" t="n"/>
-      <c r="G519" s="6" t="n"/>
-      <c r="H519" s="4" t="n"/>
-      <c r="I519" s="7" t="n"/>
-      <c r="J519" s="4" t="n"/>
-    </row>
-    <row r="520" ht="22" customHeight="1">
-      <c r="A520" s="3">
-        <f>IF(C520="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B520" s="3" t="n"/>
-      <c r="C520" s="3" t="n"/>
-      <c r="D520" s="4" t="n"/>
-      <c r="E520" s="4" t="n"/>
-      <c r="F520" s="5" t="n"/>
-      <c r="G520" s="6" t="n"/>
-      <c r="H520" s="4" t="n"/>
-      <c r="I520" s="7" t="n"/>
-      <c r="J520" s="4" t="n"/>
-    </row>
-    <row r="521" ht="22" customHeight="1">
-      <c r="A521" s="3">
-        <f>IF(C521="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B521" s="3" t="n"/>
-      <c r="C521" s="3" t="n"/>
-      <c r="D521" s="4" t="n"/>
-      <c r="E521" s="4" t="n"/>
-      <c r="F521" s="5" t="n"/>
-      <c r="G521" s="6" t="n"/>
-      <c r="H521" s="4" t="n"/>
-      <c r="I521" s="7" t="n"/>
-      <c r="J521" s="4" t="n"/>
-    </row>
-    <row r="522" ht="22" customHeight="1">
-      <c r="A522" s="3">
-        <f>IF(C522="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B522" s="3" t="n"/>
-      <c r="C522" s="3" t="n"/>
-      <c r="D522" s="4" t="n"/>
-      <c r="E522" s="4" t="n"/>
-      <c r="F522" s="5" t="n"/>
-      <c r="G522" s="6" t="n"/>
-      <c r="H522" s="4" t="n"/>
-      <c r="I522" s="7" t="n"/>
-      <c r="J522" s="4" t="n"/>
-    </row>
-    <row r="523" ht="22" customHeight="1">
-      <c r="A523" s="3">
-        <f>IF(C523="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B523" s="3" t="n"/>
-      <c r="C523" s="3" t="n"/>
-      <c r="D523" s="4" t="n"/>
-      <c r="E523" s="4" t="n"/>
-      <c r="F523" s="5" t="n"/>
-      <c r="G523" s="6" t="n"/>
-      <c r="H523" s="4" t="n"/>
-      <c r="I523" s="7" t="n"/>
-      <c r="J523" s="4" t="n"/>
-    </row>
-    <row r="524" ht="22" customHeight="1">
-      <c r="A524" s="3">
-        <f>IF(C524="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B524" s="3" t="n"/>
-      <c r="C524" s="3" t="n"/>
-      <c r="D524" s="4" t="n"/>
-      <c r="E524" s="4" t="n"/>
-      <c r="F524" s="5" t="n"/>
-      <c r="G524" s="6" t="n"/>
-      <c r="H524" s="4" t="n"/>
-      <c r="I524" s="7" t="n"/>
-      <c r="J524" s="4" t="n"/>
-    </row>
-    <row r="525" ht="22" customHeight="1">
-      <c r="A525" s="3">
-        <f>IF(C525="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B525" s="3" t="n"/>
-      <c r="C525" s="3" t="n"/>
-      <c r="D525" s="4" t="n"/>
-      <c r="E525" s="4" t="n"/>
-      <c r="F525" s="5" t="n"/>
-      <c r="G525" s="6" t="n"/>
-      <c r="H525" s="4" t="n"/>
-      <c r="I525" s="7" t="n"/>
-      <c r="J525" s="4" t="n"/>
-    </row>
-    <row r="526" ht="22" customHeight="1">
-      <c r="A526" s="3">
-        <f>IF(C526="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B526" s="3" t="n"/>
-      <c r="C526" s="3" t="n"/>
-      <c r="D526" s="4" t="n"/>
-      <c r="E526" s="4" t="n"/>
-      <c r="F526" s="5" t="n"/>
-      <c r="G526" s="6" t="n"/>
-      <c r="H526" s="4" t="n"/>
-      <c r="I526" s="7" t="n"/>
-      <c r="J526" s="4" t="n"/>
-    </row>
-    <row r="527" ht="22" customHeight="1">
-      <c r="A527" s="3">
-        <f>IF(C527="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B527" s="3" t="n"/>
-      <c r="C527" s="3" t="n"/>
-      <c r="D527" s="4" t="n"/>
-      <c r="E527" s="4" t="n"/>
-      <c r="F527" s="5" t="n"/>
-      <c r="G527" s="6" t="n"/>
-      <c r="H527" s="4" t="n"/>
-      <c r="I527" s="7" t="n"/>
-      <c r="J527" s="4" t="n"/>
-    </row>
-    <row r="528" ht="22" customHeight="1">
-      <c r="A528" s="3">
-        <f>IF(C528="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B528" s="3" t="n"/>
-      <c r="C528" s="3" t="n"/>
-      <c r="D528" s="4" t="n"/>
-      <c r="E528" s="4" t="n"/>
-      <c r="F528" s="5" t="n"/>
-      <c r="G528" s="6" t="n"/>
-      <c r="H528" s="4" t="n"/>
-      <c r="I528" s="7" t="n"/>
-      <c r="J528" s="4" t="n"/>
-    </row>
-    <row r="529" ht="22" customHeight="1">
-      <c r="A529" s="3">
-        <f>IF(C529="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B529" s="3" t="n"/>
-      <c r="C529" s="3" t="n"/>
-      <c r="D529" s="4" t="n"/>
-      <c r="E529" s="4" t="n"/>
-      <c r="F529" s="5" t="n"/>
-      <c r="G529" s="6" t="n"/>
-      <c r="H529" s="4" t="n"/>
-      <c r="I529" s="7" t="n"/>
-      <c r="J529" s="4" t="n"/>
-    </row>
-    <row r="530" ht="22" customHeight="1">
-      <c r="A530" s="3">
-        <f>IF(C530="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B530" s="3" t="n"/>
-      <c r="C530" s="3" t="n"/>
-      <c r="D530" s="4" t="n"/>
-      <c r="E530" s="4" t="n"/>
-      <c r="F530" s="5" t="n"/>
-      <c r="G530" s="6" t="n"/>
-      <c r="H530" s="4" t="n"/>
-      <c r="I530" s="7" t="n"/>
-      <c r="J530" s="4" t="n"/>
-    </row>
-    <row r="531" ht="22" customHeight="1">
-      <c r="A531" s="3">
-        <f>IF(C531="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B531" s="3" t="n"/>
-      <c r="C531" s="3" t="n"/>
-      <c r="D531" s="4" t="n"/>
-      <c r="E531" s="4" t="n"/>
-      <c r="F531" s="5" t="n"/>
-      <c r="G531" s="6" t="n"/>
-      <c r="H531" s="4" t="n"/>
-      <c r="I531" s="7" t="n"/>
-      <c r="J531" s="4" t="n"/>
-    </row>
-    <row r="532" ht="22" customHeight="1">
-      <c r="A532" s="3">
-        <f>IF(C532="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B532" s="3" t="n"/>
-      <c r="C532" s="3" t="n"/>
-      <c r="D532" s="4" t="n"/>
-      <c r="E532" s="4" t="n"/>
-      <c r="F532" s="5" t="n"/>
-      <c r="G532" s="6" t="n"/>
-      <c r="H532" s="4" t="n"/>
-      <c r="I532" s="7" t="n"/>
-      <c r="J532" s="4" t="n"/>
-    </row>
-    <row r="533" ht="22" customHeight="1">
-      <c r="A533" s="3">
-        <f>IF(C533="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B533" s="3" t="n"/>
-      <c r="C533" s="3" t="n"/>
-      <c r="D533" s="4" t="n"/>
-      <c r="E533" s="4" t="n"/>
-      <c r="F533" s="5" t="n"/>
-      <c r="G533" s="6" t="n"/>
-      <c r="H533" s="4" t="n"/>
-      <c r="I533" s="7" t="n"/>
-      <c r="J533" s="4" t="n"/>
-    </row>
-    <row r="534" ht="22" customHeight="1">
-      <c r="A534" s="3">
-        <f>IF(C534="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B534" s="3" t="n"/>
-      <c r="C534" s="3" t="n"/>
-      <c r="D534" s="4" t="n"/>
-      <c r="E534" s="4" t="n"/>
-      <c r="F534" s="5" t="n"/>
-      <c r="G534" s="6" t="n"/>
-      <c r="H534" s="4" t="n"/>
-      <c r="I534" s="7" t="n"/>
-      <c r="J534" s="4" t="n"/>
-    </row>
-    <row r="535" ht="22" customHeight="1">
-      <c r="A535" s="3">
-        <f>IF(C535="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B535" s="3" t="n"/>
-      <c r="C535" s="3" t="n"/>
-      <c r="D535" s="4" t="n"/>
-      <c r="E535" s="4" t="n"/>
-      <c r="F535" s="5" t="n"/>
-      <c r="G535" s="6" t="n"/>
-      <c r="H535" s="4" t="n"/>
-      <c r="I535" s="7" t="n"/>
-      <c r="J535" s="4" t="n"/>
-    </row>
-    <row r="536" ht="22" customHeight="1">
-      <c r="A536" s="3">
-        <f>IF(C536="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B536" s="3" t="n"/>
-      <c r="C536" s="3" t="n"/>
-      <c r="D536" s="4" t="n"/>
-      <c r="E536" s="4" t="n"/>
-      <c r="F536" s="5" t="n"/>
-      <c r="G536" s="6" t="n"/>
-      <c r="H536" s="4" t="n"/>
-      <c r="I536" s="7" t="n"/>
-      <c r="J536" s="4" t="n"/>
-    </row>
-    <row r="537" ht="22" customHeight="1">
-      <c r="A537" s="3">
-        <f>IF(C537="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B537" s="3" t="n"/>
-      <c r="C537" s="3" t="n"/>
-      <c r="D537" s="4" t="n"/>
-      <c r="E537" s="4" t="n"/>
-      <c r="F537" s="5" t="n"/>
-      <c r="G537" s="6" t="n"/>
-      <c r="H537" s="4" t="n"/>
-      <c r="I537" s="7" t="n"/>
-      <c r="J537" s="4" t="n"/>
-    </row>
-    <row r="538" ht="22" customHeight="1">
-      <c r="A538" s="3">
-        <f>IF(C538="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B538" s="3" t="n"/>
-      <c r="C538" s="3" t="n"/>
-      <c r="D538" s="4" t="n"/>
-      <c r="E538" s="4" t="n"/>
-      <c r="F538" s="5" t="n"/>
-      <c r="G538" s="6" t="n"/>
-      <c r="H538" s="4" t="n"/>
-      <c r="I538" s="7" t="n"/>
-      <c r="J538" s="4" t="n"/>
-    </row>
-    <row r="539" ht="22" customHeight="1">
-      <c r="A539" s="3">
-        <f>IF(C539="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B539" s="3" t="n"/>
-      <c r="C539" s="3" t="n"/>
-      <c r="D539" s="4" t="n"/>
-      <c r="E539" s="4" t="n"/>
-      <c r="F539" s="5" t="n"/>
-      <c r="G539" s="6" t="n"/>
-      <c r="H539" s="4" t="n"/>
-      <c r="I539" s="7" t="n"/>
-      <c r="J539" s="4" t="n"/>
-    </row>
-    <row r="540" ht="22" customHeight="1">
-      <c r="A540" s="3">
-        <f>IF(C540="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B540" s="3" t="n"/>
-      <c r="C540" s="3" t="n"/>
-      <c r="D540" s="4" t="n"/>
-      <c r="E540" s="4" t="n"/>
-      <c r="F540" s="5" t="n"/>
-      <c r="G540" s="6" t="n"/>
-      <c r="H540" s="4" t="n"/>
-      <c r="I540" s="7" t="n"/>
-      <c r="J540" s="4" t="n"/>
-    </row>
-    <row r="541" ht="22" customHeight="1">
-      <c r="A541" s="3">
-        <f>IF(C541="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B541" s="3" t="n"/>
-      <c r="C541" s="3" t="n"/>
-      <c r="D541" s="4" t="n"/>
-      <c r="E541" s="4" t="n"/>
-      <c r="F541" s="5" t="n"/>
-      <c r="G541" s="6" t="n"/>
-      <c r="H541" s="4" t="n"/>
-      <c r="I541" s="7" t="n"/>
-      <c r="J541" s="4" t="n"/>
-    </row>
-    <row r="542" ht="22" customHeight="1">
-      <c r="A542" s="3">
-        <f>IF(C542="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B542" s="3" t="n"/>
-      <c r="C542" s="3" t="n"/>
-      <c r="D542" s="4" t="n"/>
-      <c r="E542" s="4" t="n"/>
-      <c r="F542" s="5" t="n"/>
-      <c r="G542" s="6" t="n"/>
-      <c r="H542" s="4" t="n"/>
-      <c r="I542" s="7" t="n"/>
-      <c r="J542" s="4" t="n"/>
-    </row>
-    <row r="543" ht="22" customHeight="1">
-      <c r="A543" s="3">
-        <f>IF(C543="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B543" s="3" t="n"/>
-      <c r="C543" s="3" t="n"/>
-      <c r="D543" s="4" t="n"/>
-      <c r="E543" s="4" t="n"/>
-      <c r="F543" s="5" t="n"/>
-      <c r="G543" s="6" t="n"/>
-      <c r="H543" s="4" t="n"/>
-      <c r="I543" s="7" t="n"/>
-      <c r="J543" s="4" t="n"/>
-    </row>
-    <row r="544" ht="22" customHeight="1">
-      <c r="A544" s="3">
-        <f>IF(C544="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B544" s="3" t="n"/>
-      <c r="C544" s="3" t="n"/>
-      <c r="D544" s="4" t="n"/>
-      <c r="E544" s="4" t="n"/>
-      <c r="F544" s="5" t="n"/>
-      <c r="G544" s="6" t="n"/>
-      <c r="H544" s="4" t="n"/>
-      <c r="I544" s="7" t="n"/>
-      <c r="J544" s="4" t="n"/>
-    </row>
-    <row r="545" ht="22" customHeight="1">
-      <c r="A545" s="3">
-        <f>IF(C545="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B545" s="3" t="n"/>
-      <c r="C545" s="3" t="n"/>
-      <c r="D545" s="4" t="n"/>
-      <c r="E545" s="4" t="n"/>
-      <c r="F545" s="5" t="n"/>
-      <c r="G545" s="6" t="n"/>
-      <c r="H545" s="4" t="n"/>
-      <c r="I545" s="7" t="n"/>
-      <c r="J545" s="4" t="n"/>
-    </row>
-    <row r="546" ht="22" customHeight="1">
-      <c r="A546" s="3">
-        <f>IF(C546="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B546" s="3" t="n"/>
-      <c r="C546" s="3" t="n"/>
-      <c r="D546" s="4" t="n"/>
-      <c r="E546" s="4" t="n"/>
-      <c r="F546" s="5" t="n"/>
-      <c r="G546" s="6" t="n"/>
-      <c r="H546" s="4" t="n"/>
-      <c r="I546" s="7" t="n"/>
-      <c r="J546" s="4" t="n"/>
-    </row>
-    <row r="547" ht="22" customHeight="1">
-      <c r="A547" s="3">
-        <f>IF(C547="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B547" s="3" t="n"/>
-      <c r="C547" s="3" t="n"/>
-      <c r="D547" s="4" t="n"/>
-      <c r="E547" s="4" t="n"/>
-      <c r="F547" s="5" t="n"/>
-      <c r="G547" s="6" t="n"/>
-      <c r="H547" s="4" t="n"/>
-      <c r="I547" s="7" t="n"/>
-      <c r="J547" s="4" t="n"/>
-    </row>
-    <row r="548" ht="22" customHeight="1">
-      <c r="A548" s="3">
-        <f>IF(C548="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B548" s="3" t="n"/>
-      <c r="C548" s="3" t="n"/>
-      <c r="D548" s="4" t="n"/>
-      <c r="E548" s="4" t="n"/>
-      <c r="F548" s="5" t="n"/>
-      <c r="G548" s="6" t="n"/>
-      <c r="H548" s="4" t="n"/>
-      <c r="I548" s="7" t="n"/>
-      <c r="J548" s="4" t="n"/>
-    </row>
-    <row r="549" ht="22" customHeight="1">
-      <c r="A549" s="3">
-        <f>IF(C549="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B549" s="3" t="n"/>
-      <c r="C549" s="3" t="n"/>
-      <c r="D549" s="4" t="n"/>
-      <c r="E549" s="4" t="n"/>
-      <c r="F549" s="5" t="n"/>
-      <c r="G549" s="6" t="n"/>
-      <c r="H549" s="4" t="n"/>
-      <c r="I549" s="7" t="n"/>
-      <c r="J549" s="4" t="n"/>
-    </row>
-    <row r="550" ht="22" customHeight="1">
-      <c r="A550" s="3">
-        <f>IF(C550="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B550" s="3" t="n"/>
-      <c r="C550" s="3" t="n"/>
-      <c r="D550" s="4" t="n"/>
-      <c r="E550" s="4" t="n"/>
-      <c r="F550" s="5" t="n"/>
-      <c r="G550" s="6" t="n"/>
-      <c r="H550" s="4" t="n"/>
-      <c r="I550" s="7" t="n"/>
-      <c r="J550" s="4" t="n"/>
-    </row>
-    <row r="551" ht="22" customHeight="1">
-      <c r="A551" s="3">
-        <f>IF(C551="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B551" s="3" t="n"/>
-      <c r="C551" s="3" t="n"/>
-      <c r="D551" s="4" t="n"/>
-      <c r="E551" s="4" t="n"/>
-      <c r="F551" s="5" t="n"/>
-      <c r="G551" s="6" t="n"/>
-      <c r="H551" s="4" t="n"/>
-      <c r="I551" s="7" t="n"/>
-      <c r="J551" s="4" t="n"/>
-    </row>
-    <row r="552" ht="22" customHeight="1">
-      <c r="A552" s="3">
-        <f>IF(C552="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B552" s="3" t="n"/>
-      <c r="C552" s="3" t="n"/>
-      <c r="D552" s="4" t="n"/>
-      <c r="E552" s="4" t="n"/>
-      <c r="F552" s="5" t="n"/>
-      <c r="G552" s="6" t="n"/>
-      <c r="H552" s="4" t="n"/>
-      <c r="I552" s="7" t="n"/>
-      <c r="J552" s="4" t="n"/>
-    </row>
-    <row r="553" ht="22" customHeight="1">
-      <c r="A553" s="3">
-        <f>IF(C553="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B553" s="3" t="n"/>
-      <c r="C553" s="3" t="n"/>
-      <c r="D553" s="4" t="n"/>
-      <c r="E553" s="4" t="n"/>
-      <c r="F553" s="5" t="n"/>
-      <c r="G553" s="6" t="n"/>
-      <c r="H553" s="4" t="n"/>
-      <c r="I553" s="7" t="n"/>
-      <c r="J553" s="4" t="n"/>
-    </row>
-    <row r="554" ht="22" customHeight="1">
-      <c r="A554" s="3">
-        <f>IF(C554="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B554" s="3" t="n"/>
-      <c r="C554" s="3" t="n"/>
-      <c r="D554" s="4" t="n"/>
-      <c r="E554" s="4" t="n"/>
-      <c r="F554" s="5" t="n"/>
-      <c r="G554" s="6" t="n"/>
-      <c r="H554" s="4" t="n"/>
-      <c r="I554" s="7" t="n"/>
-      <c r="J554" s="4" t="n"/>
-    </row>
-    <row r="555" ht="22" customHeight="1">
-      <c r="A555" s="3">
-        <f>IF(C555="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B555" s="3" t="n"/>
-      <c r="C555" s="3" t="n"/>
-      <c r="D555" s="4" t="n"/>
-      <c r="E555" s="4" t="n"/>
-      <c r="F555" s="5" t="n"/>
-      <c r="G555" s="6" t="n"/>
-      <c r="H555" s="4" t="n"/>
-      <c r="I555" s="7" t="n"/>
-      <c r="J555" s="4" t="n"/>
-    </row>
-    <row r="556" ht="22" customHeight="1">
-      <c r="A556" s="3">
-        <f>IF(C556="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B556" s="3" t="n"/>
-      <c r="C556" s="3" t="n"/>
-      <c r="D556" s="4" t="n"/>
-      <c r="E556" s="4" t="n"/>
-      <c r="F556" s="5" t="n"/>
-      <c r="G556" s="6" t="n"/>
-      <c r="H556" s="4" t="n"/>
-      <c r="I556" s="7" t="n"/>
-      <c r="J556" s="4" t="n"/>
-    </row>
-    <row r="557" ht="22" customHeight="1">
-      <c r="A557" s="3">
-        <f>IF(C557="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B557" s="3" t="n"/>
-      <c r="C557" s="3" t="n"/>
-      <c r="D557" s="4" t="n"/>
-      <c r="E557" s="4" t="n"/>
-      <c r="F557" s="5" t="n"/>
-      <c r="G557" s="6" t="n"/>
-      <c r="H557" s="4" t="n"/>
-      <c r="I557" s="7" t="n"/>
-      <c r="J557" s="4" t="n"/>
-    </row>
-    <row r="558" ht="22" customHeight="1">
-      <c r="A558" s="3">
-        <f>IF(C558="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B558" s="3" t="n"/>
-      <c r="C558" s="3" t="n"/>
-      <c r="D558" s="4" t="n"/>
-      <c r="E558" s="4" t="n"/>
-      <c r="F558" s="5" t="n"/>
-      <c r="G558" s="6" t="n"/>
-      <c r="H558" s="4" t="n"/>
-      <c r="I558" s="7" t="n"/>
-      <c r="J558" s="4" t="n"/>
-    </row>
-    <row r="559" ht="22" customHeight="1">
-      <c r="A559" s="3">
-        <f>IF(C559="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B559" s="3" t="n"/>
-      <c r="C559" s="3" t="n"/>
-      <c r="D559" s="4" t="n"/>
-      <c r="E559" s="4" t="n"/>
-      <c r="F559" s="5" t="n"/>
-      <c r="G559" s="6" t="n"/>
-      <c r="H559" s="4" t="n"/>
-      <c r="I559" s="7" t="n"/>
-      <c r="J559" s="4" t="n"/>
-    </row>
-    <row r="560" ht="22" customHeight="1">
-      <c r="A560" s="3">
-        <f>IF(C560="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B560" s="3" t="n"/>
-      <c r="C560" s="3" t="n"/>
-      <c r="D560" s="4" t="n"/>
-      <c r="E560" s="4" t="n"/>
-      <c r="F560" s="5" t="n"/>
-      <c r="G560" s="6" t="n"/>
-      <c r="H560" s="4" t="n"/>
-      <c r="I560" s="7" t="n"/>
-      <c r="J560" s="4" t="n"/>
-    </row>
-    <row r="561" ht="22" customHeight="1">
-      <c r="A561" s="3">
-        <f>IF(C561="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B561" s="3" t="n"/>
-      <c r="C561" s="3" t="n"/>
-      <c r="D561" s="4" t="n"/>
-      <c r="E561" s="4" t="n"/>
-      <c r="F561" s="5" t="n"/>
-      <c r="G561" s="6" t="n"/>
-      <c r="H561" s="4" t="n"/>
-      <c r="I561" s="7" t="n"/>
-      <c r="J561" s="4" t="n"/>
-    </row>
-    <row r="562" ht="22" customHeight="1">
-      <c r="A562" s="3">
-        <f>IF(C562="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B562" s="3" t="n"/>
-      <c r="C562" s="3" t="n"/>
-      <c r="D562" s="4" t="n"/>
-      <c r="E562" s="4" t="n"/>
-      <c r="F562" s="5" t="n"/>
-      <c r="G562" s="6" t="n"/>
-      <c r="H562" s="4" t="n"/>
-      <c r="I562" s="7" t="n"/>
-      <c r="J562" s="4" t="n"/>
-    </row>
-    <row r="563" ht="22" customHeight="1">
-      <c r="A563" s="3">
-        <f>IF(C563="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B563" s="3" t="n"/>
-      <c r="C563" s="3" t="n"/>
-      <c r="D563" s="4" t="n"/>
-      <c r="E563" s="4" t="n"/>
-      <c r="F563" s="5" t="n"/>
-      <c r="G563" s="6" t="n"/>
-      <c r="H563" s="4" t="n"/>
-      <c r="I563" s="7" t="n"/>
-      <c r="J563" s="4" t="n"/>
-    </row>
-    <row r="564" ht="22" customHeight="1">
-      <c r="A564" s="3">
-        <f>IF(C564="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B564" s="3" t="n"/>
-      <c r="C564" s="3" t="n"/>
-      <c r="D564" s="4" t="n"/>
-      <c r="E564" s="4" t="n"/>
-      <c r="F564" s="5" t="n"/>
-      <c r="G564" s="6" t="n"/>
-      <c r="H564" s="4" t="n"/>
-      <c r="I564" s="7" t="n"/>
-      <c r="J564" s="4" t="n"/>
-    </row>
-    <row r="565" ht="22" customHeight="1">
-      <c r="A565" s="3">
-        <f>IF(C565="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B565" s="3" t="n"/>
-      <c r="C565" s="3" t="n"/>
-      <c r="D565" s="4" t="n"/>
-      <c r="E565" s="4" t="n"/>
-      <c r="F565" s="5" t="n"/>
-      <c r="G565" s="6" t="n"/>
-      <c r="H565" s="4" t="n"/>
-      <c r="I565" s="7" t="n"/>
-      <c r="J565" s="4" t="n"/>
-    </row>
-    <row r="566" ht="22" customHeight="1">
-      <c r="A566" s="3">
-        <f>IF(C566="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B566" s="3" t="n"/>
-      <c r="C566" s="3" t="n"/>
-      <c r="D566" s="4" t="n"/>
-      <c r="E566" s="4" t="n"/>
-      <c r="F566" s="5" t="n"/>
-      <c r="G566" s="6" t="n"/>
-      <c r="H566" s="4" t="n"/>
-      <c r="I566" s="7" t="n"/>
-      <c r="J566" s="4" t="n"/>
-    </row>
-    <row r="567" ht="22" customHeight="1">
-      <c r="A567" s="3">
-        <f>IF(C567="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B567" s="3" t="n"/>
-      <c r="C567" s="3" t="n"/>
-      <c r="D567" s="4" t="n"/>
-      <c r="E567" s="4" t="n"/>
-      <c r="F567" s="5" t="n"/>
-      <c r="G567" s="6" t="n"/>
-      <c r="H567" s="4" t="n"/>
-      <c r="I567" s="7" t="n"/>
-      <c r="J567" s="4" t="n"/>
-    </row>
-    <row r="568" ht="22" customHeight="1">
-      <c r="A568" s="3">
-        <f>IF(C568="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B568" s="3" t="n"/>
-      <c r="C568" s="3" t="n"/>
-      <c r="D568" s="4" t="n"/>
-      <c r="E568" s="4" t="n"/>
-      <c r="F568" s="5" t="n"/>
-      <c r="G568" s="6" t="n"/>
-      <c r="H568" s="4" t="n"/>
-      <c r="I568" s="7" t="n"/>
-      <c r="J568" s="4" t="n"/>
-    </row>
-    <row r="569" ht="22" customHeight="1">
-      <c r="A569" s="3">
-        <f>IF(C569="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B569" s="3" t="n"/>
-      <c r="C569" s="3" t="n"/>
-      <c r="D569" s="4" t="n"/>
-      <c r="E569" s="4" t="n"/>
-      <c r="F569" s="5" t="n"/>
-      <c r="G569" s="6" t="n"/>
-      <c r="H569" s="4" t="n"/>
-      <c r="I569" s="7" t="n"/>
-      <c r="J569" s="4" t="n"/>
-    </row>
-    <row r="570" ht="22" customHeight="1">
-      <c r="A570" s="3">
-        <f>IF(C570="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B570" s="3" t="n"/>
-      <c r="C570" s="3" t="n"/>
-      <c r="D570" s="4" t="n"/>
-      <c r="E570" s="4" t="n"/>
-      <c r="F570" s="5" t="n"/>
-      <c r="G570" s="6" t="n"/>
-      <c r="H570" s="4" t="n"/>
-      <c r="I570" s="7" t="n"/>
-      <c r="J570" s="4" t="n"/>
-    </row>
-    <row r="571" ht="22" customHeight="1">
-      <c r="A571" s="3">
-        <f>IF(C571="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B571" s="3" t="n"/>
-      <c r="C571" s="3" t="n"/>
-      <c r="D571" s="4" t="n"/>
-      <c r="E571" s="4" t="n"/>
-      <c r="F571" s="5" t="n"/>
-      <c r="G571" s="6" t="n"/>
-      <c r="H571" s="4" t="n"/>
-      <c r="I571" s="7" t="n"/>
-      <c r="J571" s="4" t="n"/>
-    </row>
-    <row r="572" ht="22" customHeight="1">
-      <c r="A572" s="3">
-        <f>IF(C572="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B572" s="3" t="n"/>
-      <c r="C572" s="3" t="n"/>
-      <c r="D572" s="4" t="n"/>
-      <c r="E572" s="4" t="n"/>
-      <c r="F572" s="5" t="n"/>
-      <c r="G572" s="6" t="n"/>
-      <c r="H572" s="4" t="n"/>
-      <c r="I572" s="7" t="n"/>
-      <c r="J572" s="4" t="n"/>
-    </row>
-    <row r="573" ht="22" customHeight="1">
-      <c r="A573" s="3">
-        <f>IF(C573="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B573" s="3" t="n"/>
-      <c r="C573" s="3" t="n"/>
-      <c r="D573" s="4" t="n"/>
-      <c r="E573" s="4" t="n"/>
-      <c r="F573" s="5" t="n"/>
-      <c r="G573" s="6" t="n"/>
-      <c r="H573" s="4" t="n"/>
-      <c r="I573" s="7" t="n"/>
-      <c r="J573" s="4" t="n"/>
-    </row>
-    <row r="574" ht="22" customHeight="1">
-      <c r="A574" s="3">
-        <f>IF(C574="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B574" s="3" t="n"/>
-      <c r="C574" s="3" t="n"/>
-      <c r="D574" s="4" t="n"/>
-      <c r="E574" s="4" t="n"/>
-      <c r="F574" s="5" t="n"/>
-      <c r="G574" s="6" t="n"/>
-      <c r="H574" s="4" t="n"/>
-      <c r="I574" s="7" t="n"/>
-      <c r="J574" s="4" t="n"/>
-    </row>
-    <row r="575" ht="22" customHeight="1">
-      <c r="A575" s="3">
-        <f>IF(C575="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B575" s="3" t="n"/>
-      <c r="C575" s="3" t="n"/>
-      <c r="D575" s="4" t="n"/>
-      <c r="E575" s="4" t="n"/>
-      <c r="F575" s="5" t="n"/>
-      <c r="G575" s="6" t="n"/>
-      <c r="H575" s="4" t="n"/>
-      <c r="I575" s="7" t="n"/>
-      <c r="J575" s="4" t="n"/>
-    </row>
-    <row r="576" ht="22" customHeight="1">
-      <c r="A576" s="3">
-        <f>IF(C576="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B576" s="3" t="n"/>
-      <c r="C576" s="3" t="n"/>
-      <c r="D576" s="4" t="n"/>
-      <c r="E576" s="4" t="n"/>
-      <c r="F576" s="5" t="n"/>
-      <c r="G576" s="6" t="n"/>
-      <c r="H576" s="4" t="n"/>
-      <c r="I576" s="7" t="n"/>
-      <c r="J576" s="4" t="n"/>
-    </row>
-    <row r="577" ht="22" customHeight="1">
-      <c r="A577" s="3">
-        <f>IF(C577="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B577" s="3" t="n"/>
-      <c r="C577" s="3" t="n"/>
-      <c r="D577" s="4" t="n"/>
-      <c r="E577" s="4" t="n"/>
-      <c r="F577" s="5" t="n"/>
-      <c r="G577" s="6" t="n"/>
-      <c r="H577" s="4" t="n"/>
-      <c r="I577" s="7" t="n"/>
-      <c r="J577" s="4" t="n"/>
-    </row>
-    <row r="578" ht="22" customHeight="1">
-      <c r="A578" s="3">
-        <f>IF(C578="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B578" s="3" t="n"/>
-      <c r="C578" s="3" t="n"/>
-      <c r="D578" s="4" t="n"/>
-      <c r="E578" s="4" t="n"/>
-      <c r="F578" s="5" t="n"/>
-      <c r="G578" s="6" t="n"/>
-      <c r="H578" s="4" t="n"/>
-      <c r="I578" s="7" t="n"/>
-      <c r="J578" s="4" t="n"/>
-    </row>
-    <row r="579" ht="22" customHeight="1">
-      <c r="A579" s="3">
-        <f>IF(C579="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B579" s="3" t="n"/>
-      <c r="C579" s="3" t="n"/>
-      <c r="D579" s="4" t="n"/>
-      <c r="E579" s="4" t="n"/>
-      <c r="F579" s="5" t="n"/>
-      <c r="G579" s="6" t="n"/>
-      <c r="H579" s="4" t="n"/>
-      <c r="I579" s="7" t="n"/>
-      <c r="J579" s="4" t="n"/>
-    </row>
-    <row r="580" ht="22" customHeight="1">
-      <c r="A580" s="3">
-        <f>IF(C580="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B580" s="3" t="n"/>
-      <c r="C580" s="3" t="n"/>
-      <c r="D580" s="4" t="n"/>
-      <c r="E580" s="4" t="n"/>
-      <c r="F580" s="5" t="n"/>
-      <c r="G580" s="6" t="n"/>
-      <c r="H580" s="4" t="n"/>
-      <c r="I580" s="7" t="n"/>
-      <c r="J580" s="4" t="n"/>
-    </row>
-    <row r="581" ht="22" customHeight="1">
-      <c r="A581" s="3">
-        <f>IF(C581="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B581" s="3" t="n"/>
-      <c r="C581" s="3" t="n"/>
-      <c r="D581" s="4" t="n"/>
-      <c r="E581" s="4" t="n"/>
-      <c r="F581" s="5" t="n"/>
-      <c r="G581" s="6" t="n"/>
-      <c r="H581" s="4" t="n"/>
-      <c r="I581" s="7" t="n"/>
-      <c r="J581" s="4" t="n"/>
-    </row>
-    <row r="582" ht="22" customHeight="1">
-      <c r="A582" s="3">
-        <f>IF(C582="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B582" s="3" t="n"/>
-      <c r="C582" s="3" t="n"/>
-      <c r="D582" s="4" t="n"/>
-      <c r="E582" s="4" t="n"/>
-      <c r="F582" s="5" t="n"/>
-      <c r="G582" s="6" t="n"/>
-      <c r="H582" s="4" t="n"/>
-      <c r="I582" s="7" t="n"/>
-      <c r="J582" s="4" t="n"/>
-    </row>
-    <row r="583" ht="22" customHeight="1">
-      <c r="A583" s="3">
-        <f>IF(C583="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B583" s="3" t="n"/>
-      <c r="C583" s="3" t="n"/>
-      <c r="D583" s="4" t="n"/>
-      <c r="E583" s="4" t="n"/>
-      <c r="F583" s="5" t="n"/>
-      <c r="G583" s="6" t="n"/>
-      <c r="H583" s="4" t="n"/>
-      <c r="I583" s="7" t="n"/>
-      <c r="J583" s="4" t="n"/>
-    </row>
-    <row r="584" ht="22" customHeight="1">
-      <c r="A584" s="3">
-        <f>IF(C584="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B584" s="3" t="n"/>
-      <c r="C584" s="3" t="n"/>
-      <c r="D584" s="4" t="n"/>
-      <c r="E584" s="4" t="n"/>
-      <c r="F584" s="5" t="n"/>
-      <c r="G584" s="6" t="n"/>
-      <c r="H584" s="4" t="n"/>
-      <c r="I584" s="7" t="n"/>
-      <c r="J584" s="4" t="n"/>
-    </row>
-    <row r="585" ht="22" customHeight="1">
-      <c r="A585" s="3">
-        <f>IF(C585="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B585" s="3" t="n"/>
-      <c r="C585" s="3" t="n"/>
-      <c r="D585" s="4" t="n"/>
-      <c r="E585" s="4" t="n"/>
-      <c r="F585" s="5" t="n"/>
-      <c r="G585" s="6" t="n"/>
-      <c r="H585" s="4" t="n"/>
-      <c r="I585" s="7" t="n"/>
-      <c r="J585" s="4" t="n"/>
-    </row>
-    <row r="586" ht="22" customHeight="1">
-      <c r="A586" s="3">
-        <f>IF(C586="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B586" s="3" t="n"/>
-      <c r="C586" s="3" t="n"/>
-      <c r="D586" s="4" t="n"/>
-      <c r="E586" s="4" t="n"/>
-      <c r="F586" s="5" t="n"/>
-      <c r="G586" s="6" t="n"/>
-      <c r="H586" s="4" t="n"/>
-      <c r="I586" s="7" t="n"/>
-      <c r="J586" s="4" t="n"/>
-    </row>
-    <row r="587" ht="22" customHeight="1">
-      <c r="A587" s="3">
-        <f>IF(C587="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B587" s="3" t="n"/>
-      <c r="C587" s="3" t="n"/>
-      <c r="D587" s="4" t="n"/>
-      <c r="E587" s="4" t="n"/>
-      <c r="F587" s="5" t="n"/>
-      <c r="G587" s="6" t="n"/>
-      <c r="H587" s="4" t="n"/>
-      <c r="I587" s="7" t="n"/>
-      <c r="J587" s="4" t="n"/>
-    </row>
-    <row r="588" ht="22" customHeight="1">
-      <c r="A588" s="3">
-        <f>IF(C588="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B588" s="3" t="n"/>
-      <c r="C588" s="3" t="n"/>
-      <c r="D588" s="4" t="n"/>
-      <c r="E588" s="4" t="n"/>
-      <c r="F588" s="5" t="n"/>
-      <c r="G588" s="6" t="n"/>
-      <c r="H588" s="4" t="n"/>
-      <c r="I588" s="7" t="n"/>
-      <c r="J588" s="4" t="n"/>
-    </row>
-    <row r="589" ht="22" customHeight="1">
-      <c r="A589" s="3">
-        <f>IF(C589="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B589" s="3" t="n"/>
-      <c r="C589" s="3" t="n"/>
-      <c r="D589" s="4" t="n"/>
-      <c r="E589" s="4" t="n"/>
-      <c r="F589" s="5" t="n"/>
-      <c r="G589" s="6" t="n"/>
-      <c r="H589" s="4" t="n"/>
-      <c r="I589" s="7" t="n"/>
-      <c r="J589" s="4" t="n"/>
-    </row>
-    <row r="590" ht="22" customHeight="1">
-      <c r="A590" s="3">
-        <f>IF(C590="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B590" s="3" t="n"/>
-      <c r="C590" s="3" t="n"/>
-      <c r="D590" s="4" t="n"/>
-      <c r="E590" s="4" t="n"/>
-      <c r="F590" s="5" t="n"/>
-      <c r="G590" s="6" t="n"/>
-      <c r="H590" s="4" t="n"/>
-      <c r="I590" s="7" t="n"/>
-      <c r="J590" s="4" t="n"/>
-    </row>
-    <row r="591" ht="22" customHeight="1">
-      <c r="A591" s="3">
-        <f>IF(C591="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B591" s="3" t="n"/>
-      <c r="C591" s="3" t="n"/>
-      <c r="D591" s="4" t="n"/>
-      <c r="E591" s="4" t="n"/>
-      <c r="F591" s="5" t="n"/>
-      <c r="G591" s="6" t="n"/>
-      <c r="H591" s="4" t="n"/>
-      <c r="I591" s="7" t="n"/>
-      <c r="J591" s="4" t="n"/>
-    </row>
-    <row r="592" ht="22" customHeight="1">
-      <c r="A592" s="3">
-        <f>IF(C592="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B592" s="3" t="n"/>
-      <c r="C592" s="3" t="n"/>
-      <c r="D592" s="4" t="n"/>
-      <c r="E592" s="4" t="n"/>
-      <c r="F592" s="5" t="n"/>
-      <c r="G592" s="6" t="n"/>
-      <c r="H592" s="4" t="n"/>
-      <c r="I592" s="7" t="n"/>
-      <c r="J592" s="4" t="n"/>
-    </row>
-    <row r="593" ht="22" customHeight="1">
-      <c r="A593" s="3">
-        <f>IF(C593="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B593" s="3" t="n"/>
-      <c r="C593" s="3" t="n"/>
-      <c r="D593" s="4" t="n"/>
-      <c r="E593" s="4" t="n"/>
-      <c r="F593" s="5" t="n"/>
-      <c r="G593" s="6" t="n"/>
-      <c r="H593" s="4" t="n"/>
-      <c r="I593" s="7" t="n"/>
-      <c r="J593" s="4" t="n"/>
-    </row>
-    <row r="594" ht="22" customHeight="1">
-      <c r="A594" s="3">
-        <f>IF(C594="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B594" s="3" t="n"/>
-      <c r="C594" s="3" t="n"/>
-      <c r="D594" s="4" t="n"/>
-      <c r="E594" s="4" t="n"/>
-      <c r="F594" s="5" t="n"/>
-      <c r="G594" s="6" t="n"/>
-      <c r="H594" s="4" t="n"/>
-      <c r="I594" s="7" t="n"/>
-      <c r="J594" s="4" t="n"/>
-    </row>
-    <row r="595" ht="22" customHeight="1">
-      <c r="A595" s="3">
-        <f>IF(C595="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B595" s="3" t="n"/>
-      <c r="C595" s="3" t="n"/>
-      <c r="D595" s="4" t="n"/>
-      <c r="E595" s="4" t="n"/>
-      <c r="F595" s="5" t="n"/>
-      <c r="G595" s="6" t="n"/>
-      <c r="H595" s="4" t="n"/>
-      <c r="I595" s="7" t="n"/>
-      <c r="J595" s="4" t="n"/>
-    </row>
-    <row r="596" ht="22" customHeight="1">
-      <c r="A596" s="3">
-        <f>IF(C596="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B596" s="3" t="n"/>
-      <c r="C596" s="3" t="n"/>
-      <c r="D596" s="4" t="n"/>
-      <c r="E596" s="4" t="n"/>
-      <c r="F596" s="5" t="n"/>
-      <c r="G596" s="6" t="n"/>
-      <c r="H596" s="4" t="n"/>
-      <c r="I596" s="7" t="n"/>
-      <c r="J596" s="4" t="n"/>
-    </row>
-    <row r="597" ht="22" customHeight="1">
-      <c r="A597" s="3">
-        <f>IF(C597="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B597" s="3" t="n"/>
-      <c r="C597" s="3" t="n"/>
-      <c r="D597" s="4" t="n"/>
-      <c r="E597" s="4" t="n"/>
-      <c r="F597" s="5" t="n"/>
-      <c r="G597" s="6" t="n"/>
-      <c r="H597" s="4" t="n"/>
-      <c r="I597" s="7" t="n"/>
-      <c r="J597" s="4" t="n"/>
-    </row>
-    <row r="598" ht="22" customHeight="1">
-      <c r="A598" s="3">
-        <f>IF(C598="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B598" s="3" t="n"/>
-      <c r="C598" s="3" t="n"/>
-      <c r="D598" s="4" t="n"/>
-      <c r="E598" s="4" t="n"/>
-      <c r="F598" s="5" t="n"/>
-      <c r="G598" s="6" t="n"/>
-      <c r="H598" s="4" t="n"/>
-      <c r="I598" s="7" t="n"/>
-      <c r="J598" s="4" t="n"/>
-    </row>
-    <row r="599" ht="22" customHeight="1">
-      <c r="A599" s="3">
-        <f>IF(C599="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B599" s="3" t="n"/>
-      <c r="C599" s="3" t="n"/>
-      <c r="D599" s="4" t="n"/>
-      <c r="E599" s="4" t="n"/>
-      <c r="F599" s="5" t="n"/>
-      <c r="G599" s="6" t="n"/>
-      <c r="H599" s="4" t="n"/>
-      <c r="I599" s="7" t="n"/>
-      <c r="J599" s="4" t="n"/>
-    </row>
-    <row r="600" ht="22" customHeight="1">
-      <c r="A600" s="3">
-        <f>IF(C600="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B600" s="3" t="n"/>
-      <c r="C600" s="3" t="n"/>
-      <c r="D600" s="4" t="n"/>
-      <c r="E600" s="4" t="n"/>
-      <c r="F600" s="5" t="n"/>
-      <c r="G600" s="6" t="n"/>
-      <c r="H600" s="4" t="n"/>
-      <c r="I600" s="7" t="n"/>
-      <c r="J600" s="4" t="n"/>
-    </row>
-    <row r="601" ht="22" customHeight="1">
-      <c r="A601" s="3">
-        <f>IF(C601="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B601" s="3" t="n"/>
-      <c r="C601" s="3" t="n"/>
-      <c r="D601" s="4" t="n"/>
-      <c r="E601" s="4" t="n"/>
-      <c r="F601" s="5" t="n"/>
-      <c r="G601" s="6" t="n"/>
-      <c r="H601" s="4" t="n"/>
-      <c r="I601" s="7" t="n"/>
-      <c r="J601" s="4" t="n"/>
-    </row>
-    <row r="602" ht="22" customHeight="1">
-      <c r="A602" s="3">
-        <f>IF(C602="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B602" s="3" t="n"/>
-      <c r="C602" s="3" t="n"/>
-      <c r="D602" s="4" t="n"/>
-      <c r="E602" s="4" t="n"/>
-      <c r="F602" s="5" t="n"/>
-      <c r="G602" s="6" t="n"/>
-      <c r="H602" s="4" t="n"/>
-      <c r="I602" s="7" t="n"/>
-      <c r="J602" s="4" t="n"/>
-    </row>
-    <row r="603" ht="22" customHeight="1">
-      <c r="A603" s="3">
-        <f>IF(C603="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B603" s="3" t="n"/>
-      <c r="C603" s="3" t="n"/>
-      <c r="D603" s="4" t="n"/>
-      <c r="E603" s="4" t="n"/>
-      <c r="F603" s="5" t="n"/>
-      <c r="G603" s="6" t="n"/>
-      <c r="H603" s="4" t="n"/>
-      <c r="I603" s="7" t="n"/>
-      <c r="J603" s="4" t="n"/>
-    </row>
-    <row r="604" ht="22" customHeight="1">
-      <c r="A604" s="3">
-        <f>IF(C604="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B604" s="3" t="n"/>
-      <c r="C604" s="3" t="n"/>
-      <c r="D604" s="4" t="n"/>
-      <c r="E604" s="4" t="n"/>
-      <c r="F604" s="5" t="n"/>
-      <c r="G604" s="6" t="n"/>
-      <c r="H604" s="4" t="n"/>
-      <c r="I604" s="7" t="n"/>
-      <c r="J604" s="4" t="n"/>
-    </row>
-    <row r="605" ht="22" customHeight="1">
-      <c r="A605" s="3">
-        <f>IF(C605="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B605" s="3" t="n"/>
-      <c r="C605" s="3" t="n"/>
-      <c r="D605" s="4" t="n"/>
-      <c r="E605" s="4" t="n"/>
-      <c r="F605" s="5" t="n"/>
-      <c r="G605" s="6" t="n"/>
-      <c r="H605" s="4" t="n"/>
-      <c r="I605" s="7" t="n"/>
-      <c r="J605" s="4" t="n"/>
-    </row>
-    <row r="606" ht="22" customHeight="1">
-      <c r="A606" s="3">
-        <f>IF(C606="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B606" s="3" t="n"/>
-      <c r="C606" s="3" t="n"/>
-      <c r="D606" s="4" t="n"/>
-      <c r="E606" s="4" t="n"/>
-      <c r="F606" s="5" t="n"/>
-      <c r="G606" s="6" t="n"/>
-      <c r="H606" s="4" t="n"/>
-      <c r="I606" s="7" t="n"/>
-      <c r="J606" s="4" t="n"/>
-    </row>
-    <row r="607" ht="22" customHeight="1">
-      <c r="A607" s="3">
-        <f>IF(C607="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B607" s="3" t="n"/>
-      <c r="C607" s="3" t="n"/>
-      <c r="D607" s="4" t="n"/>
-      <c r="E607" s="4" t="n"/>
-      <c r="F607" s="5" t="n"/>
-      <c r="G607" s="6" t="n"/>
-      <c r="H607" s="4" t="n"/>
-      <c r="I607" s="7" t="n"/>
-      <c r="J607" s="4" t="n"/>
-    </row>
-    <row r="608" ht="22" customHeight="1">
-      <c r="A608" s="3">
-        <f>IF(C608="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B608" s="3" t="n"/>
-      <c r="C608" s="3" t="n"/>
-      <c r="D608" s="4" t="n"/>
-      <c r="E608" s="4" t="n"/>
-      <c r="F608" s="5" t="n"/>
-      <c r="G608" s="6" t="n"/>
-      <c r="H608" s="4" t="n"/>
-      <c r="I608" s="7" t="n"/>
-      <c r="J608" s="4" t="n"/>
-    </row>
-    <row r="609" ht="22" customHeight="1">
-      <c r="A609" s="3">
-        <f>IF(C609="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B609" s="3" t="n"/>
-      <c r="C609" s="3" t="n"/>
-      <c r="D609" s="4" t="n"/>
-      <c r="E609" s="4" t="n"/>
-      <c r="F609" s="5" t="n"/>
-      <c r="G609" s="6" t="n"/>
-      <c r="H609" s="4" t="n"/>
-      <c r="I609" s="7" t="n"/>
-      <c r="J609" s="4" t="n"/>
-    </row>
-    <row r="610" ht="22" customHeight="1">
-      <c r="A610" s="3">
-        <f>IF(C610="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B610" s="3" t="n"/>
-      <c r="C610" s="3" t="n"/>
-      <c r="D610" s="4" t="n"/>
-      <c r="E610" s="4" t="n"/>
-      <c r="F610" s="5" t="n"/>
-      <c r="G610" s="6" t="n"/>
-      <c r="H610" s="4" t="n"/>
-      <c r="I610" s="7" t="n"/>
-      <c r="J610" s="4" t="n"/>
-    </row>
-    <row r="611" ht="22" customHeight="1">
-      <c r="A611" s="3">
-        <f>IF(C611="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B611" s="3" t="n"/>
-      <c r="C611" s="3" t="n"/>
-      <c r="D611" s="4" t="n"/>
-      <c r="E611" s="4" t="n"/>
-      <c r="F611" s="5" t="n"/>
-      <c r="G611" s="6" t="n"/>
-      <c r="H611" s="4" t="n"/>
-      <c r="I611" s="7" t="n"/>
-      <c r="J611" s="4" t="n"/>
-    </row>
-    <row r="612" ht="22" customHeight="1">
-      <c r="A612" s="3">
-        <f>IF(C612="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B612" s="3" t="n"/>
-      <c r="C612" s="3" t="n"/>
-      <c r="D612" s="4" t="n"/>
-      <c r="E612" s="4" t="n"/>
-      <c r="F612" s="5" t="n"/>
-      <c r="G612" s="6" t="n"/>
-      <c r="H612" s="4" t="n"/>
-      <c r="I612" s="7" t="n"/>
-      <c r="J612" s="4" t="n"/>
-    </row>
-    <row r="613" ht="22" customHeight="1">
-      <c r="A613" s="3">
-        <f>IF(C613="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B613" s="3" t="n"/>
-      <c r="C613" s="3" t="n"/>
-      <c r="D613" s="4" t="n"/>
-      <c r="E613" s="4" t="n"/>
-      <c r="F613" s="5" t="n"/>
-      <c r="G613" s="6" t="n"/>
-      <c r="H613" s="4" t="n"/>
-      <c r="I613" s="7" t="n"/>
-      <c r="J613" s="4" t="n"/>
-    </row>
-    <row r="614" ht="22" customHeight="1">
-      <c r="A614" s="3">
-        <f>IF(C614="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B614" s="3" t="n"/>
-      <c r="C614" s="3" t="n"/>
-      <c r="D614" s="4" t="n"/>
-      <c r="E614" s="4" t="n"/>
-      <c r="F614" s="5" t="n"/>
-      <c r="G614" s="6" t="n"/>
-      <c r="H614" s="4" t="n"/>
-      <c r="I614" s="7" t="n"/>
-      <c r="J614" s="4" t="n"/>
-    </row>
-    <row r="615" ht="22" customHeight="1">
-      <c r="A615" s="3">
-        <f>IF(C615="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B615" s="3" t="n"/>
-      <c r="C615" s="3" t="n"/>
-      <c r="D615" s="4" t="n"/>
-      <c r="E615" s="4" t="n"/>
-      <c r="F615" s="5" t="n"/>
-      <c r="G615" s="6" t="n"/>
-      <c r="H615" s="4" t="n"/>
-      <c r="I615" s="7" t="n"/>
-      <c r="J615" s="4" t="n"/>
-    </row>
-    <row r="616" ht="22" customHeight="1">
-      <c r="A616" s="3">
-        <f>IF(C616="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B616" s="3" t="n"/>
-      <c r="C616" s="3" t="n"/>
-      <c r="D616" s="4" t="n"/>
-      <c r="E616" s="4" t="n"/>
-      <c r="F616" s="5" t="n"/>
-      <c r="G616" s="6" t="n"/>
-      <c r="H616" s="4" t="n"/>
-      <c r="I616" s="7" t="n"/>
-      <c r="J616" s="4" t="n"/>
-    </row>
-    <row r="617" ht="22" customHeight="1">
-      <c r="A617" s="3">
-        <f>IF(C617="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B617" s="3" t="n"/>
-      <c r="C617" s="3" t="n"/>
-      <c r="D617" s="4" t="n"/>
-      <c r="E617" s="4" t="n"/>
-      <c r="F617" s="5" t="n"/>
-      <c r="G617" s="6" t="n"/>
-      <c r="H617" s="4" t="n"/>
-      <c r="I617" s="7" t="n"/>
-      <c r="J617" s="4" t="n"/>
-    </row>
-    <row r="618" ht="22" customHeight="1">
-      <c r="A618" s="3">
-        <f>IF(C618="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B618" s="3" t="n"/>
-      <c r="C618" s="3" t="n"/>
-      <c r="D618" s="4" t="n"/>
-      <c r="E618" s="4" t="n"/>
-      <c r="F618" s="5" t="n"/>
-      <c r="G618" s="6" t="n"/>
-      <c r="H618" s="4" t="n"/>
-      <c r="I618" s="7" t="n"/>
-      <c r="J618" s="4" t="n"/>
-    </row>
-    <row r="619" ht="22" customHeight="1">
-      <c r="A619" s="3">
-        <f>IF(C619="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B619" s="3" t="n"/>
-      <c r="C619" s="3" t="n"/>
-      <c r="D619" s="4" t="n"/>
-      <c r="E619" s="4" t="n"/>
-      <c r="F619" s="5" t="n"/>
-      <c r="G619" s="6" t="n"/>
-      <c r="H619" s="4" t="n"/>
-      <c r="I619" s="7" t="n"/>
-      <c r="J619" s="4" t="n"/>
-    </row>
-    <row r="620" ht="22" customHeight="1">
-      <c r="A620" s="3">
-        <f>IF(C620="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B620" s="3" t="n"/>
-      <c r="C620" s="3" t="n"/>
-      <c r="D620" s="4" t="n"/>
-      <c r="E620" s="4" t="n"/>
-      <c r="F620" s="5" t="n"/>
-      <c r="G620" s="6" t="n"/>
-      <c r="H620" s="4" t="n"/>
-      <c r="I620" s="7" t="n"/>
-      <c r="J620" s="4" t="n"/>
-    </row>
-    <row r="621" ht="22" customHeight="1">
-      <c r="A621" s="3">
-        <f>IF(C621="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B621" s="3" t="n"/>
-      <c r="C621" s="3" t="n"/>
-      <c r="D621" s="4" t="n"/>
-      <c r="E621" s="4" t="n"/>
-      <c r="F621" s="5" t="n"/>
-      <c r="G621" s="6" t="n"/>
-      <c r="H621" s="4" t="n"/>
-      <c r="I621" s="7" t="n"/>
-      <c r="J621" s="4" t="n"/>
-    </row>
-    <row r="622" ht="22" customHeight="1">
-      <c r="A622" s="3">
-        <f>IF(C622="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B622" s="3" t="n"/>
-      <c r="C622" s="3" t="n"/>
-      <c r="D622" s="4" t="n"/>
-      <c r="E622" s="4" t="n"/>
-      <c r="F622" s="5" t="n"/>
-      <c r="G622" s="6" t="n"/>
-      <c r="H622" s="4" t="n"/>
-      <c r="I622" s="7" t="n"/>
-      <c r="J622" s="4" t="n"/>
-    </row>
-    <row r="623" ht="22" customHeight="1">
-      <c r="A623" s="3">
-        <f>IF(C623="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B623" s="3" t="n"/>
-      <c r="C623" s="3" t="n"/>
-      <c r="D623" s="4" t="n"/>
-      <c r="E623" s="4" t="n"/>
-      <c r="F623" s="5" t="n"/>
-      <c r="G623" s="6" t="n"/>
-      <c r="H623" s="4" t="n"/>
-      <c r="I623" s="7" t="n"/>
-      <c r="J623" s="4" t="n"/>
-    </row>
-    <row r="624" ht="22" customHeight="1">
-      <c r="A624" s="3">
-        <f>IF(C624="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B624" s="3" t="n"/>
-      <c r="C624" s="3" t="n"/>
-      <c r="D624" s="4" t="n"/>
-      <c r="E624" s="4" t="n"/>
-      <c r="F624" s="5" t="n"/>
-      <c r="G624" s="6" t="n"/>
-      <c r="H624" s="4" t="n"/>
-      <c r="I624" s="7" t="n"/>
-      <c r="J624" s="4" t="n"/>
-    </row>
-    <row r="625" ht="22" customHeight="1">
-      <c r="A625" s="3">
-        <f>IF(C625="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B625" s="3" t="n"/>
-      <c r="C625" s="3" t="n"/>
-      <c r="D625" s="4" t="n"/>
-      <c r="E625" s="4" t="n"/>
-      <c r="F625" s="5" t="n"/>
-      <c r="G625" s="6" t="n"/>
-      <c r="H625" s="4" t="n"/>
-      <c r="I625" s="7" t="n"/>
-      <c r="J625" s="4" t="n"/>
-    </row>
-    <row r="626" ht="22" customHeight="1">
-      <c r="A626" s="3">
-        <f>IF(C626="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B626" s="3" t="n"/>
-      <c r="C626" s="3" t="n"/>
-      <c r="D626" s="4" t="n"/>
-      <c r="E626" s="4" t="n"/>
-      <c r="F626" s="5" t="n"/>
-      <c r="G626" s="6" t="n"/>
-      <c r="H626" s="4" t="n"/>
-      <c r="I626" s="7" t="n"/>
-      <c r="J626" s="4" t="n"/>
-    </row>
-    <row r="627" ht="22" customHeight="1">
-      <c r="A627" s="3">
-        <f>IF(C627="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B627" s="3" t="n"/>
-      <c r="C627" s="3" t="n"/>
-      <c r="D627" s="4" t="n"/>
-      <c r="E627" s="4" t="n"/>
-      <c r="F627" s="5" t="n"/>
-      <c r="G627" s="6" t="n"/>
-      <c r="H627" s="4" t="n"/>
-      <c r="I627" s="7" t="n"/>
-      <c r="J627" s="4" t="n"/>
-    </row>
-    <row r="628" ht="22" customHeight="1">
-      <c r="A628" s="3">
-        <f>IF(C628="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B628" s="3" t="n"/>
-      <c r="C628" s="3" t="n"/>
-      <c r="D628" s="4" t="n"/>
-      <c r="E628" s="4" t="n"/>
-      <c r="F628" s="5" t="n"/>
-      <c r="G628" s="6" t="n"/>
-      <c r="H628" s="4" t="n"/>
-      <c r="I628" s="7" t="n"/>
-      <c r="J628" s="4" t="n"/>
-    </row>
-    <row r="629" ht="22" customHeight="1">
-      <c r="A629" s="3">
-        <f>IF(C629="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B629" s="3" t="n"/>
-      <c r="C629" s="3" t="n"/>
-      <c r="D629" s="4" t="n"/>
-      <c r="E629" s="4" t="n"/>
-      <c r="F629" s="5" t="n"/>
-      <c r="G629" s="6" t="n"/>
-      <c r="H629" s="4" t="n"/>
-      <c r="I629" s="7" t="n"/>
-      <c r="J629" s="4" t="n"/>
-    </row>
-    <row r="630" ht="22" customHeight="1">
-      <c r="A630" s="3">
-        <f>IF(C630="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B630" s="3" t="n"/>
-      <c r="C630" s="3" t="n"/>
-      <c r="D630" s="4" t="n"/>
-      <c r="E630" s="4" t="n"/>
-      <c r="F630" s="5" t="n"/>
-      <c r="G630" s="6" t="n"/>
-      <c r="H630" s="4" t="n"/>
-      <c r="I630" s="7" t="n"/>
-      <c r="J630" s="4" t="n"/>
-    </row>
-    <row r="631" ht="22" customHeight="1">
-      <c r="A631" s="3">
-        <f>IF(C631="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B631" s="3" t="n"/>
-      <c r="C631" s="3" t="n"/>
-      <c r="D631" s="4" t="n"/>
-      <c r="E631" s="4" t="n"/>
-      <c r="F631" s="5" t="n"/>
-      <c r="G631" s="6" t="n"/>
-      <c r="H631" s="4" t="n"/>
-      <c r="I631" s="7" t="n"/>
-      <c r="J631" s="4" t="n"/>
-    </row>
-    <row r="632" ht="22" customHeight="1">
-      <c r="A632" s="3">
-        <f>IF(C632="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B632" s="3" t="n"/>
-      <c r="C632" s="3" t="n"/>
-      <c r="D632" s="4" t="n"/>
-      <c r="E632" s="4" t="n"/>
-      <c r="F632" s="5" t="n"/>
-      <c r="G632" s="6" t="n"/>
-      <c r="H632" s="4" t="n"/>
-      <c r="I632" s="7" t="n"/>
-      <c r="J632" s="4" t="n"/>
-    </row>
-    <row r="633" ht="22" customHeight="1">
-      <c r="A633" s="3">
-        <f>IF(C633="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B633" s="3" t="n"/>
-      <c r="C633" s="3" t="n"/>
-      <c r="D633" s="4" t="n"/>
-      <c r="E633" s="4" t="n"/>
-      <c r="F633" s="5" t="n"/>
-      <c r="G633" s="6" t="n"/>
-      <c r="H633" s="4" t="n"/>
-      <c r="I633" s="7" t="n"/>
-      <c r="J633" s="4" t="n"/>
-    </row>
-    <row r="634" ht="22" customHeight="1">
-      <c r="A634" s="3">
-        <f>IF(C634="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B634" s="3" t="n"/>
-      <c r="C634" s="3" t="n"/>
-      <c r="D634" s="4" t="n"/>
-      <c r="E634" s="4" t="n"/>
-      <c r="F634" s="5" t="n"/>
-      <c r="G634" s="6" t="n"/>
-      <c r="H634" s="4" t="n"/>
-      <c r="I634" s="7" t="n"/>
-      <c r="J634" s="4" t="n"/>
-    </row>
-    <row r="635" ht="22" customHeight="1">
-      <c r="A635" s="3">
-        <f>IF(C635="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B635" s="3" t="n"/>
-      <c r="C635" s="3" t="n"/>
-      <c r="D635" s="4" t="n"/>
-      <c r="E635" s="4" t="n"/>
-      <c r="F635" s="5" t="n"/>
-      <c r="G635" s="6" t="n"/>
-      <c r="H635" s="4" t="n"/>
-      <c r="I635" s="7" t="n"/>
-      <c r="J635" s="4" t="n"/>
-    </row>
-    <row r="636" ht="22" customHeight="1">
-      <c r="A636" s="3">
-        <f>IF(C636="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B636" s="3" t="n"/>
-      <c r="C636" s="3" t="n"/>
-      <c r="D636" s="4" t="n"/>
-      <c r="E636" s="4" t="n"/>
-      <c r="F636" s="5" t="n"/>
-      <c r="G636" s="6" t="n"/>
-      <c r="H636" s="4" t="n"/>
-      <c r="I636" s="7" t="n"/>
-      <c r="J636" s="4" t="n"/>
-    </row>
-    <row r="637" ht="22" customHeight="1">
-      <c r="A637" s="3">
-        <f>IF(C637="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B637" s="3" t="n"/>
-      <c r="C637" s="3" t="n"/>
-      <c r="D637" s="4" t="n"/>
-      <c r="E637" s="4" t="n"/>
-      <c r="F637" s="5" t="n"/>
-      <c r="G637" s="6" t="n"/>
-      <c r="H637" s="4" t="n"/>
-      <c r="I637" s="7" t="n"/>
-      <c r="J637" s="4" t="n"/>
-    </row>
-    <row r="638" ht="22" customHeight="1">
-      <c r="A638" s="3">
-        <f>IF(C638="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B638" s="3" t="n"/>
-      <c r="C638" s="3" t="n"/>
-      <c r="D638" s="4" t="n"/>
-      <c r="E638" s="4" t="n"/>
-      <c r="F638" s="5" t="n"/>
-      <c r="G638" s="6" t="n"/>
-      <c r="H638" s="4" t="n"/>
-      <c r="I638" s="7" t="n"/>
-      <c r="J638" s="4" t="n"/>
-    </row>
-    <row r="639" ht="22" customHeight="1">
-      <c r="A639" s="3">
-        <f>IF(C639="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B639" s="3" t="n"/>
-      <c r="C639" s="3" t="n"/>
-      <c r="D639" s="4" t="n"/>
-      <c r="E639" s="4" t="n"/>
-      <c r="F639" s="5" t="n"/>
-      <c r="G639" s="6" t="n"/>
-      <c r="H639" s="4" t="n"/>
-      <c r="I639" s="7" t="n"/>
-      <c r="J639" s="4" t="n"/>
-    </row>
-    <row r="640" ht="22" customHeight="1">
-      <c r="A640" s="3">
-        <f>IF(C640="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B640" s="3" t="n"/>
-      <c r="C640" s="3" t="n"/>
-      <c r="D640" s="4" t="n"/>
-      <c r="E640" s="4" t="n"/>
-      <c r="F640" s="5" t="n"/>
-      <c r="G640" s="6" t="n"/>
-      <c r="H640" s="4" t="n"/>
-      <c r="I640" s="7" t="n"/>
-      <c r="J640" s="4" t="n"/>
-    </row>
-    <row r="641" ht="22" customHeight="1">
-      <c r="A641" s="3">
-        <f>IF(C641="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B641" s="3" t="n"/>
-      <c r="C641" s="3" t="n"/>
-      <c r="D641" s="4" t="n"/>
-      <c r="E641" s="4" t="n"/>
-      <c r="F641" s="5" t="n"/>
-      <c r="G641" s="6" t="n"/>
-      <c r="H641" s="4" t="n"/>
-      <c r="I641" s="7" t="n"/>
-      <c r="J641" s="4" t="n"/>
-    </row>
-    <row r="642" ht="22" customHeight="1">
-      <c r="A642" s="3">
-        <f>IF(C642="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B642" s="3" t="n"/>
-      <c r="C642" s="3" t="n"/>
-      <c r="D642" s="4" t="n"/>
-      <c r="E642" s="4" t="n"/>
-      <c r="F642" s="5" t="n"/>
-      <c r="G642" s="6" t="n"/>
-      <c r="H642" s="4" t="n"/>
-      <c r="I642" s="7" t="n"/>
-      <c r="J642" s="4" t="n"/>
-    </row>
-    <row r="643" ht="22" customHeight="1">
-      <c r="A643" s="3">
-        <f>IF(C643="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B643" s="3" t="n"/>
-      <c r="C643" s="3" t="n"/>
-      <c r="D643" s="4" t="n"/>
-      <c r="E643" s="4" t="n"/>
-      <c r="F643" s="5" t="n"/>
-      <c r="G643" s="6" t="n"/>
-      <c r="H643" s="4" t="n"/>
-      <c r="I643" s="7" t="n"/>
-      <c r="J643" s="4" t="n"/>
-    </row>
-    <row r="644" ht="22" customHeight="1">
-      <c r="A644" s="3">
-        <f>IF(C644="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B644" s="3" t="n"/>
-      <c r="C644" s="3" t="n"/>
-      <c r="D644" s="4" t="n"/>
-      <c r="E644" s="4" t="n"/>
-      <c r="F644" s="5" t="n"/>
-      <c r="G644" s="6" t="n"/>
-      <c r="H644" s="4" t="n"/>
-      <c r="I644" s="7" t="n"/>
-      <c r="J644" s="4" t="n"/>
-    </row>
-    <row r="645" ht="22" customHeight="1">
-      <c r="A645" s="3">
-        <f>IF(C645="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B645" s="3" t="n"/>
-      <c r="C645" s="3" t="n"/>
-      <c r="D645" s="4" t="n"/>
-      <c r="E645" s="4" t="n"/>
-      <c r="F645" s="5" t="n"/>
-      <c r="G645" s="6" t="n"/>
-      <c r="H645" s="4" t="n"/>
-      <c r="I645" s="7" t="n"/>
-      <c r="J645" s="4" t="n"/>
-    </row>
-    <row r="646" ht="22" customHeight="1">
-      <c r="A646" s="3">
-        <f>IF(C646="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B646" s="3" t="n"/>
-      <c r="C646" s="3" t="n"/>
-      <c r="D646" s="4" t="n"/>
-      <c r="E646" s="4" t="n"/>
-      <c r="F646" s="5" t="n"/>
-      <c r="G646" s="6" t="n"/>
-      <c r="H646" s="4" t="n"/>
-      <c r="I646" s="7" t="n"/>
-      <c r="J646" s="4" t="n"/>
-    </row>
-    <row r="647" ht="22" customHeight="1">
-      <c r="A647" s="3">
-        <f>IF(C647="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B647" s="3" t="n"/>
-      <c r="C647" s="3" t="n"/>
-      <c r="D647" s="4" t="n"/>
-      <c r="E647" s="4" t="n"/>
-      <c r="F647" s="5" t="n"/>
-      <c r="G647" s="6" t="n"/>
-      <c r="H647" s="4" t="n"/>
-      <c r="I647" s="7" t="n"/>
-      <c r="J647" s="4" t="n"/>
-    </row>
-    <row r="648" ht="22" customHeight="1">
-      <c r="A648" s="3">
-        <f>IF(C648="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B648" s="3" t="n"/>
-      <c r="C648" s="3" t="n"/>
-      <c r="D648" s="4" t="n"/>
-      <c r="E648" s="4" t="n"/>
-      <c r="F648" s="5" t="n"/>
-      <c r="G648" s="6" t="n"/>
-      <c r="H648" s="4" t="n"/>
-      <c r="I648" s="7" t="n"/>
-      <c r="J648" s="4" t="n"/>
-    </row>
-    <row r="649" ht="22" customHeight="1">
-      <c r="A649" s="3">
-        <f>IF(C649="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B649" s="3" t="n"/>
-      <c r="C649" s="3" t="n"/>
-      <c r="D649" s="4" t="n"/>
-      <c r="E649" s="4" t="n"/>
-      <c r="F649" s="5" t="n"/>
-      <c r="G649" s="6" t="n"/>
-      <c r="H649" s="4" t="n"/>
-      <c r="I649" s="7" t="n"/>
-      <c r="J649" s="4" t="n"/>
-    </row>
-    <row r="650" ht="22" customHeight="1">
-      <c r="A650" s="3">
-        <f>IF(C650="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B650" s="3" t="n"/>
-      <c r="C650" s="3" t="n"/>
-      <c r="D650" s="4" t="n"/>
-      <c r="E650" s="4" t="n"/>
-      <c r="F650" s="5" t="n"/>
-      <c r="G650" s="6" t="n"/>
-      <c r="H650" s="4" t="n"/>
-      <c r="I650" s="7" t="n"/>
-      <c r="J650" s="4" t="n"/>
-    </row>
-    <row r="651" ht="22" customHeight="1">
-      <c r="A651" s="3">
-        <f>IF(C651="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B651" s="3" t="n"/>
-      <c r="C651" s="3" t="n"/>
-      <c r="D651" s="4" t="n"/>
-      <c r="E651" s="4" t="n"/>
-      <c r="F651" s="5" t="n"/>
-      <c r="G651" s="6" t="n"/>
-      <c r="H651" s="4" t="n"/>
-      <c r="I651" s="7" t="n"/>
-      <c r="J651" s="4" t="n"/>
-    </row>
-    <row r="652" ht="22" customHeight="1">
-      <c r="A652" s="3">
-        <f>IF(C652="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B652" s="3" t="n"/>
-      <c r="C652" s="3" t="n"/>
-      <c r="D652" s="4" t="n"/>
-      <c r="E652" s="4" t="n"/>
-      <c r="F652" s="5" t="n"/>
-      <c r="G652" s="6" t="n"/>
-      <c r="H652" s="4" t="n"/>
-      <c r="I652" s="7" t="n"/>
-      <c r="J652" s="4" t="n"/>
-    </row>
-    <row r="653" ht="22" customHeight="1">
-      <c r="A653" s="3">
-        <f>IF(C653="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B653" s="3" t="n"/>
-      <c r="C653" s="3" t="n"/>
-      <c r="D653" s="4" t="n"/>
-      <c r="E653" s="4" t="n"/>
-      <c r="F653" s="5" t="n"/>
-      <c r="G653" s="6" t="n"/>
-      <c r="H653" s="4" t="n"/>
-      <c r="I653" s="7" t="n"/>
-      <c r="J653" s="4" t="n"/>
-    </row>
-    <row r="654" ht="22" customHeight="1">
-      <c r="A654" s="3">
-        <f>IF(C654="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B654" s="3" t="n"/>
-      <c r="C654" s="3" t="n"/>
-      <c r="D654" s="4" t="n"/>
-      <c r="E654" s="4" t="n"/>
-      <c r="F654" s="5" t="n"/>
-      <c r="G654" s="6" t="n"/>
-      <c r="H654" s="4" t="n"/>
-      <c r="I654" s="7" t="n"/>
-      <c r="J654" s="4" t="n"/>
-    </row>
-    <row r="655" ht="22" customHeight="1">
-      <c r="A655" s="3">
-        <f>IF(C655="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B655" s="3" t="n"/>
-      <c r="C655" s="3" t="n"/>
-      <c r="D655" s="4" t="n"/>
-      <c r="E655" s="4" t="n"/>
-      <c r="F655" s="5" t="n"/>
-      <c r="G655" s="6" t="n"/>
-      <c r="H655" s="4" t="n"/>
-      <c r="I655" s="7" t="n"/>
-      <c r="J655" s="4" t="n"/>
-    </row>
-    <row r="656" ht="22" customHeight="1">
-      <c r="A656" s="3">
-        <f>IF(C656="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B656" s="3" t="n"/>
-      <c r="C656" s="3" t="n"/>
-      <c r="D656" s="4" t="n"/>
-      <c r="E656" s="4" t="n"/>
-      <c r="F656" s="5" t="n"/>
-      <c r="G656" s="6" t="n"/>
-      <c r="H656" s="4" t="n"/>
-      <c r="I656" s="7" t="n"/>
-      <c r="J656" s="4" t="n"/>
-    </row>
-    <row r="657" ht="22" customHeight="1">
-      <c r="A657" s="3">
-        <f>IF(C657="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B657" s="3" t="n"/>
-      <c r="C657" s="3" t="n"/>
-      <c r="D657" s="4" t="n"/>
-      <c r="E657" s="4" t="n"/>
-      <c r="F657" s="5" t="n"/>
-      <c r="G657" s="6" t="n"/>
-      <c r="H657" s="4" t="n"/>
-      <c r="I657" s="7" t="n"/>
-      <c r="J657" s="4" t="n"/>
-    </row>
-    <row r="658" ht="22" customHeight="1">
-      <c r="A658" s="3">
-        <f>IF(C658="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B658" s="3" t="n"/>
-      <c r="C658" s="3" t="n"/>
-      <c r="D658" s="4" t="n"/>
-      <c r="E658" s="4" t="n"/>
-      <c r="F658" s="5" t="n"/>
-      <c r="G658" s="6" t="n"/>
-      <c r="H658" s="4" t="n"/>
-      <c r="I658" s="7" t="n"/>
-      <c r="J658" s="4" t="n"/>
-    </row>
-    <row r="659" ht="22" customHeight="1">
-      <c r="A659" s="3">
-        <f>IF(C659="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B659" s="3" t="n"/>
-      <c r="C659" s="3" t="n"/>
-      <c r="D659" s="4" t="n"/>
-      <c r="E659" s="4" t="n"/>
-      <c r="F659" s="5" t="n"/>
-      <c r="G659" s="6" t="n"/>
-      <c r="H659" s="4" t="n"/>
-      <c r="I659" s="7" t="n"/>
-      <c r="J659" s="4" t="n"/>
-    </row>
-    <row r="660" ht="22" customHeight="1">
-      <c r="A660" s="3">
-        <f>IF(C660="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B660" s="3" t="n"/>
-      <c r="C660" s="3" t="n"/>
-      <c r="D660" s="4" t="n"/>
-      <c r="E660" s="4" t="n"/>
-      <c r="F660" s="5" t="n"/>
-      <c r="G660" s="6" t="n"/>
-      <c r="H660" s="4" t="n"/>
-      <c r="I660" s="7" t="n"/>
-      <c r="J660" s="4" t="n"/>
-    </row>
-    <row r="661" ht="22" customHeight="1">
-      <c r="A661" s="3">
-        <f>IF(C661="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B661" s="3" t="n"/>
-      <c r="C661" s="3" t="n"/>
-      <c r="D661" s="4" t="n"/>
-      <c r="E661" s="4" t="n"/>
-      <c r="F661" s="5" t="n"/>
-      <c r="G661" s="6" t="n"/>
-      <c r="H661" s="4" t="n"/>
-      <c r="I661" s="7" t="n"/>
-      <c r="J661" s="4" t="n"/>
-    </row>
-    <row r="662" ht="22" customHeight="1">
-      <c r="A662" s="3">
-        <f>IF(C662="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B662" s="3" t="n"/>
-      <c r="C662" s="3" t="n"/>
-      <c r="D662" s="4" t="n"/>
-      <c r="E662" s="4" t="n"/>
-      <c r="F662" s="5" t="n"/>
-      <c r="G662" s="6" t="n"/>
-      <c r="H662" s="4" t="n"/>
-      <c r="I662" s="7" t="n"/>
-      <c r="J662" s="4" t="n"/>
-    </row>
-    <row r="663" ht="22" customHeight="1">
-      <c r="A663" s="3">
-        <f>IF(C663="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B663" s="3" t="n"/>
-      <c r="C663" s="3" t="n"/>
-      <c r="D663" s="4" t="n"/>
-      <c r="E663" s="4" t="n"/>
-      <c r="F663" s="5" t="n"/>
-      <c r="G663" s="6" t="n"/>
-      <c r="H663" s="4" t="n"/>
-      <c r="I663" s="7" t="n"/>
-      <c r="J663" s="4" t="n"/>
-    </row>
-    <row r="664" ht="22" customHeight="1">
-      <c r="A664" s="3">
-        <f>IF(C664="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B664" s="3" t="n"/>
-      <c r="C664" s="3" t="n"/>
-      <c r="D664" s="4" t="n"/>
-      <c r="E664" s="4" t="n"/>
-      <c r="F664" s="5" t="n"/>
-      <c r="G664" s="6" t="n"/>
-      <c r="H664" s="4" t="n"/>
-      <c r="I664" s="7" t="n"/>
-      <c r="J664" s="4" t="n"/>
-    </row>
-    <row r="665" ht="22" customHeight="1">
-      <c r="A665" s="3">
-        <f>IF(C665="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B665" s="3" t="n"/>
-      <c r="C665" s="3" t="n"/>
-      <c r="D665" s="4" t="n"/>
-      <c r="E665" s="4" t="n"/>
-      <c r="F665" s="5" t="n"/>
-      <c r="G665" s="6" t="n"/>
-      <c r="H665" s="4" t="n"/>
-      <c r="I665" s="7" t="n"/>
-      <c r="J665" s="4" t="n"/>
-    </row>
-    <row r="666" ht="22" customHeight="1">
-      <c r="A666" s="3">
-        <f>IF(C666="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B666" s="3" t="n"/>
-      <c r="C666" s="3" t="n"/>
-      <c r="D666" s="4" t="n"/>
-      <c r="E666" s="4" t="n"/>
-      <c r="F666" s="5" t="n"/>
-      <c r="G666" s="6" t="n"/>
-      <c r="H666" s="4" t="n"/>
-      <c r="I666" s="7" t="n"/>
-      <c r="J666" s="4" t="n"/>
-    </row>
-    <row r="667" ht="22" customHeight="1">
-      <c r="A667" s="3">
-        <f>IF(C667="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B667" s="3" t="n"/>
-      <c r="C667" s="3" t="n"/>
-      <c r="D667" s="4" t="n"/>
-      <c r="E667" s="4" t="n"/>
-      <c r="F667" s="5" t="n"/>
-      <c r="G667" s="6" t="n"/>
-      <c r="H667" s="4" t="n"/>
-      <c r="I667" s="7" t="n"/>
-      <c r="J667" s="4" t="n"/>
-    </row>
-    <row r="668" ht="22" customHeight="1">
-      <c r="A668" s="3">
-        <f>IF(C668="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B668" s="3" t="n"/>
-      <c r="C668" s="3" t="n"/>
-      <c r="D668" s="4" t="n"/>
-      <c r="E668" s="4" t="n"/>
-      <c r="F668" s="5" t="n"/>
-      <c r="G668" s="6" t="n"/>
-      <c r="H668" s="4" t="n"/>
-      <c r="I668" s="7" t="n"/>
-      <c r="J668" s="4" t="n"/>
-    </row>
-    <row r="669" ht="22" customHeight="1">
-      <c r="A669" s="3">
-        <f>IF(C669="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B669" s="3" t="n"/>
-      <c r="C669" s="3" t="n"/>
-      <c r="D669" s="4" t="n"/>
-      <c r="E669" s="4" t="n"/>
-      <c r="F669" s="5" t="n"/>
-      <c r="G669" s="6" t="n"/>
-      <c r="H669" s="4" t="n"/>
-      <c r="I669" s="7" t="n"/>
-      <c r="J669" s="4" t="n"/>
-    </row>
-    <row r="670" ht="22" customHeight="1">
-      <c r="A670" s="3">
-        <f>IF(C670="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B670" s="3" t="n"/>
-      <c r="C670" s="3" t="n"/>
-      <c r="D670" s="4" t="n"/>
-      <c r="E670" s="4" t="n"/>
-      <c r="F670" s="5" t="n"/>
-      <c r="G670" s="6" t="n"/>
-      <c r="H670" s="4" t="n"/>
-      <c r="I670" s="7" t="n"/>
-      <c r="J670" s="4" t="n"/>
-    </row>
-    <row r="671" ht="22" customHeight="1">
-      <c r="A671" s="3">
-        <f>IF(C671="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B671" s="3" t="n"/>
-      <c r="C671" s="3" t="n"/>
-      <c r="D671" s="4" t="n"/>
-      <c r="E671" s="4" t="n"/>
-      <c r="F671" s="5" t="n"/>
-      <c r="G671" s="6" t="n"/>
-      <c r="H671" s="4" t="n"/>
-      <c r="I671" s="7" t="n"/>
-      <c r="J671" s="4" t="n"/>
-    </row>
-    <row r="672" ht="22" customHeight="1">
-      <c r="A672" s="3">
-        <f>IF(C672="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B672" s="3" t="n"/>
-      <c r="C672" s="3" t="n"/>
-      <c r="D672" s="4" t="n"/>
-      <c r="E672" s="4" t="n"/>
-      <c r="F672" s="5" t="n"/>
-      <c r="G672" s="6" t="n"/>
-      <c r="H672" s="4" t="n"/>
-      <c r="I672" s="7" t="n"/>
-      <c r="J672" s="4" t="n"/>
-    </row>
-    <row r="673" ht="22" customHeight="1">
-      <c r="A673" s="3">
-        <f>IF(C673="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B673" s="3" t="n"/>
-      <c r="C673" s="3" t="n"/>
-      <c r="D673" s="4" t="n"/>
-      <c r="E673" s="4" t="n"/>
-      <c r="F673" s="5" t="n"/>
-      <c r="G673" s="6" t="n"/>
-      <c r="H673" s="4" t="n"/>
-      <c r="I673" s="7" t="n"/>
-      <c r="J673" s="4" t="n"/>
-    </row>
-    <row r="674" ht="22" customHeight="1">
-      <c r="A674" s="3">
-        <f>IF(C674="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B674" s="3" t="n"/>
-      <c r="C674" s="3" t="n"/>
-      <c r="D674" s="4" t="n"/>
-      <c r="E674" s="4" t="n"/>
-      <c r="F674" s="5" t="n"/>
-      <c r="G674" s="6" t="n"/>
-      <c r="H674" s="4" t="n"/>
-      <c r="I674" s="7" t="n"/>
-      <c r="J674" s="4" t="n"/>
-    </row>
-    <row r="675" ht="22" customHeight="1">
-      <c r="A675" s="3">
-        <f>IF(C675="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B675" s="3" t="n"/>
-      <c r="C675" s="3" t="n"/>
-      <c r="D675" s="4" t="n"/>
-      <c r="E675" s="4" t="n"/>
-      <c r="F675" s="5" t="n"/>
-      <c r="G675" s="6" t="n"/>
-      <c r="H675" s="4" t="n"/>
-      <c r="I675" s="7" t="n"/>
-      <c r="J675" s="4" t="n"/>
-    </row>
-    <row r="676" ht="22" customHeight="1">
-      <c r="A676" s="3">
-        <f>IF(C676="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B676" s="3" t="n"/>
-      <c r="C676" s="3" t="n"/>
-      <c r="D676" s="4" t="n"/>
-      <c r="E676" s="4" t="n"/>
-      <c r="F676" s="5" t="n"/>
-      <c r="G676" s="6" t="n"/>
-      <c r="H676" s="4" t="n"/>
-      <c r="I676" s="7" t="n"/>
-      <c r="J676" s="4" t="n"/>
-    </row>
-    <row r="677" ht="22" customHeight="1">
-      <c r="A677" s="3">
-        <f>IF(C677="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B677" s="3" t="n"/>
-      <c r="C677" s="3" t="n"/>
-      <c r="D677" s="4" t="n"/>
-      <c r="E677" s="4" t="n"/>
-      <c r="F677" s="5" t="n"/>
-      <c r="G677" s="6" t="n"/>
-      <c r="H677" s="4" t="n"/>
-      <c r="I677" s="7" t="n"/>
-      <c r="J677" s="4" t="n"/>
-    </row>
-    <row r="678" ht="22" customHeight="1">
-      <c r="A678" s="3">
-        <f>IF(C678="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B678" s="3" t="n"/>
-      <c r="C678" s="3" t="n"/>
-      <c r="D678" s="4" t="n"/>
-      <c r="E678" s="4" t="n"/>
-      <c r="F678" s="5" t="n"/>
-      <c r="G678" s="6" t="n"/>
-      <c r="H678" s="4" t="n"/>
-      <c r="I678" s="7" t="n"/>
-      <c r="J678" s="4" t="n"/>
-    </row>
-    <row r="679" ht="22" customHeight="1">
-      <c r="A679" s="3">
-        <f>IF(C679="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B679" s="3" t="n"/>
-      <c r="C679" s="3" t="n"/>
-      <c r="D679" s="4" t="n"/>
-      <c r="E679" s="4" t="n"/>
-      <c r="F679" s="5" t="n"/>
-      <c r="G679" s="6" t="n"/>
-      <c r="H679" s="4" t="n"/>
-      <c r="I679" s="7" t="n"/>
-      <c r="J679" s="4" t="n"/>
-    </row>
-    <row r="680" ht="22" customHeight="1">
-      <c r="A680" s="3">
-        <f>IF(C680="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B680" s="3" t="n"/>
-      <c r="C680" s="3" t="n"/>
-      <c r="D680" s="4" t="n"/>
-      <c r="E680" s="4" t="n"/>
-      <c r="F680" s="5" t="n"/>
-      <c r="G680" s="6" t="n"/>
-      <c r="H680" s="4" t="n"/>
-      <c r="I680" s="7" t="n"/>
-      <c r="J680" s="4" t="n"/>
-    </row>
-    <row r="681" ht="22" customHeight="1">
-      <c r="A681" s="3">
-        <f>IF(C681="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B681" s="3" t="n"/>
-      <c r="C681" s="3" t="n"/>
-      <c r="D681" s="4" t="n"/>
-      <c r="E681" s="4" t="n"/>
-      <c r="F681" s="5" t="n"/>
-      <c r="G681" s="6" t="n"/>
-      <c r="H681" s="4" t="n"/>
-      <c r="I681" s="7" t="n"/>
-      <c r="J681" s="4" t="n"/>
-    </row>
-    <row r="682" ht="22" customHeight="1">
-      <c r="A682" s="3">
-        <f>IF(C682="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B682" s="3" t="n"/>
-      <c r="C682" s="3" t="n"/>
-      <c r="D682" s="4" t="n"/>
-      <c r="E682" s="4" t="n"/>
-      <c r="F682" s="5" t="n"/>
-      <c r="G682" s="6" t="n"/>
-      <c r="H682" s="4" t="n"/>
-      <c r="I682" s="7" t="n"/>
-      <c r="J682" s="4" t="n"/>
-    </row>
-    <row r="683" ht="22" customHeight="1">
-      <c r="A683" s="3">
-        <f>IF(C683="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B683" s="3" t="n"/>
-      <c r="C683" s="3" t="n"/>
-      <c r="D683" s="4" t="n"/>
-      <c r="E683" s="4" t="n"/>
-      <c r="F683" s="5" t="n"/>
-      <c r="G683" s="6" t="n"/>
-      <c r="H683" s="4" t="n"/>
-      <c r="I683" s="7" t="n"/>
-      <c r="J683" s="4" t="n"/>
-    </row>
-    <row r="684" ht="22" customHeight="1">
-      <c r="A684" s="3">
-        <f>IF(C684="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B684" s="3" t="n"/>
-      <c r="C684" s="3" t="n"/>
-      <c r="D684" s="4" t="n"/>
-      <c r="E684" s="4" t="n"/>
-      <c r="F684" s="5" t="n"/>
-      <c r="G684" s="6" t="n"/>
-      <c r="H684" s="4" t="n"/>
-      <c r="I684" s="7" t="n"/>
-      <c r="J684" s="4" t="n"/>
-    </row>
-    <row r="685" ht="22" customHeight="1">
-      <c r="A685" s="3">
-        <f>IF(C685="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B685" s="3" t="n"/>
-      <c r="C685" s="3" t="n"/>
-      <c r="D685" s="4" t="n"/>
-      <c r="E685" s="4" t="n"/>
-      <c r="F685" s="5" t="n"/>
-      <c r="G685" s="6" t="n"/>
-      <c r="H685" s="4" t="n"/>
-      <c r="I685" s="7" t="n"/>
-      <c r="J685" s="4" t="n"/>
-    </row>
-    <row r="686" ht="22" customHeight="1">
-      <c r="A686" s="3">
-        <f>IF(C686="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B686" s="3" t="n"/>
-      <c r="C686" s="3" t="n"/>
-      <c r="D686" s="4" t="n"/>
-      <c r="E686" s="4" t="n"/>
-      <c r="F686" s="5" t="n"/>
-      <c r="G686" s="6" t="n"/>
-      <c r="H686" s="4" t="n"/>
-      <c r="I686" s="7" t="n"/>
-      <c r="J686" s="4" t="n"/>
-    </row>
-    <row r="687" ht="22" customHeight="1">
-      <c r="A687" s="3">
-        <f>IF(C687="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B687" s="3" t="n"/>
-      <c r="C687" s="3" t="n"/>
-      <c r="D687" s="4" t="n"/>
-      <c r="E687" s="4" t="n"/>
-      <c r="F687" s="5" t="n"/>
-      <c r="G687" s="6" t="n"/>
-      <c r="H687" s="4" t="n"/>
-      <c r="I687" s="7" t="n"/>
-      <c r="J687" s="4" t="n"/>
-    </row>
-    <row r="688" ht="22" customHeight="1">
-      <c r="A688" s="3">
-        <f>IF(C688="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B688" s="3" t="n"/>
-      <c r="C688" s="3" t="n"/>
-      <c r="D688" s="4" t="n"/>
-      <c r="E688" s="4" t="n"/>
-      <c r="F688" s="5" t="n"/>
-      <c r="G688" s="6" t="n"/>
-      <c r="H688" s="4" t="n"/>
-      <c r="I688" s="7" t="n"/>
-      <c r="J688" s="4" t="n"/>
-    </row>
-    <row r="689" ht="22" customHeight="1">
-      <c r="A689" s="3">
-        <f>IF(C689="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B689" s="3" t="n"/>
-      <c r="C689" s="3" t="n"/>
-      <c r="D689" s="4" t="n"/>
-      <c r="E689" s="4" t="n"/>
-      <c r="F689" s="5" t="n"/>
-      <c r="G689" s="6" t="n"/>
-      <c r="H689" s="4" t="n"/>
-      <c r="I689" s="7" t="n"/>
-      <c r="J689" s="4" t="n"/>
-    </row>
-    <row r="690" ht="22" customHeight="1">
-      <c r="A690" s="3">
-        <f>IF(C690="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B690" s="3" t="n"/>
-      <c r="C690" s="3" t="n"/>
-      <c r="D690" s="4" t="n"/>
-      <c r="E690" s="4" t="n"/>
-      <c r="F690" s="5" t="n"/>
-      <c r="G690" s="6" t="n"/>
-      <c r="H690" s="4" t="n"/>
-      <c r="I690" s="7" t="n"/>
-      <c r="J690" s="4" t="n"/>
-    </row>
-    <row r="691" ht="22" customHeight="1">
-      <c r="A691" s="3">
-        <f>IF(C691="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B691" s="3" t="n"/>
-      <c r="C691" s="3" t="n"/>
-      <c r="D691" s="4" t="n"/>
-      <c r="E691" s="4" t="n"/>
-      <c r="F691" s="5" t="n"/>
-      <c r="G691" s="6" t="n"/>
-      <c r="H691" s="4" t="n"/>
-      <c r="I691" s="7" t="n"/>
-      <c r="J691" s="4" t="n"/>
-    </row>
-    <row r="692" ht="22" customHeight="1">
-      <c r="A692" s="3">
-        <f>IF(C692="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B692" s="3" t="n"/>
-      <c r="C692" s="3" t="n"/>
-      <c r="D692" s="4" t="n"/>
-      <c r="E692" s="4" t="n"/>
-      <c r="F692" s="5" t="n"/>
-      <c r="G692" s="6" t="n"/>
-      <c r="H692" s="4" t="n"/>
-      <c r="I692" s="7" t="n"/>
-      <c r="J692" s="4" t="n"/>
-    </row>
-    <row r="693" ht="22" customHeight="1">
-      <c r="A693" s="3">
-        <f>IF(C693="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B693" s="3" t="n"/>
-      <c r="C693" s="3" t="n"/>
-      <c r="D693" s="4" t="n"/>
-      <c r="E693" s="4" t="n"/>
-      <c r="F693" s="5" t="n"/>
-      <c r="G693" s="6" t="n"/>
-      <c r="H693" s="4" t="n"/>
-      <c r="I693" s="7" t="n"/>
-      <c r="J693" s="4" t="n"/>
-    </row>
-    <row r="694" ht="22" customHeight="1">
-      <c r="A694" s="3">
-        <f>IF(C694="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B694" s="3" t="n"/>
-      <c r="C694" s="3" t="n"/>
-      <c r="D694" s="4" t="n"/>
-      <c r="E694" s="4" t="n"/>
-      <c r="F694" s="5" t="n"/>
-      <c r="G694" s="6" t="n"/>
-      <c r="H694" s="4" t="n"/>
-      <c r="I694" s="7" t="n"/>
-      <c r="J694" s="4" t="n"/>
-    </row>
-    <row r="695" ht="22" customHeight="1">
-      <c r="A695" s="3">
-        <f>IF(C695="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B695" s="3" t="n"/>
-      <c r="C695" s="3" t="n"/>
-      <c r="D695" s="4" t="n"/>
-      <c r="E695" s="4" t="n"/>
-      <c r="F695" s="5" t="n"/>
-      <c r="G695" s="6" t="n"/>
-      <c r="H695" s="4" t="n"/>
-      <c r="I695" s="7" t="n"/>
-      <c r="J695" s="4" t="n"/>
-    </row>
-    <row r="696" ht="22" customHeight="1">
-      <c r="A696" s="3">
-        <f>IF(C696="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B696" s="3" t="n"/>
-      <c r="C696" s="3" t="n"/>
-      <c r="D696" s="4" t="n"/>
-      <c r="E696" s="4" t="n"/>
-      <c r="F696" s="5" t="n"/>
-      <c r="G696" s="6" t="n"/>
-      <c r="H696" s="4" t="n"/>
-      <c r="I696" s="7" t="n"/>
-      <c r="J696" s="4" t="n"/>
-    </row>
-    <row r="697" ht="22" customHeight="1">
-      <c r="A697" s="3">
-        <f>IF(C697="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B697" s="3" t="n"/>
-      <c r="C697" s="3" t="n"/>
-      <c r="D697" s="4" t="n"/>
-      <c r="E697" s="4" t="n"/>
-      <c r="F697" s="5" t="n"/>
-      <c r="G697" s="6" t="n"/>
-      <c r="H697" s="4" t="n"/>
-      <c r="I697" s="7" t="n"/>
-      <c r="J697" s="4" t="n"/>
-    </row>
-    <row r="698" ht="22" customHeight="1">
-      <c r="A698" s="3">
-        <f>IF(C698="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B698" s="3" t="n"/>
-      <c r="C698" s="3" t="n"/>
-      <c r="D698" s="4" t="n"/>
-      <c r="E698" s="4" t="n"/>
-      <c r="F698" s="5" t="n"/>
-      <c r="G698" s="6" t="n"/>
-      <c r="H698" s="4" t="n"/>
-      <c r="I698" s="7" t="n"/>
-      <c r="J698" s="4" t="n"/>
-    </row>
-    <row r="699" ht="22" customHeight="1">
-      <c r="A699" s="3">
-        <f>IF(C699="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B699" s="3" t="n"/>
-      <c r="C699" s="3" t="n"/>
-      <c r="D699" s="4" t="n"/>
-      <c r="E699" s="4" t="n"/>
-      <c r="F699" s="5" t="n"/>
-      <c r="G699" s="6" t="n"/>
-      <c r="H699" s="4" t="n"/>
-      <c r="I699" s="7" t="n"/>
-      <c r="J699" s="4" t="n"/>
-    </row>
-    <row r="700" ht="22" customHeight="1">
-      <c r="A700" s="3">
-        <f>IF(C700="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B700" s="3" t="n"/>
-      <c r="C700" s="3" t="n"/>
-      <c r="D700" s="4" t="n"/>
-      <c r="E700" s="4" t="n"/>
-      <c r="F700" s="5" t="n"/>
-      <c r="G700" s="6" t="n"/>
-      <c r="H700" s="4" t="n"/>
-      <c r="I700" s="7" t="n"/>
-      <c r="J700" s="4" t="n"/>
-    </row>
-    <row r="701" ht="22" customHeight="1">
-      <c r="A701" s="3">
-        <f>IF(C701="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B701" s="3" t="n"/>
-      <c r="C701" s="3" t="n"/>
-      <c r="D701" s="4" t="n"/>
-      <c r="E701" s="4" t="n"/>
-      <c r="F701" s="5" t="n"/>
-      <c r="G701" s="6" t="n"/>
-      <c r="H701" s="4" t="n"/>
-      <c r="I701" s="7" t="n"/>
-      <c r="J701" s="4" t="n"/>
-    </row>
-    <row r="702" ht="22" customHeight="1">
-      <c r="A702" s="3">
-        <f>IF(C702="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B702" s="3" t="n"/>
-      <c r="C702" s="3" t="n"/>
-      <c r="D702" s="4" t="n"/>
-      <c r="E702" s="4" t="n"/>
-      <c r="F702" s="5" t="n"/>
-      <c r="G702" s="6" t="n"/>
-      <c r="H702" s="4" t="n"/>
-      <c r="I702" s="7" t="n"/>
-      <c r="J702" s="4" t="n"/>
-    </row>
-    <row r="703" ht="22" customHeight="1">
-      <c r="A703" s="3">
-        <f>IF(C703="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B703" s="3" t="n"/>
-      <c r="C703" s="3" t="n"/>
-      <c r="D703" s="4" t="n"/>
-      <c r="E703" s="4" t="n"/>
-      <c r="F703" s="5" t="n"/>
-      <c r="G703" s="6" t="n"/>
-      <c r="H703" s="4" t="n"/>
-      <c r="I703" s="7" t="n"/>
-      <c r="J703" s="4" t="n"/>
-    </row>
-    <row r="704" ht="22" customHeight="1">
-      <c r="A704" s="3">
-        <f>IF(C704="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B704" s="3" t="n"/>
-      <c r="C704" s="3" t="n"/>
-      <c r="D704" s="4" t="n"/>
-      <c r="E704" s="4" t="n"/>
-      <c r="F704" s="5" t="n"/>
-      <c r="G704" s="6" t="n"/>
-      <c r="H704" s="4" t="n"/>
-      <c r="I704" s="7" t="n"/>
-      <c r="J704" s="4" t="n"/>
-    </row>
-    <row r="705" ht="22" customHeight="1">
-      <c r="A705" s="3">
-        <f>IF(C705="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B705" s="3" t="n"/>
-      <c r="C705" s="3" t="n"/>
-      <c r="D705" s="4" t="n"/>
-      <c r="E705" s="4" t="n"/>
-      <c r="F705" s="5" t="n"/>
-      <c r="G705" s="6" t="n"/>
-      <c r="H705" s="4" t="n"/>
-      <c r="I705" s="7" t="n"/>
-      <c r="J705" s="4" t="n"/>
-    </row>
-    <row r="706" ht="22" customHeight="1">
-      <c r="A706" s="3">
-        <f>IF(C706="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B706" s="3" t="n"/>
-      <c r="C706" s="3" t="n"/>
-      <c r="D706" s="4" t="n"/>
-      <c r="E706" s="4" t="n"/>
-      <c r="F706" s="5" t="n"/>
-      <c r="G706" s="6" t="n"/>
-      <c r="H706" s="4" t="n"/>
-      <c r="I706" s="7" t="n"/>
-      <c r="J706" s="4" t="n"/>
-    </row>
-    <row r="707" ht="22" customHeight="1">
-      <c r="A707" s="3">
-        <f>IF(C707="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B707" s="3" t="n"/>
-      <c r="C707" s="3" t="n"/>
-      <c r="D707" s="4" t="n"/>
-      <c r="E707" s="4" t="n"/>
-      <c r="F707" s="5" t="n"/>
-      <c r="G707" s="6" t="n"/>
-      <c r="H707" s="4" t="n"/>
-      <c r="I707" s="7" t="n"/>
-      <c r="J707" s="4" t="n"/>
-    </row>
-    <row r="708" ht="22" customHeight="1">
-      <c r="A708" s="3">
-        <f>IF(C708="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B708" s="3" t="n"/>
-      <c r="C708" s="3" t="n"/>
-      <c r="D708" s="4" t="n"/>
-      <c r="E708" s="4" t="n"/>
-      <c r="F708" s="5" t="n"/>
-      <c r="G708" s="6" t="n"/>
-      <c r="H708" s="4" t="n"/>
-      <c r="I708" s="7" t="n"/>
-      <c r="J708" s="4" t="n"/>
-    </row>
-    <row r="709" ht="22" customHeight="1">
-      <c r="A709" s="3">
-        <f>IF(C709="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B709" s="3" t="n"/>
-      <c r="C709" s="3" t="n"/>
-      <c r="D709" s="4" t="n"/>
-      <c r="E709" s="4" t="n"/>
-      <c r="F709" s="5" t="n"/>
-      <c r="G709" s="6" t="n"/>
-      <c r="H709" s="4" t="n"/>
-      <c r="I709" s="7" t="n"/>
-      <c r="J709" s="4" t="n"/>
-    </row>
-    <row r="710" ht="22" customHeight="1">
-      <c r="A710" s="3">
-        <f>IF(C710="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B710" s="3" t="n"/>
-      <c r="C710" s="3" t="n"/>
-      <c r="D710" s="4" t="n"/>
-      <c r="E710" s="4" t="n"/>
-      <c r="F710" s="5" t="n"/>
-      <c r="G710" s="6" t="n"/>
-      <c r="H710" s="4" t="n"/>
-      <c r="I710" s="7" t="n"/>
-      <c r="J710" s="4" t="n"/>
-    </row>
-    <row r="711" ht="22" customHeight="1">
-      <c r="A711" s="3">
-        <f>IF(C711="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B711" s="3" t="n"/>
-      <c r="C711" s="3" t="n"/>
-      <c r="D711" s="4" t="n"/>
-      <c r="E711" s="4" t="n"/>
-      <c r="F711" s="5" t="n"/>
-      <c r="G711" s="6" t="n"/>
-      <c r="H711" s="4" t="n"/>
-      <c r="I711" s="7" t="n"/>
-      <c r="J711" s="4" t="n"/>
-    </row>
-    <row r="712" ht="22" customHeight="1">
-      <c r="A712" s="3">
-        <f>IF(C712="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B712" s="3" t="n"/>
-      <c r="C712" s="3" t="n"/>
-      <c r="D712" s="4" t="n"/>
-      <c r="E712" s="4" t="n"/>
-      <c r="F712" s="5" t="n"/>
-      <c r="G712" s="6" t="n"/>
-      <c r="H712" s="4" t="n"/>
-      <c r="I712" s="7" t="n"/>
-      <c r="J712" s="4" t="n"/>
-    </row>
-    <row r="713" ht="22" customHeight="1">
-      <c r="A713" s="3">
-        <f>IF(C713="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B713" s="3" t="n"/>
-      <c r="C713" s="3" t="n"/>
-      <c r="D713" s="4" t="n"/>
-      <c r="E713" s="4" t="n"/>
-      <c r="F713" s="5" t="n"/>
-      <c r="G713" s="6" t="n"/>
-      <c r="H713" s="4" t="n"/>
-      <c r="I713" s="7" t="n"/>
-      <c r="J713" s="4" t="n"/>
-    </row>
-    <row r="714" ht="22" customHeight="1">
-      <c r="A714" s="3">
-        <f>IF(C714="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B714" s="3" t="n"/>
-      <c r="C714" s="3" t="n"/>
-      <c r="D714" s="4" t="n"/>
-      <c r="E714" s="4" t="n"/>
-      <c r="F714" s="5" t="n"/>
-      <c r="G714" s="6" t="n"/>
-      <c r="H714" s="4" t="n"/>
-      <c r="I714" s="7" t="n"/>
-      <c r="J714" s="4" t="n"/>
-    </row>
-    <row r="715" ht="22" customHeight="1">
-      <c r="A715" s="3">
-        <f>IF(C715="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B715" s="3" t="n"/>
-      <c r="C715" s="3" t="n"/>
-      <c r="D715" s="4" t="n"/>
-      <c r="E715" s="4" t="n"/>
-      <c r="F715" s="5" t="n"/>
-      <c r="G715" s="6" t="n"/>
-      <c r="H715" s="4" t="n"/>
-      <c r="I715" s="7" t="n"/>
-      <c r="J715" s="4" t="n"/>
-    </row>
-    <row r="716" ht="22" customHeight="1">
-      <c r="A716" s="3">
-        <f>IF(C716="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B716" s="3" t="n"/>
-      <c r="C716" s="3" t="n"/>
-      <c r="D716" s="4" t="n"/>
-      <c r="E716" s="4" t="n"/>
-      <c r="F716" s="5" t="n"/>
-      <c r="G716" s="6" t="n"/>
-      <c r="H716" s="4" t="n"/>
-      <c r="I716" s="7" t="n"/>
-      <c r="J716" s="4" t="n"/>
-    </row>
-    <row r="717" ht="22" customHeight="1">
-      <c r="A717" s="3">
-        <f>IF(C717="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B717" s="3" t="n"/>
-      <c r="C717" s="3" t="n"/>
-      <c r="D717" s="4" t="n"/>
-      <c r="E717" s="4" t="n"/>
-      <c r="F717" s="5" t="n"/>
-      <c r="G717" s="6" t="n"/>
-      <c r="H717" s="4" t="n"/>
-      <c r="I717" s="7" t="n"/>
-      <c r="J717" s="4" t="n"/>
-    </row>
-    <row r="718" ht="22" customHeight="1">
-      <c r="A718" s="3">
-        <f>IF(C718="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B718" s="3" t="n"/>
-      <c r="C718" s="3" t="n"/>
-      <c r="D718" s="4" t="n"/>
-      <c r="E718" s="4" t="n"/>
-      <c r="F718" s="5" t="n"/>
-      <c r="G718" s="6" t="n"/>
-      <c r="H718" s="4" t="n"/>
-      <c r="I718" s="7" t="n"/>
-      <c r="J718" s="4" t="n"/>
-    </row>
-    <row r="719" ht="22" customHeight="1">
-      <c r="A719" s="3">
-        <f>IF(C719="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B719" s="3" t="n"/>
-      <c r="C719" s="3" t="n"/>
-      <c r="D719" s="4" t="n"/>
-      <c r="E719" s="4" t="n"/>
-      <c r="F719" s="5" t="n"/>
-      <c r="G719" s="6" t="n"/>
-      <c r="H719" s="4" t="n"/>
-      <c r="I719" s="7" t="n"/>
-      <c r="J719" s="4" t="n"/>
-    </row>
-    <row r="720" ht="22" customHeight="1">
-      <c r="A720" s="3">
-        <f>IF(C720="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B720" s="3" t="n"/>
-      <c r="C720" s="3" t="n"/>
-      <c r="D720" s="4" t="n"/>
-      <c r="E720" s="4" t="n"/>
-      <c r="F720" s="5" t="n"/>
-      <c r="G720" s="6" t="n"/>
-      <c r="H720" s="4" t="n"/>
-      <c r="I720" s="7" t="n"/>
-      <c r="J720" s="4" t="n"/>
-    </row>
-    <row r="721" ht="22" customHeight="1">
-      <c r="A721" s="3">
-        <f>IF(C721="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B721" s="3" t="n"/>
-      <c r="C721" s="3" t="n"/>
-      <c r="D721" s="4" t="n"/>
-      <c r="E721" s="4" t="n"/>
-      <c r="F721" s="5" t="n"/>
-      <c r="G721" s="6" t="n"/>
-      <c r="H721" s="4" t="n"/>
-      <c r="I721" s="7" t="n"/>
-      <c r="J721" s="4" t="n"/>
-    </row>
-    <row r="722" ht="22" customHeight="1">
-      <c r="A722" s="3">
-        <f>IF(C722="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B722" s="3" t="n"/>
-      <c r="C722" s="3" t="n"/>
-      <c r="D722" s="4" t="n"/>
-      <c r="E722" s="4" t="n"/>
-      <c r="F722" s="5" t="n"/>
-      <c r="G722" s="6" t="n"/>
-      <c r="H722" s="4" t="n"/>
-      <c r="I722" s="7" t="n"/>
-      <c r="J722" s="4" t="n"/>
-    </row>
-    <row r="723" ht="22" customHeight="1">
-      <c r="A723" s="3">
-        <f>IF(C723="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B723" s="3" t="n"/>
-      <c r="C723" s="3" t="n"/>
-      <c r="D723" s="4" t="n"/>
-      <c r="E723" s="4" t="n"/>
-      <c r="F723" s="5" t="n"/>
-      <c r="G723" s="6" t="n"/>
-      <c r="H723" s="4" t="n"/>
-      <c r="I723" s="7" t="n"/>
-      <c r="J723" s="4" t="n"/>
-    </row>
-    <row r="724" ht="22" customHeight="1">
-      <c r="A724" s="3">
-        <f>IF(C724="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B724" s="3" t="n"/>
-      <c r="C724" s="3" t="n"/>
-      <c r="D724" s="4" t="n"/>
-      <c r="E724" s="4" t="n"/>
-      <c r="F724" s="5" t="n"/>
-      <c r="G724" s="6" t="n"/>
-      <c r="H724" s="4" t="n"/>
-      <c r="I724" s="7" t="n"/>
-      <c r="J724" s="4" t="n"/>
-    </row>
-    <row r="725" ht="22" customHeight="1">
-      <c r="A725" s="3">
-        <f>IF(C725="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B725" s="3" t="n"/>
-      <c r="C725" s="3" t="n"/>
-      <c r="D725" s="4" t="n"/>
-      <c r="E725" s="4" t="n"/>
-      <c r="F725" s="5" t="n"/>
-      <c r="G725" s="6" t="n"/>
-      <c r="H725" s="4" t="n"/>
-      <c r="I725" s="7" t="n"/>
-      <c r="J725" s="4" t="n"/>
-    </row>
-    <row r="726" ht="22" customHeight="1">
-      <c r="A726" s="3">
-        <f>IF(C726="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B726" s="3" t="n"/>
-      <c r="C726" s="3" t="n"/>
-      <c r="D726" s="4" t="n"/>
-      <c r="E726" s="4" t="n"/>
-      <c r="F726" s="5" t="n"/>
-      <c r="G726" s="6" t="n"/>
-      <c r="H726" s="4" t="n"/>
-      <c r="I726" s="7" t="n"/>
-      <c r="J726" s="4" t="n"/>
-    </row>
-    <row r="727" ht="22" customHeight="1">
-      <c r="A727" s="3">
-        <f>IF(C727="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B727" s="3" t="n"/>
-      <c r="C727" s="3" t="n"/>
-      <c r="D727" s="4" t="n"/>
-      <c r="E727" s="4" t="n"/>
-      <c r="F727" s="5" t="n"/>
-      <c r="G727" s="6" t="n"/>
-      <c r="H727" s="4" t="n"/>
-      <c r="I727" s="7" t="n"/>
-      <c r="J727" s="4" t="n"/>
-    </row>
-    <row r="728" ht="22" customHeight="1">
-      <c r="A728" s="3">
-        <f>IF(C728="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B728" s="3" t="n"/>
-      <c r="C728" s="3" t="n"/>
-      <c r="D728" s="4" t="n"/>
-      <c r="E728" s="4" t="n"/>
-      <c r="F728" s="5" t="n"/>
-      <c r="G728" s="6" t="n"/>
-      <c r="H728" s="4" t="n"/>
-      <c r="I728" s="7" t="n"/>
-      <c r="J728" s="4" t="n"/>
-    </row>
-    <row r="729" ht="22" customHeight="1">
-      <c r="A729" s="3">
-        <f>IF(C729="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B729" s="3" t="n"/>
-      <c r="C729" s="3" t="n"/>
-      <c r="D729" s="4" t="n"/>
-      <c r="E729" s="4" t="n"/>
-      <c r="F729" s="5" t="n"/>
-      <c r="G729" s="6" t="n"/>
-      <c r="H729" s="4" t="n"/>
-      <c r="I729" s="7" t="n"/>
-      <c r="J729" s="4" t="n"/>
-    </row>
-    <row r="730" ht="22" customHeight="1">
-      <c r="A730" s="3">
-        <f>IF(C730="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B730" s="3" t="n"/>
-      <c r="C730" s="3" t="n"/>
-      <c r="D730" s="4" t="n"/>
-      <c r="E730" s="4" t="n"/>
-      <c r="F730" s="5" t="n"/>
-      <c r="G730" s="6" t="n"/>
-      <c r="H730" s="4" t="n"/>
-      <c r="I730" s="7" t="n"/>
-      <c r="J730" s="4" t="n"/>
-    </row>
-    <row r="731" ht="22" customHeight="1">
-      <c r="A731" s="3">
-        <f>IF(C731="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B731" s="3" t="n"/>
-      <c r="C731" s="3" t="n"/>
-      <c r="D731" s="4" t="n"/>
-      <c r="E731" s="4" t="n"/>
-      <c r="F731" s="5" t="n"/>
-      <c r="G731" s="6" t="n"/>
-      <c r="H731" s="4" t="n"/>
-      <c r="I731" s="7" t="n"/>
-      <c r="J731" s="4" t="n"/>
-    </row>
-    <row r="732" ht="22" customHeight="1">
-      <c r="A732" s="3">
-        <f>IF(C732="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B732" s="3" t="n"/>
-      <c r="C732" s="3" t="n"/>
-      <c r="D732" s="4" t="n"/>
-      <c r="E732" s="4" t="n"/>
-      <c r="F732" s="5" t="n"/>
-      <c r="G732" s="6" t="n"/>
-      <c r="H732" s="4" t="n"/>
-      <c r="I732" s="7" t="n"/>
-      <c r="J732" s="4" t="n"/>
-    </row>
-    <row r="733" ht="22" customHeight="1">
-      <c r="A733" s="3">
-        <f>IF(C733="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B733" s="3" t="n"/>
-      <c r="C733" s="3" t="n"/>
-      <c r="D733" s="4" t="n"/>
-      <c r="E733" s="4" t="n"/>
-      <c r="F733" s="5" t="n"/>
-      <c r="G733" s="6" t="n"/>
-      <c r="H733" s="4" t="n"/>
-      <c r="I733" s="7" t="n"/>
-      <c r="J733" s="4" t="n"/>
-    </row>
-    <row r="734" ht="22" customHeight="1">
-      <c r="A734" s="3">
-        <f>IF(C734="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B734" s="3" t="n"/>
-      <c r="C734" s="3" t="n"/>
-      <c r="D734" s="4" t="n"/>
-      <c r="E734" s="4" t="n"/>
-      <c r="F734" s="5" t="n"/>
-      <c r="G734" s="6" t="n"/>
-      <c r="H734" s="4" t="n"/>
-      <c r="I734" s="7" t="n"/>
-      <c r="J734" s="4" t="n"/>
-    </row>
-    <row r="735" ht="22" customHeight="1">
-      <c r="A735" s="3">
-        <f>IF(C735="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B735" s="3" t="n"/>
-      <c r="C735" s="3" t="n"/>
-      <c r="D735" s="4" t="n"/>
-      <c r="E735" s="4" t="n"/>
-      <c r="F735" s="5" t="n"/>
-      <c r="G735" s="6" t="n"/>
-      <c r="H735" s="4" t="n"/>
-      <c r="I735" s="7" t="n"/>
-      <c r="J735" s="4" t="n"/>
-    </row>
-    <row r="736" ht="22" customHeight="1">
-      <c r="A736" s="3">
-        <f>IF(C736="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B736" s="3" t="n"/>
-      <c r="C736" s="3" t="n"/>
-      <c r="D736" s="4" t="n"/>
-      <c r="E736" s="4" t="n"/>
-      <c r="F736" s="5" t="n"/>
-      <c r="G736" s="6" t="n"/>
-      <c r="H736" s="4" t="n"/>
-      <c r="I736" s="7" t="n"/>
-      <c r="J736" s="4" t="n"/>
-    </row>
-    <row r="737" ht="22" customHeight="1">
-      <c r="A737" s="3">
-        <f>IF(C737="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B737" s="3" t="n"/>
-      <c r="C737" s="3" t="n"/>
-      <c r="D737" s="4" t="n"/>
-      <c r="E737" s="4" t="n"/>
-      <c r="F737" s="5" t="n"/>
-      <c r="G737" s="6" t="n"/>
-      <c r="H737" s="4" t="n"/>
-      <c r="I737" s="7" t="n"/>
-      <c r="J737" s="4" t="n"/>
-    </row>
-    <row r="738" ht="22" customHeight="1">
-      <c r="A738" s="3">
-        <f>IF(C738="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B738" s="3" t="n"/>
-      <c r="C738" s="3" t="n"/>
-      <c r="D738" s="4" t="n"/>
-      <c r="E738" s="4" t="n"/>
-      <c r="F738" s="5" t="n"/>
-      <c r="G738" s="6" t="n"/>
-      <c r="H738" s="4" t="n"/>
-      <c r="I738" s="7" t="n"/>
-      <c r="J738" s="4" t="n"/>
-    </row>
-    <row r="739" ht="22" customHeight="1">
-      <c r="A739" s="3">
-        <f>IF(C739="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B739" s="3" t="n"/>
-      <c r="C739" s="3" t="n"/>
-      <c r="D739" s="4" t="n"/>
-      <c r="E739" s="4" t="n"/>
-      <c r="F739" s="5" t="n"/>
-      <c r="G739" s="6" t="n"/>
-      <c r="H739" s="4" t="n"/>
-      <c r="I739" s="7" t="n"/>
-      <c r="J739" s="4" t="n"/>
-    </row>
-    <row r="740" ht="22" customHeight="1">
-      <c r="A740" s="3">
-        <f>IF(C740="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B740" s="3" t="n"/>
-      <c r="C740" s="3" t="n"/>
-      <c r="D740" s="4" t="n"/>
-      <c r="E740" s="4" t="n"/>
-      <c r="F740" s="5" t="n"/>
-      <c r="G740" s="6" t="n"/>
-      <c r="H740" s="4" t="n"/>
-      <c r="I740" s="7" t="n"/>
-      <c r="J740" s="4" t="n"/>
-    </row>
-    <row r="741" ht="22" customHeight="1">
-      <c r="A741" s="3">
-        <f>IF(C741="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B741" s="3" t="n"/>
-      <c r="C741" s="3" t="n"/>
-      <c r="D741" s="4" t="n"/>
-      <c r="E741" s="4" t="n"/>
-      <c r="F741" s="5" t="n"/>
-      <c r="G741" s="6" t="n"/>
-      <c r="H741" s="4" t="n"/>
-      <c r="I741" s="7" t="n"/>
-      <c r="J741" s="4" t="n"/>
-    </row>
-    <row r="742" ht="22" customHeight="1">
-      <c r="A742" s="3">
-        <f>IF(C742="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B742" s="3" t="n"/>
-      <c r="C742" s="3" t="n"/>
-      <c r="D742" s="4" t="n"/>
-      <c r="E742" s="4" t="n"/>
-      <c r="F742" s="5" t="n"/>
-      <c r="G742" s="6" t="n"/>
-      <c r="H742" s="4" t="n"/>
-      <c r="I742" s="7" t="n"/>
-      <c r="J742" s="4" t="n"/>
-    </row>
-    <row r="743" ht="22" customHeight="1">
-      <c r="A743" s="3">
-        <f>IF(C743="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B743" s="3" t="n"/>
-      <c r="C743" s="3" t="n"/>
-      <c r="D743" s="4" t="n"/>
-      <c r="E743" s="4" t="n"/>
-      <c r="F743" s="5" t="n"/>
-      <c r="G743" s="6" t="n"/>
-      <c r="H743" s="4" t="n"/>
-      <c r="I743" s="7" t="n"/>
-      <c r="J743" s="4" t="n"/>
-    </row>
-    <row r="744" ht="22" customHeight="1">
-      <c r="A744" s="3">
-        <f>IF(C744="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B744" s="3" t="n"/>
-      <c r="C744" s="3" t="n"/>
-      <c r="D744" s="4" t="n"/>
-      <c r="E744" s="4" t="n"/>
-      <c r="F744" s="5" t="n"/>
-      <c r="G744" s="6" t="n"/>
-      <c r="H744" s="4" t="n"/>
-      <c r="I744" s="7" t="n"/>
-      <c r="J744" s="4" t="n"/>
-    </row>
-    <row r="745" ht="22" customHeight="1">
-      <c r="A745" s="3">
-        <f>IF(C745="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B745" s="3" t="n"/>
-      <c r="C745" s="3" t="n"/>
-      <c r="D745" s="4" t="n"/>
-      <c r="E745" s="4" t="n"/>
-      <c r="F745" s="5" t="n"/>
-      <c r="G745" s="6" t="n"/>
-      <c r="H745" s="4" t="n"/>
-      <c r="I745" s="7" t="n"/>
-      <c r="J745" s="4" t="n"/>
-    </row>
-    <row r="746" ht="22" customHeight="1">
-      <c r="A746" s="3">
-        <f>IF(C746="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B746" s="3" t="n"/>
-      <c r="C746" s="3" t="n"/>
-      <c r="D746" s="4" t="n"/>
-      <c r="E746" s="4" t="n"/>
-      <c r="F746" s="5" t="n"/>
-      <c r="G746" s="6" t="n"/>
-      <c r="H746" s="4" t="n"/>
-      <c r="I746" s="7" t="n"/>
-      <c r="J746" s="4" t="n"/>
-    </row>
-    <row r="747" ht="22" customHeight="1">
-      <c r="A747" s="3">
-        <f>IF(C747="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B747" s="3" t="n"/>
-      <c r="C747" s="3" t="n"/>
-      <c r="D747" s="4" t="n"/>
-      <c r="E747" s="4" t="n"/>
-      <c r="F747" s="5" t="n"/>
-      <c r="G747" s="6" t="n"/>
-      <c r="H747" s="4" t="n"/>
-      <c r="I747" s="7" t="n"/>
-      <c r="J747" s="4" t="n"/>
-    </row>
-    <row r="748" ht="22" customHeight="1">
-      <c r="A748" s="3">
-        <f>IF(C748="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B748" s="3" t="n"/>
-      <c r="C748" s="3" t="n"/>
-      <c r="D748" s="4" t="n"/>
-      <c r="E748" s="4" t="n"/>
-      <c r="F748" s="5" t="n"/>
-      <c r="G748" s="6" t="n"/>
-      <c r="H748" s="4" t="n"/>
-      <c r="I748" s="7" t="n"/>
-      <c r="J748" s="4" t="n"/>
-    </row>
-    <row r="749" ht="22" customHeight="1">
-      <c r="A749" s="3">
-        <f>IF(C749="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B749" s="3" t="n"/>
-      <c r="C749" s="3" t="n"/>
-      <c r="D749" s="4" t="n"/>
-      <c r="E749" s="4" t="n"/>
-      <c r="F749" s="5" t="n"/>
-      <c r="G749" s="6" t="n"/>
-      <c r="H749" s="4" t="n"/>
-      <c r="I749" s="7" t="n"/>
-      <c r="J749" s="4" t="n"/>
-    </row>
-    <row r="750" ht="22" customHeight="1">
-      <c r="A750" s="3">
-        <f>IF(C750="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B750" s="3" t="n"/>
-      <c r="C750" s="3" t="n"/>
-      <c r="D750" s="4" t="n"/>
-      <c r="E750" s="4" t="n"/>
-      <c r="F750" s="5" t="n"/>
-      <c r="G750" s="6" t="n"/>
-      <c r="H750" s="4" t="n"/>
-      <c r="I750" s="7" t="n"/>
-      <c r="J750" s="4" t="n"/>
-    </row>
-    <row r="751" ht="22" customHeight="1">
-      <c r="A751" s="3">
-        <f>IF(C751="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B751" s="3" t="n"/>
-      <c r="C751" s="3" t="n"/>
-      <c r="D751" s="4" t="n"/>
-      <c r="E751" s="4" t="n"/>
-      <c r="F751" s="5" t="n"/>
-      <c r="G751" s="6" t="n"/>
-      <c r="H751" s="4" t="n"/>
-      <c r="I751" s="7" t="n"/>
-      <c r="J751" s="4" t="n"/>
-    </row>
-    <row r="752" ht="22" customHeight="1">
-      <c r="A752" s="3">
-        <f>IF(C752="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B752" s="3" t="n"/>
-      <c r="C752" s="3" t="n"/>
-      <c r="D752" s="4" t="n"/>
-      <c r="E752" s="4" t="n"/>
-      <c r="F752" s="5" t="n"/>
-      <c r="G752" s="6" t="n"/>
-      <c r="H752" s="4" t="n"/>
-      <c r="I752" s="7" t="n"/>
-      <c r="J752" s="4" t="n"/>
-    </row>
-    <row r="753" ht="22" customHeight="1">
-      <c r="A753" s="3">
-        <f>IF(C753="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B753" s="3" t="n"/>
-      <c r="C753" s="3" t="n"/>
-      <c r="D753" s="4" t="n"/>
-      <c r="E753" s="4" t="n"/>
-      <c r="F753" s="5" t="n"/>
-      <c r="G753" s="6" t="n"/>
-      <c r="H753" s="4" t="n"/>
-      <c r="I753" s="7" t="n"/>
-      <c r="J753" s="4" t="n"/>
-    </row>
-    <row r="754" ht="22" customHeight="1">
-      <c r="A754" s="3">
-        <f>IF(C754="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B754" s="3" t="n"/>
-      <c r="C754" s="3" t="n"/>
-      <c r="D754" s="4" t="n"/>
-      <c r="E754" s="4" t="n"/>
-      <c r="F754" s="5" t="n"/>
-      <c r="G754" s="6" t="n"/>
-      <c r="H754" s="4" t="n"/>
-      <c r="I754" s="7" t="n"/>
-      <c r="J754" s="4" t="n"/>
-    </row>
-    <row r="755" ht="22" customHeight="1">
-      <c r="A755" s="3">
-        <f>IF(C755="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B755" s="3" t="n"/>
-      <c r="C755" s="3" t="n"/>
-      <c r="D755" s="4" t="n"/>
-      <c r="E755" s="4" t="n"/>
-      <c r="F755" s="5" t="n"/>
-      <c r="G755" s="6" t="n"/>
-      <c r="H755" s="4" t="n"/>
-      <c r="I755" s="7" t="n"/>
-      <c r="J755" s="4" t="n"/>
-    </row>
-    <row r="756" ht="22" customHeight="1">
-      <c r="A756" s="3">
-        <f>IF(C756="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B756" s="3" t="n"/>
-      <c r="C756" s="3" t="n"/>
-      <c r="D756" s="4" t="n"/>
-      <c r="E756" s="4" t="n"/>
-      <c r="F756" s="5" t="n"/>
-      <c r="G756" s="6" t="n"/>
-      <c r="H756" s="4" t="n"/>
-      <c r="I756" s="7" t="n"/>
-      <c r="J756" s="4" t="n"/>
-    </row>
-    <row r="757" ht="22" customHeight="1">
-      <c r="A757" s="3">
-        <f>IF(C757="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B757" s="3" t="n"/>
-      <c r="C757" s="3" t="n"/>
-      <c r="D757" s="4" t="n"/>
-      <c r="E757" s="4" t="n"/>
-      <c r="F757" s="5" t="n"/>
-      <c r="G757" s="6" t="n"/>
-      <c r="H757" s="4" t="n"/>
-      <c r="I757" s="7" t="n"/>
-      <c r="J757" s="4" t="n"/>
-    </row>
-    <row r="758" ht="22" customHeight="1">
-      <c r="A758" s="3">
-        <f>IF(C758="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B758" s="3" t="n"/>
-      <c r="C758" s="3" t="n"/>
-      <c r="D758" s="4" t="n"/>
-      <c r="E758" s="4" t="n"/>
-      <c r="F758" s="5" t="n"/>
-      <c r="G758" s="6" t="n"/>
-      <c r="H758" s="4" t="n"/>
-      <c r="I758" s="7" t="n"/>
-      <c r="J758" s="4" t="n"/>
-    </row>
-    <row r="759" ht="22" customHeight="1">
-      <c r="A759" s="3">
-        <f>IF(C759="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B759" s="3" t="n"/>
-      <c r="C759" s="3" t="n"/>
-      <c r="D759" s="4" t="n"/>
-      <c r="E759" s="4" t="n"/>
-      <c r="F759" s="5" t="n"/>
-      <c r="G759" s="6" t="n"/>
-      <c r="H759" s="4" t="n"/>
-      <c r="I759" s="7" t="n"/>
-      <c r="J759" s="4" t="n"/>
-    </row>
-    <row r="760" ht="22" customHeight="1">
-      <c r="A760" s="3">
-        <f>IF(C760="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B760" s="3" t="n"/>
-      <c r="C760" s="3" t="n"/>
-      <c r="D760" s="4" t="n"/>
-      <c r="E760" s="4" t="n"/>
-      <c r="F760" s="5" t="n"/>
-      <c r="G760" s="6" t="n"/>
-      <c r="H760" s="4" t="n"/>
-      <c r="I760" s="7" t="n"/>
-      <c r="J760" s="4" t="n"/>
-    </row>
-    <row r="761" ht="22" customHeight="1">
-      <c r="A761" s="3">
-        <f>IF(C761="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B761" s="3" t="n"/>
-      <c r="C761" s="3" t="n"/>
-      <c r="D761" s="4" t="n"/>
-      <c r="E761" s="4" t="n"/>
-      <c r="F761" s="5" t="n"/>
-      <c r="G761" s="6" t="n"/>
-      <c r="H761" s="4" t="n"/>
-      <c r="I761" s="7" t="n"/>
-      <c r="J761" s="4" t="n"/>
-    </row>
-    <row r="762" ht="22" customHeight="1">
-      <c r="A762" s="3">
-        <f>IF(C762="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B762" s="3" t="n"/>
-      <c r="C762" s="3" t="n"/>
-      <c r="D762" s="4" t="n"/>
-      <c r="E762" s="4" t="n"/>
-      <c r="F762" s="5" t="n"/>
-      <c r="G762" s="6" t="n"/>
-      <c r="H762" s="4" t="n"/>
-      <c r="I762" s="7" t="n"/>
-      <c r="J762" s="4" t="n"/>
-    </row>
-    <row r="763" ht="22" customHeight="1">
-      <c r="A763" s="3">
-        <f>IF(C763="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B763" s="3" t="n"/>
-      <c r="C763" s="3" t="n"/>
-      <c r="D763" s="4" t="n"/>
-      <c r="E763" s="4" t="n"/>
-      <c r="F763" s="5" t="n"/>
-      <c r="G763" s="6" t="n"/>
-      <c r="H763" s="4" t="n"/>
-      <c r="I763" s="7" t="n"/>
-      <c r="J763" s="4" t="n"/>
-    </row>
-    <row r="764" ht="22" customHeight="1">
-      <c r="A764" s="3">
-        <f>IF(C764="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B764" s="3" t="n"/>
-      <c r="C764" s="3" t="n"/>
-      <c r="D764" s="4" t="n"/>
-      <c r="E764" s="4" t="n"/>
-      <c r="F764" s="5" t="n"/>
-      <c r="G764" s="6" t="n"/>
-      <c r="H764" s="4" t="n"/>
-      <c r="I764" s="7" t="n"/>
-      <c r="J764" s="4" t="n"/>
-    </row>
-    <row r="765" ht="22" customHeight="1">
-      <c r="A765" s="3">
-        <f>IF(C765="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B765" s="3" t="n"/>
-      <c r="C765" s="3" t="n"/>
-      <c r="D765" s="4" t="n"/>
-      <c r="E765" s="4" t="n"/>
-      <c r="F765" s="5" t="n"/>
-      <c r="G765" s="6" t="n"/>
-      <c r="H765" s="4" t="n"/>
-      <c r="I765" s="7" t="n"/>
-      <c r="J765" s="4" t="n"/>
-    </row>
-    <row r="766" ht="22" customHeight="1">
-      <c r="A766" s="3">
-        <f>IF(C766="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B766" s="3" t="n"/>
-      <c r="C766" s="3" t="n"/>
-      <c r="D766" s="4" t="n"/>
-      <c r="E766" s="4" t="n"/>
-      <c r="F766" s="5" t="n"/>
-      <c r="G766" s="6" t="n"/>
-      <c r="H766" s="4" t="n"/>
-      <c r="I766" s="7" t="n"/>
-      <c r="J766" s="4" t="n"/>
-    </row>
-    <row r="767" ht="22" customHeight="1">
-      <c r="A767" s="3">
-        <f>IF(C767="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B767" s="3" t="n"/>
-      <c r="C767" s="3" t="n"/>
-      <c r="D767" s="4" t="n"/>
-      <c r="E767" s="4" t="n"/>
-      <c r="F767" s="5" t="n"/>
-      <c r="G767" s="6" t="n"/>
-      <c r="H767" s="4" t="n"/>
-      <c r="I767" s="7" t="n"/>
-      <c r="J767" s="4" t="n"/>
-    </row>
-    <row r="768" ht="22" customHeight="1">
-      <c r="A768" s="3">
-        <f>IF(C768="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B768" s="3" t="n"/>
-      <c r="C768" s="3" t="n"/>
-      <c r="D768" s="4" t="n"/>
-      <c r="E768" s="4" t="n"/>
-      <c r="F768" s="5" t="n"/>
-      <c r="G768" s="6" t="n"/>
-      <c r="H768" s="4" t="n"/>
-      <c r="I768" s="7" t="n"/>
-      <c r="J768" s="4" t="n"/>
-    </row>
-    <row r="769" ht="22" customHeight="1">
-      <c r="A769" s="3">
-        <f>IF(C769="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B769" s="3" t="n"/>
-      <c r="C769" s="3" t="n"/>
-      <c r="D769" s="4" t="n"/>
-      <c r="E769" s="4" t="n"/>
-      <c r="F769" s="5" t="n"/>
-      <c r="G769" s="6" t="n"/>
-      <c r="H769" s="4" t="n"/>
-      <c r="I769" s="7" t="n"/>
-      <c r="J769" s="4" t="n"/>
-    </row>
-    <row r="770" ht="22" customHeight="1">
-      <c r="A770" s="3">
-        <f>IF(C770="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B770" s="3" t="n"/>
-      <c r="C770" s="3" t="n"/>
-      <c r="D770" s="4" t="n"/>
-      <c r="E770" s="4" t="n"/>
-      <c r="F770" s="5" t="n"/>
-      <c r="G770" s="6" t="n"/>
-      <c r="H770" s="4" t="n"/>
-      <c r="I770" s="7" t="n"/>
-      <c r="J770" s="4" t="n"/>
-    </row>
-    <row r="771" ht="22" customHeight="1">
-      <c r="A771" s="3">
-        <f>IF(C771="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B771" s="3" t="n"/>
-      <c r="C771" s="3" t="n"/>
-      <c r="D771" s="4" t="n"/>
-      <c r="E771" s="4" t="n"/>
-      <c r="F771" s="5" t="n"/>
-      <c r="G771" s="6" t="n"/>
-      <c r="H771" s="4" t="n"/>
-      <c r="I771" s="7" t="n"/>
-      <c r="J771" s="4" t="n"/>
-    </row>
-    <row r="772" ht="22" customHeight="1">
-      <c r="A772" s="3">
-        <f>IF(C772="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B772" s="3" t="n"/>
-      <c r="C772" s="3" t="n"/>
-      <c r="D772" s="4" t="n"/>
-      <c r="E772" s="4" t="n"/>
-      <c r="F772" s="5" t="n"/>
-      <c r="G772" s="6" t="n"/>
-      <c r="H772" s="4" t="n"/>
-      <c r="I772" s="7" t="n"/>
-      <c r="J772" s="4" t="n"/>
-    </row>
-    <row r="773" ht="22" customHeight="1">
-      <c r="A773" s="3">
-        <f>IF(C773="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B773" s="3" t="n"/>
-      <c r="C773" s="3" t="n"/>
-      <c r="D773" s="4" t="n"/>
-      <c r="E773" s="4" t="n"/>
-      <c r="F773" s="5" t="n"/>
-      <c r="G773" s="6" t="n"/>
-      <c r="H773" s="4" t="n"/>
-      <c r="I773" s="7" t="n"/>
-      <c r="J773" s="4" t="n"/>
-    </row>
-    <row r="774" ht="22" customHeight="1">
-      <c r="A774" s="3">
-        <f>IF(C774="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B774" s="3" t="n"/>
-      <c r="C774" s="3" t="n"/>
-      <c r="D774" s="4" t="n"/>
-      <c r="E774" s="4" t="n"/>
-      <c r="F774" s="5" t="n"/>
-      <c r="G774" s="6" t="n"/>
-      <c r="H774" s="4" t="n"/>
-      <c r="I774" s="7" t="n"/>
-      <c r="J774" s="4" t="n"/>
-    </row>
-    <row r="775" ht="22" customHeight="1">
-      <c r="A775" s="3">
-        <f>IF(C775="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B775" s="3" t="n"/>
-      <c r="C775" s="3" t="n"/>
-      <c r="D775" s="4" t="n"/>
-      <c r="E775" s="4" t="n"/>
-      <c r="F775" s="5" t="n"/>
-      <c r="G775" s="6" t="n"/>
-      <c r="H775" s="4" t="n"/>
-      <c r="I775" s="7" t="n"/>
-      <c r="J775" s="4" t="n"/>
-    </row>
-    <row r="776" ht="22" customHeight="1">
-      <c r="A776" s="3">
-        <f>IF(C776="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B776" s="3" t="n"/>
-      <c r="C776" s="3" t="n"/>
-      <c r="D776" s="4" t="n"/>
-      <c r="E776" s="4" t="n"/>
-      <c r="F776" s="5" t="n"/>
-      <c r="G776" s="6" t="n"/>
-      <c r="H776" s="4" t="n"/>
-      <c r="I776" s="7" t="n"/>
-      <c r="J776" s="4" t="n"/>
-    </row>
-    <row r="777" ht="22" customHeight="1">
-      <c r="A777" s="3">
-        <f>IF(C777="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B777" s="3" t="n"/>
-      <c r="C777" s="3" t="n"/>
-      <c r="D777" s="4" t="n"/>
-      <c r="E777" s="4" t="n"/>
-      <c r="F777" s="5" t="n"/>
-      <c r="G777" s="6" t="n"/>
-      <c r="H777" s="4" t="n"/>
-      <c r="I777" s="7" t="n"/>
-      <c r="J777" s="4" t="n"/>
-    </row>
-    <row r="778" ht="22" customHeight="1">
-      <c r="A778" s="3">
-        <f>IF(C778="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B778" s="3" t="n"/>
-      <c r="C778" s="3" t="n"/>
-      <c r="D778" s="4" t="n"/>
-      <c r="E778" s="4" t="n"/>
-      <c r="F778" s="5" t="n"/>
-      <c r="G778" s="6" t="n"/>
-      <c r="H778" s="4" t="n"/>
-      <c r="I778" s="7" t="n"/>
-      <c r="J778" s="4" t="n"/>
-    </row>
-    <row r="779" ht="22" customHeight="1">
-      <c r="A779" s="3">
-        <f>IF(C779="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B779" s="3" t="n"/>
-      <c r="C779" s="3" t="n"/>
-      <c r="D779" s="4" t="n"/>
-      <c r="E779" s="4" t="n"/>
-      <c r="F779" s="5" t="n"/>
-      <c r="G779" s="6" t="n"/>
-      <c r="H779" s="4" t="n"/>
-      <c r="I779" s="7" t="n"/>
-      <c r="J779" s="4" t="n"/>
-    </row>
-    <row r="780" ht="22" customHeight="1">
-      <c r="A780" s="3">
-        <f>IF(C780="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B780" s="3" t="n"/>
-      <c r="C780" s="3" t="n"/>
-      <c r="D780" s="4" t="n"/>
-      <c r="E780" s="4" t="n"/>
-      <c r="F780" s="5" t="n"/>
-      <c r="G780" s="6" t="n"/>
-      <c r="H780" s="4" t="n"/>
-      <c r="I780" s="7" t="n"/>
-      <c r="J780" s="4" t="n"/>
-    </row>
-    <row r="781" ht="22" customHeight="1">
-      <c r="A781" s="3">
-        <f>IF(C781="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B781" s="3" t="n"/>
-      <c r="C781" s="3" t="n"/>
-      <c r="D781" s="4" t="n"/>
-      <c r="E781" s="4" t="n"/>
-      <c r="F781" s="5" t="n"/>
-      <c r="G781" s="6" t="n"/>
-      <c r="H781" s="4" t="n"/>
-      <c r="I781" s="7" t="n"/>
-      <c r="J781" s="4" t="n"/>
-    </row>
-    <row r="782" ht="22" customHeight="1">
-      <c r="A782" s="3">
-        <f>IF(C782="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B782" s="3" t="n"/>
-      <c r="C782" s="3" t="n"/>
-      <c r="D782" s="4" t="n"/>
-      <c r="E782" s="4" t="n"/>
-      <c r="F782" s="5" t="n"/>
-      <c r="G782" s="6" t="n"/>
-      <c r="H782" s="4" t="n"/>
-      <c r="I782" s="7" t="n"/>
-      <c r="J782" s="4" t="n"/>
-    </row>
-    <row r="783" ht="22" customHeight="1">
-      <c r="A783" s="3">
-        <f>IF(C783="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B783" s="3" t="n"/>
-      <c r="C783" s="3" t="n"/>
-      <c r="D783" s="4" t="n"/>
-      <c r="E783" s="4" t="n"/>
-      <c r="F783" s="5" t="n"/>
-      <c r="G783" s="6" t="n"/>
-      <c r="H783" s="4" t="n"/>
-      <c r="I783" s="7" t="n"/>
-      <c r="J783" s="4" t="n"/>
-    </row>
-    <row r="784" ht="22" customHeight="1">
-      <c r="A784" s="3">
-        <f>IF(C784="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B784" s="3" t="n"/>
-      <c r="C784" s="3" t="n"/>
-      <c r="D784" s="4" t="n"/>
-      <c r="E784" s="4" t="n"/>
-      <c r="F784" s="5" t="n"/>
-      <c r="G784" s="6" t="n"/>
-      <c r="H784" s="4" t="n"/>
-      <c r="I784" s="7" t="n"/>
-      <c r="J784" s="4" t="n"/>
-    </row>
-    <row r="785" ht="22" customHeight="1">
-      <c r="A785" s="3">
-        <f>IF(C785="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B785" s="3" t="n"/>
-      <c r="C785" s="3" t="n"/>
-      <c r="D785" s="4" t="n"/>
-      <c r="E785" s="4" t="n"/>
-      <c r="F785" s="5" t="n"/>
-      <c r="G785" s="6" t="n"/>
-      <c r="H785" s="4" t="n"/>
-      <c r="I785" s="7" t="n"/>
-      <c r="J785" s="4" t="n"/>
-    </row>
-    <row r="786" ht="22" customHeight="1">
-      <c r="A786" s="3">
-        <f>IF(C786="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B786" s="3" t="n"/>
-      <c r="C786" s="3" t="n"/>
-      <c r="D786" s="4" t="n"/>
-      <c r="E786" s="4" t="n"/>
-      <c r="F786" s="5" t="n"/>
-      <c r="G786" s="6" t="n"/>
-      <c r="H786" s="4" t="n"/>
-      <c r="I786" s="7" t="n"/>
-      <c r="J786" s="4" t="n"/>
-    </row>
-    <row r="787" ht="22" customHeight="1">
-      <c r="A787" s="3">
-        <f>IF(C787="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B787" s="3" t="n"/>
-      <c r="C787" s="3" t="n"/>
-      <c r="D787" s="4" t="n"/>
-      <c r="E787" s="4" t="n"/>
-      <c r="F787" s="5" t="n"/>
-      <c r="G787" s="6" t="n"/>
-      <c r="H787" s="4" t="n"/>
-      <c r="I787" s="7" t="n"/>
-      <c r="J787" s="4" t="n"/>
-    </row>
-    <row r="788" ht="22" customHeight="1">
-      <c r="A788" s="3">
-        <f>IF(C788="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B788" s="3" t="n"/>
-      <c r="C788" s="3" t="n"/>
-      <c r="D788" s="4" t="n"/>
-      <c r="E788" s="4" t="n"/>
-      <c r="F788" s="5" t="n"/>
-      <c r="G788" s="6" t="n"/>
-      <c r="H788" s="4" t="n"/>
-      <c r="I788" s="7" t="n"/>
-      <c r="J788" s="4" t="n"/>
-    </row>
-    <row r="789" ht="22" customHeight="1">
-      <c r="A789" s="3">
-        <f>IF(C789="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B789" s="3" t="n"/>
-      <c r="C789" s="3" t="n"/>
-      <c r="D789" s="4" t="n"/>
-      <c r="E789" s="4" t="n"/>
-      <c r="F789" s="5" t="n"/>
-      <c r="G789" s="6" t="n"/>
-      <c r="H789" s="4" t="n"/>
-      <c r="I789" s="7" t="n"/>
-      <c r="J789" s="4" t="n"/>
-    </row>
-    <row r="790" ht="22" customHeight="1">
-      <c r="A790" s="3">
-        <f>IF(C790="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B790" s="3" t="n"/>
-      <c r="C790" s="3" t="n"/>
-      <c r="D790" s="4" t="n"/>
-      <c r="E790" s="4" t="n"/>
-      <c r="F790" s="5" t="n"/>
-      <c r="G790" s="6" t="n"/>
-      <c r="H790" s="4" t="n"/>
-      <c r="I790" s="7" t="n"/>
-      <c r="J790" s="4" t="n"/>
-    </row>
-    <row r="791" ht="22" customHeight="1">
-      <c r="A791" s="3">
-        <f>IF(C791="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B791" s="3" t="n"/>
-      <c r="C791" s="3" t="n"/>
-      <c r="D791" s="4" t="n"/>
-      <c r="E791" s="4" t="n"/>
-      <c r="F791" s="5" t="n"/>
-      <c r="G791" s="6" t="n"/>
-      <c r="H791" s="4" t="n"/>
-      <c r="I791" s="7" t="n"/>
-      <c r="J791" s="4" t="n"/>
-    </row>
-    <row r="792" ht="22" customHeight="1">
-      <c r="A792" s="3">
-        <f>IF(C792="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B792" s="3" t="n"/>
-      <c r="C792" s="3" t="n"/>
-      <c r="D792" s="4" t="n"/>
-      <c r="E792" s="4" t="n"/>
-      <c r="F792" s="5" t="n"/>
-      <c r="G792" s="6" t="n"/>
-      <c r="H792" s="4" t="n"/>
-      <c r="I792" s="7" t="n"/>
-      <c r="J792" s="4" t="n"/>
-    </row>
-    <row r="793" ht="22" customHeight="1">
-      <c r="A793" s="3">
-        <f>IF(C793="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B793" s="3" t="n"/>
-      <c r="C793" s="3" t="n"/>
-      <c r="D793" s="4" t="n"/>
-      <c r="E793" s="4" t="n"/>
-      <c r="F793" s="5" t="n"/>
-      <c r="G793" s="6" t="n"/>
-      <c r="H793" s="4" t="n"/>
-      <c r="I793" s="7" t="n"/>
-      <c r="J793" s="4" t="n"/>
-    </row>
-    <row r="794" ht="22" customHeight="1">
-      <c r="A794" s="3">
-        <f>IF(C794="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B794" s="3" t="n"/>
-      <c r="C794" s="3" t="n"/>
-      <c r="D794" s="4" t="n"/>
-      <c r="E794" s="4" t="n"/>
-      <c r="F794" s="5" t="n"/>
-      <c r="G794" s="6" t="n"/>
-      <c r="H794" s="4" t="n"/>
-      <c r="I794" s="7" t="n"/>
-      <c r="J794" s="4" t="n"/>
-    </row>
-    <row r="795" ht="22" customHeight="1">
-      <c r="A795" s="3">
-        <f>IF(C795="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B795" s="3" t="n"/>
-      <c r="C795" s="3" t="n"/>
-      <c r="D795" s="4" t="n"/>
-      <c r="E795" s="4" t="n"/>
-      <c r="F795" s="5" t="n"/>
-      <c r="G795" s="6" t="n"/>
-      <c r="H795" s="4" t="n"/>
-      <c r="I795" s="7" t="n"/>
-      <c r="J795" s="4" t="n"/>
-    </row>
-    <row r="796" ht="22" customHeight="1">
-      <c r="A796" s="3">
-        <f>IF(C796="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B796" s="3" t="n"/>
-      <c r="C796" s="3" t="n"/>
-      <c r="D796" s="4" t="n"/>
-      <c r="E796" s="4" t="n"/>
-      <c r="F796" s="5" t="n"/>
-      <c r="G796" s="6" t="n"/>
-      <c r="H796" s="4" t="n"/>
-      <c r="I796" s="7" t="n"/>
-      <c r="J796" s="4" t="n"/>
-    </row>
-    <row r="797" ht="22" customHeight="1">
-      <c r="A797" s="3">
-        <f>IF(C797="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B797" s="3" t="n"/>
-      <c r="C797" s="3" t="n"/>
-      <c r="D797" s="4" t="n"/>
-      <c r="E797" s="4" t="n"/>
-      <c r="F797" s="5" t="n"/>
-      <c r="G797" s="6" t="n"/>
-      <c r="H797" s="4" t="n"/>
-      <c r="I797" s="7" t="n"/>
-      <c r="J797" s="4" t="n"/>
-    </row>
-    <row r="798" ht="22" customHeight="1">
-      <c r="A798" s="3">
-        <f>IF(C798="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B798" s="3" t="n"/>
-      <c r="C798" s="3" t="n"/>
-      <c r="D798" s="4" t="n"/>
-      <c r="E798" s="4" t="n"/>
-      <c r="F798" s="5" t="n"/>
-      <c r="G798" s="6" t="n"/>
-      <c r="H798" s="4" t="n"/>
-      <c r="I798" s="7" t="n"/>
-      <c r="J798" s="4" t="n"/>
-    </row>
-    <row r="799" ht="22" customHeight="1">
-      <c r="A799" s="3">
-        <f>IF(C799="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B799" s="3" t="n"/>
-      <c r="C799" s="3" t="n"/>
-      <c r="D799" s="4" t="n"/>
-      <c r="E799" s="4" t="n"/>
-      <c r="F799" s="5" t="n"/>
-      <c r="G799" s="6" t="n"/>
-      <c r="H799" s="4" t="n"/>
-      <c r="I799" s="7" t="n"/>
-      <c r="J799" s="4" t="n"/>
-    </row>
-    <row r="800" ht="22" customHeight="1">
-      <c r="A800" s="3">
-        <f>IF(C800="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B800" s="3" t="n"/>
-      <c r="C800" s="3" t="n"/>
-      <c r="D800" s="4" t="n"/>
-      <c r="E800" s="4" t="n"/>
-      <c r="F800" s="5" t="n"/>
-      <c r="G800" s="6" t="n"/>
-      <c r="H800" s="4" t="n"/>
-      <c r="I800" s="7" t="n"/>
-      <c r="J800" s="4" t="n"/>
-    </row>
-    <row r="801" ht="22" customHeight="1">
-      <c r="A801" s="3">
-        <f>IF(C801="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B801" s="3" t="n"/>
-      <c r="C801" s="3" t="n"/>
-      <c r="D801" s="4" t="n"/>
-      <c r="E801" s="4" t="n"/>
-      <c r="F801" s="5" t="n"/>
-      <c r="G801" s="6" t="n"/>
-      <c r="H801" s="4" t="n"/>
-      <c r="I801" s="7" t="n"/>
-      <c r="J801" s="4" t="n"/>
-    </row>
-    <row r="802" ht="22" customHeight="1">
-      <c r="A802" s="3">
-        <f>IF(C802="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B802" s="3" t="n"/>
-      <c r="C802" s="3" t="n"/>
-      <c r="D802" s="4" t="n"/>
-      <c r="E802" s="4" t="n"/>
-      <c r="F802" s="5" t="n"/>
-      <c r="G802" s="6" t="n"/>
-      <c r="H802" s="4" t="n"/>
-      <c r="I802" s="7" t="n"/>
-      <c r="J802" s="4" t="n"/>
-    </row>
-    <row r="803" ht="22" customHeight="1">
-      <c r="A803" s="3">
-        <f>IF(C803="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B803" s="3" t="n"/>
-      <c r="C803" s="3" t="n"/>
-      <c r="D803" s="4" t="n"/>
-      <c r="E803" s="4" t="n"/>
-      <c r="F803" s="5" t="n"/>
-      <c r="G803" s="6" t="n"/>
-      <c r="H803" s="4" t="n"/>
-      <c r="I803" s="7" t="n"/>
-      <c r="J803" s="4" t="n"/>
-    </row>
-    <row r="804" ht="22" customHeight="1">
-      <c r="A804" s="3">
-        <f>IF(C804="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B804" s="3" t="n"/>
-      <c r="C804" s="3" t="n"/>
-      <c r="D804" s="4" t="n"/>
-      <c r="E804" s="4" t="n"/>
-      <c r="F804" s="5" t="n"/>
-      <c r="G804" s="6" t="n"/>
-      <c r="H804" s="4" t="n"/>
-      <c r="I804" s="7" t="n"/>
-      <c r="J804" s="4" t="n"/>
-    </row>
-    <row r="805" ht="22" customHeight="1">
-      <c r="A805" s="3">
-        <f>IF(C805="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B805" s="3" t="n"/>
-      <c r="C805" s="3" t="n"/>
-      <c r="D805" s="4" t="n"/>
-      <c r="E805" s="4" t="n"/>
-      <c r="F805" s="5" t="n"/>
-      <c r="G805" s="6" t="n"/>
-      <c r="H805" s="4" t="n"/>
-      <c r="I805" s="7" t="n"/>
-      <c r="J805" s="4" t="n"/>
-    </row>
-    <row r="806" ht="22" customHeight="1">
-      <c r="A806" s="3">
-        <f>IF(C806="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B806" s="3" t="n"/>
-      <c r="C806" s="3" t="n"/>
-      <c r="D806" s="4" t="n"/>
-      <c r="E806" s="4" t="n"/>
-      <c r="F806" s="5" t="n"/>
-      <c r="G806" s="6" t="n"/>
-      <c r="H806" s="4" t="n"/>
-      <c r="I806" s="7" t="n"/>
-      <c r="J806" s="4" t="n"/>
-    </row>
-    <row r="807" ht="22" customHeight="1">
-      <c r="A807" s="3">
-        <f>IF(C807="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B807" s="3" t="n"/>
-      <c r="C807" s="3" t="n"/>
-      <c r="D807" s="4" t="n"/>
-      <c r="E807" s="4" t="n"/>
-      <c r="F807" s="5" t="n"/>
-      <c r="G807" s="6" t="n"/>
-      <c r="H807" s="4" t="n"/>
-      <c r="I807" s="7" t="n"/>
-      <c r="J807" s="4" t="n"/>
-    </row>
-    <row r="808" ht="22" customHeight="1">
-      <c r="A808" s="3">
-        <f>IF(C808="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B808" s="3" t="n"/>
-      <c r="C808" s="3" t="n"/>
-      <c r="D808" s="4" t="n"/>
-      <c r="E808" s="4" t="n"/>
-      <c r="F808" s="5" t="n"/>
-      <c r="G808" s="6" t="n"/>
-      <c r="H808" s="4" t="n"/>
-      <c r="I808" s="7" t="n"/>
-      <c r="J808" s="4" t="n"/>
-    </row>
-    <row r="809" ht="22" customHeight="1">
-      <c r="A809" s="3">
-        <f>IF(C809="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B809" s="3" t="n"/>
-      <c r="C809" s="3" t="n"/>
-      <c r="D809" s="4" t="n"/>
-      <c r="E809" s="4" t="n"/>
-      <c r="F809" s="5" t="n"/>
-      <c r="G809" s="6" t="n"/>
-      <c r="H809" s="4" t="n"/>
-      <c r="I809" s="7" t="n"/>
-      <c r="J809" s="4" t="n"/>
-    </row>
-    <row r="810" ht="22" customHeight="1">
-      <c r="A810" s="3">
-        <f>IF(C810="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B810" s="3" t="n"/>
-      <c r="C810" s="3" t="n"/>
-      <c r="D810" s="4" t="n"/>
-      <c r="E810" s="4" t="n"/>
-      <c r="F810" s="5" t="n"/>
-      <c r="G810" s="6" t="n"/>
-      <c r="H810" s="4" t="n"/>
-      <c r="I810" s="7" t="n"/>
-      <c r="J810" s="4" t="n"/>
-    </row>
-    <row r="811" ht="22" customHeight="1">
-      <c r="A811" s="3">
-        <f>IF(C811="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B811" s="3" t="n"/>
-      <c r="C811" s="3" t="n"/>
-      <c r="D811" s="4" t="n"/>
-      <c r="E811" s="4" t="n"/>
-      <c r="F811" s="5" t="n"/>
-      <c r="G811" s="6" t="n"/>
-      <c r="H811" s="4" t="n"/>
-      <c r="I811" s="7" t="n"/>
-      <c r="J811" s="4" t="n"/>
-    </row>
-    <row r="812" ht="22" customHeight="1">
-      <c r="A812" s="3">
-        <f>IF(C812="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B812" s="3" t="n"/>
-      <c r="C812" s="3" t="n"/>
-      <c r="D812" s="4" t="n"/>
-      <c r="E812" s="4" t="n"/>
-      <c r="F812" s="5" t="n"/>
-      <c r="G812" s="6" t="n"/>
-      <c r="H812" s="4" t="n"/>
-      <c r="I812" s="7" t="n"/>
-      <c r="J812" s="4" t="n"/>
-    </row>
-    <row r="813" ht="22" customHeight="1">
-      <c r="A813" s="3">
-        <f>IF(C813="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B813" s="3" t="n"/>
-      <c r="C813" s="3" t="n"/>
-      <c r="D813" s="4" t="n"/>
-      <c r="E813" s="4" t="n"/>
-      <c r="F813" s="5" t="n"/>
-      <c r="G813" s="6" t="n"/>
-      <c r="H813" s="4" t="n"/>
-      <c r="I813" s="7" t="n"/>
-      <c r="J813" s="4" t="n"/>
-    </row>
-    <row r="814" ht="22" customHeight="1">
-      <c r="A814" s="3">
-        <f>IF(C814="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B814" s="3" t="n"/>
-      <c r="C814" s="3" t="n"/>
-      <c r="D814" s="4" t="n"/>
-      <c r="E814" s="4" t="n"/>
-      <c r="F814" s="5" t="n"/>
-      <c r="G814" s="6" t="n"/>
-      <c r="H814" s="4" t="n"/>
-      <c r="I814" s="7" t="n"/>
-      <c r="J814" s="4" t="n"/>
-    </row>
-    <row r="815" ht="22" customHeight="1">
-      <c r="A815" s="3">
-        <f>IF(C815="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B815" s="3" t="n"/>
-      <c r="C815" s="3" t="n"/>
-      <c r="D815" s="4" t="n"/>
-      <c r="E815" s="4" t="n"/>
-      <c r="F815" s="5" t="n"/>
-      <c r="G815" s="6" t="n"/>
-      <c r="H815" s="4" t="n"/>
-      <c r="I815" s="7" t="n"/>
-      <c r="J815" s="4" t="n"/>
-    </row>
-    <row r="816" ht="22" customHeight="1">
-      <c r="A816" s="3">
-        <f>IF(C816="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B816" s="3" t="n"/>
-      <c r="C816" s="3" t="n"/>
-      <c r="D816" s="4" t="n"/>
-      <c r="E816" s="4" t="n"/>
-      <c r="F816" s="5" t="n"/>
-      <c r="G816" s="6" t="n"/>
-      <c r="H816" s="4" t="n"/>
-      <c r="I816" s="7" t="n"/>
-      <c r="J816" s="4" t="n"/>
-    </row>
-    <row r="817" ht="22" customHeight="1">
-      <c r="A817" s="3">
-        <f>IF(C817="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B817" s="3" t="n"/>
-      <c r="C817" s="3" t="n"/>
-      <c r="D817" s="4" t="n"/>
-      <c r="E817" s="4" t="n"/>
-      <c r="F817" s="5" t="n"/>
-      <c r="G817" s="6" t="n"/>
-      <c r="H817" s="4" t="n"/>
-      <c r="I817" s="7" t="n"/>
-      <c r="J817" s="4" t="n"/>
-    </row>
-    <row r="818" ht="22" customHeight="1">
-      <c r="A818" s="3">
-        <f>IF(C818="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B818" s="3" t="n"/>
-      <c r="C818" s="3" t="n"/>
-      <c r="D818" s="4" t="n"/>
-      <c r="E818" s="4" t="n"/>
-      <c r="F818" s="5" t="n"/>
-      <c r="G818" s="6" t="n"/>
-      <c r="H818" s="4" t="n"/>
-      <c r="I818" s="7" t="n"/>
-      <c r="J818" s="4" t="n"/>
-    </row>
-    <row r="819" ht="22" customHeight="1">
-      <c r="A819" s="3">
-        <f>IF(C819="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B819" s="3" t="n"/>
-      <c r="C819" s="3" t="n"/>
-      <c r="D819" s="4" t="n"/>
-      <c r="E819" s="4" t="n"/>
-      <c r="F819" s="5" t="n"/>
-      <c r="G819" s="6" t="n"/>
-      <c r="H819" s="4" t="n"/>
-      <c r="I819" s="7" t="n"/>
-      <c r="J819" s="4" t="n"/>
-    </row>
-    <row r="820" ht="22" customHeight="1">
-      <c r="A820" s="3">
-        <f>IF(C820="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B820" s="3" t="n"/>
-      <c r="C820" s="3" t="n"/>
-      <c r="D820" s="4" t="n"/>
-      <c r="E820" s="4" t="n"/>
-      <c r="F820" s="5" t="n"/>
-      <c r="G820" s="6" t="n"/>
-      <c r="H820" s="4" t="n"/>
-      <c r="I820" s="7" t="n"/>
-      <c r="J820" s="4" t="n"/>
-    </row>
-    <row r="821" ht="22" customHeight="1">
-      <c r="A821" s="3">
-        <f>IF(C821="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B821" s="3" t="n"/>
-      <c r="C821" s="3" t="n"/>
-      <c r="D821" s="4" t="n"/>
-      <c r="E821" s="4" t="n"/>
-      <c r="F821" s="5" t="n"/>
-      <c r="G821" s="6" t="n"/>
-      <c r="H821" s="4" t="n"/>
-      <c r="I821" s="7" t="n"/>
-      <c r="J821" s="4" t="n"/>
-    </row>
-    <row r="822" ht="22" customHeight="1">
-      <c r="A822" s="3">
-        <f>IF(C822="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B822" s="3" t="n"/>
-      <c r="C822" s="3" t="n"/>
-      <c r="D822" s="4" t="n"/>
-      <c r="E822" s="4" t="n"/>
-      <c r="F822" s="5" t="n"/>
-      <c r="G822" s="6" t="n"/>
-      <c r="H822" s="4" t="n"/>
-      <c r="I822" s="7" t="n"/>
-      <c r="J822" s="4" t="n"/>
-    </row>
-    <row r="823" ht="22" customHeight="1">
-      <c r="A823" s="3">
-        <f>IF(C823="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B823" s="3" t="n"/>
-      <c r="C823" s="3" t="n"/>
-      <c r="D823" s="4" t="n"/>
-      <c r="E823" s="4" t="n"/>
-      <c r="F823" s="5" t="n"/>
-      <c r="G823" s="6" t="n"/>
-      <c r="H823" s="4" t="n"/>
-      <c r="I823" s="7" t="n"/>
-      <c r="J823" s="4" t="n"/>
-    </row>
-    <row r="824" ht="22" customHeight="1">
-      <c r="A824" s="3">
-        <f>IF(C824="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B824" s="3" t="n"/>
-      <c r="C824" s="3" t="n"/>
-      <c r="D824" s="4" t="n"/>
-      <c r="E824" s="4" t="n"/>
-      <c r="F824" s="5" t="n"/>
-      <c r="G824" s="6" t="n"/>
-      <c r="H824" s="4" t="n"/>
-      <c r="I824" s="7" t="n"/>
-      <c r="J824" s="4" t="n"/>
-    </row>
-    <row r="825" ht="22" customHeight="1">
-      <c r="A825" s="3">
-        <f>IF(C825="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B825" s="3" t="n"/>
-      <c r="C825" s="3" t="n"/>
-      <c r="D825" s="4" t="n"/>
-      <c r="E825" s="4" t="n"/>
-      <c r="F825" s="5" t="n"/>
-      <c r="G825" s="6" t="n"/>
-      <c r="H825" s="4" t="n"/>
-      <c r="I825" s="7" t="n"/>
-      <c r="J825" s="4" t="n"/>
-    </row>
-    <row r="826" ht="22" customHeight="1">
-      <c r="A826" s="3">
-        <f>IF(C826="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B826" s="3" t="n"/>
-      <c r="C826" s="3" t="n"/>
-      <c r="D826" s="4" t="n"/>
-      <c r="E826" s="4" t="n"/>
-      <c r="F826" s="5" t="n"/>
-      <c r="G826" s="6" t="n"/>
-      <c r="H826" s="4" t="n"/>
-      <c r="I826" s="7" t="n"/>
-      <c r="J826" s="4" t="n"/>
-    </row>
-    <row r="827" ht="22" customHeight="1">
-      <c r="A827" s="3">
-        <f>IF(C827="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B827" s="3" t="n"/>
-      <c r="C827" s="3" t="n"/>
-      <c r="D827" s="4" t="n"/>
-      <c r="E827" s="4" t="n"/>
-      <c r="F827" s="5" t="n"/>
-      <c r="G827" s="6" t="n"/>
-      <c r="H827" s="4" t="n"/>
-      <c r="I827" s="7" t="n"/>
-      <c r="J827" s="4" t="n"/>
-    </row>
-    <row r="828" ht="22" customHeight="1">
-      <c r="A828" s="3">
-        <f>IF(C828="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B828" s="3" t="n"/>
-      <c r="C828" s="3" t="n"/>
-      <c r="D828" s="4" t="n"/>
-      <c r="E828" s="4" t="n"/>
-      <c r="F828" s="5" t="n"/>
-      <c r="G828" s="6" t="n"/>
-      <c r="H828" s="4" t="n"/>
-      <c r="I828" s="7" t="n"/>
-      <c r="J828" s="4" t="n"/>
-    </row>
-    <row r="829" ht="22" customHeight="1">
-      <c r="A829" s="3">
-        <f>IF(C829="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B829" s="3" t="n"/>
-      <c r="C829" s="3" t="n"/>
-      <c r="D829" s="4" t="n"/>
-      <c r="E829" s="4" t="n"/>
-      <c r="F829" s="5" t="n"/>
-      <c r="G829" s="6" t="n"/>
-      <c r="H829" s="4" t="n"/>
-      <c r="I829" s="7" t="n"/>
-      <c r="J829" s="4" t="n"/>
-    </row>
-    <row r="830" ht="22" customHeight="1">
-      <c r="A830" s="3">
-        <f>IF(C830="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B830" s="3" t="n"/>
-      <c r="C830" s="3" t="n"/>
-      <c r="D830" s="4" t="n"/>
-      <c r="E830" s="4" t="n"/>
-      <c r="F830" s="5" t="n"/>
-      <c r="G830" s="6" t="n"/>
-      <c r="H830" s="4" t="n"/>
-      <c r="I830" s="7" t="n"/>
-      <c r="J830" s="4" t="n"/>
-    </row>
-    <row r="831" ht="22" customHeight="1">
-      <c r="A831" s="3">
-        <f>IF(C831="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B831" s="3" t="n"/>
-      <c r="C831" s="3" t="n"/>
-      <c r="D831" s="4" t="n"/>
-      <c r="E831" s="4" t="n"/>
-      <c r="F831" s="5" t="n"/>
-      <c r="G831" s="6" t="n"/>
-      <c r="H831" s="4" t="n"/>
-      <c r="I831" s="7" t="n"/>
-      <c r="J831" s="4" t="n"/>
-    </row>
-    <row r="832" ht="22" customHeight="1">
-      <c r="A832" s="3">
-        <f>IF(C832="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B832" s="3" t="n"/>
-      <c r="C832" s="3" t="n"/>
-      <c r="D832" s="4" t="n"/>
-      <c r="E832" s="4" t="n"/>
-      <c r="F832" s="5" t="n"/>
-      <c r="G832" s="6" t="n"/>
-      <c r="H832" s="4" t="n"/>
-      <c r="I832" s="7" t="n"/>
-      <c r="J832" s="4" t="n"/>
-    </row>
-    <row r="833" ht="22" customHeight="1">
-      <c r="A833" s="3">
-        <f>IF(C833="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B833" s="3" t="n"/>
-      <c r="C833" s="3" t="n"/>
-      <c r="D833" s="4" t="n"/>
-      <c r="E833" s="4" t="n"/>
-      <c r="F833" s="5" t="n"/>
-      <c r="G833" s="6" t="n"/>
-      <c r="H833" s="4" t="n"/>
-      <c r="I833" s="7" t="n"/>
-      <c r="J833" s="4" t="n"/>
-    </row>
-    <row r="834" ht="22" customHeight="1">
-      <c r="A834" s="3">
-        <f>IF(C834="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B834" s="3" t="n"/>
-      <c r="C834" s="3" t="n"/>
-      <c r="D834" s="4" t="n"/>
-      <c r="E834" s="4" t="n"/>
-      <c r="F834" s="5" t="n"/>
-      <c r="G834" s="6" t="n"/>
-      <c r="H834" s="4" t="n"/>
-      <c r="I834" s="7" t="n"/>
-      <c r="J834" s="4" t="n"/>
-    </row>
-    <row r="835" ht="22" customHeight="1">
-      <c r="A835" s="3">
-        <f>IF(C835="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B835" s="3" t="n"/>
-      <c r="C835" s="3" t="n"/>
-      <c r="D835" s="4" t="n"/>
-      <c r="E835" s="4" t="n"/>
-      <c r="F835" s="5" t="n"/>
-      <c r="G835" s="6" t="n"/>
-      <c r="H835" s="4" t="n"/>
-      <c r="I835" s="7" t="n"/>
-      <c r="J835" s="4" t="n"/>
-    </row>
-    <row r="836" ht="22" customHeight="1">
-      <c r="A836" s="3">
-        <f>IF(C836="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B836" s="3" t="n"/>
-      <c r="C836" s="3" t="n"/>
-      <c r="D836" s="4" t="n"/>
-      <c r="E836" s="4" t="n"/>
-      <c r="F836" s="5" t="n"/>
-      <c r="G836" s="6" t="n"/>
-      <c r="H836" s="4" t="n"/>
-      <c r="I836" s="7" t="n"/>
-      <c r="J836" s="4" t="n"/>
-    </row>
-    <row r="837" ht="22" customHeight="1">
-      <c r="A837" s="3">
-        <f>IF(C837="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B837" s="3" t="n"/>
-      <c r="C837" s="3" t="n"/>
-      <c r="D837" s="4" t="n"/>
-      <c r="E837" s="4" t="n"/>
-      <c r="F837" s="5" t="n"/>
-      <c r="G837" s="6" t="n"/>
-      <c r="H837" s="4" t="n"/>
-      <c r="I837" s="7" t="n"/>
-      <c r="J837" s="4" t="n"/>
-    </row>
-    <row r="838" ht="22" customHeight="1">
-      <c r="A838" s="3">
-        <f>IF(C838="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B838" s="3" t="n"/>
-      <c r="C838" s="3" t="n"/>
-      <c r="D838" s="4" t="n"/>
-      <c r="E838" s="4" t="n"/>
-      <c r="F838" s="5" t="n"/>
-      <c r="G838" s="6" t="n"/>
-      <c r="H838" s="4" t="n"/>
-      <c r="I838" s="7" t="n"/>
-      <c r="J838" s="4" t="n"/>
-    </row>
-    <row r="839" ht="22" customHeight="1">
-      <c r="A839" s="3">
-        <f>IF(C839="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B839" s="3" t="n"/>
-      <c r="C839" s="3" t="n"/>
-      <c r="D839" s="4" t="n"/>
-      <c r="E839" s="4" t="n"/>
-      <c r="F839" s="5" t="n"/>
-      <c r="G839" s="6" t="n"/>
-      <c r="H839" s="4" t="n"/>
-      <c r="I839" s="7" t="n"/>
-      <c r="J839" s="4" t="n"/>
-    </row>
-    <row r="840" ht="22" customHeight="1">
-      <c r="A840" s="3">
-        <f>IF(C840="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B840" s="3" t="n"/>
-      <c r="C840" s="3" t="n"/>
-      <c r="D840" s="4" t="n"/>
-      <c r="E840" s="4" t="n"/>
-      <c r="F840" s="5" t="n"/>
-      <c r="G840" s="6" t="n"/>
-      <c r="H840" s="4" t="n"/>
-      <c r="I840" s="7" t="n"/>
-      <c r="J840" s="4" t="n"/>
-    </row>
-    <row r="841" ht="22" customHeight="1">
-      <c r="A841" s="3">
-        <f>IF(C841="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B841" s="3" t="n"/>
-      <c r="C841" s="3" t="n"/>
-      <c r="D841" s="4" t="n"/>
-      <c r="E841" s="4" t="n"/>
-      <c r="F841" s="5" t="n"/>
-      <c r="G841" s="6" t="n"/>
-      <c r="H841" s="4" t="n"/>
-      <c r="I841" s="7" t="n"/>
-      <c r="J841" s="4" t="n"/>
-    </row>
-    <row r="842" ht="22" customHeight="1">
-      <c r="A842" s="3">
-        <f>IF(C842="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B842" s="3" t="n"/>
-      <c r="C842" s="3" t="n"/>
-      <c r="D842" s="4" t="n"/>
-      <c r="E842" s="4" t="n"/>
-      <c r="F842" s="5" t="n"/>
-      <c r="G842" s="6" t="n"/>
-      <c r="H842" s="4" t="n"/>
-      <c r="I842" s="7" t="n"/>
-      <c r="J842" s="4" t="n"/>
-    </row>
-    <row r="843" ht="22" customHeight="1">
-      <c r="A843" s="3">
-        <f>IF(C843="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B843" s="3" t="n"/>
-      <c r="C843" s="3" t="n"/>
-      <c r="D843" s="4" t="n"/>
-      <c r="E843" s="4" t="n"/>
-      <c r="F843" s="5" t="n"/>
-      <c r="G843" s="6" t="n"/>
-      <c r="H843" s="4" t="n"/>
-      <c r="I843" s="7" t="n"/>
-      <c r="J843" s="4" t="n"/>
-    </row>
-    <row r="844" ht="22" customHeight="1">
-      <c r="A844" s="3">
-        <f>IF(C844="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B844" s="3" t="n"/>
-      <c r="C844" s="3" t="n"/>
-      <c r="D844" s="4" t="n"/>
-      <c r="E844" s="4" t="n"/>
-      <c r="F844" s="5" t="n"/>
-      <c r="G844" s="6" t="n"/>
-      <c r="H844" s="4" t="n"/>
-      <c r="I844" s="7" t="n"/>
-      <c r="J844" s="4" t="n"/>
-    </row>
-    <row r="845" ht="22" customHeight="1">
-      <c r="A845" s="3">
-        <f>IF(C845="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B845" s="3" t="n"/>
-      <c r="C845" s="3" t="n"/>
-      <c r="D845" s="4" t="n"/>
-      <c r="E845" s="4" t="n"/>
-      <c r="F845" s="5" t="n"/>
-      <c r="G845" s="6" t="n"/>
-      <c r="H845" s="4" t="n"/>
-      <c r="I845" s="7" t="n"/>
-      <c r="J845" s="4" t="n"/>
-    </row>
-    <row r="846" ht="22" customHeight="1">
-      <c r="A846" s="3">
-        <f>IF(C846="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B846" s="3" t="n"/>
-      <c r="C846" s="3" t="n"/>
-      <c r="D846" s="4" t="n"/>
-      <c r="E846" s="4" t="n"/>
-      <c r="F846" s="5" t="n"/>
-      <c r="G846" s="6" t="n"/>
-      <c r="H846" s="4" t="n"/>
-      <c r="I846" s="7" t="n"/>
-      <c r="J846" s="4" t="n"/>
-    </row>
-    <row r="847" ht="22" customHeight="1">
-      <c r="A847" s="3">
-        <f>IF(C847="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B847" s="3" t="n"/>
-      <c r="C847" s="3" t="n"/>
-      <c r="D847" s="4" t="n"/>
-      <c r="E847" s="4" t="n"/>
-      <c r="F847" s="5" t="n"/>
-      <c r="G847" s="6" t="n"/>
-      <c r="H847" s="4" t="n"/>
-      <c r="I847" s="7" t="n"/>
-      <c r="J847" s="4" t="n"/>
-    </row>
-    <row r="848" ht="22" customHeight="1">
-      <c r="A848" s="3">
-        <f>IF(C848="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B848" s="3" t="n"/>
-      <c r="C848" s="3" t="n"/>
-      <c r="D848" s="4" t="n"/>
-      <c r="E848" s="4" t="n"/>
-      <c r="F848" s="5" t="n"/>
-      <c r="G848" s="6" t="n"/>
-      <c r="H848" s="4" t="n"/>
-      <c r="I848" s="7" t="n"/>
-      <c r="J848" s="4" t="n"/>
-    </row>
-    <row r="849" ht="22" customHeight="1">
-      <c r="A849" s="3">
-        <f>IF(C849="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B849" s="3" t="n"/>
-      <c r="C849" s="3" t="n"/>
-      <c r="D849" s="4" t="n"/>
-      <c r="E849" s="4" t="n"/>
-      <c r="F849" s="5" t="n"/>
-      <c r="G849" s="6" t="n"/>
-      <c r="H849" s="4" t="n"/>
-      <c r="I849" s="7" t="n"/>
-      <c r="J849" s="4" t="n"/>
-    </row>
-    <row r="850" ht="22" customHeight="1">
-      <c r="A850" s="3">
-        <f>IF(C850="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B850" s="3" t="n"/>
-      <c r="C850" s="3" t="n"/>
-      <c r="D850" s="4" t="n"/>
-      <c r="E850" s="4" t="n"/>
-      <c r="F850" s="5" t="n"/>
-      <c r="G850" s="6" t="n"/>
-      <c r="H850" s="4" t="n"/>
-      <c r="I850" s="7" t="n"/>
-      <c r="J850" s="4" t="n"/>
-    </row>
-    <row r="851" ht="22" customHeight="1">
-      <c r="A851" s="3">
-        <f>IF(C851="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B851" s="3" t="n"/>
-      <c r="C851" s="3" t="n"/>
-      <c r="D851" s="4" t="n"/>
-      <c r="E851" s="4" t="n"/>
-      <c r="F851" s="5" t="n"/>
-      <c r="G851" s="6" t="n"/>
-      <c r="H851" s="4" t="n"/>
-      <c r="I851" s="7" t="n"/>
-      <c r="J851" s="4" t="n"/>
-    </row>
-    <row r="852" ht="22" customHeight="1">
-      <c r="A852" s="3">
-        <f>IF(C852="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B852" s="3" t="n"/>
-      <c r="C852" s="3" t="n"/>
-      <c r="D852" s="4" t="n"/>
-      <c r="E852" s="4" t="n"/>
-      <c r="F852" s="5" t="n"/>
-      <c r="G852" s="6" t="n"/>
-      <c r="H852" s="4" t="n"/>
-      <c r="I852" s="7" t="n"/>
-      <c r="J852" s="4" t="n"/>
-    </row>
-    <row r="853" ht="22" customHeight="1">
-      <c r="A853" s="3">
-        <f>IF(C853="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B853" s="3" t="n"/>
-      <c r="C853" s="3" t="n"/>
-      <c r="D853" s="4" t="n"/>
-      <c r="E853" s="4" t="n"/>
-      <c r="F853" s="5" t="n"/>
-      <c r="G853" s="6" t="n"/>
-      <c r="H853" s="4" t="n"/>
-      <c r="I853" s="7" t="n"/>
-      <c r="J853" s="4" t="n"/>
-    </row>
-    <row r="854" ht="22" customHeight="1">
-      <c r="A854" s="3">
-        <f>IF(C854="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B854" s="3" t="n"/>
-      <c r="C854" s="3" t="n"/>
-      <c r="D854" s="4" t="n"/>
-      <c r="E854" s="4" t="n"/>
-      <c r="F854" s="5" t="n"/>
-      <c r="G854" s="6" t="n"/>
-      <c r="H854" s="4" t="n"/>
-      <c r="I854" s="7" t="n"/>
-      <c r="J854" s="4" t="n"/>
-    </row>
-    <row r="855" ht="22" customHeight="1">
-      <c r="A855" s="3">
-        <f>IF(C855="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B855" s="3" t="n"/>
-      <c r="C855" s="3" t="n"/>
-      <c r="D855" s="4" t="n"/>
-      <c r="E855" s="4" t="n"/>
-      <c r="F855" s="5" t="n"/>
-      <c r="G855" s="6" t="n"/>
-      <c r="H855" s="4" t="n"/>
-      <c r="I855" s="7" t="n"/>
-      <c r="J855" s="4" t="n"/>
-    </row>
-    <row r="856" ht="22" customHeight="1">
-      <c r="A856" s="3">
-        <f>IF(C856="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B856" s="3" t="n"/>
-      <c r="C856" s="3" t="n"/>
-      <c r="D856" s="4" t="n"/>
-      <c r="E856" s="4" t="n"/>
-      <c r="F856" s="5" t="n"/>
-      <c r="G856" s="6" t="n"/>
-      <c r="H856" s="4" t="n"/>
-      <c r="I856" s="7" t="n"/>
-      <c r="J856" s="4" t="n"/>
-    </row>
-    <row r="857" ht="22" customHeight="1">
-      <c r="A857" s="3">
-        <f>IF(C857="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B857" s="3" t="n"/>
-      <c r="C857" s="3" t="n"/>
-      <c r="D857" s="4" t="n"/>
-      <c r="E857" s="4" t="n"/>
-      <c r="F857" s="5" t="n"/>
-      <c r="G857" s="6" t="n"/>
-      <c r="H857" s="4" t="n"/>
-      <c r="I857" s="7" t="n"/>
-      <c r="J857" s="4" t="n"/>
-    </row>
-    <row r="858" ht="22" customHeight="1">
-      <c r="A858" s="3">
-        <f>IF(C858="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B858" s="3" t="n"/>
-      <c r="C858" s="3" t="n"/>
-      <c r="D858" s="4" t="n"/>
-      <c r="E858" s="4" t="n"/>
-      <c r="F858" s="5" t="n"/>
-      <c r="G858" s="6" t="n"/>
-      <c r="H858" s="4" t="n"/>
-      <c r="I858" s="7" t="n"/>
-      <c r="J858" s="4" t="n"/>
-    </row>
-    <row r="859" ht="22" customHeight="1">
-      <c r="A859" s="3">
-        <f>IF(C859="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B859" s="3" t="n"/>
-      <c r="C859" s="3" t="n"/>
-      <c r="D859" s="4" t="n"/>
-      <c r="E859" s="4" t="n"/>
-      <c r="F859" s="5" t="n"/>
-      <c r="G859" s="6" t="n"/>
-      <c r="H859" s="4" t="n"/>
-      <c r="I859" s="7" t="n"/>
-      <c r="J859" s="4" t="n"/>
-    </row>
-    <row r="860" ht="22" customHeight="1">
-      <c r="A860" s="3">
-        <f>IF(C860="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B860" s="3" t="n"/>
-      <c r="C860" s="3" t="n"/>
-      <c r="D860" s="4" t="n"/>
-      <c r="E860" s="4" t="n"/>
-      <c r="F860" s="5" t="n"/>
-      <c r="G860" s="6" t="n"/>
-      <c r="H860" s="4" t="n"/>
-      <c r="I860" s="7" t="n"/>
-      <c r="J860" s="4" t="n"/>
-    </row>
-    <row r="861" ht="22" customHeight="1">
-      <c r="A861" s="3">
-        <f>IF(C861="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B861" s="3" t="n"/>
-      <c r="C861" s="3" t="n"/>
-      <c r="D861" s="4" t="n"/>
-      <c r="E861" s="4" t="n"/>
-      <c r="F861" s="5" t="n"/>
-      <c r="G861" s="6" t="n"/>
-      <c r="H861" s="4" t="n"/>
-      <c r="I861" s="7" t="n"/>
-      <c r="J861" s="4" t="n"/>
-    </row>
-    <row r="862" ht="22" customHeight="1">
-      <c r="A862" s="3">
-        <f>IF(C862="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B862" s="3" t="n"/>
-      <c r="C862" s="3" t="n"/>
-      <c r="D862" s="4" t="n"/>
-      <c r="E862" s="4" t="n"/>
-      <c r="F862" s="5" t="n"/>
-      <c r="G862" s="6" t="n"/>
-      <c r="H862" s="4" t="n"/>
-      <c r="I862" s="7" t="n"/>
-      <c r="J862" s="4" t="n"/>
-    </row>
-    <row r="863" ht="22" customHeight="1">
-      <c r="A863" s="3">
-        <f>IF(C863="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B863" s="3" t="n"/>
-      <c r="C863" s="3" t="n"/>
-      <c r="D863" s="4" t="n"/>
-      <c r="E863" s="4" t="n"/>
-      <c r="F863" s="5" t="n"/>
-      <c r="G863" s="6" t="n"/>
-      <c r="H863" s="4" t="n"/>
-      <c r="I863" s="7" t="n"/>
-      <c r="J863" s="4" t="n"/>
-    </row>
-    <row r="864" ht="22" customHeight="1">
-      <c r="A864" s="3">
-        <f>IF(C864="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B864" s="3" t="n"/>
-      <c r="C864" s="3" t="n"/>
-      <c r="D864" s="4" t="n"/>
-      <c r="E864" s="4" t="n"/>
-      <c r="F864" s="5" t="n"/>
-      <c r="G864" s="6" t="n"/>
-      <c r="H864" s="4" t="n"/>
-      <c r="I864" s="7" t="n"/>
-      <c r="J864" s="4" t="n"/>
-    </row>
-    <row r="865" ht="22" customHeight="1">
-      <c r="A865" s="3">
-        <f>IF(C865="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B865" s="3" t="n"/>
-      <c r="C865" s="3" t="n"/>
-      <c r="D865" s="4" t="n"/>
-      <c r="E865" s="4" t="n"/>
-      <c r="F865" s="5" t="n"/>
-      <c r="G865" s="6" t="n"/>
-      <c r="H865" s="4" t="n"/>
-      <c r="I865" s="7" t="n"/>
-      <c r="J865" s="4" t="n"/>
-    </row>
-    <row r="866" ht="22" customHeight="1">
-      <c r="A866" s="3">
-        <f>IF(C866="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B866" s="3" t="n"/>
-      <c r="C866" s="3" t="n"/>
-      <c r="D866" s="4" t="n"/>
-      <c r="E866" s="4" t="n"/>
-      <c r="F866" s="5" t="n"/>
-      <c r="G866" s="6" t="n"/>
-      <c r="H866" s="4" t="n"/>
-      <c r="I866" s="7" t="n"/>
-      <c r="J866" s="4" t="n"/>
-    </row>
-    <row r="867" ht="22" customHeight="1">
-      <c r="A867" s="3">
-        <f>IF(C867="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B867" s="3" t="n"/>
-      <c r="C867" s="3" t="n"/>
-      <c r="D867" s="4" t="n"/>
-      <c r="E867" s="4" t="n"/>
-      <c r="F867" s="5" t="n"/>
-      <c r="G867" s="6" t="n"/>
-      <c r="H867" s="4" t="n"/>
-      <c r="I867" s="7" t="n"/>
-      <c r="J867" s="4" t="n"/>
-    </row>
-    <row r="868" ht="22" customHeight="1">
-      <c r="A868" s="3">
-        <f>IF(C868="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B868" s="3" t="n"/>
-      <c r="C868" s="3" t="n"/>
-      <c r="D868" s="4" t="n"/>
-      <c r="E868" s="4" t="n"/>
-      <c r="F868" s="5" t="n"/>
-      <c r="G868" s="6" t="n"/>
-      <c r="H868" s="4" t="n"/>
-      <c r="I868" s="7" t="n"/>
-      <c r="J868" s="4" t="n"/>
-    </row>
-    <row r="869" ht="22" customHeight="1">
-      <c r="A869" s="3">
-        <f>IF(C869="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B869" s="3" t="n"/>
-      <c r="C869" s="3" t="n"/>
-      <c r="D869" s="4" t="n"/>
-      <c r="E869" s="4" t="n"/>
-      <c r="F869" s="5" t="n"/>
-      <c r="G869" s="6" t="n"/>
-      <c r="H869" s="4" t="n"/>
-      <c r="I869" s="7" t="n"/>
-      <c r="J869" s="4" t="n"/>
-    </row>
-    <row r="870" ht="22" customHeight="1">
-      <c r="A870" s="3">
-        <f>IF(C870="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B870" s="3" t="n"/>
-      <c r="C870" s="3" t="n"/>
-      <c r="D870" s="4" t="n"/>
-      <c r="E870" s="4" t="n"/>
-      <c r="F870" s="5" t="n"/>
-      <c r="G870" s="6" t="n"/>
-      <c r="H870" s="4" t="n"/>
-      <c r="I870" s="7" t="n"/>
-      <c r="J870" s="4" t="n"/>
-    </row>
-    <row r="871" ht="22" customHeight="1">
-      <c r="A871" s="3">
-        <f>IF(C871="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B871" s="3" t="n"/>
-      <c r="C871" s="3" t="n"/>
-      <c r="D871" s="4" t="n"/>
-      <c r="E871" s="4" t="n"/>
-      <c r="F871" s="5" t="n"/>
-      <c r="G871" s="6" t="n"/>
-      <c r="H871" s="4" t="n"/>
-      <c r="I871" s="7" t="n"/>
-      <c r="J871" s="4" t="n"/>
-    </row>
-    <row r="872" ht="22" customHeight="1">
-      <c r="A872" s="3">
-        <f>IF(C872="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B872" s="3" t="n"/>
-      <c r="C872" s="3" t="n"/>
-      <c r="D872" s="4" t="n"/>
-      <c r="E872" s="4" t="n"/>
-      <c r="F872" s="5" t="n"/>
-      <c r="G872" s="6" t="n"/>
-      <c r="H872" s="4" t="n"/>
-      <c r="I872" s="7" t="n"/>
-      <c r="J872" s="4" t="n"/>
-    </row>
-    <row r="873" ht="22" customHeight="1">
-      <c r="A873" s="3">
-        <f>IF(C873="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B873" s="3" t="n"/>
-      <c r="C873" s="3" t="n"/>
-      <c r="D873" s="4" t="n"/>
-      <c r="E873" s="4" t="n"/>
-      <c r="F873" s="5" t="n"/>
-      <c r="G873" s="6" t="n"/>
-      <c r="H873" s="4" t="n"/>
-      <c r="I873" s="7" t="n"/>
-      <c r="J873" s="4" t="n"/>
-    </row>
-    <row r="874" ht="22" customHeight="1">
-      <c r="A874" s="3">
-        <f>IF(C874="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B874" s="3" t="n"/>
-      <c r="C874" s="3" t="n"/>
-      <c r="D874" s="4" t="n"/>
-      <c r="E874" s="4" t="n"/>
-      <c r="F874" s="5" t="n"/>
-      <c r="G874" s="6" t="n"/>
-      <c r="H874" s="4" t="n"/>
-      <c r="I874" s="7" t="n"/>
-      <c r="J874" s="4" t="n"/>
-    </row>
-    <row r="875" ht="22" customHeight="1">
-      <c r="A875" s="3">
-        <f>IF(C875="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B875" s="3" t="n"/>
-      <c r="C875" s="3" t="n"/>
-      <c r="D875" s="4" t="n"/>
-      <c r="E875" s="4" t="n"/>
-      <c r="F875" s="5" t="n"/>
-      <c r="G875" s="6" t="n"/>
-      <c r="H875" s="4" t="n"/>
-      <c r="I875" s="7" t="n"/>
-      <c r="J875" s="4" t="n"/>
-    </row>
-    <row r="876" ht="22" customHeight="1">
-      <c r="A876" s="3">
-        <f>IF(C876="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B876" s="3" t="n"/>
-      <c r="C876" s="3" t="n"/>
-      <c r="D876" s="4" t="n"/>
-      <c r="E876" s="4" t="n"/>
-      <c r="F876" s="5" t="n"/>
-      <c r="G876" s="6" t="n"/>
-      <c r="H876" s="4" t="n"/>
-      <c r="I876" s="7" t="n"/>
-      <c r="J876" s="4" t="n"/>
-    </row>
-    <row r="877" ht="22" customHeight="1">
-      <c r="A877" s="3">
-        <f>IF(C877="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B877" s="3" t="n"/>
-      <c r="C877" s="3" t="n"/>
-      <c r="D877" s="4" t="n"/>
-      <c r="E877" s="4" t="n"/>
-      <c r="F877" s="5" t="n"/>
-      <c r="G877" s="6" t="n"/>
-      <c r="H877" s="4" t="n"/>
-      <c r="I877" s="7" t="n"/>
-      <c r="J877" s="4" t="n"/>
-    </row>
-    <row r="878" ht="22" customHeight="1">
-      <c r="A878" s="3">
-        <f>IF(C878="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B878" s="3" t="n"/>
-      <c r="C878" s="3" t="n"/>
-      <c r="D878" s="4" t="n"/>
-      <c r="E878" s="4" t="n"/>
-      <c r="F878" s="5" t="n"/>
-      <c r="G878" s="6" t="n"/>
-      <c r="H878" s="4" t="n"/>
-      <c r="I878" s="7" t="n"/>
-      <c r="J878" s="4" t="n"/>
-    </row>
-    <row r="879" ht="22" customHeight="1">
-      <c r="A879" s="3">
-        <f>IF(C879="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B879" s="3" t="n"/>
-      <c r="C879" s="3" t="n"/>
-      <c r="D879" s="4" t="n"/>
-      <c r="E879" s="4" t="n"/>
-      <c r="F879" s="5" t="n"/>
-      <c r="G879" s="6" t="n"/>
-      <c r="H879" s="4" t="n"/>
-      <c r="I879" s="7" t="n"/>
-      <c r="J879" s="4" t="n"/>
-    </row>
-    <row r="880" ht="22" customHeight="1">
-      <c r="A880" s="3">
-        <f>IF(C880="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B880" s="3" t="n"/>
-      <c r="C880" s="3" t="n"/>
-      <c r="D880" s="4" t="n"/>
-      <c r="E880" s="4" t="n"/>
-      <c r="F880" s="5" t="n"/>
-      <c r="G880" s="6" t="n"/>
-      <c r="H880" s="4" t="n"/>
-      <c r="I880" s="7" t="n"/>
-      <c r="J880" s="4" t="n"/>
-    </row>
-    <row r="881" ht="22" customHeight="1">
-      <c r="A881" s="3">
-        <f>IF(C881="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B881" s="3" t="n"/>
-      <c r="C881" s="3" t="n"/>
-      <c r="D881" s="4" t="n"/>
-      <c r="E881" s="4" t="n"/>
-      <c r="F881" s="5" t="n"/>
-      <c r="G881" s="6" t="n"/>
-      <c r="H881" s="4" t="n"/>
-      <c r="I881" s="7" t="n"/>
-      <c r="J881" s="4" t="n"/>
-    </row>
-    <row r="882" ht="22" customHeight="1">
-      <c r="A882" s="3">
-        <f>IF(C882="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B882" s="3" t="n"/>
-      <c r="C882" s="3" t="n"/>
-      <c r="D882" s="4" t="n"/>
-      <c r="E882" s="4" t="n"/>
-      <c r="F882" s="5" t="n"/>
-      <c r="G882" s="6" t="n"/>
-      <c r="H882" s="4" t="n"/>
-      <c r="I882" s="7" t="n"/>
-      <c r="J882" s="4" t="n"/>
-    </row>
-    <row r="883" ht="22" customHeight="1">
-      <c r="A883" s="3">
-        <f>IF(C883="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B883" s="3" t="n"/>
-      <c r="C883" s="3" t="n"/>
-      <c r="D883" s="4" t="n"/>
-      <c r="E883" s="4" t="n"/>
-      <c r="F883" s="5" t="n"/>
-      <c r="G883" s="6" t="n"/>
-      <c r="H883" s="4" t="n"/>
-      <c r="I883" s="7" t="n"/>
-      <c r="J883" s="4" t="n"/>
-    </row>
-    <row r="884" ht="22" customHeight="1">
-      <c r="A884" s="3">
-        <f>IF(C884="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B884" s="3" t="n"/>
-      <c r="C884" s="3" t="n"/>
-      <c r="D884" s="4" t="n"/>
-      <c r="E884" s="4" t="n"/>
-      <c r="F884" s="5" t="n"/>
-      <c r="G884" s="6" t="n"/>
-      <c r="H884" s="4" t="n"/>
-      <c r="I884" s="7" t="n"/>
-      <c r="J884" s="4" t="n"/>
-    </row>
-    <row r="885" ht="22" customHeight="1">
-      <c r="A885" s="3">
-        <f>IF(C885="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B885" s="3" t="n"/>
-      <c r="C885" s="3" t="n"/>
-      <c r="D885" s="4" t="n"/>
-      <c r="E885" s="4" t="n"/>
-      <c r="F885" s="5" t="n"/>
-      <c r="G885" s="6" t="n"/>
-      <c r="H885" s="4" t="n"/>
-      <c r="I885" s="7" t="n"/>
-      <c r="J885" s="4" t="n"/>
-    </row>
-    <row r="886" ht="22" customHeight="1">
-      <c r="A886" s="3">
-        <f>IF(C886="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B886" s="3" t="n"/>
-      <c r="C886" s="3" t="n"/>
-      <c r="D886" s="4" t="n"/>
-      <c r="E886" s="4" t="n"/>
-      <c r="F886" s="5" t="n"/>
-      <c r="G886" s="6" t="n"/>
-      <c r="H886" s="4" t="n"/>
-      <c r="I886" s="7" t="n"/>
-      <c r="J886" s="4" t="n"/>
-    </row>
-    <row r="887" ht="22" customHeight="1">
-      <c r="A887" s="3">
-        <f>IF(C887="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B887" s="3" t="n"/>
-      <c r="C887" s="3" t="n"/>
-      <c r="D887" s="4" t="n"/>
-      <c r="E887" s="4" t="n"/>
-      <c r="F887" s="5" t="n"/>
-      <c r="G887" s="6" t="n"/>
-      <c r="H887" s="4" t="n"/>
-      <c r="I887" s="7" t="n"/>
-      <c r="J887" s="4" t="n"/>
-    </row>
-    <row r="888" ht="22" customHeight="1">
-      <c r="A888" s="3">
-        <f>IF(C888="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B888" s="3" t="n"/>
-      <c r="C888" s="3" t="n"/>
-      <c r="D888" s="4" t="n"/>
-      <c r="E888" s="4" t="n"/>
-      <c r="F888" s="5" t="n"/>
-      <c r="G888" s="6" t="n"/>
-      <c r="H888" s="4" t="n"/>
-      <c r="I888" s="7" t="n"/>
-      <c r="J888" s="4" t="n"/>
-    </row>
-    <row r="889" ht="22" customHeight="1">
-      <c r="A889" s="3">
-        <f>IF(C889="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B889" s="3" t="n"/>
-      <c r="C889" s="3" t="n"/>
-      <c r="D889" s="4" t="n"/>
-      <c r="E889" s="4" t="n"/>
-      <c r="F889" s="5" t="n"/>
-      <c r="G889" s="6" t="n"/>
-      <c r="H889" s="4" t="n"/>
-      <c r="I889" s="7" t="n"/>
-      <c r="J889" s="4" t="n"/>
-    </row>
-    <row r="890" ht="22" customHeight="1">
-      <c r="A890" s="3">
-        <f>IF(C890="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B890" s="3" t="n"/>
-      <c r="C890" s="3" t="n"/>
-      <c r="D890" s="4" t="n"/>
-      <c r="E890" s="4" t="n"/>
-      <c r="F890" s="5" t="n"/>
-      <c r="G890" s="6" t="n"/>
-      <c r="H890" s="4" t="n"/>
-      <c r="I890" s="7" t="n"/>
-      <c r="J890" s="4" t="n"/>
-    </row>
-    <row r="891" ht="22" customHeight="1">
-      <c r="A891" s="3">
-        <f>IF(C891="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B891" s="3" t="n"/>
-      <c r="C891" s="3" t="n"/>
-      <c r="D891" s="4" t="n"/>
-      <c r="E891" s="4" t="n"/>
-      <c r="F891" s="5" t="n"/>
-      <c r="G891" s="6" t="n"/>
-      <c r="H891" s="4" t="n"/>
-      <c r="I891" s="7" t="n"/>
-      <c r="J891" s="4" t="n"/>
-    </row>
-    <row r="892" ht="22" customHeight="1">
-      <c r="A892" s="3">
-        <f>IF(C892="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B892" s="3" t="n"/>
-      <c r="C892" s="3" t="n"/>
-      <c r="D892" s="4" t="n"/>
-      <c r="E892" s="4" t="n"/>
-      <c r="F892" s="5" t="n"/>
-      <c r="G892" s="6" t="n"/>
-      <c r="H892" s="4" t="n"/>
-      <c r="I892" s="7" t="n"/>
-      <c r="J892" s="4" t="n"/>
-    </row>
-    <row r="893" ht="22" customHeight="1">
-      <c r="A893" s="3">
-        <f>IF(C893="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B893" s="3" t="n"/>
-      <c r="C893" s="3" t="n"/>
-      <c r="D893" s="4" t="n"/>
-      <c r="E893" s="4" t="n"/>
-      <c r="F893" s="5" t="n"/>
-      <c r="G893" s="6" t="n"/>
-      <c r="H893" s="4" t="n"/>
-      <c r="I893" s="7" t="n"/>
-      <c r="J893" s="4" t="n"/>
-    </row>
-    <row r="894" ht="22" customHeight="1">
-      <c r="A894" s="3">
-        <f>IF(C894="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B894" s="3" t="n"/>
-      <c r="C894" s="3" t="n"/>
-      <c r="D894" s="4" t="n"/>
-      <c r="E894" s="4" t="n"/>
-      <c r="F894" s="5" t="n"/>
-      <c r="G894" s="6" t="n"/>
-      <c r="H894" s="4" t="n"/>
-      <c r="I894" s="7" t="n"/>
-      <c r="J894" s="4" t="n"/>
-    </row>
-    <row r="895" ht="22" customHeight="1">
-      <c r="A895" s="3">
-        <f>IF(C895="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B895" s="3" t="n"/>
-      <c r="C895" s="3" t="n"/>
-      <c r="D895" s="4" t="n"/>
-      <c r="E895" s="4" t="n"/>
-      <c r="F895" s="5" t="n"/>
-      <c r="G895" s="6" t="n"/>
-      <c r="H895" s="4" t="n"/>
-      <c r="I895" s="7" t="n"/>
-      <c r="J895" s="4" t="n"/>
-    </row>
-    <row r="896" ht="22" customHeight="1">
-      <c r="A896" s="3">
-        <f>IF(C896="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B896" s="3" t="n"/>
-      <c r="C896" s="3" t="n"/>
-      <c r="D896" s="4" t="n"/>
-      <c r="E896" s="4" t="n"/>
-      <c r="F896" s="5" t="n"/>
-      <c r="G896" s="6" t="n"/>
-      <c r="H896" s="4" t="n"/>
-      <c r="I896" s="7" t="n"/>
-      <c r="J896" s="4" t="n"/>
-    </row>
-    <row r="897" ht="22" customHeight="1">
-      <c r="A897" s="3">
-        <f>IF(C897="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B897" s="3" t="n"/>
-      <c r="C897" s="3" t="n"/>
-      <c r="D897" s="4" t="n"/>
-      <c r="E897" s="4" t="n"/>
-      <c r="F897" s="5" t="n"/>
-      <c r="G897" s="6" t="n"/>
-      <c r="H897" s="4" t="n"/>
-      <c r="I897" s="7" t="n"/>
-      <c r="J897" s="4" t="n"/>
-    </row>
-    <row r="898" ht="22" customHeight="1">
-      <c r="A898" s="3">
-        <f>IF(C898="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B898" s="3" t="n"/>
-      <c r="C898" s="3" t="n"/>
-      <c r="D898" s="4" t="n"/>
-      <c r="E898" s="4" t="n"/>
-      <c r="F898" s="5" t="n"/>
-      <c r="G898" s="6" t="n"/>
-      <c r="H898" s="4" t="n"/>
-      <c r="I898" s="7" t="n"/>
-      <c r="J898" s="4" t="n"/>
-    </row>
-    <row r="899" ht="22" customHeight="1">
-      <c r="A899" s="3">
-        <f>IF(C899="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B899" s="3" t="n"/>
-      <c r="C899" s="3" t="n"/>
-      <c r="D899" s="4" t="n"/>
-      <c r="E899" s="4" t="n"/>
-      <c r="F899" s="5" t="n"/>
-      <c r="G899" s="6" t="n"/>
-      <c r="H899" s="4" t="n"/>
-      <c r="I899" s="7" t="n"/>
-      <c r="J899" s="4" t="n"/>
-    </row>
-    <row r="900" ht="22" customHeight="1">
-      <c r="A900" s="3">
-        <f>IF(C900="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B900" s="3" t="n"/>
-      <c r="C900" s="3" t="n"/>
-      <c r="D900" s="4" t="n"/>
-      <c r="E900" s="4" t="n"/>
-      <c r="F900" s="5" t="n"/>
-      <c r="G900" s="6" t="n"/>
-      <c r="H900" s="4" t="n"/>
-      <c r="I900" s="7" t="n"/>
-      <c r="J900" s="4" t="n"/>
-    </row>
-    <row r="901" ht="22" customHeight="1">
-      <c r="A901" s="3">
-        <f>IF(C901="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B901" s="3" t="n"/>
-      <c r="C901" s="3" t="n"/>
-      <c r="D901" s="4" t="n"/>
-      <c r="E901" s="4" t="n"/>
-      <c r="F901" s="5" t="n"/>
-      <c r="G901" s="6" t="n"/>
-      <c r="H901" s="4" t="n"/>
-      <c r="I901" s="7" t="n"/>
-      <c r="J901" s="4" t="n"/>
-    </row>
-    <row r="902" ht="22" customHeight="1">
-      <c r="A902" s="3">
-        <f>IF(C902="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B902" s="3" t="n"/>
-      <c r="C902" s="3" t="n"/>
-      <c r="D902" s="4" t="n"/>
-      <c r="E902" s="4" t="n"/>
-      <c r="F902" s="5" t="n"/>
-      <c r="G902" s="6" t="n"/>
-      <c r="H902" s="4" t="n"/>
-      <c r="I902" s="7" t="n"/>
-      <c r="J902" s="4" t="n"/>
-    </row>
-    <row r="903" ht="22" customHeight="1">
-      <c r="A903" s="3">
-        <f>IF(C903="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B903" s="3" t="n"/>
-      <c r="C903" s="3" t="n"/>
-      <c r="D903" s="4" t="n"/>
-      <c r="E903" s="4" t="n"/>
-      <c r="F903" s="5" t="n"/>
-      <c r="G903" s="6" t="n"/>
-      <c r="H903" s="4" t="n"/>
-      <c r="I903" s="7" t="n"/>
-      <c r="J903" s="4" t="n"/>
-    </row>
-    <row r="904" ht="22" customHeight="1">
-      <c r="A904" s="3">
-        <f>IF(C904="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B904" s="3" t="n"/>
-      <c r="C904" s="3" t="n"/>
-      <c r="D904" s="4" t="n"/>
-      <c r="E904" s="4" t="n"/>
-      <c r="F904" s="5" t="n"/>
-      <c r="G904" s="6" t="n"/>
-      <c r="H904" s="4" t="n"/>
-      <c r="I904" s="7" t="n"/>
-      <c r="J904" s="4" t="n"/>
-    </row>
-    <row r="905" ht="22" customHeight="1">
-      <c r="A905" s="3">
-        <f>IF(C905="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B905" s="3" t="n"/>
-      <c r="C905" s="3" t="n"/>
-      <c r="D905" s="4" t="n"/>
-      <c r="E905" s="4" t="n"/>
-      <c r="F905" s="5" t="n"/>
-      <c r="G905" s="6" t="n"/>
-      <c r="H905" s="4" t="n"/>
-      <c r="I905" s="7" t="n"/>
-      <c r="J905" s="4" t="n"/>
-    </row>
-    <row r="906" ht="22" customHeight="1">
-      <c r="A906" s="3">
-        <f>IF(C906="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B906" s="3" t="n"/>
-      <c r="C906" s="3" t="n"/>
-      <c r="D906" s="4" t="n"/>
-      <c r="E906" s="4" t="n"/>
-      <c r="F906" s="5" t="n"/>
-      <c r="G906" s="6" t="n"/>
-      <c r="H906" s="4" t="n"/>
-      <c r="I906" s="7" t="n"/>
-      <c r="J906" s="4" t="n"/>
-    </row>
-    <row r="907" ht="22" customHeight="1">
-      <c r="A907" s="3">
-        <f>IF(C907="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B907" s="3" t="n"/>
-      <c r="C907" s="3" t="n"/>
-      <c r="D907" s="4" t="n"/>
-      <c r="E907" s="4" t="n"/>
-      <c r="F907" s="5" t="n"/>
-      <c r="G907" s="6" t="n"/>
-      <c r="H907" s="4" t="n"/>
-      <c r="I907" s="7" t="n"/>
-      <c r="J907" s="4" t="n"/>
-    </row>
-    <row r="908" ht="22" customHeight="1">
-      <c r="A908" s="3">
-        <f>IF(C908="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B908" s="3" t="n"/>
-      <c r="C908" s="3" t="n"/>
-      <c r="D908" s="4" t="n"/>
-      <c r="E908" s="4" t="n"/>
-      <c r="F908" s="5" t="n"/>
-      <c r="G908" s="6" t="n"/>
-      <c r="H908" s="4" t="n"/>
-      <c r="I908" s="7" t="n"/>
-      <c r="J908" s="4" t="n"/>
-    </row>
-    <row r="909" ht="22" customHeight="1">
-      <c r="A909" s="3">
-        <f>IF(C909="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B909" s="3" t="n"/>
-      <c r="C909" s="3" t="n"/>
-      <c r="D909" s="4" t="n"/>
-      <c r="E909" s="4" t="n"/>
-      <c r="F909" s="5" t="n"/>
-      <c r="G909" s="6" t="n"/>
-      <c r="H909" s="4" t="n"/>
-      <c r="I909" s="7" t="n"/>
-      <c r="J909" s="4" t="n"/>
-    </row>
-    <row r="910" ht="22" customHeight="1">
-      <c r="A910" s="3">
-        <f>IF(C910="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B910" s="3" t="n"/>
-      <c r="C910" s="3" t="n"/>
-      <c r="D910" s="4" t="n"/>
-      <c r="E910" s="4" t="n"/>
-      <c r="F910" s="5" t="n"/>
-      <c r="G910" s="6" t="n"/>
-      <c r="H910" s="4" t="n"/>
-      <c r="I910" s="7" t="n"/>
-      <c r="J910" s="4" t="n"/>
-    </row>
-    <row r="911" ht="22" customHeight="1">
-      <c r="A911" s="3">
-        <f>IF(C911="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B911" s="3" t="n"/>
-      <c r="C911" s="3" t="n"/>
-      <c r="D911" s="4" t="n"/>
-      <c r="E911" s="4" t="n"/>
-      <c r="F911" s="5" t="n"/>
-      <c r="G911" s="6" t="n"/>
-      <c r="H911" s="4" t="n"/>
-      <c r="I911" s="7" t="n"/>
-      <c r="J911" s="4" t="n"/>
-    </row>
-    <row r="912" ht="22" customHeight="1">
-      <c r="A912" s="3">
-        <f>IF(C912="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B912" s="3" t="n"/>
-      <c r="C912" s="3" t="n"/>
-      <c r="D912" s="4" t="n"/>
-      <c r="E912" s="4" t="n"/>
-      <c r="F912" s="5" t="n"/>
-      <c r="G912" s="6" t="n"/>
-      <c r="H912" s="4" t="n"/>
-      <c r="I912" s="7" t="n"/>
-      <c r="J912" s="4" t="n"/>
-    </row>
-    <row r="913" ht="22" customHeight="1">
-      <c r="A913" s="3">
-        <f>IF(C913="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B913" s="3" t="n"/>
-      <c r="C913" s="3" t="n"/>
-      <c r="D913" s="4" t="n"/>
-      <c r="E913" s="4" t="n"/>
-      <c r="F913" s="5" t="n"/>
-      <c r="G913" s="6" t="n"/>
-      <c r="H913" s="4" t="n"/>
-      <c r="I913" s="7" t="n"/>
-      <c r="J913" s="4" t="n"/>
-    </row>
-    <row r="914" ht="22" customHeight="1">
-      <c r="A914" s="3">
-        <f>IF(C914="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B914" s="3" t="n"/>
-      <c r="C914" s="3" t="n"/>
-      <c r="D914" s="4" t="n"/>
-      <c r="E914" s="4" t="n"/>
-      <c r="F914" s="5" t="n"/>
-      <c r="G914" s="6" t="n"/>
-      <c r="H914" s="4" t="n"/>
-      <c r="I914" s="7" t="n"/>
-      <c r="J914" s="4" t="n"/>
-    </row>
-    <row r="915" ht="22" customHeight="1">
-      <c r="A915" s="3">
-        <f>IF(C915="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B915" s="3" t="n"/>
-      <c r="C915" s="3" t="n"/>
-      <c r="D915" s="4" t="n"/>
-      <c r="E915" s="4" t="n"/>
-      <c r="F915" s="5" t="n"/>
-      <c r="G915" s="6" t="n"/>
-      <c r="H915" s="4" t="n"/>
-      <c r="I915" s="7" t="n"/>
-      <c r="J915" s="4" t="n"/>
-    </row>
-    <row r="916" ht="22" customHeight="1">
-      <c r="A916" s="3">
-        <f>IF(C916="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B916" s="3" t="n"/>
-      <c r="C916" s="3" t="n"/>
-      <c r="D916" s="4" t="n"/>
-      <c r="E916" s="4" t="n"/>
-      <c r="F916" s="5" t="n"/>
-      <c r="G916" s="6" t="n"/>
-      <c r="H916" s="4" t="n"/>
-      <c r="I916" s="7" t="n"/>
-      <c r="J916" s="4" t="n"/>
-    </row>
-    <row r="917" ht="22" customHeight="1">
-      <c r="A917" s="3">
-        <f>IF(C917="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B917" s="3" t="n"/>
-      <c r="C917" s="3" t="n"/>
-      <c r="D917" s="4" t="n"/>
-      <c r="E917" s="4" t="n"/>
-      <c r="F917" s="5" t="n"/>
-      <c r="G917" s="6" t="n"/>
-      <c r="H917" s="4" t="n"/>
-      <c r="I917" s="7" t="n"/>
-      <c r="J917" s="4" t="n"/>
-    </row>
-    <row r="918" ht="22" customHeight="1">
-      <c r="A918" s="3">
-        <f>IF(C918="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B918" s="3" t="n"/>
-      <c r="C918" s="3" t="n"/>
-      <c r="D918" s="4" t="n"/>
-      <c r="E918" s="4" t="n"/>
-      <c r="F918" s="5" t="n"/>
-      <c r="G918" s="6" t="n"/>
-      <c r="H918" s="4" t="n"/>
-      <c r="I918" s="7" t="n"/>
-      <c r="J918" s="4" t="n"/>
-    </row>
-    <row r="919" ht="22" customHeight="1">
-      <c r="A919" s="3">
-        <f>IF(C919="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B919" s="3" t="n"/>
-      <c r="C919" s="3" t="n"/>
-      <c r="D919" s="4" t="n"/>
-      <c r="E919" s="4" t="n"/>
-      <c r="F919" s="5" t="n"/>
-      <c r="G919" s="6" t="n"/>
-      <c r="H919" s="4" t="n"/>
-      <c r="I919" s="7" t="n"/>
-      <c r="J919" s="4" t="n"/>
-    </row>
-    <row r="920" ht="22" customHeight="1">
-      <c r="A920" s="3">
-        <f>IF(C920="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B920" s="3" t="n"/>
-      <c r="C920" s="3" t="n"/>
-      <c r="D920" s="4" t="n"/>
-      <c r="E920" s="4" t="n"/>
-      <c r="F920" s="5" t="n"/>
-      <c r="G920" s="6" t="n"/>
-      <c r="H920" s="4" t="n"/>
-      <c r="I920" s="7" t="n"/>
-      <c r="J920" s="4" t="n"/>
-    </row>
-    <row r="921" ht="22" customHeight="1">
-      <c r="A921" s="3">
-        <f>IF(C921="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B921" s="3" t="n"/>
-      <c r="C921" s="3" t="n"/>
-      <c r="D921" s="4" t="n"/>
-      <c r="E921" s="4" t="n"/>
-      <c r="F921" s="5" t="n"/>
-      <c r="G921" s="6" t="n"/>
-      <c r="H921" s="4" t="n"/>
-      <c r="I921" s="7" t="n"/>
-      <c r="J921" s="4" t="n"/>
-    </row>
-    <row r="922" ht="22" customHeight="1">
-      <c r="A922" s="3">
-        <f>IF(C922="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B922" s="3" t="n"/>
-      <c r="C922" s="3" t="n"/>
-      <c r="D922" s="4" t="n"/>
-      <c r="E922" s="4" t="n"/>
-      <c r="F922" s="5" t="n"/>
-      <c r="G922" s="6" t="n"/>
-      <c r="H922" s="4" t="n"/>
-      <c r="I922" s="7" t="n"/>
-      <c r="J922" s="4" t="n"/>
-    </row>
-    <row r="923" ht="22" customHeight="1">
-      <c r="A923" s="3">
-        <f>IF(C923="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B923" s="3" t="n"/>
-      <c r="C923" s="3" t="n"/>
-      <c r="D923" s="4" t="n"/>
-      <c r="E923" s="4" t="n"/>
-      <c r="F923" s="5" t="n"/>
-      <c r="G923" s="6" t="n"/>
-      <c r="H923" s="4" t="n"/>
-      <c r="I923" s="7" t="n"/>
-      <c r="J923" s="4" t="n"/>
-    </row>
-    <row r="924" ht="22" customHeight="1">
-      <c r="A924" s="3">
-        <f>IF(C924="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B924" s="3" t="n"/>
-      <c r="C924" s="3" t="n"/>
-      <c r="D924" s="4" t="n"/>
-      <c r="E924" s="4" t="n"/>
-      <c r="F924" s="5" t="n"/>
-      <c r="G924" s="6" t="n"/>
-      <c r="H924" s="4" t="n"/>
-      <c r="I924" s="7" t="n"/>
-      <c r="J924" s="4" t="n"/>
-    </row>
-    <row r="925" ht="22" customHeight="1">
-      <c r="A925" s="3">
-        <f>IF(C925="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B925" s="3" t="n"/>
-      <c r="C925" s="3" t="n"/>
-      <c r="D925" s="4" t="n"/>
-      <c r="E925" s="4" t="n"/>
-      <c r="F925" s="5" t="n"/>
-      <c r="G925" s="6" t="n"/>
-      <c r="H925" s="4" t="n"/>
-      <c r="I925" s="7" t="n"/>
-      <c r="J925" s="4" t="n"/>
-    </row>
-    <row r="926" ht="22" customHeight="1">
-      <c r="A926" s="3">
-        <f>IF(C926="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B926" s="3" t="n"/>
-      <c r="C926" s="3" t="n"/>
-      <c r="D926" s="4" t="n"/>
-      <c r="E926" s="4" t="n"/>
-      <c r="F926" s="5" t="n"/>
-      <c r="G926" s="6" t="n"/>
-      <c r="H926" s="4" t="n"/>
-      <c r="I926" s="7" t="n"/>
-      <c r="J926" s="4" t="n"/>
-    </row>
-    <row r="927" ht="22" customHeight="1">
-      <c r="A927" s="3">
-        <f>IF(C927="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B927" s="3" t="n"/>
-      <c r="C927" s="3" t="n"/>
-      <c r="D927" s="4" t="n"/>
-      <c r="E927" s="4" t="n"/>
-      <c r="F927" s="5" t="n"/>
-      <c r="G927" s="6" t="n"/>
-      <c r="H927" s="4" t="n"/>
-      <c r="I927" s="7" t="n"/>
-      <c r="J927" s="4" t="n"/>
-    </row>
-    <row r="928" ht="22" customHeight="1">
-      <c r="A928" s="3">
-        <f>IF(C928="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B928" s="3" t="n"/>
-      <c r="C928" s="3" t="n"/>
-      <c r="D928" s="4" t="n"/>
-      <c r="E928" s="4" t="n"/>
-      <c r="F928" s="5" t="n"/>
-      <c r="G928" s="6" t="n"/>
-      <c r="H928" s="4" t="n"/>
-      <c r="I928" s="7" t="n"/>
-      <c r="J928" s="4" t="n"/>
-    </row>
-    <row r="929" ht="22" customHeight="1">
-      <c r="A929" s="3">
-        <f>IF(C929="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B929" s="3" t="n"/>
-      <c r="C929" s="3" t="n"/>
-      <c r="D929" s="4" t="n"/>
-      <c r="E929" s="4" t="n"/>
-      <c r="F929" s="5" t="n"/>
-      <c r="G929" s="6" t="n"/>
-      <c r="H929" s="4" t="n"/>
-      <c r="I929" s="7" t="n"/>
-      <c r="J929" s="4" t="n"/>
-    </row>
-    <row r="930" ht="22" customHeight="1">
-      <c r="A930" s="3">
-        <f>IF(C930="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B930" s="3" t="n"/>
-      <c r="C930" s="3" t="n"/>
-      <c r="D930" s="4" t="n"/>
-      <c r="E930" s="4" t="n"/>
-      <c r="F930" s="5" t="n"/>
-      <c r="G930" s="6" t="n"/>
-      <c r="H930" s="4" t="n"/>
-      <c r="I930" s="7" t="n"/>
-      <c r="J930" s="4" t="n"/>
-    </row>
-    <row r="931" ht="22" customHeight="1">
-      <c r="A931" s="3">
-        <f>IF(C931="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B931" s="3" t="n"/>
-      <c r="C931" s="3" t="n"/>
-      <c r="D931" s="4" t="n"/>
-      <c r="E931" s="4" t="n"/>
-      <c r="F931" s="5" t="n"/>
-      <c r="G931" s="6" t="n"/>
-      <c r="H931" s="4" t="n"/>
-      <c r="I931" s="7" t="n"/>
-      <c r="J931" s="4" t="n"/>
-    </row>
-    <row r="932" ht="22" customHeight="1">
-      <c r="A932" s="3">
-        <f>IF(C932="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B932" s="3" t="n"/>
-      <c r="C932" s="3" t="n"/>
-      <c r="D932" s="4" t="n"/>
-      <c r="E932" s="4" t="n"/>
-      <c r="F932" s="5" t="n"/>
-      <c r="G932" s="6" t="n"/>
-      <c r="H932" s="4" t="n"/>
-      <c r="I932" s="7" t="n"/>
-      <c r="J932" s="4" t="n"/>
-    </row>
-    <row r="933" ht="22" customHeight="1">
-      <c r="A933" s="3">
-        <f>IF(C933="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B933" s="3" t="n"/>
-      <c r="C933" s="3" t="n"/>
-      <c r="D933" s="4" t="n"/>
-      <c r="E933" s="4" t="n"/>
-      <c r="F933" s="5" t="n"/>
-      <c r="G933" s="6" t="n"/>
-      <c r="H933" s="4" t="n"/>
-      <c r="I933" s="7" t="n"/>
-      <c r="J933" s="4" t="n"/>
-    </row>
-    <row r="934" ht="22" customHeight="1">
-      <c r="A934" s="3">
-        <f>IF(C934="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B934" s="3" t="n"/>
-      <c r="C934" s="3" t="n"/>
-      <c r="D934" s="4" t="n"/>
-      <c r="E934" s="4" t="n"/>
-      <c r="F934" s="5" t="n"/>
-      <c r="G934" s="6" t="n"/>
-      <c r="H934" s="4" t="n"/>
-      <c r="I934" s="7" t="n"/>
-      <c r="J934" s="4" t="n"/>
-    </row>
-    <row r="935" ht="22" customHeight="1">
-      <c r="A935" s="3">
-        <f>IF(C935="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B935" s="3" t="n"/>
-      <c r="C935" s="3" t="n"/>
-      <c r="D935" s="4" t="n"/>
-      <c r="E935" s="4" t="n"/>
-      <c r="F935" s="5" t="n"/>
-      <c r="G935" s="6" t="n"/>
-      <c r="H935" s="4" t="n"/>
-      <c r="I935" s="7" t="n"/>
-      <c r="J935" s="4" t="n"/>
-    </row>
-    <row r="936" ht="22" customHeight="1">
-      <c r="A936" s="3">
-        <f>IF(C936="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B936" s="3" t="n"/>
-      <c r="C936" s="3" t="n"/>
-      <c r="D936" s="4" t="n"/>
-      <c r="E936" s="4" t="n"/>
-      <c r="F936" s="5" t="n"/>
-      <c r="G936" s="6" t="n"/>
-      <c r="H936" s="4" t="n"/>
-      <c r="I936" s="7" t="n"/>
-      <c r="J936" s="4" t="n"/>
-    </row>
-    <row r="937" ht="22" customHeight="1">
-      <c r="A937" s="3">
-        <f>IF(C937="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B937" s="3" t="n"/>
-      <c r="C937" s="3" t="n"/>
-      <c r="D937" s="4" t="n"/>
-      <c r="E937" s="4" t="n"/>
-      <c r="F937" s="5" t="n"/>
-      <c r="G937" s="6" t="n"/>
-      <c r="H937" s="4" t="n"/>
-      <c r="I937" s="7" t="n"/>
-      <c r="J937" s="4" t="n"/>
-    </row>
-    <row r="938" ht="22" customHeight="1">
-      <c r="A938" s="3">
-        <f>IF(C938="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B938" s="3" t="n"/>
-      <c r="C938" s="3" t="n"/>
-      <c r="D938" s="4" t="n"/>
-      <c r="E938" s="4" t="n"/>
-      <c r="F938" s="5" t="n"/>
-      <c r="G938" s="6" t="n"/>
-      <c r="H938" s="4" t="n"/>
-      <c r="I938" s="7" t="n"/>
-      <c r="J938" s="4" t="n"/>
-    </row>
-    <row r="939" ht="22" customHeight="1">
-      <c r="A939" s="3">
-        <f>IF(C939="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B939" s="3" t="n"/>
-      <c r="C939" s="3" t="n"/>
-      <c r="D939" s="4" t="n"/>
-      <c r="E939" s="4" t="n"/>
-      <c r="F939" s="5" t="n"/>
-      <c r="G939" s="6" t="n"/>
-      <c r="H939" s="4" t="n"/>
-      <c r="I939" s="7" t="n"/>
-      <c r="J939" s="4" t="n"/>
-    </row>
-    <row r="940" ht="22" customHeight="1">
-      <c r="A940" s="3">
-        <f>IF(C940="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B940" s="3" t="n"/>
-      <c r="C940" s="3" t="n"/>
-      <c r="D940" s="4" t="n"/>
-      <c r="E940" s="4" t="n"/>
-      <c r="F940" s="5" t="n"/>
-      <c r="G940" s="6" t="n"/>
-      <c r="H940" s="4" t="n"/>
-      <c r="I940" s="7" t="n"/>
-      <c r="J940" s="4" t="n"/>
-    </row>
-    <row r="941" ht="22" customHeight="1">
-      <c r="A941" s="3">
-        <f>IF(C941="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B941" s="3" t="n"/>
-      <c r="C941" s="3" t="n"/>
-      <c r="D941" s="4" t="n"/>
-      <c r="E941" s="4" t="n"/>
-      <c r="F941" s="5" t="n"/>
-      <c r="G941" s="6" t="n"/>
-      <c r="H941" s="4" t="n"/>
-      <c r="I941" s="7" t="n"/>
-      <c r="J941" s="4" t="n"/>
-    </row>
-    <row r="942" ht="22" customHeight="1">
-      <c r="A942" s="3">
-        <f>IF(C942="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B942" s="3" t="n"/>
-      <c r="C942" s="3" t="n"/>
-      <c r="D942" s="4" t="n"/>
-      <c r="E942" s="4" t="n"/>
-      <c r="F942" s="5" t="n"/>
-      <c r="G942" s="6" t="n"/>
-      <c r="H942" s="4" t="n"/>
-      <c r="I942" s="7" t="n"/>
-      <c r="J942" s="4" t="n"/>
-    </row>
-    <row r="943" ht="22" customHeight="1">
-      <c r="A943" s="3">
-        <f>IF(C943="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B943" s="3" t="n"/>
-      <c r="C943" s="3" t="n"/>
-      <c r="D943" s="4" t="n"/>
-      <c r="E943" s="4" t="n"/>
-      <c r="F943" s="5" t="n"/>
-      <c r="G943" s="6" t="n"/>
-      <c r="H943" s="4" t="n"/>
-      <c r="I943" s="7" t="n"/>
-      <c r="J943" s="4" t="n"/>
-    </row>
-    <row r="944" ht="22" customHeight="1">
-      <c r="A944" s="3">
-        <f>IF(C944="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B944" s="3" t="n"/>
-      <c r="C944" s="3" t="n"/>
-      <c r="D944" s="4" t="n"/>
-      <c r="E944" s="4" t="n"/>
-      <c r="F944" s="5" t="n"/>
-      <c r="G944" s="6" t="n"/>
-      <c r="H944" s="4" t="n"/>
-      <c r="I944" s="7" t="n"/>
-      <c r="J944" s="4" t="n"/>
-    </row>
-    <row r="945" ht="22" customHeight="1">
-      <c r="A945" s="3">
-        <f>IF(C945="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B945" s="3" t="n"/>
-      <c r="C945" s="3" t="n"/>
-      <c r="D945" s="4" t="n"/>
-      <c r="E945" s="4" t="n"/>
-      <c r="F945" s="5" t="n"/>
-      <c r="G945" s="6" t="n"/>
-      <c r="H945" s="4" t="n"/>
-      <c r="I945" s="7" t="n"/>
-      <c r="J945" s="4" t="n"/>
-    </row>
-    <row r="946" ht="22" customHeight="1">
-      <c r="A946" s="3">
-        <f>IF(C946="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B946" s="3" t="n"/>
-      <c r="C946" s="3" t="n"/>
-      <c r="D946" s="4" t="n"/>
-      <c r="E946" s="4" t="n"/>
-      <c r="F946" s="5" t="n"/>
-      <c r="G946" s="6" t="n"/>
-      <c r="H946" s="4" t="n"/>
-      <c r="I946" s="7" t="n"/>
-      <c r="J946" s="4" t="n"/>
-    </row>
-    <row r="947" ht="22" customHeight="1">
-      <c r="A947" s="3">
-        <f>IF(C947="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B947" s="3" t="n"/>
-      <c r="C947" s="3" t="n"/>
-      <c r="D947" s="4" t="n"/>
-      <c r="E947" s="4" t="n"/>
-      <c r="F947" s="5" t="n"/>
-      <c r="G947" s="6" t="n"/>
-      <c r="H947" s="4" t="n"/>
-      <c r="I947" s="7" t="n"/>
-      <c r="J947" s="4" t="n"/>
-    </row>
-    <row r="948" ht="22" customHeight="1">
-      <c r="A948" s="3">
-        <f>IF(C948="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B948" s="3" t="n"/>
-      <c r="C948" s="3" t="n"/>
-      <c r="D948" s="4" t="n"/>
-      <c r="E948" s="4" t="n"/>
-      <c r="F948" s="5" t="n"/>
-      <c r="G948" s="6" t="n"/>
-      <c r="H948" s="4" t="n"/>
-      <c r="I948" s="7" t="n"/>
-      <c r="J948" s="4" t="n"/>
-    </row>
-    <row r="949" ht="22" customHeight="1">
-      <c r="A949" s="3">
-        <f>IF(C949="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B949" s="3" t="n"/>
-      <c r="C949" s="3" t="n"/>
-      <c r="D949" s="4" t="n"/>
-      <c r="E949" s="4" t="n"/>
-      <c r="F949" s="5" t="n"/>
-      <c r="G949" s="6" t="n"/>
-      <c r="H949" s="4" t="n"/>
-      <c r="I949" s="7" t="n"/>
-      <c r="J949" s="4" t="n"/>
-    </row>
-    <row r="950" ht="22" customHeight="1">
-      <c r="A950" s="3">
-        <f>IF(C950="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B950" s="3" t="n"/>
-      <c r="C950" s="3" t="n"/>
-      <c r="D950" s="4" t="n"/>
-      <c r="E950" s="4" t="n"/>
-      <c r="F950" s="5" t="n"/>
-      <c r="G950" s="6" t="n"/>
-      <c r="H950" s="4" t="n"/>
-      <c r="I950" s="7" t="n"/>
-      <c r="J950" s="4" t="n"/>
-    </row>
-    <row r="951" ht="22" customHeight="1">
-      <c r="A951" s="3">
-        <f>IF(C951="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B951" s="3" t="n"/>
-      <c r="C951" s="3" t="n"/>
-      <c r="D951" s="4" t="n"/>
-      <c r="E951" s="4" t="n"/>
-      <c r="F951" s="5" t="n"/>
-      <c r="G951" s="6" t="n"/>
-      <c r="H951" s="4" t="n"/>
-      <c r="I951" s="7" t="n"/>
-      <c r="J951" s="4" t="n"/>
-    </row>
-    <row r="952" ht="22" customHeight="1">
-      <c r="A952" s="3">
-        <f>IF(C952="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B952" s="3" t="n"/>
-      <c r="C952" s="3" t="n"/>
-      <c r="D952" s="4" t="n"/>
-      <c r="E952" s="4" t="n"/>
-      <c r="F952" s="5" t="n"/>
-      <c r="G952" s="6" t="n"/>
-      <c r="H952" s="4" t="n"/>
-      <c r="I952" s="7" t="n"/>
-      <c r="J952" s="4" t="n"/>
-    </row>
-    <row r="953" ht="22" customHeight="1">
-      <c r="A953" s="3">
-        <f>IF(C953="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B953" s="3" t="n"/>
-      <c r="C953" s="3" t="n"/>
-      <c r="D953" s="4" t="n"/>
-      <c r="E953" s="4" t="n"/>
-      <c r="F953" s="5" t="n"/>
-      <c r="G953" s="6" t="n"/>
-      <c r="H953" s="4" t="n"/>
-      <c r="I953" s="7" t="n"/>
-      <c r="J953" s="4" t="n"/>
-    </row>
-    <row r="954" ht="22" customHeight="1">
-      <c r="A954" s="3">
-        <f>IF(C954="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B954" s="3" t="n"/>
-      <c r="C954" s="3" t="n"/>
-      <c r="D954" s="4" t="n"/>
-      <c r="E954" s="4" t="n"/>
-      <c r="F954" s="5" t="n"/>
-      <c r="G954" s="6" t="n"/>
-      <c r="H954" s="4" t="n"/>
-      <c r="I954" s="7" t="n"/>
-      <c r="J954" s="4" t="n"/>
-    </row>
-    <row r="955" ht="22" customHeight="1">
-      <c r="A955" s="3">
-        <f>IF(C955="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B955" s="3" t="n"/>
-      <c r="C955" s="3" t="n"/>
-      <c r="D955" s="4" t="n"/>
-      <c r="E955" s="4" t="n"/>
-      <c r="F955" s="5" t="n"/>
-      <c r="G955" s="6" t="n"/>
-      <c r="H955" s="4" t="n"/>
-      <c r="I955" s="7" t="n"/>
-      <c r="J955" s="4" t="n"/>
-    </row>
-    <row r="956" ht="22" customHeight="1">
-      <c r="A956" s="3">
-        <f>IF(C956="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B956" s="3" t="n"/>
-      <c r="C956" s="3" t="n"/>
-      <c r="D956" s="4" t="n"/>
-      <c r="E956" s="4" t="n"/>
-      <c r="F956" s="5" t="n"/>
-      <c r="G956" s="6" t="n"/>
-      <c r="H956" s="4" t="n"/>
-      <c r="I956" s="7" t="n"/>
-      <c r="J956" s="4" t="n"/>
-    </row>
-    <row r="957" ht="22" customHeight="1">
-      <c r="A957" s="3">
-        <f>IF(C957="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B957" s="3" t="n"/>
-      <c r="C957" s="3" t="n"/>
-      <c r="D957" s="4" t="n"/>
-      <c r="E957" s="4" t="n"/>
-      <c r="F957" s="5" t="n"/>
-      <c r="G957" s="6" t="n"/>
-      <c r="H957" s="4" t="n"/>
-      <c r="I957" s="7" t="n"/>
-      <c r="J957" s="4" t="n"/>
-    </row>
-    <row r="958" ht="22" customHeight="1">
-      <c r="A958" s="3">
-        <f>IF(C958="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B958" s="3" t="n"/>
-      <c r="C958" s="3" t="n"/>
-      <c r="D958" s="4" t="n"/>
-      <c r="E958" s="4" t="n"/>
-      <c r="F958" s="5" t="n"/>
-      <c r="G958" s="6" t="n"/>
-      <c r="H958" s="4" t="n"/>
-      <c r="I958" s="7" t="n"/>
-      <c r="J958" s="4" t="n"/>
-    </row>
-    <row r="959" ht="22" customHeight="1">
-      <c r="A959" s="3">
-        <f>IF(C959="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B959" s="3" t="n"/>
-      <c r="C959" s="3" t="n"/>
-      <c r="D959" s="4" t="n"/>
-      <c r="E959" s="4" t="n"/>
-      <c r="F959" s="5" t="n"/>
-      <c r="G959" s="6" t="n"/>
-      <c r="H959" s="4" t="n"/>
-      <c r="I959" s="7" t="n"/>
-      <c r="J959" s="4" t="n"/>
-    </row>
-    <row r="960" ht="22" customHeight="1">
-      <c r="A960" s="3">
-        <f>IF(C960="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B960" s="3" t="n"/>
-      <c r="C960" s="3" t="n"/>
-      <c r="D960" s="4" t="n"/>
-      <c r="E960" s="4" t="n"/>
-      <c r="F960" s="5" t="n"/>
-      <c r="G960" s="6" t="n"/>
-      <c r="H960" s="4" t="n"/>
-      <c r="I960" s="7" t="n"/>
-      <c r="J960" s="4" t="n"/>
-    </row>
-    <row r="961" ht="22" customHeight="1">
-      <c r="A961" s="3">
-        <f>IF(C961="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B961" s="3" t="n"/>
-      <c r="C961" s="3" t="n"/>
-      <c r="D961" s="4" t="n"/>
-      <c r="E961" s="4" t="n"/>
-      <c r="F961" s="5" t="n"/>
-      <c r="G961" s="6" t="n"/>
-      <c r="H961" s="4" t="n"/>
-      <c r="I961" s="7" t="n"/>
-      <c r="J961" s="4" t="n"/>
-    </row>
-    <row r="962" ht="22" customHeight="1">
-      <c r="A962" s="3">
-        <f>IF(C962="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B962" s="3" t="n"/>
-      <c r="C962" s="3" t="n"/>
-      <c r="D962" s="4" t="n"/>
-      <c r="E962" s="4" t="n"/>
-      <c r="F962" s="5" t="n"/>
-      <c r="G962" s="6" t="n"/>
-      <c r="H962" s="4" t="n"/>
-      <c r="I962" s="7" t="n"/>
-      <c r="J962" s="4" t="n"/>
-    </row>
-    <row r="963" ht="22" customHeight="1">
-      <c r="A963" s="3">
-        <f>IF(C963="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B963" s="3" t="n"/>
-      <c r="C963" s="3" t="n"/>
-      <c r="D963" s="4" t="n"/>
-      <c r="E963" s="4" t="n"/>
-      <c r="F963" s="5" t="n"/>
-      <c r="G963" s="6" t="n"/>
-      <c r="H963" s="4" t="n"/>
-      <c r="I963" s="7" t="n"/>
-      <c r="J963" s="4" t="n"/>
-    </row>
-    <row r="964" ht="22" customHeight="1">
-      <c r="A964" s="3">
-        <f>IF(C964="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B964" s="3" t="n"/>
-      <c r="C964" s="3" t="n"/>
-      <c r="D964" s="4" t="n"/>
-      <c r="E964" s="4" t="n"/>
-      <c r="F964" s="5" t="n"/>
-      <c r="G964" s="6" t="n"/>
-      <c r="H964" s="4" t="n"/>
-      <c r="I964" s="7" t="n"/>
-      <c r="J964" s="4" t="n"/>
-    </row>
-    <row r="965" ht="22" customHeight="1">
-      <c r="A965" s="3">
-        <f>IF(C965="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B965" s="3" t="n"/>
-      <c r="C965" s="3" t="n"/>
-      <c r="D965" s="4" t="n"/>
-      <c r="E965" s="4" t="n"/>
-      <c r="F965" s="5" t="n"/>
-      <c r="G965" s="6" t="n"/>
-      <c r="H965" s="4" t="n"/>
-      <c r="I965" s="7" t="n"/>
-      <c r="J965" s="4" t="n"/>
-    </row>
-    <row r="966" ht="22" customHeight="1">
-      <c r="A966" s="3">
-        <f>IF(C966="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B966" s="3" t="n"/>
-      <c r="C966" s="3" t="n"/>
-      <c r="D966" s="4" t="n"/>
-      <c r="E966" s="4" t="n"/>
-      <c r="F966" s="5" t="n"/>
-      <c r="G966" s="6" t="n"/>
-      <c r="H966" s="4" t="n"/>
-      <c r="I966" s="7" t="n"/>
-      <c r="J966" s="4" t="n"/>
-    </row>
-    <row r="967" ht="22" customHeight="1">
-      <c r="A967" s="3">
-        <f>IF(C967="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B967" s="3" t="n"/>
-      <c r="C967" s="3" t="n"/>
-      <c r="D967" s="4" t="n"/>
-      <c r="E967" s="4" t="n"/>
-      <c r="F967" s="5" t="n"/>
-      <c r="G967" s="6" t="n"/>
-      <c r="H967" s="4" t="n"/>
-      <c r="I967" s="7" t="n"/>
-      <c r="J967" s="4" t="n"/>
-    </row>
-    <row r="968" ht="22" customHeight="1">
-      <c r="A968" s="3">
-        <f>IF(C968="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B968" s="3" t="n"/>
-      <c r="C968" s="3" t="n"/>
-      <c r="D968" s="4" t="n"/>
-      <c r="E968" s="4" t="n"/>
-      <c r="F968" s="5" t="n"/>
-      <c r="G968" s="6" t="n"/>
-      <c r="H968" s="4" t="n"/>
-      <c r="I968" s="7" t="n"/>
-      <c r="J968" s="4" t="n"/>
-    </row>
-    <row r="969" ht="22" customHeight="1">
-      <c r="A969" s="3">
-        <f>IF(C969="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B969" s="3" t="n"/>
-      <c r="C969" s="3" t="n"/>
-      <c r="D969" s="4" t="n"/>
-      <c r="E969" s="4" t="n"/>
-      <c r="F969" s="5" t="n"/>
-      <c r="G969" s="6" t="n"/>
-      <c r="H969" s="4" t="n"/>
-      <c r="I969" s="7" t="n"/>
-      <c r="J969" s="4" t="n"/>
-    </row>
-    <row r="970" ht="22" customHeight="1">
-      <c r="A970" s="3">
-        <f>IF(C970="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B970" s="3" t="n"/>
-      <c r="C970" s="3" t="n"/>
-      <c r="D970" s="4" t="n"/>
-      <c r="E970" s="4" t="n"/>
-      <c r="F970" s="5" t="n"/>
-      <c r="G970" s="6" t="n"/>
-      <c r="H970" s="4" t="n"/>
-      <c r="I970" s="7" t="n"/>
-      <c r="J970" s="4" t="n"/>
-    </row>
-    <row r="971" ht="22" customHeight="1">
-      <c r="A971" s="3">
-        <f>IF(C971="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B971" s="3" t="n"/>
-      <c r="C971" s="3" t="n"/>
-      <c r="D971" s="4" t="n"/>
-      <c r="E971" s="4" t="n"/>
-      <c r="F971" s="5" t="n"/>
-      <c r="G971" s="6" t="n"/>
-      <c r="H971" s="4" t="n"/>
-      <c r="I971" s="7" t="n"/>
-      <c r="J971" s="4" t="n"/>
-    </row>
-    <row r="972" ht="22" customHeight="1">
-      <c r="A972" s="3">
-        <f>IF(C972="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B972" s="3" t="n"/>
-      <c r="C972" s="3" t="n"/>
-      <c r="D972" s="4" t="n"/>
-      <c r="E972" s="4" t="n"/>
-      <c r="F972" s="5" t="n"/>
-      <c r="G972" s="6" t="n"/>
-      <c r="H972" s="4" t="n"/>
-      <c r="I972" s="7" t="n"/>
-      <c r="J972" s="4" t="n"/>
-    </row>
-    <row r="973" ht="22" customHeight="1">
-      <c r="A973" s="3">
-        <f>IF(C973="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B973" s="3" t="n"/>
-      <c r="C973" s="3" t="n"/>
-      <c r="D973" s="4" t="n"/>
-      <c r="E973" s="4" t="n"/>
-      <c r="F973" s="5" t="n"/>
-      <c r="G973" s="6" t="n"/>
-      <c r="H973" s="4" t="n"/>
-      <c r="I973" s="7" t="n"/>
-      <c r="J973" s="4" t="n"/>
-    </row>
-    <row r="974" ht="22" customHeight="1">
-      <c r="A974" s="3">
-        <f>IF(C974="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B974" s="3" t="n"/>
-      <c r="C974" s="3" t="n"/>
-      <c r="D974" s="4" t="n"/>
-      <c r="E974" s="4" t="n"/>
-      <c r="F974" s="5" t="n"/>
-      <c r="G974" s="6" t="n"/>
-      <c r="H974" s="4" t="n"/>
-      <c r="I974" s="7" t="n"/>
-      <c r="J974" s="4" t="n"/>
-    </row>
-    <row r="975" ht="22" customHeight="1">
-      <c r="A975" s="3">
-        <f>IF(C975="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B975" s="3" t="n"/>
-      <c r="C975" s="3" t="n"/>
-      <c r="D975" s="4" t="n"/>
-      <c r="E975" s="4" t="n"/>
-      <c r="F975" s="5" t="n"/>
-      <c r="G975" s="6" t="n"/>
-      <c r="H975" s="4" t="n"/>
-      <c r="I975" s="7" t="n"/>
-      <c r="J975" s="4" t="n"/>
-    </row>
-    <row r="976" ht="22" customHeight="1">
-      <c r="A976" s="3">
-        <f>IF(C976="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B976" s="3" t="n"/>
-      <c r="C976" s="3" t="n"/>
-      <c r="D976" s="4" t="n"/>
-      <c r="E976" s="4" t="n"/>
-      <c r="F976" s="5" t="n"/>
-      <c r="G976" s="6" t="n"/>
-      <c r="H976" s="4" t="n"/>
-      <c r="I976" s="7" t="n"/>
-      <c r="J976" s="4" t="n"/>
-    </row>
-    <row r="977" ht="22" customHeight="1">
-      <c r="A977" s="3">
-        <f>IF(C977="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B977" s="3" t="n"/>
-      <c r="C977" s="3" t="n"/>
-      <c r="D977" s="4" t="n"/>
-      <c r="E977" s="4" t="n"/>
-      <c r="F977" s="5" t="n"/>
-      <c r="G977" s="6" t="n"/>
-      <c r="H977" s="4" t="n"/>
-      <c r="I977" s="7" t="n"/>
-      <c r="J977" s="4" t="n"/>
-    </row>
-    <row r="978" ht="22" customHeight="1">
-      <c r="A978" s="3">
-        <f>IF(C978="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B978" s="3" t="n"/>
-      <c r="C978" s="3" t="n"/>
-      <c r="D978" s="4" t="n"/>
-      <c r="E978" s="4" t="n"/>
-      <c r="F978" s="5" t="n"/>
-      <c r="G978" s="6" t="n"/>
-      <c r="H978" s="4" t="n"/>
-      <c r="I978" s="7" t="n"/>
-      <c r="J978" s="4" t="n"/>
-    </row>
-    <row r="979" ht="22" customHeight="1">
-      <c r="A979" s="3">
-        <f>IF(C979="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B979" s="3" t="n"/>
-      <c r="C979" s="3" t="n"/>
-      <c r="D979" s="4" t="n"/>
-      <c r="E979" s="4" t="n"/>
-      <c r="F979" s="5" t="n"/>
-      <c r="G979" s="6" t="n"/>
-      <c r="H979" s="4" t="n"/>
-      <c r="I979" s="7" t="n"/>
-      <c r="J979" s="4" t="n"/>
-    </row>
-    <row r="980" ht="22" customHeight="1">
-      <c r="A980" s="3">
-        <f>IF(C980="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B980" s="3" t="n"/>
-      <c r="C980" s="3" t="n"/>
-      <c r="D980" s="4" t="n"/>
-      <c r="E980" s="4" t="n"/>
-      <c r="F980" s="5" t="n"/>
-      <c r="G980" s="6" t="n"/>
-      <c r="H980" s="4" t="n"/>
-      <c r="I980" s="7" t="n"/>
-      <c r="J980" s="4" t="n"/>
-    </row>
-    <row r="981" ht="22" customHeight="1">
-      <c r="A981" s="3">
-        <f>IF(C981="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B981" s="3" t="n"/>
-      <c r="C981" s="3" t="n"/>
-      <c r="D981" s="4" t="n"/>
-      <c r="E981" s="4" t="n"/>
-      <c r="F981" s="5" t="n"/>
-      <c r="G981" s="6" t="n"/>
-      <c r="H981" s="4" t="n"/>
-      <c r="I981" s="7" t="n"/>
-      <c r="J981" s="4" t="n"/>
-    </row>
-    <row r="982" ht="22" customHeight="1">
-      <c r="A982" s="3">
-        <f>IF(C982="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B982" s="3" t="n"/>
-      <c r="C982" s="3" t="n"/>
-      <c r="D982" s="4" t="n"/>
-      <c r="E982" s="4" t="n"/>
-      <c r="F982" s="5" t="n"/>
-      <c r="G982" s="6" t="n"/>
-      <c r="H982" s="4" t="n"/>
-      <c r="I982" s="7" t="n"/>
-      <c r="J982" s="4" t="n"/>
-    </row>
-    <row r="983" ht="22" customHeight="1">
-      <c r="A983" s="3">
-        <f>IF(C983="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B983" s="3" t="n"/>
-      <c r="C983" s="3" t="n"/>
-      <c r="D983" s="4" t="n"/>
-      <c r="E983" s="4" t="n"/>
-      <c r="F983" s="5" t="n"/>
-      <c r="G983" s="6" t="n"/>
-      <c r="H983" s="4" t="n"/>
-      <c r="I983" s="7" t="n"/>
-      <c r="J983" s="4" t="n"/>
-    </row>
-    <row r="984" ht="22" customHeight="1">
-      <c r="A984" s="3">
-        <f>IF(C984="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B984" s="3" t="n"/>
-      <c r="C984" s="3" t="n"/>
-      <c r="D984" s="4" t="n"/>
-      <c r="E984" s="4" t="n"/>
-      <c r="F984" s="5" t="n"/>
-      <c r="G984" s="6" t="n"/>
-      <c r="H984" s="4" t="n"/>
-      <c r="I984" s="7" t="n"/>
-      <c r="J984" s="4" t="n"/>
-    </row>
-    <row r="985" ht="22" customHeight="1">
-      <c r="A985" s="3">
-        <f>IF(C985="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B985" s="3" t="n"/>
-      <c r="C985" s="3" t="n"/>
-      <c r="D985" s="4" t="n"/>
-      <c r="E985" s="4" t="n"/>
-      <c r="F985" s="5" t="n"/>
-      <c r="G985" s="6" t="n"/>
-      <c r="H985" s="4" t="n"/>
-      <c r="I985" s="7" t="n"/>
-      <c r="J985" s="4" t="n"/>
-    </row>
-    <row r="986" ht="22" customHeight="1">
-      <c r="A986" s="3">
-        <f>IF(C986="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B986" s="3" t="n"/>
-      <c r="C986" s="3" t="n"/>
-      <c r="D986" s="4" t="n"/>
-      <c r="E986" s="4" t="n"/>
-      <c r="F986" s="5" t="n"/>
-      <c r="G986" s="6" t="n"/>
-      <c r="H986" s="4" t="n"/>
-      <c r="I986" s="7" t="n"/>
-      <c r="J986" s="4" t="n"/>
-    </row>
-    <row r="987" ht="22" customHeight="1">
-      <c r="A987" s="3">
-        <f>IF(C987="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B987" s="3" t="n"/>
-      <c r="C987" s="3" t="n"/>
-      <c r="D987" s="4" t="n"/>
-      <c r="E987" s="4" t="n"/>
-      <c r="F987" s="5" t="n"/>
-      <c r="G987" s="6" t="n"/>
-      <c r="H987" s="4" t="n"/>
-      <c r="I987" s="7" t="n"/>
-      <c r="J987" s="4" t="n"/>
-    </row>
-    <row r="988" ht="22" customHeight="1">
-      <c r="A988" s="3">
-        <f>IF(C988="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B988" s="3" t="n"/>
-      <c r="C988" s="3" t="n"/>
-      <c r="D988" s="4" t="n"/>
-      <c r="E988" s="4" t="n"/>
-      <c r="F988" s="5" t="n"/>
-      <c r="G988" s="6" t="n"/>
-      <c r="H988" s="4" t="n"/>
-      <c r="I988" s="7" t="n"/>
-      <c r="J988" s="4" t="n"/>
-    </row>
-    <row r="989" ht="22" customHeight="1">
-      <c r="A989" s="3">
-        <f>IF(C989="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B989" s="3" t="n"/>
-      <c r="C989" s="3" t="n"/>
-      <c r="D989" s="4" t="n"/>
-      <c r="E989" s="4" t="n"/>
-      <c r="F989" s="5" t="n"/>
-      <c r="G989" s="6" t="n"/>
-      <c r="H989" s="4" t="n"/>
-      <c r="I989" s="7" t="n"/>
-      <c r="J989" s="4" t="n"/>
-    </row>
-    <row r="990" ht="22" customHeight="1">
-      <c r="A990" s="3">
-        <f>IF(C990="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B990" s="3" t="n"/>
-      <c r="C990" s="3" t="n"/>
-      <c r="D990" s="4" t="n"/>
-      <c r="E990" s="4" t="n"/>
-      <c r="F990" s="5" t="n"/>
-      <c r="G990" s="6" t="n"/>
-      <c r="H990" s="4" t="n"/>
-      <c r="I990" s="7" t="n"/>
-      <c r="J990" s="4" t="n"/>
-    </row>
-    <row r="991" ht="22" customHeight="1">
-      <c r="A991" s="3">
-        <f>IF(C991="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B991" s="3" t="n"/>
-      <c r="C991" s="3" t="n"/>
-      <c r="D991" s="4" t="n"/>
-      <c r="E991" s="4" t="n"/>
-      <c r="F991" s="5" t="n"/>
-      <c r="G991" s="6" t="n"/>
-      <c r="H991" s="4" t="n"/>
-      <c r="I991" s="7" t="n"/>
-      <c r="J991" s="4" t="n"/>
-    </row>
-    <row r="992" ht="22" customHeight="1">
-      <c r="A992" s="3">
-        <f>IF(C992="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B992" s="3" t="n"/>
-      <c r="C992" s="3" t="n"/>
-      <c r="D992" s="4" t="n"/>
-      <c r="E992" s="4" t="n"/>
-      <c r="F992" s="5" t="n"/>
-      <c r="G992" s="6" t="n"/>
-      <c r="H992" s="4" t="n"/>
-      <c r="I992" s="7" t="n"/>
-      <c r="J992" s="4" t="n"/>
-    </row>
-    <row r="993" ht="22" customHeight="1">
-      <c r="A993" s="3">
-        <f>IF(C993="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B993" s="3" t="n"/>
-      <c r="C993" s="3" t="n"/>
-      <c r="D993" s="4" t="n"/>
-      <c r="E993" s="4" t="n"/>
-      <c r="F993" s="5" t="n"/>
-      <c r="G993" s="6" t="n"/>
-      <c r="H993" s="4" t="n"/>
-      <c r="I993" s="7" t="n"/>
-      <c r="J993" s="4" t="n"/>
-    </row>
-    <row r="994" ht="22" customHeight="1">
-      <c r="A994" s="3">
-        <f>IF(C994="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B994" s="3" t="n"/>
-      <c r="C994" s="3" t="n"/>
-      <c r="D994" s="4" t="n"/>
-      <c r="E994" s="4" t="n"/>
-      <c r="F994" s="5" t="n"/>
-      <c r="G994" s="6" t="n"/>
-      <c r="H994" s="4" t="n"/>
-      <c r="I994" s="7" t="n"/>
-      <c r="J994" s="4" t="n"/>
-    </row>
-    <row r="995" ht="22" customHeight="1">
-      <c r="A995" s="3">
-        <f>IF(C995="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B995" s="3" t="n"/>
-      <c r="C995" s="3" t="n"/>
-      <c r="D995" s="4" t="n"/>
-      <c r="E995" s="4" t="n"/>
-      <c r="F995" s="5" t="n"/>
-      <c r="G995" s="6" t="n"/>
-      <c r="H995" s="4" t="n"/>
-      <c r="I995" s="7" t="n"/>
-      <c r="J995" s="4" t="n"/>
-    </row>
-    <row r="996" ht="22" customHeight="1">
-      <c r="A996" s="3">
-        <f>IF(C996="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B996" s="3" t="n"/>
-      <c r="C996" s="3" t="n"/>
-      <c r="D996" s="4" t="n"/>
-      <c r="E996" s="4" t="n"/>
-      <c r="F996" s="5" t="n"/>
-      <c r="G996" s="6" t="n"/>
-      <c r="H996" s="4" t="n"/>
-      <c r="I996" s="7" t="n"/>
-      <c r="J996" s="4" t="n"/>
-    </row>
-    <row r="997" ht="22" customHeight="1">
-      <c r="A997" s="3">
-        <f>IF(C997="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B997" s="3" t="n"/>
-      <c r="C997" s="3" t="n"/>
-      <c r="D997" s="4" t="n"/>
-      <c r="E997" s="4" t="n"/>
-      <c r="F997" s="5" t="n"/>
-      <c r="G997" s="6" t="n"/>
-      <c r="H997" s="4" t="n"/>
-      <c r="I997" s="7" t="n"/>
-      <c r="J997" s="4" t="n"/>
-    </row>
-    <row r="998" ht="22" customHeight="1">
-      <c r="A998" s="3">
-        <f>IF(C998="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B998" s="3" t="n"/>
-      <c r="C998" s="3" t="n"/>
-      <c r="D998" s="4" t="n"/>
-      <c r="E998" s="4" t="n"/>
-      <c r="F998" s="5" t="n"/>
-      <c r="G998" s="6" t="n"/>
-      <c r="H998" s="4" t="n"/>
-      <c r="I998" s="7" t="n"/>
-      <c r="J998" s="4" t="n"/>
-    </row>
-    <row r="999" ht="22" customHeight="1">
-      <c r="A999" s="3">
-        <f>IF(C999="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B999" s="3" t="n"/>
-      <c r="C999" s="3" t="n"/>
-      <c r="D999" s="4" t="n"/>
-      <c r="E999" s="4" t="n"/>
-      <c r="F999" s="5" t="n"/>
-      <c r="G999" s="6" t="n"/>
-      <c r="H999" s="4" t="n"/>
-      <c r="I999" s="7" t="n"/>
-      <c r="J999" s="4" t="n"/>
-    </row>
-    <row r="1000" ht="22" customHeight="1">
-      <c r="A1000" s="3">
-        <f>IF(C1000="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B1000" s="3" t="n"/>
-      <c r="C1000" s="3" t="n"/>
-      <c r="D1000" s="4" t="n"/>
-      <c r="E1000" s="4" t="n"/>
-      <c r="F1000" s="5" t="n"/>
-      <c r="G1000" s="6" t="n"/>
-      <c r="H1000" s="4" t="n"/>
-      <c r="I1000" s="7" t="n"/>
-      <c r="J1000" s="4" t="n"/>
-    </row>
-    <row r="1001" ht="22" customHeight="1">
-      <c r="A1001" s="3">
-        <f>IF(C1001="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B1001" s="3" t="n"/>
-      <c r="C1001" s="3" t="n"/>
-      <c r="D1001" s="4" t="n"/>
-      <c r="E1001" s="4" t="n"/>
-      <c r="F1001" s="5" t="n"/>
-      <c r="G1001" s="6" t="n"/>
-      <c r="H1001" s="4" t="n"/>
-      <c r="I1001" s="7" t="n"/>
-      <c r="J1001" s="4" t="n"/>
-    </row>
-    <row r="1002" ht="22" customHeight="1">
-      <c r="A1002" s="3">
-        <f>IF(C1002="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B1002" s="3" t="n"/>
-      <c r="C1002" s="3" t="n"/>
-      <c r="D1002" s="4" t="n"/>
-      <c r="E1002" s="4" t="n"/>
-      <c r="F1002" s="5" t="n"/>
-      <c r="G1002" s="6" t="n"/>
-      <c r="H1002" s="4" t="n"/>
-      <c r="I1002" s="7" t="n"/>
-      <c r="J1002" s="4" t="n"/>
-    </row>
-    <row r="1004" ht="28" customHeight="1">
-      <c r="A1004" s="8" t="inlineStr">
+    <row r="504" ht="28" customHeight="1">
+      <c r="A504" s="8" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G1004" s="9">
-        <f>SUM(G3:G1002)</f>
-        <v/>
-      </c>
-      <c r="H1004" s="10">
-        <f>COUNTA(C3:C1002) &amp; " 笔订单"</f>
+      <c r="G504" s="9">
+        <f>SUM(G3:G502)</f>
+        <v/>
+      </c>
+      <c r="H504" s="10">
+        <f>COUNTA(C3:C502) &amp; " 笔订单"</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1004:F1004"/>
+    <mergeCell ref="A504:F504"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H1004:J1004"/>
+    <mergeCell ref="H504:J504"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16176,11 +8676,11 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=1)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=1)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
       <c r="E3" s="6">
@@ -16202,11 +8702,11 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=2)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,2,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=2)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,2,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
       <c r="E4" s="6">
@@ -16228,11 +8728,11 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=3)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,3,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=3)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,3,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
       <c r="E5" s="6">
@@ -16254,11 +8754,11 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=4)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,4,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=4)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,4,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
       <c r="E6" s="6">
@@ -16280,11 +8780,11 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=5)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,5,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=5)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,5,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
       <c r="E7" s="6">
@@ -16306,11 +8806,11 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=6)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,6,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=6)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,6,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
       <c r="E8" s="6">
@@ -16332,11 +8832,11 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=7)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,7,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=7)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,7,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
       <c r="E9" s="6">
@@ -16358,11 +8858,11 @@
         </is>
       </c>
       <c r="C10" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=8)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,8,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=8)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,8,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,9,1))</f>
         <v/>
       </c>
       <c r="E10" s="6">
@@ -16384,11 +8884,11 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=9)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,9,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,10,1))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=9)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,9,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,10,1))</f>
         <v/>
       </c>
       <c r="E11" s="6">
@@ -16410,11 +8910,11 @@
         </is>
       </c>
       <c r="C12" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=10)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,10,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,11,1))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=10)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,10,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,11,1))</f>
         <v/>
       </c>
       <c r="E12" s="6">
@@ -16436,11 +8936,11 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=11)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,11,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,12,1))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=11)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,11,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,12,1))</f>
         <v/>
       </c>
       <c r="E13" s="6">
@@ -16462,11 +8962,11 @@
         </is>
       </c>
       <c r="C14" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=12)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,12,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,1,1)+365)</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*(MONTH('🛒购买记录明细'!C3:C1002)=12)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,12,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,1,1)+365)</f>
         <v/>
       </c>
       <c r="E14" s="6">
@@ -16568,11 +9068,11 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C3" s="6">
-        <f>SUMPRODUCT((YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D3" s="6">
@@ -16640,11 +9140,11 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="抖音")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"抖音",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C3" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="抖音")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"抖音",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D3" s="11">
@@ -16659,11 +9159,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="1688")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"1688",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="1688")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"1688",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D4" s="11">
@@ -16678,11 +9178,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="淘宝")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"淘宝",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="淘宝")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"淘宝",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D5" s="11">
@@ -16697,11 +9197,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="京东")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"京东",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="京东")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"京东",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D6" s="11">
@@ -16716,11 +9216,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="拼多多")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"拼多多",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="拼多多")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"拼多多",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D7" s="11">
@@ -16735,11 +9235,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="天猫")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"天猫",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="天猫")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"天猫",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D8" s="11">
@@ -16754,11 +9254,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="苏宁")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"苏宁",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="苏宁")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"苏宁",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D9" s="11">
@@ -16773,11 +9273,11 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="其他")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!C3:C1002&lt;&gt;""))</f>
+        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"其他",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>SUMPRODUCT(('🛒购买记录明细'!B3:B1002="其他")*(YEAR('🛒购买记录明细'!C3:C1002)=2026)*('🛒购买记录明细'!G3:G1002))</f>
+        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"其他",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
         <v/>
       </c>
       <c r="D10" s="11">

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -83,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -105,11 +107,55 @@
         <color rgb="008EAADB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="008EAADB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="008EAADB"/>
+      </right>
+      <top style="thin">
+        <color rgb="008EAADB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="008EAADB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008EAADB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="008EAADB"/>
+      </right>
+      <top style="thin">
+        <color rgb="008EAADB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008EAADB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +190,11 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -222,7 +273,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -513,7 +563,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -1090,13 +1139,35 @@
         <f>IF(C3="","",ROW()-2)</f>
         <v/>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="4" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>46215.5080787037</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>创意世界杯足球大力神杯</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>3311879379799327755</t>
+        </is>
+      </c>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
@@ -1105,13 +1176,35 @@
         <f>IF(C4="","",ROW()-2)</f>
         <v/>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>抖音商城</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>46221.42550925926</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球杯</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>500ml琥珀圆形大力神杯(牛皮纸盒包装)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>6928046994516508348</t>
+        </is>
+      </c>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
@@ -8599,6 +8692,8 @@
         <f>COUNTA(C3:C502) &amp; " 笔订单"</f>
         <v/>
       </c>
+      <c r="I504" s="13" t="n"/>
+      <c r="J504" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8984,7 +9079,7 @@
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
+      <c r="B15" s="14" t="n"/>
       <c r="C15" s="10">
         <f>SUM(C3:C14)</f>
         <v/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -19,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -155,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -190,11 +189,26 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -273,6 +287,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -503,6 +518,107 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>2026年 购买统计</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'📈年度统计'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'📈年度统计'!$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'📈年度统计'!$C$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>金额(元)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
@@ -537,12 +653,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'🏪平台分布'!$A$3:$A$10</f>
+              <f>'🏪平台分布'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🏪平台分布'!$C$3:$C$10</f>
+              <f>'🏪平台分布'!$C$3:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -561,8 +677,9 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -598,12 +715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'🏪平台分布'!$A$3:$A$10</f>
+              <f>'🏪平台分布'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🏪平台分布'!$B$3:$B$10</f>
+              <f>'🏪平台分布'!$B$3:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -723,6 +840,33 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1135,16 +1279,15 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3">
-        <f>IF(C3="","",ROW()-2)</f>
-        <v/>
+      <c r="A3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>1688</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="15" t="n">
         <v>46215.5080787037</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1172,16 +1315,15 @@
       <c r="J3" s="4" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3">
-        <f>IF(C4="","",ROW()-2)</f>
-        <v/>
+      <c r="A4" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>抖音商城</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="15" t="n">
         <v>46221.42550925926</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1209,10 +1351,7 @@
       <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3">
-        <f>IF(C5="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A5" s="3" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="4" t="n"/>
@@ -1223,26 +1362,30 @@
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3">
-        <f>IF(C6="","",ROW()-2)</f>
-        <v/>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="4" t="n"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>2 笔订单</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="14" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3">
-        <f>IF(C7="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A7" s="3" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="4" t="n"/>
@@ -1254,10 +1397,7 @@
       <c r="J7" s="4" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3">
-        <f>IF(C8="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A8" s="3" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="4" t="n"/>
@@ -1269,10 +1409,7 @@
       <c r="J8" s="4" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3">
-        <f>IF(C9="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A9" s="3" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="4" t="n"/>
@@ -1284,10 +1421,7 @@
       <c r="J9" s="4" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3">
-        <f>IF(C10="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A10" s="3" t="n"/>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -1299,10 +1433,7 @@
       <c r="J10" s="4" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3">
-        <f>IF(C11="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A11" s="3" t="n"/>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="4" t="n"/>
@@ -1314,10 +1445,7 @@
       <c r="J11" s="4" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3">
-        <f>IF(C12="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A12" s="3" t="n"/>
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="4" t="n"/>
@@ -1329,10 +1457,7 @@
       <c r="J12" s="4" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3">
-        <f>IF(C13="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A13" s="3" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="4" t="n"/>
@@ -1344,10 +1469,7 @@
       <c r="J13" s="4" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3">
-        <f>IF(C14="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A14" s="3" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="4" t="n"/>
@@ -1359,10 +1481,7 @@
       <c r="J14" s="4" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3">
-        <f>IF(C15="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="4" t="n"/>
@@ -1374,10 +1493,7 @@
       <c r="J15" s="4" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3">
-        <f>IF(C16="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A16" s="3" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="4" t="n"/>
@@ -1389,10 +1505,7 @@
       <c r="J16" s="4" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3">
-        <f>IF(C17="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A17" s="3" t="n"/>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="4" t="n"/>
@@ -1404,10 +1517,7 @@
       <c r="J17" s="4" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3">
-        <f>IF(C18="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A18" s="3" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="4" t="n"/>
@@ -1419,10 +1529,7 @@
       <c r="J18" s="4" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3">
-        <f>IF(C19="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A19" s="3" t="n"/>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="4" t="n"/>
@@ -1434,10 +1541,7 @@
       <c r="J19" s="4" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3">
-        <f>IF(C20="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A20" s="3" t="n"/>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="4" t="n"/>
@@ -1449,10 +1553,7 @@
       <c r="J20" s="4" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3">
-        <f>IF(C21="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A21" s="3" t="n"/>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="4" t="n"/>
@@ -1464,10 +1565,7 @@
       <c r="J21" s="4" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3">
-        <f>IF(C22="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="4" t="n"/>
@@ -1479,10 +1577,7 @@
       <c r="J22" s="4" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="3">
-        <f>IF(C23="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A23" s="3" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="4" t="n"/>
@@ -1494,10 +1589,7 @@
       <c r="J23" s="4" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="3">
-        <f>IF(C24="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A24" s="3" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="4" t="n"/>
@@ -1509,10 +1601,7 @@
       <c r="J24" s="4" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="3">
-        <f>IF(C25="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A25" s="3" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="4" t="n"/>
@@ -1524,10 +1613,7 @@
       <c r="J25" s="4" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="3">
-        <f>IF(C26="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="4" t="n"/>
@@ -1539,10 +1625,7 @@
       <c r="J26" s="4" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3">
-        <f>IF(C27="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="4" t="n"/>
@@ -1554,10 +1637,7 @@
       <c r="J27" s="4" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3">
-        <f>IF(C28="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="4" t="n"/>
@@ -1569,10 +1649,7 @@
       <c r="J28" s="4" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3">
-        <f>IF(C29="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A29" s="3" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="4" t="n"/>
@@ -1584,10 +1661,7 @@
       <c r="J29" s="4" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="3">
-        <f>IF(C30="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A30" s="3" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="4" t="n"/>
@@ -1599,10 +1673,7 @@
       <c r="J30" s="4" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3">
-        <f>IF(C31="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="4" t="n"/>
@@ -1614,10 +1685,7 @@
       <c r="J31" s="4" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3">
-        <f>IF(C32="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A32" s="3" t="n"/>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="4" t="n"/>
@@ -1629,10 +1697,7 @@
       <c r="J32" s="4" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3">
-        <f>IF(C33="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A33" s="3" t="n"/>
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="4" t="n"/>
@@ -1644,10 +1709,7 @@
       <c r="J33" s="4" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="3">
-        <f>IF(C34="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A34" s="3" t="n"/>
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="4" t="n"/>
@@ -1659,10 +1721,7 @@
       <c r="J34" s="4" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="3">
-        <f>IF(C35="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A35" s="3" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="4" t="n"/>
@@ -1674,10 +1733,7 @@
       <c r="J35" s="4" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="3">
-        <f>IF(C36="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A36" s="3" t="n"/>
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="4" t="n"/>
@@ -1689,10 +1745,7 @@
       <c r="J36" s="4" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="3">
-        <f>IF(C37="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A37" s="3" t="n"/>
       <c r="B37" s="3" t="n"/>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="4" t="n"/>
@@ -1704,10 +1757,7 @@
       <c r="J37" s="4" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="3">
-        <f>IF(C38="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A38" s="3" t="n"/>
       <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="4" t="n"/>
@@ -1719,10 +1769,7 @@
       <c r="J38" s="4" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="3">
-        <f>IF(C39="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A39" s="3" t="n"/>
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="4" t="n"/>
@@ -1734,10 +1781,7 @@
       <c r="J39" s="4" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="3">
-        <f>IF(C40="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A40" s="3" t="n"/>
       <c r="B40" s="3" t="n"/>
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="4" t="n"/>
@@ -1749,10 +1793,7 @@
       <c r="J40" s="4" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="3">
-        <f>IF(C41="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A41" s="3" t="n"/>
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="4" t="n"/>
@@ -1764,10 +1805,7 @@
       <c r="J41" s="4" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="3">
-        <f>IF(C42="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A42" s="3" t="n"/>
       <c r="B42" s="3" t="n"/>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="4" t="n"/>
@@ -1779,10 +1817,7 @@
       <c r="J42" s="4" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="3">
-        <f>IF(C43="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A43" s="3" t="n"/>
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="4" t="n"/>
@@ -1794,10 +1829,7 @@
       <c r="J43" s="4" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="3">
-        <f>IF(C44="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A44" s="3" t="n"/>
       <c r="B44" s="3" t="n"/>
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="4" t="n"/>
@@ -1809,10 +1841,7 @@
       <c r="J44" s="4" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="3">
-        <f>IF(C45="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A45" s="3" t="n"/>
       <c r="B45" s="3" t="n"/>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="4" t="n"/>
@@ -1824,10 +1853,7 @@
       <c r="J45" s="4" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="3">
-        <f>IF(C46="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A46" s="3" t="n"/>
       <c r="B46" s="3" t="n"/>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="4" t="n"/>
@@ -1839,10 +1865,7 @@
       <c r="J46" s="4" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="3">
-        <f>IF(C47="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A47" s="3" t="n"/>
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="4" t="n"/>
@@ -1854,10 +1877,7 @@
       <c r="J47" s="4" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3">
-        <f>IF(C48="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A48" s="3" t="n"/>
       <c r="B48" s="3" t="n"/>
       <c r="C48" s="3" t="n"/>
       <c r="D48" s="4" t="n"/>
@@ -1869,10 +1889,7 @@
       <c r="J48" s="4" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="3">
-        <f>IF(C49="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A49" s="3" t="n"/>
       <c r="B49" s="3" t="n"/>
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="4" t="n"/>
@@ -1884,10 +1901,7 @@
       <c r="J49" s="4" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="3">
-        <f>IF(C50="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A50" s="3" t="n"/>
       <c r="B50" s="3" t="n"/>
       <c r="C50" s="3" t="n"/>
       <c r="D50" s="4" t="n"/>
@@ -1899,10 +1913,7 @@
       <c r="J50" s="4" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3">
-        <f>IF(C51="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A51" s="3" t="n"/>
       <c r="B51" s="3" t="n"/>
       <c r="C51" s="3" t="n"/>
       <c r="D51" s="4" t="n"/>
@@ -1914,10 +1925,7 @@
       <c r="J51" s="4" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="3">
-        <f>IF(C52="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A52" s="3" t="n"/>
       <c r="B52" s="3" t="n"/>
       <c r="C52" s="3" t="n"/>
       <c r="D52" s="4" t="n"/>
@@ -1929,10 +1937,7 @@
       <c r="J52" s="4" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="3">
-        <f>IF(C53="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A53" s="3" t="n"/>
       <c r="B53" s="3" t="n"/>
       <c r="C53" s="3" t="n"/>
       <c r="D53" s="4" t="n"/>
@@ -1944,10 +1949,7 @@
       <c r="J53" s="4" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="3">
-        <f>IF(C54="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A54" s="3" t="n"/>
       <c r="B54" s="3" t="n"/>
       <c r="C54" s="3" t="n"/>
       <c r="D54" s="4" t="n"/>
@@ -1959,10 +1961,7 @@
       <c r="J54" s="4" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="3">
-        <f>IF(C55="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A55" s="3" t="n"/>
       <c r="B55" s="3" t="n"/>
       <c r="C55" s="3" t="n"/>
       <c r="D55" s="4" t="n"/>
@@ -1974,10 +1973,7 @@
       <c r="J55" s="4" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="3">
-        <f>IF(C56="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A56" s="3" t="n"/>
       <c r="B56" s="3" t="n"/>
       <c r="C56" s="3" t="n"/>
       <c r="D56" s="4" t="n"/>
@@ -1989,10 +1985,7 @@
       <c r="J56" s="4" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="3">
-        <f>IF(C57="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A57" s="3" t="n"/>
       <c r="B57" s="3" t="n"/>
       <c r="C57" s="3" t="n"/>
       <c r="D57" s="4" t="n"/>
@@ -2004,10 +1997,7 @@
       <c r="J57" s="4" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="3">
-        <f>IF(C58="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A58" s="3" t="n"/>
       <c r="B58" s="3" t="n"/>
       <c r="C58" s="3" t="n"/>
       <c r="D58" s="4" t="n"/>
@@ -2019,10 +2009,7 @@
       <c r="J58" s="4" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="3">
-        <f>IF(C59="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A59" s="3" t="n"/>
       <c r="B59" s="3" t="n"/>
       <c r="C59" s="3" t="n"/>
       <c r="D59" s="4" t="n"/>
@@ -2034,10 +2021,7 @@
       <c r="J59" s="4" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="3">
-        <f>IF(C60="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A60" s="3" t="n"/>
       <c r="B60" s="3" t="n"/>
       <c r="C60" s="3" t="n"/>
       <c r="D60" s="4" t="n"/>
@@ -2049,10 +2033,7 @@
       <c r="J60" s="4" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="3">
-        <f>IF(C61="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A61" s="3" t="n"/>
       <c r="B61" s="3" t="n"/>
       <c r="C61" s="3" t="n"/>
       <c r="D61" s="4" t="n"/>
@@ -2064,10 +2045,7 @@
       <c r="J61" s="4" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="3">
-        <f>IF(C62="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A62" s="3" t="n"/>
       <c r="B62" s="3" t="n"/>
       <c r="C62" s="3" t="n"/>
       <c r="D62" s="4" t="n"/>
@@ -2079,10 +2057,7 @@
       <c r="J62" s="4" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="3">
-        <f>IF(C63="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A63" s="3" t="n"/>
       <c r="B63" s="3" t="n"/>
       <c r="C63" s="3" t="n"/>
       <c r="D63" s="4" t="n"/>
@@ -2094,10 +2069,7 @@
       <c r="J63" s="4" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="3">
-        <f>IF(C64="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A64" s="3" t="n"/>
       <c r="B64" s="3" t="n"/>
       <c r="C64" s="3" t="n"/>
       <c r="D64" s="4" t="n"/>
@@ -2109,10 +2081,7 @@
       <c r="J64" s="4" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="3">
-        <f>IF(C65="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A65" s="3" t="n"/>
       <c r="B65" s="3" t="n"/>
       <c r="C65" s="3" t="n"/>
       <c r="D65" s="4" t="n"/>
@@ -2124,10 +2093,7 @@
       <c r="J65" s="4" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="3">
-        <f>IF(C66="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A66" s="3" t="n"/>
       <c r="B66" s="3" t="n"/>
       <c r="C66" s="3" t="n"/>
       <c r="D66" s="4" t="n"/>
@@ -2139,10 +2105,7 @@
       <c r="J66" s="4" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="3">
-        <f>IF(C67="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A67" s="3" t="n"/>
       <c r="B67" s="3" t="n"/>
       <c r="C67" s="3" t="n"/>
       <c r="D67" s="4" t="n"/>
@@ -2154,10 +2117,7 @@
       <c r="J67" s="4" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="3">
-        <f>IF(C68="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A68" s="3" t="n"/>
       <c r="B68" s="3" t="n"/>
       <c r="C68" s="3" t="n"/>
       <c r="D68" s="4" t="n"/>
@@ -2169,10 +2129,7 @@
       <c r="J68" s="4" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="3">
-        <f>IF(C69="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A69" s="3" t="n"/>
       <c r="B69" s="3" t="n"/>
       <c r="C69" s="3" t="n"/>
       <c r="D69" s="4" t="n"/>
@@ -2184,10 +2141,7 @@
       <c r="J69" s="4" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="3">
-        <f>IF(C70="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A70" s="3" t="n"/>
       <c r="B70" s="3" t="n"/>
       <c r="C70" s="3" t="n"/>
       <c r="D70" s="4" t="n"/>
@@ -2199,10 +2153,7 @@
       <c r="J70" s="4" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="3">
-        <f>IF(C71="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A71" s="3" t="n"/>
       <c r="B71" s="3" t="n"/>
       <c r="C71" s="3" t="n"/>
       <c r="D71" s="4" t="n"/>
@@ -2214,10 +2165,7 @@
       <c r="J71" s="4" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="3">
-        <f>IF(C72="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A72" s="3" t="n"/>
       <c r="B72" s="3" t="n"/>
       <c r="C72" s="3" t="n"/>
       <c r="D72" s="4" t="n"/>
@@ -2229,10 +2177,7 @@
       <c r="J72" s="4" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="3">
-        <f>IF(C73="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A73" s="3" t="n"/>
       <c r="B73" s="3" t="n"/>
       <c r="C73" s="3" t="n"/>
       <c r="D73" s="4" t="n"/>
@@ -2244,10 +2189,7 @@
       <c r="J73" s="4" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="3">
-        <f>IF(C74="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A74" s="3" t="n"/>
       <c r="B74" s="3" t="n"/>
       <c r="C74" s="3" t="n"/>
       <c r="D74" s="4" t="n"/>
@@ -2259,10 +2201,7 @@
       <c r="J74" s="4" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="3">
-        <f>IF(C75="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A75" s="3" t="n"/>
       <c r="B75" s="3" t="n"/>
       <c r="C75" s="3" t="n"/>
       <c r="D75" s="4" t="n"/>
@@ -2274,10 +2213,7 @@
       <c r="J75" s="4" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="3">
-        <f>IF(C76="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A76" s="3" t="n"/>
       <c r="B76" s="3" t="n"/>
       <c r="C76" s="3" t="n"/>
       <c r="D76" s="4" t="n"/>
@@ -2289,10 +2225,7 @@
       <c r="J76" s="4" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="3">
-        <f>IF(C77="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A77" s="3" t="n"/>
       <c r="B77" s="3" t="n"/>
       <c r="C77" s="3" t="n"/>
       <c r="D77" s="4" t="n"/>
@@ -2304,10 +2237,7 @@
       <c r="J77" s="4" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="3">
-        <f>IF(C78="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A78" s="3" t="n"/>
       <c r="B78" s="3" t="n"/>
       <c r="C78" s="3" t="n"/>
       <c r="D78" s="4" t="n"/>
@@ -2319,10 +2249,7 @@
       <c r="J78" s="4" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="3">
-        <f>IF(C79="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A79" s="3" t="n"/>
       <c r="B79" s="3" t="n"/>
       <c r="C79" s="3" t="n"/>
       <c r="D79" s="4" t="n"/>
@@ -2334,10 +2261,7 @@
       <c r="J79" s="4" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="3">
-        <f>IF(C80="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A80" s="3" t="n"/>
       <c r="B80" s="3" t="n"/>
       <c r="C80" s="3" t="n"/>
       <c r="D80" s="4" t="n"/>
@@ -2349,10 +2273,7 @@
       <c r="J80" s="4" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="3">
-        <f>IF(C81="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A81" s="3" t="n"/>
       <c r="B81" s="3" t="n"/>
       <c r="C81" s="3" t="n"/>
       <c r="D81" s="4" t="n"/>
@@ -2364,10 +2285,7 @@
       <c r="J81" s="4" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="3">
-        <f>IF(C82="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A82" s="3" t="n"/>
       <c r="B82" s="3" t="n"/>
       <c r="C82" s="3" t="n"/>
       <c r="D82" s="4" t="n"/>
@@ -2379,10 +2297,7 @@
       <c r="J82" s="4" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="3">
-        <f>IF(C83="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A83" s="3" t="n"/>
       <c r="B83" s="3" t="n"/>
       <c r="C83" s="3" t="n"/>
       <c r="D83" s="4" t="n"/>
@@ -2394,10 +2309,7 @@
       <c r="J83" s="4" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="3">
-        <f>IF(C84="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A84" s="3" t="n"/>
       <c r="B84" s="3" t="n"/>
       <c r="C84" s="3" t="n"/>
       <c r="D84" s="4" t="n"/>
@@ -2409,10 +2321,7 @@
       <c r="J84" s="4" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="3">
-        <f>IF(C85="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A85" s="3" t="n"/>
       <c r="B85" s="3" t="n"/>
       <c r="C85" s="3" t="n"/>
       <c r="D85" s="4" t="n"/>
@@ -2424,10 +2333,7 @@
       <c r="J85" s="4" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="3">
-        <f>IF(C86="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A86" s="3" t="n"/>
       <c r="B86" s="3" t="n"/>
       <c r="C86" s="3" t="n"/>
       <c r="D86" s="4" t="n"/>
@@ -2439,10 +2345,7 @@
       <c r="J86" s="4" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="3">
-        <f>IF(C87="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A87" s="3" t="n"/>
       <c r="B87" s="3" t="n"/>
       <c r="C87" s="3" t="n"/>
       <c r="D87" s="4" t="n"/>
@@ -2454,10 +2357,7 @@
       <c r="J87" s="4" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="3">
-        <f>IF(C88="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A88" s="3" t="n"/>
       <c r="B88" s="3" t="n"/>
       <c r="C88" s="3" t="n"/>
       <c r="D88" s="4" t="n"/>
@@ -2469,10 +2369,7 @@
       <c r="J88" s="4" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="3">
-        <f>IF(C89="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A89" s="3" t="n"/>
       <c r="B89" s="3" t="n"/>
       <c r="C89" s="3" t="n"/>
       <c r="D89" s="4" t="n"/>
@@ -2484,10 +2381,7 @@
       <c r="J89" s="4" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="3">
-        <f>IF(C90="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A90" s="3" t="n"/>
       <c r="B90" s="3" t="n"/>
       <c r="C90" s="3" t="n"/>
       <c r="D90" s="4" t="n"/>
@@ -2499,10 +2393,7 @@
       <c r="J90" s="4" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="3">
-        <f>IF(C91="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A91" s="3" t="n"/>
       <c r="B91" s="3" t="n"/>
       <c r="C91" s="3" t="n"/>
       <c r="D91" s="4" t="n"/>
@@ -2514,10 +2405,7 @@
       <c r="J91" s="4" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="3">
-        <f>IF(C92="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A92" s="3" t="n"/>
       <c r="B92" s="3" t="n"/>
       <c r="C92" s="3" t="n"/>
       <c r="D92" s="4" t="n"/>
@@ -2529,10 +2417,7 @@
       <c r="J92" s="4" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="3">
-        <f>IF(C93="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A93" s="3" t="n"/>
       <c r="B93" s="3" t="n"/>
       <c r="C93" s="3" t="n"/>
       <c r="D93" s="4" t="n"/>
@@ -2544,10 +2429,7 @@
       <c r="J93" s="4" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="3">
-        <f>IF(C94="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A94" s="3" t="n"/>
       <c r="B94" s="3" t="n"/>
       <c r="C94" s="3" t="n"/>
       <c r="D94" s="4" t="n"/>
@@ -2559,10 +2441,7 @@
       <c r="J94" s="4" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="3">
-        <f>IF(C95="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A95" s="3" t="n"/>
       <c r="B95" s="3" t="n"/>
       <c r="C95" s="3" t="n"/>
       <c r="D95" s="4" t="n"/>
@@ -2574,10 +2453,7 @@
       <c r="J95" s="4" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="3">
-        <f>IF(C96="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A96" s="3" t="n"/>
       <c r="B96" s="3" t="n"/>
       <c r="C96" s="3" t="n"/>
       <c r="D96" s="4" t="n"/>
@@ -2589,10 +2465,7 @@
       <c r="J96" s="4" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="3">
-        <f>IF(C97="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A97" s="3" t="n"/>
       <c r="B97" s="3" t="n"/>
       <c r="C97" s="3" t="n"/>
       <c r="D97" s="4" t="n"/>
@@ -2604,10 +2477,7 @@
       <c r="J97" s="4" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="3">
-        <f>IF(C98="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A98" s="3" t="n"/>
       <c r="B98" s="3" t="n"/>
       <c r="C98" s="3" t="n"/>
       <c r="D98" s="4" t="n"/>
@@ -2619,10 +2489,7 @@
       <c r="J98" s="4" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="3">
-        <f>IF(C99="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A99" s="3" t="n"/>
       <c r="B99" s="3" t="n"/>
       <c r="C99" s="3" t="n"/>
       <c r="D99" s="4" t="n"/>
@@ -2634,10 +2501,7 @@
       <c r="J99" s="4" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="3">
-        <f>IF(C100="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A100" s="3" t="n"/>
       <c r="B100" s="3" t="n"/>
       <c r="C100" s="3" t="n"/>
       <c r="D100" s="4" t="n"/>
@@ -2649,10 +2513,7 @@
       <c r="J100" s="4" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="3">
-        <f>IF(C101="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A101" s="3" t="n"/>
       <c r="B101" s="3" t="n"/>
       <c r="C101" s="3" t="n"/>
       <c r="D101" s="4" t="n"/>
@@ -2664,10 +2525,7 @@
       <c r="J101" s="4" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="3">
-        <f>IF(C102="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A102" s="3" t="n"/>
       <c r="B102" s="3" t="n"/>
       <c r="C102" s="3" t="n"/>
       <c r="D102" s="4" t="n"/>
@@ -2679,10 +2537,7 @@
       <c r="J102" s="4" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="3">
-        <f>IF(C103="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A103" s="3" t="n"/>
       <c r="B103" s="3" t="n"/>
       <c r="C103" s="3" t="n"/>
       <c r="D103" s="4" t="n"/>
@@ -2694,10 +2549,7 @@
       <c r="J103" s="4" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="3">
-        <f>IF(C104="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A104" s="3" t="n"/>
       <c r="B104" s="3" t="n"/>
       <c r="C104" s="3" t="n"/>
       <c r="D104" s="4" t="n"/>
@@ -2709,10 +2561,7 @@
       <c r="J104" s="4" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="3">
-        <f>IF(C105="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A105" s="3" t="n"/>
       <c r="B105" s="3" t="n"/>
       <c r="C105" s="3" t="n"/>
       <c r="D105" s="4" t="n"/>
@@ -2724,10 +2573,7 @@
       <c r="J105" s="4" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="3">
-        <f>IF(C106="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A106" s="3" t="n"/>
       <c r="B106" s="3" t="n"/>
       <c r="C106" s="3" t="n"/>
       <c r="D106" s="4" t="n"/>
@@ -2739,10 +2585,7 @@
       <c r="J106" s="4" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="3">
-        <f>IF(C107="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A107" s="3" t="n"/>
       <c r="B107" s="3" t="n"/>
       <c r="C107" s="3" t="n"/>
       <c r="D107" s="4" t="n"/>
@@ -2754,10 +2597,7 @@
       <c r="J107" s="4" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="3">
-        <f>IF(C108="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A108" s="3" t="n"/>
       <c r="B108" s="3" t="n"/>
       <c r="C108" s="3" t="n"/>
       <c r="D108" s="4" t="n"/>
@@ -2769,10 +2609,7 @@
       <c r="J108" s="4" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="3">
-        <f>IF(C109="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A109" s="3" t="n"/>
       <c r="B109" s="3" t="n"/>
       <c r="C109" s="3" t="n"/>
       <c r="D109" s="4" t="n"/>
@@ -2784,10 +2621,7 @@
       <c r="J109" s="4" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="3">
-        <f>IF(C110="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A110" s="3" t="n"/>
       <c r="B110" s="3" t="n"/>
       <c r="C110" s="3" t="n"/>
       <c r="D110" s="4" t="n"/>
@@ -2799,10 +2633,7 @@
       <c r="J110" s="4" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="3">
-        <f>IF(C111="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A111" s="3" t="n"/>
       <c r="B111" s="3" t="n"/>
       <c r="C111" s="3" t="n"/>
       <c r="D111" s="4" t="n"/>
@@ -2814,10 +2645,7 @@
       <c r="J111" s="4" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="3">
-        <f>IF(C112="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A112" s="3" t="n"/>
       <c r="B112" s="3" t="n"/>
       <c r="C112" s="3" t="n"/>
       <c r="D112" s="4" t="n"/>
@@ -2829,10 +2657,7 @@
       <c r="J112" s="4" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="3">
-        <f>IF(C113="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A113" s="3" t="n"/>
       <c r="B113" s="3" t="n"/>
       <c r="C113" s="3" t="n"/>
       <c r="D113" s="4" t="n"/>
@@ -2844,10 +2669,7 @@
       <c r="J113" s="4" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="3">
-        <f>IF(C114="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A114" s="3" t="n"/>
       <c r="B114" s="3" t="n"/>
       <c r="C114" s="3" t="n"/>
       <c r="D114" s="4" t="n"/>
@@ -2859,10 +2681,7 @@
       <c r="J114" s="4" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="3">
-        <f>IF(C115="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A115" s="3" t="n"/>
       <c r="B115" s="3" t="n"/>
       <c r="C115" s="3" t="n"/>
       <c r="D115" s="4" t="n"/>
@@ -2874,10 +2693,7 @@
       <c r="J115" s="4" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="3">
-        <f>IF(C116="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A116" s="3" t="n"/>
       <c r="B116" s="3" t="n"/>
       <c r="C116" s="3" t="n"/>
       <c r="D116" s="4" t="n"/>
@@ -2889,10 +2705,7 @@
       <c r="J116" s="4" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="3">
-        <f>IF(C117="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A117" s="3" t="n"/>
       <c r="B117" s="3" t="n"/>
       <c r="C117" s="3" t="n"/>
       <c r="D117" s="4" t="n"/>
@@ -2904,10 +2717,7 @@
       <c r="J117" s="4" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
-      <c r="A118" s="3">
-        <f>IF(C118="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A118" s="3" t="n"/>
       <c r="B118" s="3" t="n"/>
       <c r="C118" s="3" t="n"/>
       <c r="D118" s="4" t="n"/>
@@ -2919,10 +2729,7 @@
       <c r="J118" s="4" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="3">
-        <f>IF(C119="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A119" s="3" t="n"/>
       <c r="B119" s="3" t="n"/>
       <c r="C119" s="3" t="n"/>
       <c r="D119" s="4" t="n"/>
@@ -2934,10 +2741,7 @@
       <c r="J119" s="4" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="3">
-        <f>IF(C120="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A120" s="3" t="n"/>
       <c r="B120" s="3" t="n"/>
       <c r="C120" s="3" t="n"/>
       <c r="D120" s="4" t="n"/>
@@ -2949,10 +2753,7 @@
       <c r="J120" s="4" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="3">
-        <f>IF(C121="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A121" s="3" t="n"/>
       <c r="B121" s="3" t="n"/>
       <c r="C121" s="3" t="n"/>
       <c r="D121" s="4" t="n"/>
@@ -2964,10 +2765,7 @@
       <c r="J121" s="4" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="3">
-        <f>IF(C122="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A122" s="3" t="n"/>
       <c r="B122" s="3" t="n"/>
       <c r="C122" s="3" t="n"/>
       <c r="D122" s="4" t="n"/>
@@ -2979,10 +2777,7 @@
       <c r="J122" s="4" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
-      <c r="A123" s="3">
-        <f>IF(C123="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A123" s="3" t="n"/>
       <c r="B123" s="3" t="n"/>
       <c r="C123" s="3" t="n"/>
       <c r="D123" s="4" t="n"/>
@@ -2994,10 +2789,7 @@
       <c r="J123" s="4" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="3">
-        <f>IF(C124="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A124" s="3" t="n"/>
       <c r="B124" s="3" t="n"/>
       <c r="C124" s="3" t="n"/>
       <c r="D124" s="4" t="n"/>
@@ -3009,10 +2801,7 @@
       <c r="J124" s="4" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="3">
-        <f>IF(C125="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A125" s="3" t="n"/>
       <c r="B125" s="3" t="n"/>
       <c r="C125" s="3" t="n"/>
       <c r="D125" s="4" t="n"/>
@@ -3024,10 +2813,7 @@
       <c r="J125" s="4" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="3">
-        <f>IF(C126="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A126" s="3" t="n"/>
       <c r="B126" s="3" t="n"/>
       <c r="C126" s="3" t="n"/>
       <c r="D126" s="4" t="n"/>
@@ -3039,10 +2825,7 @@
       <c r="J126" s="4" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="3">
-        <f>IF(C127="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A127" s="3" t="n"/>
       <c r="B127" s="3" t="n"/>
       <c r="C127" s="3" t="n"/>
       <c r="D127" s="4" t="n"/>
@@ -3054,10 +2837,7 @@
       <c r="J127" s="4" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="3">
-        <f>IF(C128="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A128" s="3" t="n"/>
       <c r="B128" s="3" t="n"/>
       <c r="C128" s="3" t="n"/>
       <c r="D128" s="4" t="n"/>
@@ -3069,10 +2849,7 @@
       <c r="J128" s="4" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="3">
-        <f>IF(C129="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A129" s="3" t="n"/>
       <c r="B129" s="3" t="n"/>
       <c r="C129" s="3" t="n"/>
       <c r="D129" s="4" t="n"/>
@@ -3084,10 +2861,7 @@
       <c r="J129" s="4" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="3">
-        <f>IF(C130="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A130" s="3" t="n"/>
       <c r="B130" s="3" t="n"/>
       <c r="C130" s="3" t="n"/>
       <c r="D130" s="4" t="n"/>
@@ -3099,10 +2873,7 @@
       <c r="J130" s="4" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="3">
-        <f>IF(C131="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A131" s="3" t="n"/>
       <c r="B131" s="3" t="n"/>
       <c r="C131" s="3" t="n"/>
       <c r="D131" s="4" t="n"/>
@@ -3114,10 +2885,7 @@
       <c r="J131" s="4" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="3">
-        <f>IF(C132="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A132" s="3" t="n"/>
       <c r="B132" s="3" t="n"/>
       <c r="C132" s="3" t="n"/>
       <c r="D132" s="4" t="n"/>
@@ -3129,10 +2897,7 @@
       <c r="J132" s="4" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="3">
-        <f>IF(C133="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A133" s="3" t="n"/>
       <c r="B133" s="3" t="n"/>
       <c r="C133" s="3" t="n"/>
       <c r="D133" s="4" t="n"/>
@@ -3144,10 +2909,7 @@
       <c r="J133" s="4" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="3">
-        <f>IF(C134="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A134" s="3" t="n"/>
       <c r="B134" s="3" t="n"/>
       <c r="C134" s="3" t="n"/>
       <c r="D134" s="4" t="n"/>
@@ -3159,10 +2921,7 @@
       <c r="J134" s="4" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="3">
-        <f>IF(C135="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A135" s="3" t="n"/>
       <c r="B135" s="3" t="n"/>
       <c r="C135" s="3" t="n"/>
       <c r="D135" s="4" t="n"/>
@@ -3174,10 +2933,7 @@
       <c r="J135" s="4" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="3">
-        <f>IF(C136="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A136" s="3" t="n"/>
       <c r="B136" s="3" t="n"/>
       <c r="C136" s="3" t="n"/>
       <c r="D136" s="4" t="n"/>
@@ -3189,10 +2945,7 @@
       <c r="J136" s="4" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="3">
-        <f>IF(C137="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A137" s="3" t="n"/>
       <c r="B137" s="3" t="n"/>
       <c r="C137" s="3" t="n"/>
       <c r="D137" s="4" t="n"/>
@@ -3204,10 +2957,7 @@
       <c r="J137" s="4" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="3">
-        <f>IF(C138="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A138" s="3" t="n"/>
       <c r="B138" s="3" t="n"/>
       <c r="C138" s="3" t="n"/>
       <c r="D138" s="4" t="n"/>
@@ -3219,10 +2969,7 @@
       <c r="J138" s="4" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="3">
-        <f>IF(C139="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A139" s="3" t="n"/>
       <c r="B139" s="3" t="n"/>
       <c r="C139" s="3" t="n"/>
       <c r="D139" s="4" t="n"/>
@@ -3234,10 +2981,7 @@
       <c r="J139" s="4" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="3">
-        <f>IF(C140="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A140" s="3" t="n"/>
       <c r="B140" s="3" t="n"/>
       <c r="C140" s="3" t="n"/>
       <c r="D140" s="4" t="n"/>
@@ -3249,10 +2993,7 @@
       <c r="J140" s="4" t="n"/>
     </row>
     <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="3">
-        <f>IF(C141="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A141" s="3" t="n"/>
       <c r="B141" s="3" t="n"/>
       <c r="C141" s="3" t="n"/>
       <c r="D141" s="4" t="n"/>
@@ -3264,10 +3005,7 @@
       <c r="J141" s="4" t="n"/>
     </row>
     <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="3">
-        <f>IF(C142="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A142" s="3" t="n"/>
       <c r="B142" s="3" t="n"/>
       <c r="C142" s="3" t="n"/>
       <c r="D142" s="4" t="n"/>
@@ -3279,10 +3017,7 @@
       <c r="J142" s="4" t="n"/>
     </row>
     <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="3">
-        <f>IF(C143="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A143" s="3" t="n"/>
       <c r="B143" s="3" t="n"/>
       <c r="C143" s="3" t="n"/>
       <c r="D143" s="4" t="n"/>
@@ -3294,10 +3029,7 @@
       <c r="J143" s="4" t="n"/>
     </row>
     <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="3">
-        <f>IF(C144="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A144" s="3" t="n"/>
       <c r="B144" s="3" t="n"/>
       <c r="C144" s="3" t="n"/>
       <c r="D144" s="4" t="n"/>
@@ -3309,10 +3041,7 @@
       <c r="J144" s="4" t="n"/>
     </row>
     <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="3">
-        <f>IF(C145="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A145" s="3" t="n"/>
       <c r="B145" s="3" t="n"/>
       <c r="C145" s="3" t="n"/>
       <c r="D145" s="4" t="n"/>
@@ -3324,10 +3053,7 @@
       <c r="J145" s="4" t="n"/>
     </row>
     <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="3">
-        <f>IF(C146="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A146" s="3" t="n"/>
       <c r="B146" s="3" t="n"/>
       <c r="C146" s="3" t="n"/>
       <c r="D146" s="4" t="n"/>
@@ -3339,10 +3065,7 @@
       <c r="J146" s="4" t="n"/>
     </row>
     <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="3">
-        <f>IF(C147="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A147" s="3" t="n"/>
       <c r="B147" s="3" t="n"/>
       <c r="C147" s="3" t="n"/>
       <c r="D147" s="4" t="n"/>
@@ -3354,10 +3077,7 @@
       <c r="J147" s="4" t="n"/>
     </row>
     <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="3">
-        <f>IF(C148="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A148" s="3" t="n"/>
       <c r="B148" s="3" t="n"/>
       <c r="C148" s="3" t="n"/>
       <c r="D148" s="4" t="n"/>
@@ -3369,10 +3089,7 @@
       <c r="J148" s="4" t="n"/>
     </row>
     <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="3">
-        <f>IF(C149="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A149" s="3" t="n"/>
       <c r="B149" s="3" t="n"/>
       <c r="C149" s="3" t="n"/>
       <c r="D149" s="4" t="n"/>
@@ -3384,10 +3101,7 @@
       <c r="J149" s="4" t="n"/>
     </row>
     <row r="150" ht="22" customHeight="1">
-      <c r="A150" s="3">
-        <f>IF(C150="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A150" s="3" t="n"/>
       <c r="B150" s="3" t="n"/>
       <c r="C150" s="3" t="n"/>
       <c r="D150" s="4" t="n"/>
@@ -3399,10 +3113,7 @@
       <c r="J150" s="4" t="n"/>
     </row>
     <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="3">
-        <f>IF(C151="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A151" s="3" t="n"/>
       <c r="B151" s="3" t="n"/>
       <c r="C151" s="3" t="n"/>
       <c r="D151" s="4" t="n"/>
@@ -3414,10 +3125,7 @@
       <c r="J151" s="4" t="n"/>
     </row>
     <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="3">
-        <f>IF(C152="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A152" s="3" t="n"/>
       <c r="B152" s="3" t="n"/>
       <c r="C152" s="3" t="n"/>
       <c r="D152" s="4" t="n"/>
@@ -3429,10 +3137,7 @@
       <c r="J152" s="4" t="n"/>
     </row>
     <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="3">
-        <f>IF(C153="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A153" s="3" t="n"/>
       <c r="B153" s="3" t="n"/>
       <c r="C153" s="3" t="n"/>
       <c r="D153" s="4" t="n"/>
@@ -3444,10 +3149,7 @@
       <c r="J153" s="4" t="n"/>
     </row>
     <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="3">
-        <f>IF(C154="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A154" s="3" t="n"/>
       <c r="B154" s="3" t="n"/>
       <c r="C154" s="3" t="n"/>
       <c r="D154" s="4" t="n"/>
@@ -3459,10 +3161,7 @@
       <c r="J154" s="4" t="n"/>
     </row>
     <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="3">
-        <f>IF(C155="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A155" s="3" t="n"/>
       <c r="B155" s="3" t="n"/>
       <c r="C155" s="3" t="n"/>
       <c r="D155" s="4" t="n"/>
@@ -3474,10 +3173,7 @@
       <c r="J155" s="4" t="n"/>
     </row>
     <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="3">
-        <f>IF(C156="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A156" s="3" t="n"/>
       <c r="B156" s="3" t="n"/>
       <c r="C156" s="3" t="n"/>
       <c r="D156" s="4" t="n"/>
@@ -3489,10 +3185,7 @@
       <c r="J156" s="4" t="n"/>
     </row>
     <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="3">
-        <f>IF(C157="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A157" s="3" t="n"/>
       <c r="B157" s="3" t="n"/>
       <c r="C157" s="3" t="n"/>
       <c r="D157" s="4" t="n"/>
@@ -3504,10 +3197,7 @@
       <c r="J157" s="4" t="n"/>
     </row>
     <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="3">
-        <f>IF(C158="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A158" s="3" t="n"/>
       <c r="B158" s="3" t="n"/>
       <c r="C158" s="3" t="n"/>
       <c r="D158" s="4" t="n"/>
@@ -3519,10 +3209,7 @@
       <c r="J158" s="4" t="n"/>
     </row>
     <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="3">
-        <f>IF(C159="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A159" s="3" t="n"/>
       <c r="B159" s="3" t="n"/>
       <c r="C159" s="3" t="n"/>
       <c r="D159" s="4" t="n"/>
@@ -3534,10 +3221,7 @@
       <c r="J159" s="4" t="n"/>
     </row>
     <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="3">
-        <f>IF(C160="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A160" s="3" t="n"/>
       <c r="B160" s="3" t="n"/>
       <c r="C160" s="3" t="n"/>
       <c r="D160" s="4" t="n"/>
@@ -3549,10 +3233,7 @@
       <c r="J160" s="4" t="n"/>
     </row>
     <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="3">
-        <f>IF(C161="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A161" s="3" t="n"/>
       <c r="B161" s="3" t="n"/>
       <c r="C161" s="3" t="n"/>
       <c r="D161" s="4" t="n"/>
@@ -3564,10 +3245,7 @@
       <c r="J161" s="4" t="n"/>
     </row>
     <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="3">
-        <f>IF(C162="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A162" s="3" t="n"/>
       <c r="B162" s="3" t="n"/>
       <c r="C162" s="3" t="n"/>
       <c r="D162" s="4" t="n"/>
@@ -3579,10 +3257,7 @@
       <c r="J162" s="4" t="n"/>
     </row>
     <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="3">
-        <f>IF(C163="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A163" s="3" t="n"/>
       <c r="B163" s="3" t="n"/>
       <c r="C163" s="3" t="n"/>
       <c r="D163" s="4" t="n"/>
@@ -3594,10 +3269,7 @@
       <c r="J163" s="4" t="n"/>
     </row>
     <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="3">
-        <f>IF(C164="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A164" s="3" t="n"/>
       <c r="B164" s="3" t="n"/>
       <c r="C164" s="3" t="n"/>
       <c r="D164" s="4" t="n"/>
@@ -3609,10 +3281,7 @@
       <c r="J164" s="4" t="n"/>
     </row>
     <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="3">
-        <f>IF(C165="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A165" s="3" t="n"/>
       <c r="B165" s="3" t="n"/>
       <c r="C165" s="3" t="n"/>
       <c r="D165" s="4" t="n"/>
@@ -3624,10 +3293,7 @@
       <c r="J165" s="4" t="n"/>
     </row>
     <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="3">
-        <f>IF(C166="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A166" s="3" t="n"/>
       <c r="B166" s="3" t="n"/>
       <c r="C166" s="3" t="n"/>
       <c r="D166" s="4" t="n"/>
@@ -3639,10 +3305,7 @@
       <c r="J166" s="4" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="3">
-        <f>IF(C167="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A167" s="3" t="n"/>
       <c r="B167" s="3" t="n"/>
       <c r="C167" s="3" t="n"/>
       <c r="D167" s="4" t="n"/>
@@ -3654,10 +3317,7 @@
       <c r="J167" s="4" t="n"/>
     </row>
     <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="3">
-        <f>IF(C168="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A168" s="3" t="n"/>
       <c r="B168" s="3" t="n"/>
       <c r="C168" s="3" t="n"/>
       <c r="D168" s="4" t="n"/>
@@ -3669,10 +3329,7 @@
       <c r="J168" s="4" t="n"/>
     </row>
     <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="3">
-        <f>IF(C169="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A169" s="3" t="n"/>
       <c r="B169" s="3" t="n"/>
       <c r="C169" s="3" t="n"/>
       <c r="D169" s="4" t="n"/>
@@ -3684,10 +3341,7 @@
       <c r="J169" s="4" t="n"/>
     </row>
     <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="3">
-        <f>IF(C170="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A170" s="3" t="n"/>
       <c r="B170" s="3" t="n"/>
       <c r="C170" s="3" t="n"/>
       <c r="D170" s="4" t="n"/>
@@ -3699,10 +3353,7 @@
       <c r="J170" s="4" t="n"/>
     </row>
     <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="3">
-        <f>IF(C171="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A171" s="3" t="n"/>
       <c r="B171" s="3" t="n"/>
       <c r="C171" s="3" t="n"/>
       <c r="D171" s="4" t="n"/>
@@ -3714,10 +3365,7 @@
       <c r="J171" s="4" t="n"/>
     </row>
     <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="3">
-        <f>IF(C172="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A172" s="3" t="n"/>
       <c r="B172" s="3" t="n"/>
       <c r="C172" s="3" t="n"/>
       <c r="D172" s="4" t="n"/>
@@ -3729,10 +3377,7 @@
       <c r="J172" s="4" t="n"/>
     </row>
     <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="3">
-        <f>IF(C173="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A173" s="3" t="n"/>
       <c r="B173" s="3" t="n"/>
       <c r="C173" s="3" t="n"/>
       <c r="D173" s="4" t="n"/>
@@ -3744,10 +3389,7 @@
       <c r="J173" s="4" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="3">
-        <f>IF(C174="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A174" s="3" t="n"/>
       <c r="B174" s="3" t="n"/>
       <c r="C174" s="3" t="n"/>
       <c r="D174" s="4" t="n"/>
@@ -3759,10 +3401,7 @@
       <c r="J174" s="4" t="n"/>
     </row>
     <row r="175" ht="22" customHeight="1">
-      <c r="A175" s="3">
-        <f>IF(C175="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A175" s="3" t="n"/>
       <c r="B175" s="3" t="n"/>
       <c r="C175" s="3" t="n"/>
       <c r="D175" s="4" t="n"/>
@@ -3774,10 +3413,7 @@
       <c r="J175" s="4" t="n"/>
     </row>
     <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="3">
-        <f>IF(C176="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A176" s="3" t="n"/>
       <c r="B176" s="3" t="n"/>
       <c r="C176" s="3" t="n"/>
       <c r="D176" s="4" t="n"/>
@@ -3789,10 +3425,7 @@
       <c r="J176" s="4" t="n"/>
     </row>
     <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="3">
-        <f>IF(C177="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A177" s="3" t="n"/>
       <c r="B177" s="3" t="n"/>
       <c r="C177" s="3" t="n"/>
       <c r="D177" s="4" t="n"/>
@@ -3804,10 +3437,7 @@
       <c r="J177" s="4" t="n"/>
     </row>
     <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="3">
-        <f>IF(C178="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A178" s="3" t="n"/>
       <c r="B178" s="3" t="n"/>
       <c r="C178" s="3" t="n"/>
       <c r="D178" s="4" t="n"/>
@@ -3819,10 +3449,7 @@
       <c r="J178" s="4" t="n"/>
     </row>
     <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="3">
-        <f>IF(C179="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A179" s="3" t="n"/>
       <c r="B179" s="3" t="n"/>
       <c r="C179" s="3" t="n"/>
       <c r="D179" s="4" t="n"/>
@@ -3834,10 +3461,7 @@
       <c r="J179" s="4" t="n"/>
     </row>
     <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="3">
-        <f>IF(C180="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A180" s="3" t="n"/>
       <c r="B180" s="3" t="n"/>
       <c r="C180" s="3" t="n"/>
       <c r="D180" s="4" t="n"/>
@@ -3849,10 +3473,7 @@
       <c r="J180" s="4" t="n"/>
     </row>
     <row r="181" ht="22" customHeight="1">
-      <c r="A181" s="3">
-        <f>IF(C181="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A181" s="3" t="n"/>
       <c r="B181" s="3" t="n"/>
       <c r="C181" s="3" t="n"/>
       <c r="D181" s="4" t="n"/>
@@ -3864,10 +3485,7 @@
       <c r="J181" s="4" t="n"/>
     </row>
     <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="3">
-        <f>IF(C182="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A182" s="3" t="n"/>
       <c r="B182" s="3" t="n"/>
       <c r="C182" s="3" t="n"/>
       <c r="D182" s="4" t="n"/>
@@ -3879,10 +3497,7 @@
       <c r="J182" s="4" t="n"/>
     </row>
     <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="3">
-        <f>IF(C183="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A183" s="3" t="n"/>
       <c r="B183" s="3" t="n"/>
       <c r="C183" s="3" t="n"/>
       <c r="D183" s="4" t="n"/>
@@ -3894,10 +3509,7 @@
       <c r="J183" s="4" t="n"/>
     </row>
     <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="3">
-        <f>IF(C184="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A184" s="3" t="n"/>
       <c r="B184" s="3" t="n"/>
       <c r="C184" s="3" t="n"/>
       <c r="D184" s="4" t="n"/>
@@ -3909,10 +3521,7 @@
       <c r="J184" s="4" t="n"/>
     </row>
     <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="3">
-        <f>IF(C185="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A185" s="3" t="n"/>
       <c r="B185" s="3" t="n"/>
       <c r="C185" s="3" t="n"/>
       <c r="D185" s="4" t="n"/>
@@ -3924,10 +3533,7 @@
       <c r="J185" s="4" t="n"/>
     </row>
     <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="3">
-        <f>IF(C186="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A186" s="3" t="n"/>
       <c r="B186" s="3" t="n"/>
       <c r="C186" s="3" t="n"/>
       <c r="D186" s="4" t="n"/>
@@ -3939,10 +3545,7 @@
       <c r="J186" s="4" t="n"/>
     </row>
     <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="3">
-        <f>IF(C187="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A187" s="3" t="n"/>
       <c r="B187" s="3" t="n"/>
       <c r="C187" s="3" t="n"/>
       <c r="D187" s="4" t="n"/>
@@ -3954,10 +3557,7 @@
       <c r="J187" s="4" t="n"/>
     </row>
     <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="3">
-        <f>IF(C188="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A188" s="3" t="n"/>
       <c r="B188" s="3" t="n"/>
       <c r="C188" s="3" t="n"/>
       <c r="D188" s="4" t="n"/>
@@ -3969,10 +3569,7 @@
       <c r="J188" s="4" t="n"/>
     </row>
     <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="3">
-        <f>IF(C189="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A189" s="3" t="n"/>
       <c r="B189" s="3" t="n"/>
       <c r="C189" s="3" t="n"/>
       <c r="D189" s="4" t="n"/>
@@ -3984,10 +3581,7 @@
       <c r="J189" s="4" t="n"/>
     </row>
     <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="3">
-        <f>IF(C190="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A190" s="3" t="n"/>
       <c r="B190" s="3" t="n"/>
       <c r="C190" s="3" t="n"/>
       <c r="D190" s="4" t="n"/>
@@ -3999,10 +3593,7 @@
       <c r="J190" s="4" t="n"/>
     </row>
     <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="3">
-        <f>IF(C191="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A191" s="3" t="n"/>
       <c r="B191" s="3" t="n"/>
       <c r="C191" s="3" t="n"/>
       <c r="D191" s="4" t="n"/>
@@ -4014,10 +3605,7 @@
       <c r="J191" s="4" t="n"/>
     </row>
     <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="3">
-        <f>IF(C192="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A192" s="3" t="n"/>
       <c r="B192" s="3" t="n"/>
       <c r="C192" s="3" t="n"/>
       <c r="D192" s="4" t="n"/>
@@ -4029,10 +3617,7 @@
       <c r="J192" s="4" t="n"/>
     </row>
     <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="3">
-        <f>IF(C193="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A193" s="3" t="n"/>
       <c r="B193" s="3" t="n"/>
       <c r="C193" s="3" t="n"/>
       <c r="D193" s="4" t="n"/>
@@ -4044,10 +3629,7 @@
       <c r="J193" s="4" t="n"/>
     </row>
     <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="3">
-        <f>IF(C194="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A194" s="3" t="n"/>
       <c r="B194" s="3" t="n"/>
       <c r="C194" s="3" t="n"/>
       <c r="D194" s="4" t="n"/>
@@ -4059,10 +3641,7 @@
       <c r="J194" s="4" t="n"/>
     </row>
     <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="3">
-        <f>IF(C195="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A195" s="3" t="n"/>
       <c r="B195" s="3" t="n"/>
       <c r="C195" s="3" t="n"/>
       <c r="D195" s="4" t="n"/>
@@ -4074,10 +3653,7 @@
       <c r="J195" s="4" t="n"/>
     </row>
     <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="3">
-        <f>IF(C196="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A196" s="3" t="n"/>
       <c r="B196" s="3" t="n"/>
       <c r="C196" s="3" t="n"/>
       <c r="D196" s="4" t="n"/>
@@ -4089,10 +3665,7 @@
       <c r="J196" s="4" t="n"/>
     </row>
     <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="3">
-        <f>IF(C197="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A197" s="3" t="n"/>
       <c r="B197" s="3" t="n"/>
       <c r="C197" s="3" t="n"/>
       <c r="D197" s="4" t="n"/>
@@ -4104,10 +3677,7 @@
       <c r="J197" s="4" t="n"/>
     </row>
     <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="3">
-        <f>IF(C198="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A198" s="3" t="n"/>
       <c r="B198" s="3" t="n"/>
       <c r="C198" s="3" t="n"/>
       <c r="D198" s="4" t="n"/>
@@ -4119,10 +3689,7 @@
       <c r="J198" s="4" t="n"/>
     </row>
     <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="3">
-        <f>IF(C199="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A199" s="3" t="n"/>
       <c r="B199" s="3" t="n"/>
       <c r="C199" s="3" t="n"/>
       <c r="D199" s="4" t="n"/>
@@ -4134,10 +3701,7 @@
       <c r="J199" s="4" t="n"/>
     </row>
     <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="3">
-        <f>IF(C200="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A200" s="3" t="n"/>
       <c r="B200" s="3" t="n"/>
       <c r="C200" s="3" t="n"/>
       <c r="D200" s="4" t="n"/>
@@ -4149,10 +3713,7 @@
       <c r="J200" s="4" t="n"/>
     </row>
     <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="3">
-        <f>IF(C201="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A201" s="3" t="n"/>
       <c r="B201" s="3" t="n"/>
       <c r="C201" s="3" t="n"/>
       <c r="D201" s="4" t="n"/>
@@ -4164,10 +3725,7 @@
       <c r="J201" s="4" t="n"/>
     </row>
     <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="3">
-        <f>IF(C202="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A202" s="3" t="n"/>
       <c r="B202" s="3" t="n"/>
       <c r="C202" s="3" t="n"/>
       <c r="D202" s="4" t="n"/>
@@ -4179,10 +3737,7 @@
       <c r="J202" s="4" t="n"/>
     </row>
     <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="3">
-        <f>IF(C203="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A203" s="3" t="n"/>
       <c r="B203" s="3" t="n"/>
       <c r="C203" s="3" t="n"/>
       <c r="D203" s="4" t="n"/>
@@ -4194,10 +3749,7 @@
       <c r="J203" s="4" t="n"/>
     </row>
     <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="3">
-        <f>IF(C204="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A204" s="3" t="n"/>
       <c r="B204" s="3" t="n"/>
       <c r="C204" s="3" t="n"/>
       <c r="D204" s="4" t="n"/>
@@ -4209,10 +3761,7 @@
       <c r="J204" s="4" t="n"/>
     </row>
     <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="3">
-        <f>IF(C205="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A205" s="3" t="n"/>
       <c r="B205" s="3" t="n"/>
       <c r="C205" s="3" t="n"/>
       <c r="D205" s="4" t="n"/>
@@ -4224,10 +3773,7 @@
       <c r="J205" s="4" t="n"/>
     </row>
     <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="3">
-        <f>IF(C206="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A206" s="3" t="n"/>
       <c r="B206" s="3" t="n"/>
       <c r="C206" s="3" t="n"/>
       <c r="D206" s="4" t="n"/>
@@ -4239,10 +3785,7 @@
       <c r="J206" s="4" t="n"/>
     </row>
     <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="3">
-        <f>IF(C207="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A207" s="3" t="n"/>
       <c r="B207" s="3" t="n"/>
       <c r="C207" s="3" t="n"/>
       <c r="D207" s="4" t="n"/>
@@ -4254,10 +3797,7 @@
       <c r="J207" s="4" t="n"/>
     </row>
     <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="3">
-        <f>IF(C208="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A208" s="3" t="n"/>
       <c r="B208" s="3" t="n"/>
       <c r="C208" s="3" t="n"/>
       <c r="D208" s="4" t="n"/>
@@ -4269,10 +3809,7 @@
       <c r="J208" s="4" t="n"/>
     </row>
     <row r="209" ht="22" customHeight="1">
-      <c r="A209" s="3">
-        <f>IF(C209="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A209" s="3" t="n"/>
       <c r="B209" s="3" t="n"/>
       <c r="C209" s="3" t="n"/>
       <c r="D209" s="4" t="n"/>
@@ -4284,10 +3821,7 @@
       <c r="J209" s="4" t="n"/>
     </row>
     <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="3">
-        <f>IF(C210="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A210" s="3" t="n"/>
       <c r="B210" s="3" t="n"/>
       <c r="C210" s="3" t="n"/>
       <c r="D210" s="4" t="n"/>
@@ -4299,10 +3833,7 @@
       <c r="J210" s="4" t="n"/>
     </row>
     <row r="211" ht="22" customHeight="1">
-      <c r="A211" s="3">
-        <f>IF(C211="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A211" s="3" t="n"/>
       <c r="B211" s="3" t="n"/>
       <c r="C211" s="3" t="n"/>
       <c r="D211" s="4" t="n"/>
@@ -4314,10 +3845,7 @@
       <c r="J211" s="4" t="n"/>
     </row>
     <row r="212" ht="22" customHeight="1">
-      <c r="A212" s="3">
-        <f>IF(C212="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A212" s="3" t="n"/>
       <c r="B212" s="3" t="n"/>
       <c r="C212" s="3" t="n"/>
       <c r="D212" s="4" t="n"/>
@@ -4329,10 +3857,7 @@
       <c r="J212" s="4" t="n"/>
     </row>
     <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="3">
-        <f>IF(C213="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A213" s="3" t="n"/>
       <c r="B213" s="3" t="n"/>
       <c r="C213" s="3" t="n"/>
       <c r="D213" s="4" t="n"/>
@@ -4344,10 +3869,7 @@
       <c r="J213" s="4" t="n"/>
     </row>
     <row r="214" ht="22" customHeight="1">
-      <c r="A214" s="3">
-        <f>IF(C214="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A214" s="3" t="n"/>
       <c r="B214" s="3" t="n"/>
       <c r="C214" s="3" t="n"/>
       <c r="D214" s="4" t="n"/>
@@ -4359,10 +3881,7 @@
       <c r="J214" s="4" t="n"/>
     </row>
     <row r="215" ht="22" customHeight="1">
-      <c r="A215" s="3">
-        <f>IF(C215="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A215" s="3" t="n"/>
       <c r="B215" s="3" t="n"/>
       <c r="C215" s="3" t="n"/>
       <c r="D215" s="4" t="n"/>
@@ -4374,10 +3893,7 @@
       <c r="J215" s="4" t="n"/>
     </row>
     <row r="216" ht="22" customHeight="1">
-      <c r="A216" s="3">
-        <f>IF(C216="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A216" s="3" t="n"/>
       <c r="B216" s="3" t="n"/>
       <c r="C216" s="3" t="n"/>
       <c r="D216" s="4" t="n"/>
@@ -4389,10 +3905,7 @@
       <c r="J216" s="4" t="n"/>
     </row>
     <row r="217" ht="22" customHeight="1">
-      <c r="A217" s="3">
-        <f>IF(C217="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A217" s="3" t="n"/>
       <c r="B217" s="3" t="n"/>
       <c r="C217" s="3" t="n"/>
       <c r="D217" s="4" t="n"/>
@@ -4404,10 +3917,7 @@
       <c r="J217" s="4" t="n"/>
     </row>
     <row r="218" ht="22" customHeight="1">
-      <c r="A218" s="3">
-        <f>IF(C218="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A218" s="3" t="n"/>
       <c r="B218" s="3" t="n"/>
       <c r="C218" s="3" t="n"/>
       <c r="D218" s="4" t="n"/>
@@ -4419,10 +3929,7 @@
       <c r="J218" s="4" t="n"/>
     </row>
     <row r="219" ht="22" customHeight="1">
-      <c r="A219" s="3">
-        <f>IF(C219="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A219" s="3" t="n"/>
       <c r="B219" s="3" t="n"/>
       <c r="C219" s="3" t="n"/>
       <c r="D219" s="4" t="n"/>
@@ -4434,10 +3941,7 @@
       <c r="J219" s="4" t="n"/>
     </row>
     <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="3">
-        <f>IF(C220="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A220" s="3" t="n"/>
       <c r="B220" s="3" t="n"/>
       <c r="C220" s="3" t="n"/>
       <c r="D220" s="4" t="n"/>
@@ -4449,10 +3953,7 @@
       <c r="J220" s="4" t="n"/>
     </row>
     <row r="221" ht="22" customHeight="1">
-      <c r="A221" s="3">
-        <f>IF(C221="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A221" s="3" t="n"/>
       <c r="B221" s="3" t="n"/>
       <c r="C221" s="3" t="n"/>
       <c r="D221" s="4" t="n"/>
@@ -4464,10 +3965,7 @@
       <c r="J221" s="4" t="n"/>
     </row>
     <row r="222" ht="22" customHeight="1">
-      <c r="A222" s="3">
-        <f>IF(C222="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A222" s="3" t="n"/>
       <c r="B222" s="3" t="n"/>
       <c r="C222" s="3" t="n"/>
       <c r="D222" s="4" t="n"/>
@@ -4479,10 +3977,7 @@
       <c r="J222" s="4" t="n"/>
     </row>
     <row r="223" ht="22" customHeight="1">
-      <c r="A223" s="3">
-        <f>IF(C223="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A223" s="3" t="n"/>
       <c r="B223" s="3" t="n"/>
       <c r="C223" s="3" t="n"/>
       <c r="D223" s="4" t="n"/>
@@ -4494,10 +3989,7 @@
       <c r="J223" s="4" t="n"/>
     </row>
     <row r="224" ht="22" customHeight="1">
-      <c r="A224" s="3">
-        <f>IF(C224="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A224" s="3" t="n"/>
       <c r="B224" s="3" t="n"/>
       <c r="C224" s="3" t="n"/>
       <c r="D224" s="4" t="n"/>
@@ -4509,10 +4001,7 @@
       <c r="J224" s="4" t="n"/>
     </row>
     <row r="225" ht="22" customHeight="1">
-      <c r="A225" s="3">
-        <f>IF(C225="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A225" s="3" t="n"/>
       <c r="B225" s="3" t="n"/>
       <c r="C225" s="3" t="n"/>
       <c r="D225" s="4" t="n"/>
@@ -4524,10 +4013,7 @@
       <c r="J225" s="4" t="n"/>
     </row>
     <row r="226" ht="22" customHeight="1">
-      <c r="A226" s="3">
-        <f>IF(C226="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A226" s="3" t="n"/>
       <c r="B226" s="3" t="n"/>
       <c r="C226" s="3" t="n"/>
       <c r="D226" s="4" t="n"/>
@@ -4539,10 +4025,7 @@
       <c r="J226" s="4" t="n"/>
     </row>
     <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="3">
-        <f>IF(C227="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A227" s="3" t="n"/>
       <c r="B227" s="3" t="n"/>
       <c r="C227" s="3" t="n"/>
       <c r="D227" s="4" t="n"/>
@@ -4554,10 +4037,7 @@
       <c r="J227" s="4" t="n"/>
     </row>
     <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="3">
-        <f>IF(C228="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A228" s="3" t="n"/>
       <c r="B228" s="3" t="n"/>
       <c r="C228" s="3" t="n"/>
       <c r="D228" s="4" t="n"/>
@@ -4569,10 +4049,7 @@
       <c r="J228" s="4" t="n"/>
     </row>
     <row r="229" ht="22" customHeight="1">
-      <c r="A229" s="3">
-        <f>IF(C229="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A229" s="3" t="n"/>
       <c r="B229" s="3" t="n"/>
       <c r="C229" s="3" t="n"/>
       <c r="D229" s="4" t="n"/>
@@ -4584,10 +4061,7 @@
       <c r="J229" s="4" t="n"/>
     </row>
     <row r="230" ht="22" customHeight="1">
-      <c r="A230" s="3">
-        <f>IF(C230="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A230" s="3" t="n"/>
       <c r="B230" s="3" t="n"/>
       <c r="C230" s="3" t="n"/>
       <c r="D230" s="4" t="n"/>
@@ -4599,10 +4073,7 @@
       <c r="J230" s="4" t="n"/>
     </row>
     <row r="231" ht="22" customHeight="1">
-      <c r="A231" s="3">
-        <f>IF(C231="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A231" s="3" t="n"/>
       <c r="B231" s="3" t="n"/>
       <c r="C231" s="3" t="n"/>
       <c r="D231" s="4" t="n"/>
@@ -4614,10 +4085,7 @@
       <c r="J231" s="4" t="n"/>
     </row>
     <row r="232" ht="22" customHeight="1">
-      <c r="A232" s="3">
-        <f>IF(C232="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A232" s="3" t="n"/>
       <c r="B232" s="3" t="n"/>
       <c r="C232" s="3" t="n"/>
       <c r="D232" s="4" t="n"/>
@@ -4629,10 +4097,7 @@
       <c r="J232" s="4" t="n"/>
     </row>
     <row r="233" ht="22" customHeight="1">
-      <c r="A233" s="3">
-        <f>IF(C233="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A233" s="3" t="n"/>
       <c r="B233" s="3" t="n"/>
       <c r="C233" s="3" t="n"/>
       <c r="D233" s="4" t="n"/>
@@ -4644,10 +4109,7 @@
       <c r="J233" s="4" t="n"/>
     </row>
     <row r="234" ht="22" customHeight="1">
-      <c r="A234" s="3">
-        <f>IF(C234="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A234" s="3" t="n"/>
       <c r="B234" s="3" t="n"/>
       <c r="C234" s="3" t="n"/>
       <c r="D234" s="4" t="n"/>
@@ -4659,10 +4121,7 @@
       <c r="J234" s="4" t="n"/>
     </row>
     <row r="235" ht="22" customHeight="1">
-      <c r="A235" s="3">
-        <f>IF(C235="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A235" s="3" t="n"/>
       <c r="B235" s="3" t="n"/>
       <c r="C235" s="3" t="n"/>
       <c r="D235" s="4" t="n"/>
@@ -4674,10 +4133,7 @@
       <c r="J235" s="4" t="n"/>
     </row>
     <row r="236" ht="22" customHeight="1">
-      <c r="A236" s="3">
-        <f>IF(C236="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A236" s="3" t="n"/>
       <c r="B236" s="3" t="n"/>
       <c r="C236" s="3" t="n"/>
       <c r="D236" s="4" t="n"/>
@@ -4689,10 +4145,7 @@
       <c r="J236" s="4" t="n"/>
     </row>
     <row r="237" ht="22" customHeight="1">
-      <c r="A237" s="3">
-        <f>IF(C237="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A237" s="3" t="n"/>
       <c r="B237" s="3" t="n"/>
       <c r="C237" s="3" t="n"/>
       <c r="D237" s="4" t="n"/>
@@ -4704,10 +4157,7 @@
       <c r="J237" s="4" t="n"/>
     </row>
     <row r="238" ht="22" customHeight="1">
-      <c r="A238" s="3">
-        <f>IF(C238="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A238" s="3" t="n"/>
       <c r="B238" s="3" t="n"/>
       <c r="C238" s="3" t="n"/>
       <c r="D238" s="4" t="n"/>
@@ -4719,10 +4169,7 @@
       <c r="J238" s="4" t="n"/>
     </row>
     <row r="239" ht="22" customHeight="1">
-      <c r="A239" s="3">
-        <f>IF(C239="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A239" s="3" t="n"/>
       <c r="B239" s="3" t="n"/>
       <c r="C239" s="3" t="n"/>
       <c r="D239" s="4" t="n"/>
@@ -4734,10 +4181,7 @@
       <c r="J239" s="4" t="n"/>
     </row>
     <row r="240" ht="22" customHeight="1">
-      <c r="A240" s="3">
-        <f>IF(C240="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A240" s="3" t="n"/>
       <c r="B240" s="3" t="n"/>
       <c r="C240" s="3" t="n"/>
       <c r="D240" s="4" t="n"/>
@@ -4749,10 +4193,7 @@
       <c r="J240" s="4" t="n"/>
     </row>
     <row r="241" ht="22" customHeight="1">
-      <c r="A241" s="3">
-        <f>IF(C241="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A241" s="3" t="n"/>
       <c r="B241" s="3" t="n"/>
       <c r="C241" s="3" t="n"/>
       <c r="D241" s="4" t="n"/>
@@ -4764,10 +4205,7 @@
       <c r="J241" s="4" t="n"/>
     </row>
     <row r="242" ht="22" customHeight="1">
-      <c r="A242" s="3">
-        <f>IF(C242="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A242" s="3" t="n"/>
       <c r="B242" s="3" t="n"/>
       <c r="C242" s="3" t="n"/>
       <c r="D242" s="4" t="n"/>
@@ -4779,10 +4217,7 @@
       <c r="J242" s="4" t="n"/>
     </row>
     <row r="243" ht="22" customHeight="1">
-      <c r="A243" s="3">
-        <f>IF(C243="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A243" s="3" t="n"/>
       <c r="B243" s="3" t="n"/>
       <c r="C243" s="3" t="n"/>
       <c r="D243" s="4" t="n"/>
@@ -4794,10 +4229,7 @@
       <c r="J243" s="4" t="n"/>
     </row>
     <row r="244" ht="22" customHeight="1">
-      <c r="A244" s="3">
-        <f>IF(C244="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A244" s="3" t="n"/>
       <c r="B244" s="3" t="n"/>
       <c r="C244" s="3" t="n"/>
       <c r="D244" s="4" t="n"/>
@@ -4809,10 +4241,7 @@
       <c r="J244" s="4" t="n"/>
     </row>
     <row r="245" ht="22" customHeight="1">
-      <c r="A245" s="3">
-        <f>IF(C245="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A245" s="3" t="n"/>
       <c r="B245" s="3" t="n"/>
       <c r="C245" s="3" t="n"/>
       <c r="D245" s="4" t="n"/>
@@ -4824,10 +4253,7 @@
       <c r="J245" s="4" t="n"/>
     </row>
     <row r="246" ht="22" customHeight="1">
-      <c r="A246" s="3">
-        <f>IF(C246="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A246" s="3" t="n"/>
       <c r="B246" s="3" t="n"/>
       <c r="C246" s="3" t="n"/>
       <c r="D246" s="4" t="n"/>
@@ -4839,10 +4265,7 @@
       <c r="J246" s="4" t="n"/>
     </row>
     <row r="247" ht="22" customHeight="1">
-      <c r="A247" s="3">
-        <f>IF(C247="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A247" s="3" t="n"/>
       <c r="B247" s="3" t="n"/>
       <c r="C247" s="3" t="n"/>
       <c r="D247" s="4" t="n"/>
@@ -4854,10 +4277,7 @@
       <c r="J247" s="4" t="n"/>
     </row>
     <row r="248" ht="22" customHeight="1">
-      <c r="A248" s="3">
-        <f>IF(C248="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A248" s="3" t="n"/>
       <c r="B248" s="3" t="n"/>
       <c r="C248" s="3" t="n"/>
       <c r="D248" s="4" t="n"/>
@@ -4869,10 +4289,7 @@
       <c r="J248" s="4" t="n"/>
     </row>
     <row r="249" ht="22" customHeight="1">
-      <c r="A249" s="3">
-        <f>IF(C249="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A249" s="3" t="n"/>
       <c r="B249" s="3" t="n"/>
       <c r="C249" s="3" t="n"/>
       <c r="D249" s="4" t="n"/>
@@ -4884,10 +4301,7 @@
       <c r="J249" s="4" t="n"/>
     </row>
     <row r="250" ht="22" customHeight="1">
-      <c r="A250" s="3">
-        <f>IF(C250="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A250" s="3" t="n"/>
       <c r="B250" s="3" t="n"/>
       <c r="C250" s="3" t="n"/>
       <c r="D250" s="4" t="n"/>
@@ -4899,10 +4313,7 @@
       <c r="J250" s="4" t="n"/>
     </row>
     <row r="251" ht="22" customHeight="1">
-      <c r="A251" s="3">
-        <f>IF(C251="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A251" s="3" t="n"/>
       <c r="B251" s="3" t="n"/>
       <c r="C251" s="3" t="n"/>
       <c r="D251" s="4" t="n"/>
@@ -4914,10 +4325,7 @@
       <c r="J251" s="4" t="n"/>
     </row>
     <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="3">
-        <f>IF(C252="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A252" s="3" t="n"/>
       <c r="B252" s="3" t="n"/>
       <c r="C252" s="3" t="n"/>
       <c r="D252" s="4" t="n"/>
@@ -4929,10 +4337,7 @@
       <c r="J252" s="4" t="n"/>
     </row>
     <row r="253" ht="22" customHeight="1">
-      <c r="A253" s="3">
-        <f>IF(C253="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A253" s="3" t="n"/>
       <c r="B253" s="3" t="n"/>
       <c r="C253" s="3" t="n"/>
       <c r="D253" s="4" t="n"/>
@@ -4944,10 +4349,7 @@
       <c r="J253" s="4" t="n"/>
     </row>
     <row r="254" ht="22" customHeight="1">
-      <c r="A254" s="3">
-        <f>IF(C254="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A254" s="3" t="n"/>
       <c r="B254" s="3" t="n"/>
       <c r="C254" s="3" t="n"/>
       <c r="D254" s="4" t="n"/>
@@ -4959,10 +4361,7 @@
       <c r="J254" s="4" t="n"/>
     </row>
     <row r="255" ht="22" customHeight="1">
-      <c r="A255" s="3">
-        <f>IF(C255="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A255" s="3" t="n"/>
       <c r="B255" s="3" t="n"/>
       <c r="C255" s="3" t="n"/>
       <c r="D255" s="4" t="n"/>
@@ -4974,10 +4373,7 @@
       <c r="J255" s="4" t="n"/>
     </row>
     <row r="256" ht="22" customHeight="1">
-      <c r="A256" s="3">
-        <f>IF(C256="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A256" s="3" t="n"/>
       <c r="B256" s="3" t="n"/>
       <c r="C256" s="3" t="n"/>
       <c r="D256" s="4" t="n"/>
@@ -4989,10 +4385,7 @@
       <c r="J256" s="4" t="n"/>
     </row>
     <row r="257" ht="22" customHeight="1">
-      <c r="A257" s="3">
-        <f>IF(C257="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A257" s="3" t="n"/>
       <c r="B257" s="3" t="n"/>
       <c r="C257" s="3" t="n"/>
       <c r="D257" s="4" t="n"/>
@@ -5004,10 +4397,7 @@
       <c r="J257" s="4" t="n"/>
     </row>
     <row r="258" ht="22" customHeight="1">
-      <c r="A258" s="3">
-        <f>IF(C258="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A258" s="3" t="n"/>
       <c r="B258" s="3" t="n"/>
       <c r="C258" s="3" t="n"/>
       <c r="D258" s="4" t="n"/>
@@ -5019,10 +4409,7 @@
       <c r="J258" s="4" t="n"/>
     </row>
     <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="3">
-        <f>IF(C259="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A259" s="3" t="n"/>
       <c r="B259" s="3" t="n"/>
       <c r="C259" s="3" t="n"/>
       <c r="D259" s="4" t="n"/>
@@ -5034,10 +4421,7 @@
       <c r="J259" s="4" t="n"/>
     </row>
     <row r="260" ht="22" customHeight="1">
-      <c r="A260" s="3">
-        <f>IF(C260="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A260" s="3" t="n"/>
       <c r="B260" s="3" t="n"/>
       <c r="C260" s="3" t="n"/>
       <c r="D260" s="4" t="n"/>
@@ -5049,10 +4433,7 @@
       <c r="J260" s="4" t="n"/>
     </row>
     <row r="261" ht="22" customHeight="1">
-      <c r="A261" s="3">
-        <f>IF(C261="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A261" s="3" t="n"/>
       <c r="B261" s="3" t="n"/>
       <c r="C261" s="3" t="n"/>
       <c r="D261" s="4" t="n"/>
@@ -5064,10 +4445,7 @@
       <c r="J261" s="4" t="n"/>
     </row>
     <row r="262" ht="22" customHeight="1">
-      <c r="A262" s="3">
-        <f>IF(C262="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A262" s="3" t="n"/>
       <c r="B262" s="3" t="n"/>
       <c r="C262" s="3" t="n"/>
       <c r="D262" s="4" t="n"/>
@@ -5079,10 +4457,7 @@
       <c r="J262" s="4" t="n"/>
     </row>
     <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="3">
-        <f>IF(C263="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A263" s="3" t="n"/>
       <c r="B263" s="3" t="n"/>
       <c r="C263" s="3" t="n"/>
       <c r="D263" s="4" t="n"/>
@@ -5094,10 +4469,7 @@
       <c r="J263" s="4" t="n"/>
     </row>
     <row r="264" ht="22" customHeight="1">
-      <c r="A264" s="3">
-        <f>IF(C264="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A264" s="3" t="n"/>
       <c r="B264" s="3" t="n"/>
       <c r="C264" s="3" t="n"/>
       <c r="D264" s="4" t="n"/>
@@ -5109,10 +4481,7 @@
       <c r="J264" s="4" t="n"/>
     </row>
     <row r="265" ht="22" customHeight="1">
-      <c r="A265" s="3">
-        <f>IF(C265="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A265" s="3" t="n"/>
       <c r="B265" s="3" t="n"/>
       <c r="C265" s="3" t="n"/>
       <c r="D265" s="4" t="n"/>
@@ -5124,10 +4493,7 @@
       <c r="J265" s="4" t="n"/>
     </row>
     <row r="266" ht="22" customHeight="1">
-      <c r="A266" s="3">
-        <f>IF(C266="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A266" s="3" t="n"/>
       <c r="B266" s="3" t="n"/>
       <c r="C266" s="3" t="n"/>
       <c r="D266" s="4" t="n"/>
@@ -5139,10 +4505,7 @@
       <c r="J266" s="4" t="n"/>
     </row>
     <row r="267" ht="22" customHeight="1">
-      <c r="A267" s="3">
-        <f>IF(C267="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A267" s="3" t="n"/>
       <c r="B267" s="3" t="n"/>
       <c r="C267" s="3" t="n"/>
       <c r="D267" s="4" t="n"/>
@@ -5154,10 +4517,7 @@
       <c r="J267" s="4" t="n"/>
     </row>
     <row r="268" ht="22" customHeight="1">
-      <c r="A268" s="3">
-        <f>IF(C268="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A268" s="3" t="n"/>
       <c r="B268" s="3" t="n"/>
       <c r="C268" s="3" t="n"/>
       <c r="D268" s="4" t="n"/>
@@ -5169,10 +4529,7 @@
       <c r="J268" s="4" t="n"/>
     </row>
     <row r="269" ht="22" customHeight="1">
-      <c r="A269" s="3">
-        <f>IF(C269="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A269" s="3" t="n"/>
       <c r="B269" s="3" t="n"/>
       <c r="C269" s="3" t="n"/>
       <c r="D269" s="4" t="n"/>
@@ -5184,10 +4541,7 @@
       <c r="J269" s="4" t="n"/>
     </row>
     <row r="270" ht="22" customHeight="1">
-      <c r="A270" s="3">
-        <f>IF(C270="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A270" s="3" t="n"/>
       <c r="B270" s="3" t="n"/>
       <c r="C270" s="3" t="n"/>
       <c r="D270" s="4" t="n"/>
@@ -5199,10 +4553,7 @@
       <c r="J270" s="4" t="n"/>
     </row>
     <row r="271" ht="22" customHeight="1">
-      <c r="A271" s="3">
-        <f>IF(C271="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A271" s="3" t="n"/>
       <c r="B271" s="3" t="n"/>
       <c r="C271" s="3" t="n"/>
       <c r="D271" s="4" t="n"/>
@@ -5214,10 +4565,7 @@
       <c r="J271" s="4" t="n"/>
     </row>
     <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="3">
-        <f>IF(C272="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A272" s="3" t="n"/>
       <c r="B272" s="3" t="n"/>
       <c r="C272" s="3" t="n"/>
       <c r="D272" s="4" t="n"/>
@@ -5229,10 +4577,7 @@
       <c r="J272" s="4" t="n"/>
     </row>
     <row r="273" ht="22" customHeight="1">
-      <c r="A273" s="3">
-        <f>IF(C273="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A273" s="3" t="n"/>
       <c r="B273" s="3" t="n"/>
       <c r="C273" s="3" t="n"/>
       <c r="D273" s="4" t="n"/>
@@ -5244,10 +4589,7 @@
       <c r="J273" s="4" t="n"/>
     </row>
     <row r="274" ht="22" customHeight="1">
-      <c r="A274" s="3">
-        <f>IF(C274="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A274" s="3" t="n"/>
       <c r="B274" s="3" t="n"/>
       <c r="C274" s="3" t="n"/>
       <c r="D274" s="4" t="n"/>
@@ -5259,10 +4601,7 @@
       <c r="J274" s="4" t="n"/>
     </row>
     <row r="275" ht="22" customHeight="1">
-      <c r="A275" s="3">
-        <f>IF(C275="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A275" s="3" t="n"/>
       <c r="B275" s="3" t="n"/>
       <c r="C275" s="3" t="n"/>
       <c r="D275" s="4" t="n"/>
@@ -5274,10 +4613,7 @@
       <c r="J275" s="4" t="n"/>
     </row>
     <row r="276" ht="22" customHeight="1">
-      <c r="A276" s="3">
-        <f>IF(C276="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A276" s="3" t="n"/>
       <c r="B276" s="3" t="n"/>
       <c r="C276" s="3" t="n"/>
       <c r="D276" s="4" t="n"/>
@@ -5289,10 +4625,7 @@
       <c r="J276" s="4" t="n"/>
     </row>
     <row r="277" ht="22" customHeight="1">
-      <c r="A277" s="3">
-        <f>IF(C277="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A277" s="3" t="n"/>
       <c r="B277" s="3" t="n"/>
       <c r="C277" s="3" t="n"/>
       <c r="D277" s="4" t="n"/>
@@ -5304,10 +4637,7 @@
       <c r="J277" s="4" t="n"/>
     </row>
     <row r="278" ht="22" customHeight="1">
-      <c r="A278" s="3">
-        <f>IF(C278="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A278" s="3" t="n"/>
       <c r="B278" s="3" t="n"/>
       <c r="C278" s="3" t="n"/>
       <c r="D278" s="4" t="n"/>
@@ -5319,10 +4649,7 @@
       <c r="J278" s="4" t="n"/>
     </row>
     <row r="279" ht="22" customHeight="1">
-      <c r="A279" s="3">
-        <f>IF(C279="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A279" s="3" t="n"/>
       <c r="B279" s="3" t="n"/>
       <c r="C279" s="3" t="n"/>
       <c r="D279" s="4" t="n"/>
@@ -5334,10 +4661,7 @@
       <c r="J279" s="4" t="n"/>
     </row>
     <row r="280" ht="22" customHeight="1">
-      <c r="A280" s="3">
-        <f>IF(C280="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A280" s="3" t="n"/>
       <c r="B280" s="3" t="n"/>
       <c r="C280" s="3" t="n"/>
       <c r="D280" s="4" t="n"/>
@@ -5349,10 +4673,7 @@
       <c r="J280" s="4" t="n"/>
     </row>
     <row r="281" ht="22" customHeight="1">
-      <c r="A281" s="3">
-        <f>IF(C281="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A281" s="3" t="n"/>
       <c r="B281" s="3" t="n"/>
       <c r="C281" s="3" t="n"/>
       <c r="D281" s="4" t="n"/>
@@ -5364,10 +4685,7 @@
       <c r="J281" s="4" t="n"/>
     </row>
     <row r="282" ht="22" customHeight="1">
-      <c r="A282" s="3">
-        <f>IF(C282="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A282" s="3" t="n"/>
       <c r="B282" s="3" t="n"/>
       <c r="C282" s="3" t="n"/>
       <c r="D282" s="4" t="n"/>
@@ -5379,10 +4697,7 @@
       <c r="J282" s="4" t="n"/>
     </row>
     <row r="283" ht="22" customHeight="1">
-      <c r="A283" s="3">
-        <f>IF(C283="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A283" s="3" t="n"/>
       <c r="B283" s="3" t="n"/>
       <c r="C283" s="3" t="n"/>
       <c r="D283" s="4" t="n"/>
@@ -5394,10 +4709,7 @@
       <c r="J283" s="4" t="n"/>
     </row>
     <row r="284" ht="22" customHeight="1">
-      <c r="A284" s="3">
-        <f>IF(C284="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A284" s="3" t="n"/>
       <c r="B284" s="3" t="n"/>
       <c r="C284" s="3" t="n"/>
       <c r="D284" s="4" t="n"/>
@@ -5409,10 +4721,7 @@
       <c r="J284" s="4" t="n"/>
     </row>
     <row r="285" ht="22" customHeight="1">
-      <c r="A285" s="3">
-        <f>IF(C285="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A285" s="3" t="n"/>
       <c r="B285" s="3" t="n"/>
       <c r="C285" s="3" t="n"/>
       <c r="D285" s="4" t="n"/>
@@ -5424,10 +4733,7 @@
       <c r="J285" s="4" t="n"/>
     </row>
     <row r="286" ht="22" customHeight="1">
-      <c r="A286" s="3">
-        <f>IF(C286="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A286" s="3" t="n"/>
       <c r="B286" s="3" t="n"/>
       <c r="C286" s="3" t="n"/>
       <c r="D286" s="4" t="n"/>
@@ -5439,10 +4745,7 @@
       <c r="J286" s="4" t="n"/>
     </row>
     <row r="287" ht="22" customHeight="1">
-      <c r="A287" s="3">
-        <f>IF(C287="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A287" s="3" t="n"/>
       <c r="B287" s="3" t="n"/>
       <c r="C287" s="3" t="n"/>
       <c r="D287" s="4" t="n"/>
@@ -5454,10 +4757,7 @@
       <c r="J287" s="4" t="n"/>
     </row>
     <row r="288" ht="22" customHeight="1">
-      <c r="A288" s="3">
-        <f>IF(C288="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A288" s="3" t="n"/>
       <c r="B288" s="3" t="n"/>
       <c r="C288" s="3" t="n"/>
       <c r="D288" s="4" t="n"/>
@@ -5469,10 +4769,7 @@
       <c r="J288" s="4" t="n"/>
     </row>
     <row r="289" ht="22" customHeight="1">
-      <c r="A289" s="3">
-        <f>IF(C289="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A289" s="3" t="n"/>
       <c r="B289" s="3" t="n"/>
       <c r="C289" s="3" t="n"/>
       <c r="D289" s="4" t="n"/>
@@ -5484,10 +4781,7 @@
       <c r="J289" s="4" t="n"/>
     </row>
     <row r="290" ht="22" customHeight="1">
-      <c r="A290" s="3">
-        <f>IF(C290="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A290" s="3" t="n"/>
       <c r="B290" s="3" t="n"/>
       <c r="C290" s="3" t="n"/>
       <c r="D290" s="4" t="n"/>
@@ -5499,10 +4793,7 @@
       <c r="J290" s="4" t="n"/>
     </row>
     <row r="291" ht="22" customHeight="1">
-      <c r="A291" s="3">
-        <f>IF(C291="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A291" s="3" t="n"/>
       <c r="B291" s="3" t="n"/>
       <c r="C291" s="3" t="n"/>
       <c r="D291" s="4" t="n"/>
@@ -5514,10 +4805,7 @@
       <c r="J291" s="4" t="n"/>
     </row>
     <row r="292" ht="22" customHeight="1">
-      <c r="A292" s="3">
-        <f>IF(C292="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A292" s="3" t="n"/>
       <c r="B292" s="3" t="n"/>
       <c r="C292" s="3" t="n"/>
       <c r="D292" s="4" t="n"/>
@@ -5529,10 +4817,7 @@
       <c r="J292" s="4" t="n"/>
     </row>
     <row r="293" ht="22" customHeight="1">
-      <c r="A293" s="3">
-        <f>IF(C293="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A293" s="3" t="n"/>
       <c r="B293" s="3" t="n"/>
       <c r="C293" s="3" t="n"/>
       <c r="D293" s="4" t="n"/>
@@ -5544,10 +4829,7 @@
       <c r="J293" s="4" t="n"/>
     </row>
     <row r="294" ht="22" customHeight="1">
-      <c r="A294" s="3">
-        <f>IF(C294="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A294" s="3" t="n"/>
       <c r="B294" s="3" t="n"/>
       <c r="C294" s="3" t="n"/>
       <c r="D294" s="4" t="n"/>
@@ -5559,10 +4841,7 @@
       <c r="J294" s="4" t="n"/>
     </row>
     <row r="295" ht="22" customHeight="1">
-      <c r="A295" s="3">
-        <f>IF(C295="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A295" s="3" t="n"/>
       <c r="B295" s="3" t="n"/>
       <c r="C295" s="3" t="n"/>
       <c r="D295" s="4" t="n"/>
@@ -5574,10 +4853,7 @@
       <c r="J295" s="4" t="n"/>
     </row>
     <row r="296" ht="22" customHeight="1">
-      <c r="A296" s="3">
-        <f>IF(C296="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A296" s="3" t="n"/>
       <c r="B296" s="3" t="n"/>
       <c r="C296" s="3" t="n"/>
       <c r="D296" s="4" t="n"/>
@@ -5589,10 +4865,7 @@
       <c r="J296" s="4" t="n"/>
     </row>
     <row r="297" ht="22" customHeight="1">
-      <c r="A297" s="3">
-        <f>IF(C297="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A297" s="3" t="n"/>
       <c r="B297" s="3" t="n"/>
       <c r="C297" s="3" t="n"/>
       <c r="D297" s="4" t="n"/>
@@ -5604,10 +4877,7 @@
       <c r="J297" s="4" t="n"/>
     </row>
     <row r="298" ht="22" customHeight="1">
-      <c r="A298" s="3">
-        <f>IF(C298="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A298" s="3" t="n"/>
       <c r="B298" s="3" t="n"/>
       <c r="C298" s="3" t="n"/>
       <c r="D298" s="4" t="n"/>
@@ -5619,10 +4889,7 @@
       <c r="J298" s="4" t="n"/>
     </row>
     <row r="299" ht="22" customHeight="1">
-      <c r="A299" s="3">
-        <f>IF(C299="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A299" s="3" t="n"/>
       <c r="B299" s="3" t="n"/>
       <c r="C299" s="3" t="n"/>
       <c r="D299" s="4" t="n"/>
@@ -5634,10 +4901,7 @@
       <c r="J299" s="4" t="n"/>
     </row>
     <row r="300" ht="22" customHeight="1">
-      <c r="A300" s="3">
-        <f>IF(C300="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A300" s="3" t="n"/>
       <c r="B300" s="3" t="n"/>
       <c r="C300" s="3" t="n"/>
       <c r="D300" s="4" t="n"/>
@@ -5649,10 +4913,7 @@
       <c r="J300" s="4" t="n"/>
     </row>
     <row r="301" ht="22" customHeight="1">
-      <c r="A301" s="3">
-        <f>IF(C301="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A301" s="3" t="n"/>
       <c r="B301" s="3" t="n"/>
       <c r="C301" s="3" t="n"/>
       <c r="D301" s="4" t="n"/>
@@ -5664,10 +4925,7 @@
       <c r="J301" s="4" t="n"/>
     </row>
     <row r="302" ht="22" customHeight="1">
-      <c r="A302" s="3">
-        <f>IF(C302="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A302" s="3" t="n"/>
       <c r="B302" s="3" t="n"/>
       <c r="C302" s="3" t="n"/>
       <c r="D302" s="4" t="n"/>
@@ -5679,10 +4937,7 @@
       <c r="J302" s="4" t="n"/>
     </row>
     <row r="303" ht="22" customHeight="1">
-      <c r="A303" s="3">
-        <f>IF(C303="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A303" s="3" t="n"/>
       <c r="B303" s="3" t="n"/>
       <c r="C303" s="3" t="n"/>
       <c r="D303" s="4" t="n"/>
@@ -5694,10 +4949,7 @@
       <c r="J303" s="4" t="n"/>
     </row>
     <row r="304" ht="22" customHeight="1">
-      <c r="A304" s="3">
-        <f>IF(C304="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A304" s="3" t="n"/>
       <c r="B304" s="3" t="n"/>
       <c r="C304" s="3" t="n"/>
       <c r="D304" s="4" t="n"/>
@@ -5709,10 +4961,7 @@
       <c r="J304" s="4" t="n"/>
     </row>
     <row r="305" ht="22" customHeight="1">
-      <c r="A305" s="3">
-        <f>IF(C305="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A305" s="3" t="n"/>
       <c r="B305" s="3" t="n"/>
       <c r="C305" s="3" t="n"/>
       <c r="D305" s="4" t="n"/>
@@ -5724,10 +4973,7 @@
       <c r="J305" s="4" t="n"/>
     </row>
     <row r="306" ht="22" customHeight="1">
-      <c r="A306" s="3">
-        <f>IF(C306="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A306" s="3" t="n"/>
       <c r="B306" s="3" t="n"/>
       <c r="C306" s="3" t="n"/>
       <c r="D306" s="4" t="n"/>
@@ -5739,10 +4985,7 @@
       <c r="J306" s="4" t="n"/>
     </row>
     <row r="307" ht="22" customHeight="1">
-      <c r="A307" s="3">
-        <f>IF(C307="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A307" s="3" t="n"/>
       <c r="B307" s="3" t="n"/>
       <c r="C307" s="3" t="n"/>
       <c r="D307" s="4" t="n"/>
@@ -5754,10 +4997,7 @@
       <c r="J307" s="4" t="n"/>
     </row>
     <row r="308" ht="22" customHeight="1">
-      <c r="A308" s="3">
-        <f>IF(C308="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A308" s="3" t="n"/>
       <c r="B308" s="3" t="n"/>
       <c r="C308" s="3" t="n"/>
       <c r="D308" s="4" t="n"/>
@@ -5769,10 +5009,7 @@
       <c r="J308" s="4" t="n"/>
     </row>
     <row r="309" ht="22" customHeight="1">
-      <c r="A309" s="3">
-        <f>IF(C309="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A309" s="3" t="n"/>
       <c r="B309" s="3" t="n"/>
       <c r="C309" s="3" t="n"/>
       <c r="D309" s="4" t="n"/>
@@ -5784,10 +5021,7 @@
       <c r="J309" s="4" t="n"/>
     </row>
     <row r="310" ht="22" customHeight="1">
-      <c r="A310" s="3">
-        <f>IF(C310="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A310" s="3" t="n"/>
       <c r="B310" s="3" t="n"/>
       <c r="C310" s="3" t="n"/>
       <c r="D310" s="4" t="n"/>
@@ -5799,10 +5033,7 @@
       <c r="J310" s="4" t="n"/>
     </row>
     <row r="311" ht="22" customHeight="1">
-      <c r="A311" s="3">
-        <f>IF(C311="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A311" s="3" t="n"/>
       <c r="B311" s="3" t="n"/>
       <c r="C311" s="3" t="n"/>
       <c r="D311" s="4" t="n"/>
@@ -5814,10 +5045,7 @@
       <c r="J311" s="4" t="n"/>
     </row>
     <row r="312" ht="22" customHeight="1">
-      <c r="A312" s="3">
-        <f>IF(C312="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A312" s="3" t="n"/>
       <c r="B312" s="3" t="n"/>
       <c r="C312" s="3" t="n"/>
       <c r="D312" s="4" t="n"/>
@@ -5829,10 +5057,7 @@
       <c r="J312" s="4" t="n"/>
     </row>
     <row r="313" ht="22" customHeight="1">
-      <c r="A313" s="3">
-        <f>IF(C313="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A313" s="3" t="n"/>
       <c r="B313" s="3" t="n"/>
       <c r="C313" s="3" t="n"/>
       <c r="D313" s="4" t="n"/>
@@ -5844,10 +5069,7 @@
       <c r="J313" s="4" t="n"/>
     </row>
     <row r="314" ht="22" customHeight="1">
-      <c r="A314" s="3">
-        <f>IF(C314="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A314" s="3" t="n"/>
       <c r="B314" s="3" t="n"/>
       <c r="C314" s="3" t="n"/>
       <c r="D314" s="4" t="n"/>
@@ -5859,10 +5081,7 @@
       <c r="J314" s="4" t="n"/>
     </row>
     <row r="315" ht="22" customHeight="1">
-      <c r="A315" s="3">
-        <f>IF(C315="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A315" s="3" t="n"/>
       <c r="B315" s="3" t="n"/>
       <c r="C315" s="3" t="n"/>
       <c r="D315" s="4" t="n"/>
@@ -5874,10 +5093,7 @@
       <c r="J315" s="4" t="n"/>
     </row>
     <row r="316" ht="22" customHeight="1">
-      <c r="A316" s="3">
-        <f>IF(C316="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A316" s="3" t="n"/>
       <c r="B316" s="3" t="n"/>
       <c r="C316" s="3" t="n"/>
       <c r="D316" s="4" t="n"/>
@@ -5889,10 +5105,7 @@
       <c r="J316" s="4" t="n"/>
     </row>
     <row r="317" ht="22" customHeight="1">
-      <c r="A317" s="3">
-        <f>IF(C317="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A317" s="3" t="n"/>
       <c r="B317" s="3" t="n"/>
       <c r="C317" s="3" t="n"/>
       <c r="D317" s="4" t="n"/>
@@ -5904,10 +5117,7 @@
       <c r="J317" s="4" t="n"/>
     </row>
     <row r="318" ht="22" customHeight="1">
-      <c r="A318" s="3">
-        <f>IF(C318="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A318" s="3" t="n"/>
       <c r="B318" s="3" t="n"/>
       <c r="C318" s="3" t="n"/>
       <c r="D318" s="4" t="n"/>
@@ -5919,10 +5129,7 @@
       <c r="J318" s="4" t="n"/>
     </row>
     <row r="319" ht="22" customHeight="1">
-      <c r="A319" s="3">
-        <f>IF(C319="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A319" s="3" t="n"/>
       <c r="B319" s="3" t="n"/>
       <c r="C319" s="3" t="n"/>
       <c r="D319" s="4" t="n"/>
@@ -5934,10 +5141,7 @@
       <c r="J319" s="4" t="n"/>
     </row>
     <row r="320" ht="22" customHeight="1">
-      <c r="A320" s="3">
-        <f>IF(C320="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A320" s="3" t="n"/>
       <c r="B320" s="3" t="n"/>
       <c r="C320" s="3" t="n"/>
       <c r="D320" s="4" t="n"/>
@@ -5949,10 +5153,7 @@
       <c r="J320" s="4" t="n"/>
     </row>
     <row r="321" ht="22" customHeight="1">
-      <c r="A321" s="3">
-        <f>IF(C321="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A321" s="3" t="n"/>
       <c r="B321" s="3" t="n"/>
       <c r="C321" s="3" t="n"/>
       <c r="D321" s="4" t="n"/>
@@ -5964,10 +5165,7 @@
       <c r="J321" s="4" t="n"/>
     </row>
     <row r="322" ht="22" customHeight="1">
-      <c r="A322" s="3">
-        <f>IF(C322="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A322" s="3" t="n"/>
       <c r="B322" s="3" t="n"/>
       <c r="C322" s="3" t="n"/>
       <c r="D322" s="4" t="n"/>
@@ -5979,10 +5177,7 @@
       <c r="J322" s="4" t="n"/>
     </row>
     <row r="323" ht="22" customHeight="1">
-      <c r="A323" s="3">
-        <f>IF(C323="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A323" s="3" t="n"/>
       <c r="B323" s="3" t="n"/>
       <c r="C323" s="3" t="n"/>
       <c r="D323" s="4" t="n"/>
@@ -5994,10 +5189,7 @@
       <c r="J323" s="4" t="n"/>
     </row>
     <row r="324" ht="22" customHeight="1">
-      <c r="A324" s="3">
-        <f>IF(C324="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A324" s="3" t="n"/>
       <c r="B324" s="3" t="n"/>
       <c r="C324" s="3" t="n"/>
       <c r="D324" s="4" t="n"/>
@@ -6009,10 +5201,7 @@
       <c r="J324" s="4" t="n"/>
     </row>
     <row r="325" ht="22" customHeight="1">
-      <c r="A325" s="3">
-        <f>IF(C325="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A325" s="3" t="n"/>
       <c r="B325" s="3" t="n"/>
       <c r="C325" s="3" t="n"/>
       <c r="D325" s="4" t="n"/>
@@ -6024,10 +5213,7 @@
       <c r="J325" s="4" t="n"/>
     </row>
     <row r="326" ht="22" customHeight="1">
-      <c r="A326" s="3">
-        <f>IF(C326="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A326" s="3" t="n"/>
       <c r="B326" s="3" t="n"/>
       <c r="C326" s="3" t="n"/>
       <c r="D326" s="4" t="n"/>
@@ -6039,10 +5225,7 @@
       <c r="J326" s="4" t="n"/>
     </row>
     <row r="327" ht="22" customHeight="1">
-      <c r="A327" s="3">
-        <f>IF(C327="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A327" s="3" t="n"/>
       <c r="B327" s="3" t="n"/>
       <c r="C327" s="3" t="n"/>
       <c r="D327" s="4" t="n"/>
@@ -6054,10 +5237,7 @@
       <c r="J327" s="4" t="n"/>
     </row>
     <row r="328" ht="22" customHeight="1">
-      <c r="A328" s="3">
-        <f>IF(C328="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A328" s="3" t="n"/>
       <c r="B328" s="3" t="n"/>
       <c r="C328" s="3" t="n"/>
       <c r="D328" s="4" t="n"/>
@@ -6069,10 +5249,7 @@
       <c r="J328" s="4" t="n"/>
     </row>
     <row r="329" ht="22" customHeight="1">
-      <c r="A329" s="3">
-        <f>IF(C329="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A329" s="3" t="n"/>
       <c r="B329" s="3" t="n"/>
       <c r="C329" s="3" t="n"/>
       <c r="D329" s="4" t="n"/>
@@ -6084,10 +5261,7 @@
       <c r="J329" s="4" t="n"/>
     </row>
     <row r="330" ht="22" customHeight="1">
-      <c r="A330" s="3">
-        <f>IF(C330="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A330" s="3" t="n"/>
       <c r="B330" s="3" t="n"/>
       <c r="C330" s="3" t="n"/>
       <c r="D330" s="4" t="n"/>
@@ -6099,10 +5273,7 @@
       <c r="J330" s="4" t="n"/>
     </row>
     <row r="331" ht="22" customHeight="1">
-      <c r="A331" s="3">
-        <f>IF(C331="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A331" s="3" t="n"/>
       <c r="B331" s="3" t="n"/>
       <c r="C331" s="3" t="n"/>
       <c r="D331" s="4" t="n"/>
@@ -6114,10 +5285,7 @@
       <c r="J331" s="4" t="n"/>
     </row>
     <row r="332" ht="22" customHeight="1">
-      <c r="A332" s="3">
-        <f>IF(C332="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A332" s="3" t="n"/>
       <c r="B332" s="3" t="n"/>
       <c r="C332" s="3" t="n"/>
       <c r="D332" s="4" t="n"/>
@@ -6129,10 +5297,7 @@
       <c r="J332" s="4" t="n"/>
     </row>
     <row r="333" ht="22" customHeight="1">
-      <c r="A333" s="3">
-        <f>IF(C333="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A333" s="3" t="n"/>
       <c r="B333" s="3" t="n"/>
       <c r="C333" s="3" t="n"/>
       <c r="D333" s="4" t="n"/>
@@ -6144,10 +5309,7 @@
       <c r="J333" s="4" t="n"/>
     </row>
     <row r="334" ht="22" customHeight="1">
-      <c r="A334" s="3">
-        <f>IF(C334="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A334" s="3" t="n"/>
       <c r="B334" s="3" t="n"/>
       <c r="C334" s="3" t="n"/>
       <c r="D334" s="4" t="n"/>
@@ -6159,10 +5321,7 @@
       <c r="J334" s="4" t="n"/>
     </row>
     <row r="335" ht="22" customHeight="1">
-      <c r="A335" s="3">
-        <f>IF(C335="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A335" s="3" t="n"/>
       <c r="B335" s="3" t="n"/>
       <c r="C335" s="3" t="n"/>
       <c r="D335" s="4" t="n"/>
@@ -6174,10 +5333,7 @@
       <c r="J335" s="4" t="n"/>
     </row>
     <row r="336" ht="22" customHeight="1">
-      <c r="A336" s="3">
-        <f>IF(C336="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A336" s="3" t="n"/>
       <c r="B336" s="3" t="n"/>
       <c r="C336" s="3" t="n"/>
       <c r="D336" s="4" t="n"/>
@@ -6189,10 +5345,7 @@
       <c r="J336" s="4" t="n"/>
     </row>
     <row r="337" ht="22" customHeight="1">
-      <c r="A337" s="3">
-        <f>IF(C337="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A337" s="3" t="n"/>
       <c r="B337" s="3" t="n"/>
       <c r="C337" s="3" t="n"/>
       <c r="D337" s="4" t="n"/>
@@ -6204,10 +5357,7 @@
       <c r="J337" s="4" t="n"/>
     </row>
     <row r="338" ht="22" customHeight="1">
-      <c r="A338" s="3">
-        <f>IF(C338="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A338" s="3" t="n"/>
       <c r="B338" s="3" t="n"/>
       <c r="C338" s="3" t="n"/>
       <c r="D338" s="4" t="n"/>
@@ -6219,10 +5369,7 @@
       <c r="J338" s="4" t="n"/>
     </row>
     <row r="339" ht="22" customHeight="1">
-      <c r="A339" s="3">
-        <f>IF(C339="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A339" s="3" t="n"/>
       <c r="B339" s="3" t="n"/>
       <c r="C339" s="3" t="n"/>
       <c r="D339" s="4" t="n"/>
@@ -6234,10 +5381,7 @@
       <c r="J339" s="4" t="n"/>
     </row>
     <row r="340" ht="22" customHeight="1">
-      <c r="A340" s="3">
-        <f>IF(C340="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A340" s="3" t="n"/>
       <c r="B340" s="3" t="n"/>
       <c r="C340" s="3" t="n"/>
       <c r="D340" s="4" t="n"/>
@@ -6249,10 +5393,7 @@
       <c r="J340" s="4" t="n"/>
     </row>
     <row r="341" ht="22" customHeight="1">
-      <c r="A341" s="3">
-        <f>IF(C341="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A341" s="3" t="n"/>
       <c r="B341" s="3" t="n"/>
       <c r="C341" s="3" t="n"/>
       <c r="D341" s="4" t="n"/>
@@ -6264,10 +5405,7 @@
       <c r="J341" s="4" t="n"/>
     </row>
     <row r="342" ht="22" customHeight="1">
-      <c r="A342" s="3">
-        <f>IF(C342="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A342" s="3" t="n"/>
       <c r="B342" s="3" t="n"/>
       <c r="C342" s="3" t="n"/>
       <c r="D342" s="4" t="n"/>
@@ -6279,10 +5417,7 @@
       <c r="J342" s="4" t="n"/>
     </row>
     <row r="343" ht="22" customHeight="1">
-      <c r="A343" s="3">
-        <f>IF(C343="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A343" s="3" t="n"/>
       <c r="B343" s="3" t="n"/>
       <c r="C343" s="3" t="n"/>
       <c r="D343" s="4" t="n"/>
@@ -6294,10 +5429,7 @@
       <c r="J343" s="4" t="n"/>
     </row>
     <row r="344" ht="22" customHeight="1">
-      <c r="A344" s="3">
-        <f>IF(C344="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A344" s="3" t="n"/>
       <c r="B344" s="3" t="n"/>
       <c r="C344" s="3" t="n"/>
       <c r="D344" s="4" t="n"/>
@@ -6309,10 +5441,7 @@
       <c r="J344" s="4" t="n"/>
     </row>
     <row r="345" ht="22" customHeight="1">
-      <c r="A345" s="3">
-        <f>IF(C345="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A345" s="3" t="n"/>
       <c r="B345" s="3" t="n"/>
       <c r="C345" s="3" t="n"/>
       <c r="D345" s="4" t="n"/>
@@ -6324,10 +5453,7 @@
       <c r="J345" s="4" t="n"/>
     </row>
     <row r="346" ht="22" customHeight="1">
-      <c r="A346" s="3">
-        <f>IF(C346="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A346" s="3" t="n"/>
       <c r="B346" s="3" t="n"/>
       <c r="C346" s="3" t="n"/>
       <c r="D346" s="4" t="n"/>
@@ -6339,10 +5465,7 @@
       <c r="J346" s="4" t="n"/>
     </row>
     <row r="347" ht="22" customHeight="1">
-      <c r="A347" s="3">
-        <f>IF(C347="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A347" s="3" t="n"/>
       <c r="B347" s="3" t="n"/>
       <c r="C347" s="3" t="n"/>
       <c r="D347" s="4" t="n"/>
@@ -6354,10 +5477,7 @@
       <c r="J347" s="4" t="n"/>
     </row>
     <row r="348" ht="22" customHeight="1">
-      <c r="A348" s="3">
-        <f>IF(C348="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A348" s="3" t="n"/>
       <c r="B348" s="3" t="n"/>
       <c r="C348" s="3" t="n"/>
       <c r="D348" s="4" t="n"/>
@@ -6369,10 +5489,7 @@
       <c r="J348" s="4" t="n"/>
     </row>
     <row r="349" ht="22" customHeight="1">
-      <c r="A349" s="3">
-        <f>IF(C349="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A349" s="3" t="n"/>
       <c r="B349" s="3" t="n"/>
       <c r="C349" s="3" t="n"/>
       <c r="D349" s="4" t="n"/>
@@ -6384,10 +5501,7 @@
       <c r="J349" s="4" t="n"/>
     </row>
     <row r="350" ht="22" customHeight="1">
-      <c r="A350" s="3">
-        <f>IF(C350="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A350" s="3" t="n"/>
       <c r="B350" s="3" t="n"/>
       <c r="C350" s="3" t="n"/>
       <c r="D350" s="4" t="n"/>
@@ -6399,10 +5513,7 @@
       <c r="J350" s="4" t="n"/>
     </row>
     <row r="351" ht="22" customHeight="1">
-      <c r="A351" s="3">
-        <f>IF(C351="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A351" s="3" t="n"/>
       <c r="B351" s="3" t="n"/>
       <c r="C351" s="3" t="n"/>
       <c r="D351" s="4" t="n"/>
@@ -6414,10 +5525,7 @@
       <c r="J351" s="4" t="n"/>
     </row>
     <row r="352" ht="22" customHeight="1">
-      <c r="A352" s="3">
-        <f>IF(C352="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A352" s="3" t="n"/>
       <c r="B352" s="3" t="n"/>
       <c r="C352" s="3" t="n"/>
       <c r="D352" s="4" t="n"/>
@@ -6429,10 +5537,7 @@
       <c r="J352" s="4" t="n"/>
     </row>
     <row r="353" ht="22" customHeight="1">
-      <c r="A353" s="3">
-        <f>IF(C353="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A353" s="3" t="n"/>
       <c r="B353" s="3" t="n"/>
       <c r="C353" s="3" t="n"/>
       <c r="D353" s="4" t="n"/>
@@ -6444,10 +5549,7 @@
       <c r="J353" s="4" t="n"/>
     </row>
     <row r="354" ht="22" customHeight="1">
-      <c r="A354" s="3">
-        <f>IF(C354="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A354" s="3" t="n"/>
       <c r="B354" s="3" t="n"/>
       <c r="C354" s="3" t="n"/>
       <c r="D354" s="4" t="n"/>
@@ -6459,10 +5561,7 @@
       <c r="J354" s="4" t="n"/>
     </row>
     <row r="355" ht="22" customHeight="1">
-      <c r="A355" s="3">
-        <f>IF(C355="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A355" s="3" t="n"/>
       <c r="B355" s="3" t="n"/>
       <c r="C355" s="3" t="n"/>
       <c r="D355" s="4" t="n"/>
@@ -6474,10 +5573,7 @@
       <c r="J355" s="4" t="n"/>
     </row>
     <row r="356" ht="22" customHeight="1">
-      <c r="A356" s="3">
-        <f>IF(C356="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A356" s="3" t="n"/>
       <c r="B356" s="3" t="n"/>
       <c r="C356" s="3" t="n"/>
       <c r="D356" s="4" t="n"/>
@@ -6489,10 +5585,7 @@
       <c r="J356" s="4" t="n"/>
     </row>
     <row r="357" ht="22" customHeight="1">
-      <c r="A357" s="3">
-        <f>IF(C357="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A357" s="3" t="n"/>
       <c r="B357" s="3" t="n"/>
       <c r="C357" s="3" t="n"/>
       <c r="D357" s="4" t="n"/>
@@ -6504,10 +5597,7 @@
       <c r="J357" s="4" t="n"/>
     </row>
     <row r="358" ht="22" customHeight="1">
-      <c r="A358" s="3">
-        <f>IF(C358="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A358" s="3" t="n"/>
       <c r="B358" s="3" t="n"/>
       <c r="C358" s="3" t="n"/>
       <c r="D358" s="4" t="n"/>
@@ -6519,10 +5609,7 @@
       <c r="J358" s="4" t="n"/>
     </row>
     <row r="359" ht="22" customHeight="1">
-      <c r="A359" s="3">
-        <f>IF(C359="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A359" s="3" t="n"/>
       <c r="B359" s="3" t="n"/>
       <c r="C359" s="3" t="n"/>
       <c r="D359" s="4" t="n"/>
@@ -6534,10 +5621,7 @@
       <c r="J359" s="4" t="n"/>
     </row>
     <row r="360" ht="22" customHeight="1">
-      <c r="A360" s="3">
-        <f>IF(C360="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A360" s="3" t="n"/>
       <c r="B360" s="3" t="n"/>
       <c r="C360" s="3" t="n"/>
       <c r="D360" s="4" t="n"/>
@@ -6549,10 +5633,7 @@
       <c r="J360" s="4" t="n"/>
     </row>
     <row r="361" ht="22" customHeight="1">
-      <c r="A361" s="3">
-        <f>IF(C361="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A361" s="3" t="n"/>
       <c r="B361" s="3" t="n"/>
       <c r="C361" s="3" t="n"/>
       <c r="D361" s="4" t="n"/>
@@ -6564,10 +5645,7 @@
       <c r="J361" s="4" t="n"/>
     </row>
     <row r="362" ht="22" customHeight="1">
-      <c r="A362" s="3">
-        <f>IF(C362="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A362" s="3" t="n"/>
       <c r="B362" s="3" t="n"/>
       <c r="C362" s="3" t="n"/>
       <c r="D362" s="4" t="n"/>
@@ -6579,10 +5657,7 @@
       <c r="J362" s="4" t="n"/>
     </row>
     <row r="363" ht="22" customHeight="1">
-      <c r="A363" s="3">
-        <f>IF(C363="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A363" s="3" t="n"/>
       <c r="B363" s="3" t="n"/>
       <c r="C363" s="3" t="n"/>
       <c r="D363" s="4" t="n"/>
@@ -6594,10 +5669,7 @@
       <c r="J363" s="4" t="n"/>
     </row>
     <row r="364" ht="22" customHeight="1">
-      <c r="A364" s="3">
-        <f>IF(C364="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A364" s="3" t="n"/>
       <c r="B364" s="3" t="n"/>
       <c r="C364" s="3" t="n"/>
       <c r="D364" s="4" t="n"/>
@@ -6609,10 +5681,7 @@
       <c r="J364" s="4" t="n"/>
     </row>
     <row r="365" ht="22" customHeight="1">
-      <c r="A365" s="3">
-        <f>IF(C365="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A365" s="3" t="n"/>
       <c r="B365" s="3" t="n"/>
       <c r="C365" s="3" t="n"/>
       <c r="D365" s="4" t="n"/>
@@ -6624,10 +5693,7 @@
       <c r="J365" s="4" t="n"/>
     </row>
     <row r="366" ht="22" customHeight="1">
-      <c r="A366" s="3">
-        <f>IF(C366="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A366" s="3" t="n"/>
       <c r="B366" s="3" t="n"/>
       <c r="C366" s="3" t="n"/>
       <c r="D366" s="4" t="n"/>
@@ -6639,10 +5705,7 @@
       <c r="J366" s="4" t="n"/>
     </row>
     <row r="367" ht="22" customHeight="1">
-      <c r="A367" s="3">
-        <f>IF(C367="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A367" s="3" t="n"/>
       <c r="B367" s="3" t="n"/>
       <c r="C367" s="3" t="n"/>
       <c r="D367" s="4" t="n"/>
@@ -6654,10 +5717,7 @@
       <c r="J367" s="4" t="n"/>
     </row>
     <row r="368" ht="22" customHeight="1">
-      <c r="A368" s="3">
-        <f>IF(C368="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A368" s="3" t="n"/>
       <c r="B368" s="3" t="n"/>
       <c r="C368" s="3" t="n"/>
       <c r="D368" s="4" t="n"/>
@@ -6669,10 +5729,7 @@
       <c r="J368" s="4" t="n"/>
     </row>
     <row r="369" ht="22" customHeight="1">
-      <c r="A369" s="3">
-        <f>IF(C369="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A369" s="3" t="n"/>
       <c r="B369" s="3" t="n"/>
       <c r="C369" s="3" t="n"/>
       <c r="D369" s="4" t="n"/>
@@ -6684,10 +5741,7 @@
       <c r="J369" s="4" t="n"/>
     </row>
     <row r="370" ht="22" customHeight="1">
-      <c r="A370" s="3">
-        <f>IF(C370="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A370" s="3" t="n"/>
       <c r="B370" s="3" t="n"/>
       <c r="C370" s="3" t="n"/>
       <c r="D370" s="4" t="n"/>
@@ -6699,10 +5753,7 @@
       <c r="J370" s="4" t="n"/>
     </row>
     <row r="371" ht="22" customHeight="1">
-      <c r="A371" s="3">
-        <f>IF(C371="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A371" s="3" t="n"/>
       <c r="B371" s="3" t="n"/>
       <c r="C371" s="3" t="n"/>
       <c r="D371" s="4" t="n"/>
@@ -6714,10 +5765,7 @@
       <c r="J371" s="4" t="n"/>
     </row>
     <row r="372" ht="22" customHeight="1">
-      <c r="A372" s="3">
-        <f>IF(C372="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A372" s="3" t="n"/>
       <c r="B372" s="3" t="n"/>
       <c r="C372" s="3" t="n"/>
       <c r="D372" s="4" t="n"/>
@@ -6729,10 +5777,7 @@
       <c r="J372" s="4" t="n"/>
     </row>
     <row r="373" ht="22" customHeight="1">
-      <c r="A373" s="3">
-        <f>IF(C373="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A373" s="3" t="n"/>
       <c r="B373" s="3" t="n"/>
       <c r="C373" s="3" t="n"/>
       <c r="D373" s="4" t="n"/>
@@ -6744,10 +5789,7 @@
       <c r="J373" s="4" t="n"/>
     </row>
     <row r="374" ht="22" customHeight="1">
-      <c r="A374" s="3">
-        <f>IF(C374="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A374" s="3" t="n"/>
       <c r="B374" s="3" t="n"/>
       <c r="C374" s="3" t="n"/>
       <c r="D374" s="4" t="n"/>
@@ -6759,10 +5801,7 @@
       <c r="J374" s="4" t="n"/>
     </row>
     <row r="375" ht="22" customHeight="1">
-      <c r="A375" s="3">
-        <f>IF(C375="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A375" s="3" t="n"/>
       <c r="B375" s="3" t="n"/>
       <c r="C375" s="3" t="n"/>
       <c r="D375" s="4" t="n"/>
@@ -6774,10 +5813,7 @@
       <c r="J375" s="4" t="n"/>
     </row>
     <row r="376" ht="22" customHeight="1">
-      <c r="A376" s="3">
-        <f>IF(C376="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A376" s="3" t="n"/>
       <c r="B376" s="3" t="n"/>
       <c r="C376" s="3" t="n"/>
       <c r="D376" s="4" t="n"/>
@@ -6789,10 +5825,7 @@
       <c r="J376" s="4" t="n"/>
     </row>
     <row r="377" ht="22" customHeight="1">
-      <c r="A377" s="3">
-        <f>IF(C377="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A377" s="3" t="n"/>
       <c r="B377" s="3" t="n"/>
       <c r="C377" s="3" t="n"/>
       <c r="D377" s="4" t="n"/>
@@ -6804,10 +5837,7 @@
       <c r="J377" s="4" t="n"/>
     </row>
     <row r="378" ht="22" customHeight="1">
-      <c r="A378" s="3">
-        <f>IF(C378="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A378" s="3" t="n"/>
       <c r="B378" s="3" t="n"/>
       <c r="C378" s="3" t="n"/>
       <c r="D378" s="4" t="n"/>
@@ -6819,10 +5849,7 @@
       <c r="J378" s="4" t="n"/>
     </row>
     <row r="379" ht="22" customHeight="1">
-      <c r="A379" s="3">
-        <f>IF(C379="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A379" s="3" t="n"/>
       <c r="B379" s="3" t="n"/>
       <c r="C379" s="3" t="n"/>
       <c r="D379" s="4" t="n"/>
@@ -6834,10 +5861,7 @@
       <c r="J379" s="4" t="n"/>
     </row>
     <row r="380" ht="22" customHeight="1">
-      <c r="A380" s="3">
-        <f>IF(C380="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A380" s="3" t="n"/>
       <c r="B380" s="3" t="n"/>
       <c r="C380" s="3" t="n"/>
       <c r="D380" s="4" t="n"/>
@@ -6849,10 +5873,7 @@
       <c r="J380" s="4" t="n"/>
     </row>
     <row r="381" ht="22" customHeight="1">
-      <c r="A381" s="3">
-        <f>IF(C381="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A381" s="3" t="n"/>
       <c r="B381" s="3" t="n"/>
       <c r="C381" s="3" t="n"/>
       <c r="D381" s="4" t="n"/>
@@ -6864,10 +5885,7 @@
       <c r="J381" s="4" t="n"/>
     </row>
     <row r="382" ht="22" customHeight="1">
-      <c r="A382" s="3">
-        <f>IF(C382="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A382" s="3" t="n"/>
       <c r="B382" s="3" t="n"/>
       <c r="C382" s="3" t="n"/>
       <c r="D382" s="4" t="n"/>
@@ -6879,10 +5897,7 @@
       <c r="J382" s="4" t="n"/>
     </row>
     <row r="383" ht="22" customHeight="1">
-      <c r="A383" s="3">
-        <f>IF(C383="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A383" s="3" t="n"/>
       <c r="B383" s="3" t="n"/>
       <c r="C383" s="3" t="n"/>
       <c r="D383" s="4" t="n"/>
@@ -6894,10 +5909,7 @@
       <c r="J383" s="4" t="n"/>
     </row>
     <row r="384" ht="22" customHeight="1">
-      <c r="A384" s="3">
-        <f>IF(C384="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A384" s="3" t="n"/>
       <c r="B384" s="3" t="n"/>
       <c r="C384" s="3" t="n"/>
       <c r="D384" s="4" t="n"/>
@@ -6909,10 +5921,7 @@
       <c r="J384" s="4" t="n"/>
     </row>
     <row r="385" ht="22" customHeight="1">
-      <c r="A385" s="3">
-        <f>IF(C385="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A385" s="3" t="n"/>
       <c r="B385" s="3" t="n"/>
       <c r="C385" s="3" t="n"/>
       <c r="D385" s="4" t="n"/>
@@ -6924,10 +5933,7 @@
       <c r="J385" s="4" t="n"/>
     </row>
     <row r="386" ht="22" customHeight="1">
-      <c r="A386" s="3">
-        <f>IF(C386="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A386" s="3" t="n"/>
       <c r="B386" s="3" t="n"/>
       <c r="C386" s="3" t="n"/>
       <c r="D386" s="4" t="n"/>
@@ -6939,10 +5945,7 @@
       <c r="J386" s="4" t="n"/>
     </row>
     <row r="387" ht="22" customHeight="1">
-      <c r="A387" s="3">
-        <f>IF(C387="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A387" s="3" t="n"/>
       <c r="B387" s="3" t="n"/>
       <c r="C387" s="3" t="n"/>
       <c r="D387" s="4" t="n"/>
@@ -6954,10 +5957,7 @@
       <c r="J387" s="4" t="n"/>
     </row>
     <row r="388" ht="22" customHeight="1">
-      <c r="A388" s="3">
-        <f>IF(C388="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A388" s="3" t="n"/>
       <c r="B388" s="3" t="n"/>
       <c r="C388" s="3" t="n"/>
       <c r="D388" s="4" t="n"/>
@@ -6969,10 +5969,7 @@
       <c r="J388" s="4" t="n"/>
     </row>
     <row r="389" ht="22" customHeight="1">
-      <c r="A389" s="3">
-        <f>IF(C389="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A389" s="3" t="n"/>
       <c r="B389" s="3" t="n"/>
       <c r="C389" s="3" t="n"/>
       <c r="D389" s="4" t="n"/>
@@ -6984,10 +5981,7 @@
       <c r="J389" s="4" t="n"/>
     </row>
     <row r="390" ht="22" customHeight="1">
-      <c r="A390" s="3">
-        <f>IF(C390="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A390" s="3" t="n"/>
       <c r="B390" s="3" t="n"/>
       <c r="C390" s="3" t="n"/>
       <c r="D390" s="4" t="n"/>
@@ -6999,10 +5993,7 @@
       <c r="J390" s="4" t="n"/>
     </row>
     <row r="391" ht="22" customHeight="1">
-      <c r="A391" s="3">
-        <f>IF(C391="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A391" s="3" t="n"/>
       <c r="B391" s="3" t="n"/>
       <c r="C391" s="3" t="n"/>
       <c r="D391" s="4" t="n"/>
@@ -7014,10 +6005,7 @@
       <c r="J391" s="4" t="n"/>
     </row>
     <row r="392" ht="22" customHeight="1">
-      <c r="A392" s="3">
-        <f>IF(C392="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A392" s="3" t="n"/>
       <c r="B392" s="3" t="n"/>
       <c r="C392" s="3" t="n"/>
       <c r="D392" s="4" t="n"/>
@@ -7029,10 +6017,7 @@
       <c r="J392" s="4" t="n"/>
     </row>
     <row r="393" ht="22" customHeight="1">
-      <c r="A393" s="3">
-        <f>IF(C393="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A393" s="3" t="n"/>
       <c r="B393" s="3" t="n"/>
       <c r="C393" s="3" t="n"/>
       <c r="D393" s="4" t="n"/>
@@ -7044,10 +6029,7 @@
       <c r="J393" s="4" t="n"/>
     </row>
     <row r="394" ht="22" customHeight="1">
-      <c r="A394" s="3">
-        <f>IF(C394="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A394" s="3" t="n"/>
       <c r="B394" s="3" t="n"/>
       <c r="C394" s="3" t="n"/>
       <c r="D394" s="4" t="n"/>
@@ -7059,10 +6041,7 @@
       <c r="J394" s="4" t="n"/>
     </row>
     <row r="395" ht="22" customHeight="1">
-      <c r="A395" s="3">
-        <f>IF(C395="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A395" s="3" t="n"/>
       <c r="B395" s="3" t="n"/>
       <c r="C395" s="3" t="n"/>
       <c r="D395" s="4" t="n"/>
@@ -7074,10 +6053,7 @@
       <c r="J395" s="4" t="n"/>
     </row>
     <row r="396" ht="22" customHeight="1">
-      <c r="A396" s="3">
-        <f>IF(C396="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A396" s="3" t="n"/>
       <c r="B396" s="3" t="n"/>
       <c r="C396" s="3" t="n"/>
       <c r="D396" s="4" t="n"/>
@@ -7089,10 +6065,7 @@
       <c r="J396" s="4" t="n"/>
     </row>
     <row r="397" ht="22" customHeight="1">
-      <c r="A397" s="3">
-        <f>IF(C397="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A397" s="3" t="n"/>
       <c r="B397" s="3" t="n"/>
       <c r="C397" s="3" t="n"/>
       <c r="D397" s="4" t="n"/>
@@ -7104,10 +6077,7 @@
       <c r="J397" s="4" t="n"/>
     </row>
     <row r="398" ht="22" customHeight="1">
-      <c r="A398" s="3">
-        <f>IF(C398="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A398" s="3" t="n"/>
       <c r="B398" s="3" t="n"/>
       <c r="C398" s="3" t="n"/>
       <c r="D398" s="4" t="n"/>
@@ -7119,10 +6089,7 @@
       <c r="J398" s="4" t="n"/>
     </row>
     <row r="399" ht="22" customHeight="1">
-      <c r="A399" s="3">
-        <f>IF(C399="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A399" s="3" t="n"/>
       <c r="B399" s="3" t="n"/>
       <c r="C399" s="3" t="n"/>
       <c r="D399" s="4" t="n"/>
@@ -7134,10 +6101,7 @@
       <c r="J399" s="4" t="n"/>
     </row>
     <row r="400" ht="22" customHeight="1">
-      <c r="A400" s="3">
-        <f>IF(C400="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A400" s="3" t="n"/>
       <c r="B400" s="3" t="n"/>
       <c r="C400" s="3" t="n"/>
       <c r="D400" s="4" t="n"/>
@@ -7149,10 +6113,7 @@
       <c r="J400" s="4" t="n"/>
     </row>
     <row r="401" ht="22" customHeight="1">
-      <c r="A401" s="3">
-        <f>IF(C401="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A401" s="3" t="n"/>
       <c r="B401" s="3" t="n"/>
       <c r="C401" s="3" t="n"/>
       <c r="D401" s="4" t="n"/>
@@ -7164,10 +6125,7 @@
       <c r="J401" s="4" t="n"/>
     </row>
     <row r="402" ht="22" customHeight="1">
-      <c r="A402" s="3">
-        <f>IF(C402="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A402" s="3" t="n"/>
       <c r="B402" s="3" t="n"/>
       <c r="C402" s="3" t="n"/>
       <c r="D402" s="4" t="n"/>
@@ -7179,10 +6137,7 @@
       <c r="J402" s="4" t="n"/>
     </row>
     <row r="403" ht="22" customHeight="1">
-      <c r="A403" s="3">
-        <f>IF(C403="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A403" s="3" t="n"/>
       <c r="B403" s="3" t="n"/>
       <c r="C403" s="3" t="n"/>
       <c r="D403" s="4" t="n"/>
@@ -7194,10 +6149,7 @@
       <c r="J403" s="4" t="n"/>
     </row>
     <row r="404" ht="22" customHeight="1">
-      <c r="A404" s="3">
-        <f>IF(C404="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A404" s="3" t="n"/>
       <c r="B404" s="3" t="n"/>
       <c r="C404" s="3" t="n"/>
       <c r="D404" s="4" t="n"/>
@@ -7209,10 +6161,7 @@
       <c r="J404" s="4" t="n"/>
     </row>
     <row r="405" ht="22" customHeight="1">
-      <c r="A405" s="3">
-        <f>IF(C405="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A405" s="3" t="n"/>
       <c r="B405" s="3" t="n"/>
       <c r="C405" s="3" t="n"/>
       <c r="D405" s="4" t="n"/>
@@ -7224,10 +6173,7 @@
       <c r="J405" s="4" t="n"/>
     </row>
     <row r="406" ht="22" customHeight="1">
-      <c r="A406" s="3">
-        <f>IF(C406="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A406" s="3" t="n"/>
       <c r="B406" s="3" t="n"/>
       <c r="C406" s="3" t="n"/>
       <c r="D406" s="4" t="n"/>
@@ -7239,10 +6185,7 @@
       <c r="J406" s="4" t="n"/>
     </row>
     <row r="407" ht="22" customHeight="1">
-      <c r="A407" s="3">
-        <f>IF(C407="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A407" s="3" t="n"/>
       <c r="B407" s="3" t="n"/>
       <c r="C407" s="3" t="n"/>
       <c r="D407" s="4" t="n"/>
@@ -7254,10 +6197,7 @@
       <c r="J407" s="4" t="n"/>
     </row>
     <row r="408" ht="22" customHeight="1">
-      <c r="A408" s="3">
-        <f>IF(C408="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A408" s="3" t="n"/>
       <c r="B408" s="3" t="n"/>
       <c r="C408" s="3" t="n"/>
       <c r="D408" s="4" t="n"/>
@@ -7269,10 +6209,7 @@
       <c r="J408" s="4" t="n"/>
     </row>
     <row r="409" ht="22" customHeight="1">
-      <c r="A409" s="3">
-        <f>IF(C409="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A409" s="3" t="n"/>
       <c r="B409" s="3" t="n"/>
       <c r="C409" s="3" t="n"/>
       <c r="D409" s="4" t="n"/>
@@ -7284,10 +6221,7 @@
       <c r="J409" s="4" t="n"/>
     </row>
     <row r="410" ht="22" customHeight="1">
-      <c r="A410" s="3">
-        <f>IF(C410="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A410" s="3" t="n"/>
       <c r="B410" s="3" t="n"/>
       <c r="C410" s="3" t="n"/>
       <c r="D410" s="4" t="n"/>
@@ -7299,10 +6233,7 @@
       <c r="J410" s="4" t="n"/>
     </row>
     <row r="411" ht="22" customHeight="1">
-      <c r="A411" s="3">
-        <f>IF(C411="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A411" s="3" t="n"/>
       <c r="B411" s="3" t="n"/>
       <c r="C411" s="3" t="n"/>
       <c r="D411" s="4" t="n"/>
@@ -7314,10 +6245,7 @@
       <c r="J411" s="4" t="n"/>
     </row>
     <row r="412" ht="22" customHeight="1">
-      <c r="A412" s="3">
-        <f>IF(C412="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A412" s="3" t="n"/>
       <c r="B412" s="3" t="n"/>
       <c r="C412" s="3" t="n"/>
       <c r="D412" s="4" t="n"/>
@@ -7329,10 +6257,7 @@
       <c r="J412" s="4" t="n"/>
     </row>
     <row r="413" ht="22" customHeight="1">
-      <c r="A413" s="3">
-        <f>IF(C413="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A413" s="3" t="n"/>
       <c r="B413" s="3" t="n"/>
       <c r="C413" s="3" t="n"/>
       <c r="D413" s="4" t="n"/>
@@ -7344,10 +6269,7 @@
       <c r="J413" s="4" t="n"/>
     </row>
     <row r="414" ht="22" customHeight="1">
-      <c r="A414" s="3">
-        <f>IF(C414="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A414" s="3" t="n"/>
       <c r="B414" s="3" t="n"/>
       <c r="C414" s="3" t="n"/>
       <c r="D414" s="4" t="n"/>
@@ -7359,10 +6281,7 @@
       <c r="J414" s="4" t="n"/>
     </row>
     <row r="415" ht="22" customHeight="1">
-      <c r="A415" s="3">
-        <f>IF(C415="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A415" s="3" t="n"/>
       <c r="B415" s="3" t="n"/>
       <c r="C415" s="3" t="n"/>
       <c r="D415" s="4" t="n"/>
@@ -7374,10 +6293,7 @@
       <c r="J415" s="4" t="n"/>
     </row>
     <row r="416" ht="22" customHeight="1">
-      <c r="A416" s="3">
-        <f>IF(C416="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A416" s="3" t="n"/>
       <c r="B416" s="3" t="n"/>
       <c r="C416" s="3" t="n"/>
       <c r="D416" s="4" t="n"/>
@@ -7389,10 +6305,7 @@
       <c r="J416" s="4" t="n"/>
     </row>
     <row r="417" ht="22" customHeight="1">
-      <c r="A417" s="3">
-        <f>IF(C417="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A417" s="3" t="n"/>
       <c r="B417" s="3" t="n"/>
       <c r="C417" s="3" t="n"/>
       <c r="D417" s="4" t="n"/>
@@ -7404,10 +6317,7 @@
       <c r="J417" s="4" t="n"/>
     </row>
     <row r="418" ht="22" customHeight="1">
-      <c r="A418" s="3">
-        <f>IF(C418="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A418" s="3" t="n"/>
       <c r="B418" s="3" t="n"/>
       <c r="C418" s="3" t="n"/>
       <c r="D418" s="4" t="n"/>
@@ -7419,10 +6329,7 @@
       <c r="J418" s="4" t="n"/>
     </row>
     <row r="419" ht="22" customHeight="1">
-      <c r="A419" s="3">
-        <f>IF(C419="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A419" s="3" t="n"/>
       <c r="B419" s="3" t="n"/>
       <c r="C419" s="3" t="n"/>
       <c r="D419" s="4" t="n"/>
@@ -7434,10 +6341,7 @@
       <c r="J419" s="4" t="n"/>
     </row>
     <row r="420" ht="22" customHeight="1">
-      <c r="A420" s="3">
-        <f>IF(C420="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A420" s="3" t="n"/>
       <c r="B420" s="3" t="n"/>
       <c r="C420" s="3" t="n"/>
       <c r="D420" s="4" t="n"/>
@@ -7449,10 +6353,7 @@
       <c r="J420" s="4" t="n"/>
     </row>
     <row r="421" ht="22" customHeight="1">
-      <c r="A421" s="3">
-        <f>IF(C421="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A421" s="3" t="n"/>
       <c r="B421" s="3" t="n"/>
       <c r="C421" s="3" t="n"/>
       <c r="D421" s="4" t="n"/>
@@ -7464,10 +6365,7 @@
       <c r="J421" s="4" t="n"/>
     </row>
     <row r="422" ht="22" customHeight="1">
-      <c r="A422" s="3">
-        <f>IF(C422="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A422" s="3" t="n"/>
       <c r="B422" s="3" t="n"/>
       <c r="C422" s="3" t="n"/>
       <c r="D422" s="4" t="n"/>
@@ -7479,10 +6377,7 @@
       <c r="J422" s="4" t="n"/>
     </row>
     <row r="423" ht="22" customHeight="1">
-      <c r="A423" s="3">
-        <f>IF(C423="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A423" s="3" t="n"/>
       <c r="B423" s="3" t="n"/>
       <c r="C423" s="3" t="n"/>
       <c r="D423" s="4" t="n"/>
@@ -7494,10 +6389,7 @@
       <c r="J423" s="4" t="n"/>
     </row>
     <row r="424" ht="22" customHeight="1">
-      <c r="A424" s="3">
-        <f>IF(C424="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A424" s="3" t="n"/>
       <c r="B424" s="3" t="n"/>
       <c r="C424" s="3" t="n"/>
       <c r="D424" s="4" t="n"/>
@@ -7509,10 +6401,7 @@
       <c r="J424" s="4" t="n"/>
     </row>
     <row r="425" ht="22" customHeight="1">
-      <c r="A425" s="3">
-        <f>IF(C425="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A425" s="3" t="n"/>
       <c r="B425" s="3" t="n"/>
       <c r="C425" s="3" t="n"/>
       <c r="D425" s="4" t="n"/>
@@ -7524,10 +6413,7 @@
       <c r="J425" s="4" t="n"/>
     </row>
     <row r="426" ht="22" customHeight="1">
-      <c r="A426" s="3">
-        <f>IF(C426="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A426" s="3" t="n"/>
       <c r="B426" s="3" t="n"/>
       <c r="C426" s="3" t="n"/>
       <c r="D426" s="4" t="n"/>
@@ -7539,10 +6425,7 @@
       <c r="J426" s="4" t="n"/>
     </row>
     <row r="427" ht="22" customHeight="1">
-      <c r="A427" s="3">
-        <f>IF(C427="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A427" s="3" t="n"/>
       <c r="B427" s="3" t="n"/>
       <c r="C427" s="3" t="n"/>
       <c r="D427" s="4" t="n"/>
@@ -7554,10 +6437,7 @@
       <c r="J427" s="4" t="n"/>
     </row>
     <row r="428" ht="22" customHeight="1">
-      <c r="A428" s="3">
-        <f>IF(C428="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A428" s="3" t="n"/>
       <c r="B428" s="3" t="n"/>
       <c r="C428" s="3" t="n"/>
       <c r="D428" s="4" t="n"/>
@@ -7569,10 +6449,7 @@
       <c r="J428" s="4" t="n"/>
     </row>
     <row r="429" ht="22" customHeight="1">
-      <c r="A429" s="3">
-        <f>IF(C429="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A429" s="3" t="n"/>
       <c r="B429" s="3" t="n"/>
       <c r="C429" s="3" t="n"/>
       <c r="D429" s="4" t="n"/>
@@ -7584,10 +6461,7 @@
       <c r="J429" s="4" t="n"/>
     </row>
     <row r="430" ht="22" customHeight="1">
-      <c r="A430" s="3">
-        <f>IF(C430="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A430" s="3" t="n"/>
       <c r="B430" s="3" t="n"/>
       <c r="C430" s="3" t="n"/>
       <c r="D430" s="4" t="n"/>
@@ -7599,10 +6473,7 @@
       <c r="J430" s="4" t="n"/>
     </row>
     <row r="431" ht="22" customHeight="1">
-      <c r="A431" s="3">
-        <f>IF(C431="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A431" s="3" t="n"/>
       <c r="B431" s="3" t="n"/>
       <c r="C431" s="3" t="n"/>
       <c r="D431" s="4" t="n"/>
@@ -7614,10 +6485,7 @@
       <c r="J431" s="4" t="n"/>
     </row>
     <row r="432" ht="22" customHeight="1">
-      <c r="A432" s="3">
-        <f>IF(C432="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A432" s="3" t="n"/>
       <c r="B432" s="3" t="n"/>
       <c r="C432" s="3" t="n"/>
       <c r="D432" s="4" t="n"/>
@@ -7629,10 +6497,7 @@
       <c r="J432" s="4" t="n"/>
     </row>
     <row r="433" ht="22" customHeight="1">
-      <c r="A433" s="3">
-        <f>IF(C433="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A433" s="3" t="n"/>
       <c r="B433" s="3" t="n"/>
       <c r="C433" s="3" t="n"/>
       <c r="D433" s="4" t="n"/>
@@ -7644,10 +6509,7 @@
       <c r="J433" s="4" t="n"/>
     </row>
     <row r="434" ht="22" customHeight="1">
-      <c r="A434" s="3">
-        <f>IF(C434="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A434" s="3" t="n"/>
       <c r="B434" s="3" t="n"/>
       <c r="C434" s="3" t="n"/>
       <c r="D434" s="4" t="n"/>
@@ -7659,10 +6521,7 @@
       <c r="J434" s="4" t="n"/>
     </row>
     <row r="435" ht="22" customHeight="1">
-      <c r="A435" s="3">
-        <f>IF(C435="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A435" s="3" t="n"/>
       <c r="B435" s="3" t="n"/>
       <c r="C435" s="3" t="n"/>
       <c r="D435" s="4" t="n"/>
@@ -7674,10 +6533,7 @@
       <c r="J435" s="4" t="n"/>
     </row>
     <row r="436" ht="22" customHeight="1">
-      <c r="A436" s="3">
-        <f>IF(C436="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A436" s="3" t="n"/>
       <c r="B436" s="3" t="n"/>
       <c r="C436" s="3" t="n"/>
       <c r="D436" s="4" t="n"/>
@@ -7689,10 +6545,7 @@
       <c r="J436" s="4" t="n"/>
     </row>
     <row r="437" ht="22" customHeight="1">
-      <c r="A437" s="3">
-        <f>IF(C437="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A437" s="3" t="n"/>
       <c r="B437" s="3" t="n"/>
       <c r="C437" s="3" t="n"/>
       <c r="D437" s="4" t="n"/>
@@ -7704,10 +6557,7 @@
       <c r="J437" s="4" t="n"/>
     </row>
     <row r="438" ht="22" customHeight="1">
-      <c r="A438" s="3">
-        <f>IF(C438="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A438" s="3" t="n"/>
       <c r="B438" s="3" t="n"/>
       <c r="C438" s="3" t="n"/>
       <c r="D438" s="4" t="n"/>
@@ -7719,10 +6569,7 @@
       <c r="J438" s="4" t="n"/>
     </row>
     <row r="439" ht="22" customHeight="1">
-      <c r="A439" s="3">
-        <f>IF(C439="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A439" s="3" t="n"/>
       <c r="B439" s="3" t="n"/>
       <c r="C439" s="3" t="n"/>
       <c r="D439" s="4" t="n"/>
@@ -7734,10 +6581,7 @@
       <c r="J439" s="4" t="n"/>
     </row>
     <row r="440" ht="22" customHeight="1">
-      <c r="A440" s="3">
-        <f>IF(C440="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A440" s="3" t="n"/>
       <c r="B440" s="3" t="n"/>
       <c r="C440" s="3" t="n"/>
       <c r="D440" s="4" t="n"/>
@@ -7749,10 +6593,7 @@
       <c r="J440" s="4" t="n"/>
     </row>
     <row r="441" ht="22" customHeight="1">
-      <c r="A441" s="3">
-        <f>IF(C441="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A441" s="3" t="n"/>
       <c r="B441" s="3" t="n"/>
       <c r="C441" s="3" t="n"/>
       <c r="D441" s="4" t="n"/>
@@ -7764,10 +6605,7 @@
       <c r="J441" s="4" t="n"/>
     </row>
     <row r="442" ht="22" customHeight="1">
-      <c r="A442" s="3">
-        <f>IF(C442="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A442" s="3" t="n"/>
       <c r="B442" s="3" t="n"/>
       <c r="C442" s="3" t="n"/>
       <c r="D442" s="4" t="n"/>
@@ -7779,10 +6617,7 @@
       <c r="J442" s="4" t="n"/>
     </row>
     <row r="443" ht="22" customHeight="1">
-      <c r="A443" s="3">
-        <f>IF(C443="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A443" s="3" t="n"/>
       <c r="B443" s="3" t="n"/>
       <c r="C443" s="3" t="n"/>
       <c r="D443" s="4" t="n"/>
@@ -7794,10 +6629,7 @@
       <c r="J443" s="4" t="n"/>
     </row>
     <row r="444" ht="22" customHeight="1">
-      <c r="A444" s="3">
-        <f>IF(C444="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A444" s="3" t="n"/>
       <c r="B444" s="3" t="n"/>
       <c r="C444" s="3" t="n"/>
       <c r="D444" s="4" t="n"/>
@@ -7809,10 +6641,7 @@
       <c r="J444" s="4" t="n"/>
     </row>
     <row r="445" ht="22" customHeight="1">
-      <c r="A445" s="3">
-        <f>IF(C445="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A445" s="3" t="n"/>
       <c r="B445" s="3" t="n"/>
       <c r="C445" s="3" t="n"/>
       <c r="D445" s="4" t="n"/>
@@ -7824,10 +6653,7 @@
       <c r="J445" s="4" t="n"/>
     </row>
     <row r="446" ht="22" customHeight="1">
-      <c r="A446" s="3">
-        <f>IF(C446="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A446" s="3" t="n"/>
       <c r="B446" s="3" t="n"/>
       <c r="C446" s="3" t="n"/>
       <c r="D446" s="4" t="n"/>
@@ -7839,10 +6665,7 @@
       <c r="J446" s="4" t="n"/>
     </row>
     <row r="447" ht="22" customHeight="1">
-      <c r="A447" s="3">
-        <f>IF(C447="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A447" s="3" t="n"/>
       <c r="B447" s="3" t="n"/>
       <c r="C447" s="3" t="n"/>
       <c r="D447" s="4" t="n"/>
@@ -7854,10 +6677,7 @@
       <c r="J447" s="4" t="n"/>
     </row>
     <row r="448" ht="22" customHeight="1">
-      <c r="A448" s="3">
-        <f>IF(C448="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A448" s="3" t="n"/>
       <c r="B448" s="3" t="n"/>
       <c r="C448" s="3" t="n"/>
       <c r="D448" s="4" t="n"/>
@@ -7869,10 +6689,7 @@
       <c r="J448" s="4" t="n"/>
     </row>
     <row r="449" ht="22" customHeight="1">
-      <c r="A449" s="3">
-        <f>IF(C449="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A449" s="3" t="n"/>
       <c r="B449" s="3" t="n"/>
       <c r="C449" s="3" t="n"/>
       <c r="D449" s="4" t="n"/>
@@ -7884,10 +6701,7 @@
       <c r="J449" s="4" t="n"/>
     </row>
     <row r="450" ht="22" customHeight="1">
-      <c r="A450" s="3">
-        <f>IF(C450="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A450" s="3" t="n"/>
       <c r="B450" s="3" t="n"/>
       <c r="C450" s="3" t="n"/>
       <c r="D450" s="4" t="n"/>
@@ -7899,10 +6713,7 @@
       <c r="J450" s="4" t="n"/>
     </row>
     <row r="451" ht="22" customHeight="1">
-      <c r="A451" s="3">
-        <f>IF(C451="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A451" s="3" t="n"/>
       <c r="B451" s="3" t="n"/>
       <c r="C451" s="3" t="n"/>
       <c r="D451" s="4" t="n"/>
@@ -7914,10 +6725,7 @@
       <c r="J451" s="4" t="n"/>
     </row>
     <row r="452" ht="22" customHeight="1">
-      <c r="A452" s="3">
-        <f>IF(C452="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A452" s="3" t="n"/>
       <c r="B452" s="3" t="n"/>
       <c r="C452" s="3" t="n"/>
       <c r="D452" s="4" t="n"/>
@@ -7929,10 +6737,7 @@
       <c r="J452" s="4" t="n"/>
     </row>
     <row r="453" ht="22" customHeight="1">
-      <c r="A453" s="3">
-        <f>IF(C453="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A453" s="3" t="n"/>
       <c r="B453" s="3" t="n"/>
       <c r="C453" s="3" t="n"/>
       <c r="D453" s="4" t="n"/>
@@ -7944,10 +6749,7 @@
       <c r="J453" s="4" t="n"/>
     </row>
     <row r="454" ht="22" customHeight="1">
-      <c r="A454" s="3">
-        <f>IF(C454="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A454" s="3" t="n"/>
       <c r="B454" s="3" t="n"/>
       <c r="C454" s="3" t="n"/>
       <c r="D454" s="4" t="n"/>
@@ -7959,10 +6761,7 @@
       <c r="J454" s="4" t="n"/>
     </row>
     <row r="455" ht="22" customHeight="1">
-      <c r="A455" s="3">
-        <f>IF(C455="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A455" s="3" t="n"/>
       <c r="B455" s="3" t="n"/>
       <c r="C455" s="3" t="n"/>
       <c r="D455" s="4" t="n"/>
@@ -7974,10 +6773,7 @@
       <c r="J455" s="4" t="n"/>
     </row>
     <row r="456" ht="22" customHeight="1">
-      <c r="A456" s="3">
-        <f>IF(C456="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A456" s="3" t="n"/>
       <c r="B456" s="3" t="n"/>
       <c r="C456" s="3" t="n"/>
       <c r="D456" s="4" t="n"/>
@@ -7989,10 +6785,7 @@
       <c r="J456" s="4" t="n"/>
     </row>
     <row r="457" ht="22" customHeight="1">
-      <c r="A457" s="3">
-        <f>IF(C457="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A457" s="3" t="n"/>
       <c r="B457" s="3" t="n"/>
       <c r="C457" s="3" t="n"/>
       <c r="D457" s="4" t="n"/>
@@ -8004,10 +6797,7 @@
       <c r="J457" s="4" t="n"/>
     </row>
     <row r="458" ht="22" customHeight="1">
-      <c r="A458" s="3">
-        <f>IF(C458="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A458" s="3" t="n"/>
       <c r="B458" s="3" t="n"/>
       <c r="C458" s="3" t="n"/>
       <c r="D458" s="4" t="n"/>
@@ -8019,10 +6809,7 @@
       <c r="J458" s="4" t="n"/>
     </row>
     <row r="459" ht="22" customHeight="1">
-      <c r="A459" s="3">
-        <f>IF(C459="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A459" s="3" t="n"/>
       <c r="B459" s="3" t="n"/>
       <c r="C459" s="3" t="n"/>
       <c r="D459" s="4" t="n"/>
@@ -8034,10 +6821,7 @@
       <c r="J459" s="4" t="n"/>
     </row>
     <row r="460" ht="22" customHeight="1">
-      <c r="A460" s="3">
-        <f>IF(C460="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A460" s="3" t="n"/>
       <c r="B460" s="3" t="n"/>
       <c r="C460" s="3" t="n"/>
       <c r="D460" s="4" t="n"/>
@@ -8049,10 +6833,7 @@
       <c r="J460" s="4" t="n"/>
     </row>
     <row r="461" ht="22" customHeight="1">
-      <c r="A461" s="3">
-        <f>IF(C461="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A461" s="3" t="n"/>
       <c r="B461" s="3" t="n"/>
       <c r="C461" s="3" t="n"/>
       <c r="D461" s="4" t="n"/>
@@ -8064,10 +6845,7 @@
       <c r="J461" s="4" t="n"/>
     </row>
     <row r="462" ht="22" customHeight="1">
-      <c r="A462" s="3">
-        <f>IF(C462="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A462" s="3" t="n"/>
       <c r="B462" s="3" t="n"/>
       <c r="C462" s="3" t="n"/>
       <c r="D462" s="4" t="n"/>
@@ -8079,10 +6857,7 @@
       <c r="J462" s="4" t="n"/>
     </row>
     <row r="463" ht="22" customHeight="1">
-      <c r="A463" s="3">
-        <f>IF(C463="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A463" s="3" t="n"/>
       <c r="B463" s="3" t="n"/>
       <c r="C463" s="3" t="n"/>
       <c r="D463" s="4" t="n"/>
@@ -8094,10 +6869,7 @@
       <c r="J463" s="4" t="n"/>
     </row>
     <row r="464" ht="22" customHeight="1">
-      <c r="A464" s="3">
-        <f>IF(C464="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A464" s="3" t="n"/>
       <c r="B464" s="3" t="n"/>
       <c r="C464" s="3" t="n"/>
       <c r="D464" s="4" t="n"/>
@@ -8109,10 +6881,7 @@
       <c r="J464" s="4" t="n"/>
     </row>
     <row r="465" ht="22" customHeight="1">
-      <c r="A465" s="3">
-        <f>IF(C465="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A465" s="3" t="n"/>
       <c r="B465" s="3" t="n"/>
       <c r="C465" s="3" t="n"/>
       <c r="D465" s="4" t="n"/>
@@ -8124,10 +6893,7 @@
       <c r="J465" s="4" t="n"/>
     </row>
     <row r="466" ht="22" customHeight="1">
-      <c r="A466" s="3">
-        <f>IF(C466="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A466" s="3" t="n"/>
       <c r="B466" s="3" t="n"/>
       <c r="C466" s="3" t="n"/>
       <c r="D466" s="4" t="n"/>
@@ -8139,10 +6905,7 @@
       <c r="J466" s="4" t="n"/>
     </row>
     <row r="467" ht="22" customHeight="1">
-      <c r="A467" s="3">
-        <f>IF(C467="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A467" s="3" t="n"/>
       <c r="B467" s="3" t="n"/>
       <c r="C467" s="3" t="n"/>
       <c r="D467" s="4" t="n"/>
@@ -8154,10 +6917,7 @@
       <c r="J467" s="4" t="n"/>
     </row>
     <row r="468" ht="22" customHeight="1">
-      <c r="A468" s="3">
-        <f>IF(C468="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A468" s="3" t="n"/>
       <c r="B468" s="3" t="n"/>
       <c r="C468" s="3" t="n"/>
       <c r="D468" s="4" t="n"/>
@@ -8169,10 +6929,7 @@
       <c r="J468" s="4" t="n"/>
     </row>
     <row r="469" ht="22" customHeight="1">
-      <c r="A469" s="3">
-        <f>IF(C469="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A469" s="3" t="n"/>
       <c r="B469" s="3" t="n"/>
       <c r="C469" s="3" t="n"/>
       <c r="D469" s="4" t="n"/>
@@ -8184,10 +6941,7 @@
       <c r="J469" s="4" t="n"/>
     </row>
     <row r="470" ht="22" customHeight="1">
-      <c r="A470" s="3">
-        <f>IF(C470="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A470" s="3" t="n"/>
       <c r="B470" s="3" t="n"/>
       <c r="C470" s="3" t="n"/>
       <c r="D470" s="4" t="n"/>
@@ -8199,10 +6953,7 @@
       <c r="J470" s="4" t="n"/>
     </row>
     <row r="471" ht="22" customHeight="1">
-      <c r="A471" s="3">
-        <f>IF(C471="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A471" s="3" t="n"/>
       <c r="B471" s="3" t="n"/>
       <c r="C471" s="3" t="n"/>
       <c r="D471" s="4" t="n"/>
@@ -8214,10 +6965,7 @@
       <c r="J471" s="4" t="n"/>
     </row>
     <row r="472" ht="22" customHeight="1">
-      <c r="A472" s="3">
-        <f>IF(C472="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A472" s="3" t="n"/>
       <c r="B472" s="3" t="n"/>
       <c r="C472" s="3" t="n"/>
       <c r="D472" s="4" t="n"/>
@@ -8229,10 +6977,7 @@
       <c r="J472" s="4" t="n"/>
     </row>
     <row r="473" ht="22" customHeight="1">
-      <c r="A473" s="3">
-        <f>IF(C473="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A473" s="3" t="n"/>
       <c r="B473" s="3" t="n"/>
       <c r="C473" s="3" t="n"/>
       <c r="D473" s="4" t="n"/>
@@ -8244,10 +6989,7 @@
       <c r="J473" s="4" t="n"/>
     </row>
     <row r="474" ht="22" customHeight="1">
-      <c r="A474" s="3">
-        <f>IF(C474="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A474" s="3" t="n"/>
       <c r="B474" s="3" t="n"/>
       <c r="C474" s="3" t="n"/>
       <c r="D474" s="4" t="n"/>
@@ -8259,10 +7001,7 @@
       <c r="J474" s="4" t="n"/>
     </row>
     <row r="475" ht="22" customHeight="1">
-      <c r="A475" s="3">
-        <f>IF(C475="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A475" s="3" t="n"/>
       <c r="B475" s="3" t="n"/>
       <c r="C475" s="3" t="n"/>
       <c r="D475" s="4" t="n"/>
@@ -8274,10 +7013,7 @@
       <c r="J475" s="4" t="n"/>
     </row>
     <row r="476" ht="22" customHeight="1">
-      <c r="A476" s="3">
-        <f>IF(C476="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A476" s="3" t="n"/>
       <c r="B476" s="3" t="n"/>
       <c r="C476" s="3" t="n"/>
       <c r="D476" s="4" t="n"/>
@@ -8289,10 +7025,7 @@
       <c r="J476" s="4" t="n"/>
     </row>
     <row r="477" ht="22" customHeight="1">
-      <c r="A477" s="3">
-        <f>IF(C477="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A477" s="3" t="n"/>
       <c r="B477" s="3" t="n"/>
       <c r="C477" s="3" t="n"/>
       <c r="D477" s="4" t="n"/>
@@ -8304,10 +7037,7 @@
       <c r="J477" s="4" t="n"/>
     </row>
     <row r="478" ht="22" customHeight="1">
-      <c r="A478" s="3">
-        <f>IF(C478="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A478" s="3" t="n"/>
       <c r="B478" s="3" t="n"/>
       <c r="C478" s="3" t="n"/>
       <c r="D478" s="4" t="n"/>
@@ -8319,10 +7049,7 @@
       <c r="J478" s="4" t="n"/>
     </row>
     <row r="479" ht="22" customHeight="1">
-      <c r="A479" s="3">
-        <f>IF(C479="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A479" s="3" t="n"/>
       <c r="B479" s="3" t="n"/>
       <c r="C479" s="3" t="n"/>
       <c r="D479" s="4" t="n"/>
@@ -8334,10 +7061,7 @@
       <c r="J479" s="4" t="n"/>
     </row>
     <row r="480" ht="22" customHeight="1">
-      <c r="A480" s="3">
-        <f>IF(C480="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A480" s="3" t="n"/>
       <c r="B480" s="3" t="n"/>
       <c r="C480" s="3" t="n"/>
       <c r="D480" s="4" t="n"/>
@@ -8349,10 +7073,7 @@
       <c r="J480" s="4" t="n"/>
     </row>
     <row r="481" ht="22" customHeight="1">
-      <c r="A481" s="3">
-        <f>IF(C481="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A481" s="3" t="n"/>
       <c r="B481" s="3" t="n"/>
       <c r="C481" s="3" t="n"/>
       <c r="D481" s="4" t="n"/>
@@ -8364,10 +7085,7 @@
       <c r="J481" s="4" t="n"/>
     </row>
     <row r="482" ht="22" customHeight="1">
-      <c r="A482" s="3">
-        <f>IF(C482="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A482" s="3" t="n"/>
       <c r="B482" s="3" t="n"/>
       <c r="C482" s="3" t="n"/>
       <c r="D482" s="4" t="n"/>
@@ -8379,10 +7097,7 @@
       <c r="J482" s="4" t="n"/>
     </row>
     <row r="483" ht="22" customHeight="1">
-      <c r="A483" s="3">
-        <f>IF(C483="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A483" s="3" t="n"/>
       <c r="B483" s="3" t="n"/>
       <c r="C483" s="3" t="n"/>
       <c r="D483" s="4" t="n"/>
@@ -8394,10 +7109,7 @@
       <c r="J483" s="4" t="n"/>
     </row>
     <row r="484" ht="22" customHeight="1">
-      <c r="A484" s="3">
-        <f>IF(C484="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A484" s="3" t="n"/>
       <c r="B484" s="3" t="n"/>
       <c r="C484" s="3" t="n"/>
       <c r="D484" s="4" t="n"/>
@@ -8409,10 +7121,7 @@
       <c r="J484" s="4" t="n"/>
     </row>
     <row r="485" ht="22" customHeight="1">
-      <c r="A485" s="3">
-        <f>IF(C485="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A485" s="3" t="n"/>
       <c r="B485" s="3" t="n"/>
       <c r="C485" s="3" t="n"/>
       <c r="D485" s="4" t="n"/>
@@ -8424,10 +7133,7 @@
       <c r="J485" s="4" t="n"/>
     </row>
     <row r="486" ht="22" customHeight="1">
-      <c r="A486" s="3">
-        <f>IF(C486="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A486" s="3" t="n"/>
       <c r="B486" s="3" t="n"/>
       <c r="C486" s="3" t="n"/>
       <c r="D486" s="4" t="n"/>
@@ -8439,10 +7145,7 @@
       <c r="J486" s="4" t="n"/>
     </row>
     <row r="487" ht="22" customHeight="1">
-      <c r="A487" s="3">
-        <f>IF(C487="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A487" s="3" t="n"/>
       <c r="B487" s="3" t="n"/>
       <c r="C487" s="3" t="n"/>
       <c r="D487" s="4" t="n"/>
@@ -8454,10 +7157,7 @@
       <c r="J487" s="4" t="n"/>
     </row>
     <row r="488" ht="22" customHeight="1">
-      <c r="A488" s="3">
-        <f>IF(C488="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A488" s="3" t="n"/>
       <c r="B488" s="3" t="n"/>
       <c r="C488" s="3" t="n"/>
       <c r="D488" s="4" t="n"/>
@@ -8469,10 +7169,7 @@
       <c r="J488" s="4" t="n"/>
     </row>
     <row r="489" ht="22" customHeight="1">
-      <c r="A489" s="3">
-        <f>IF(C489="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A489" s="3" t="n"/>
       <c r="B489" s="3" t="n"/>
       <c r="C489" s="3" t="n"/>
       <c r="D489" s="4" t="n"/>
@@ -8484,10 +7181,7 @@
       <c r="J489" s="4" t="n"/>
     </row>
     <row r="490" ht="22" customHeight="1">
-      <c r="A490" s="3">
-        <f>IF(C490="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A490" s="3" t="n"/>
       <c r="B490" s="3" t="n"/>
       <c r="C490" s="3" t="n"/>
       <c r="D490" s="4" t="n"/>
@@ -8499,10 +7193,7 @@
       <c r="J490" s="4" t="n"/>
     </row>
     <row r="491" ht="22" customHeight="1">
-      <c r="A491" s="3">
-        <f>IF(C491="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A491" s="3" t="n"/>
       <c r="B491" s="3" t="n"/>
       <c r="C491" s="3" t="n"/>
       <c r="D491" s="4" t="n"/>
@@ -8514,10 +7205,7 @@
       <c r="J491" s="4" t="n"/>
     </row>
     <row r="492" ht="22" customHeight="1">
-      <c r="A492" s="3">
-        <f>IF(C492="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A492" s="3" t="n"/>
       <c r="B492" s="3" t="n"/>
       <c r="C492" s="3" t="n"/>
       <c r="D492" s="4" t="n"/>
@@ -8529,10 +7217,7 @@
       <c r="J492" s="4" t="n"/>
     </row>
     <row r="493" ht="22" customHeight="1">
-      <c r="A493" s="3">
-        <f>IF(C493="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A493" s="3" t="n"/>
       <c r="B493" s="3" t="n"/>
       <c r="C493" s="3" t="n"/>
       <c r="D493" s="4" t="n"/>
@@ -8544,10 +7229,7 @@
       <c r="J493" s="4" t="n"/>
     </row>
     <row r="494" ht="22" customHeight="1">
-      <c r="A494" s="3">
-        <f>IF(C494="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A494" s="3" t="n"/>
       <c r="B494" s="3" t="n"/>
       <c r="C494" s="3" t="n"/>
       <c r="D494" s="4" t="n"/>
@@ -8559,10 +7241,7 @@
       <c r="J494" s="4" t="n"/>
     </row>
     <row r="495" ht="22" customHeight="1">
-      <c r="A495" s="3">
-        <f>IF(C495="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A495" s="3" t="n"/>
       <c r="B495" s="3" t="n"/>
       <c r="C495" s="3" t="n"/>
       <c r="D495" s="4" t="n"/>
@@ -8574,10 +7253,7 @@
       <c r="J495" s="4" t="n"/>
     </row>
     <row r="496" ht="22" customHeight="1">
-      <c r="A496" s="3">
-        <f>IF(C496="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A496" s="3" t="n"/>
       <c r="B496" s="3" t="n"/>
       <c r="C496" s="3" t="n"/>
       <c r="D496" s="4" t="n"/>
@@ -8589,10 +7265,7 @@
       <c r="J496" s="4" t="n"/>
     </row>
     <row r="497" ht="22" customHeight="1">
-      <c r="A497" s="3">
-        <f>IF(C497="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A497" s="3" t="n"/>
       <c r="B497" s="3" t="n"/>
       <c r="C497" s="3" t="n"/>
       <c r="D497" s="4" t="n"/>
@@ -8604,10 +7277,7 @@
       <c r="J497" s="4" t="n"/>
     </row>
     <row r="498" ht="22" customHeight="1">
-      <c r="A498" s="3">
-        <f>IF(C498="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A498" s="3" t="n"/>
       <c r="B498" s="3" t="n"/>
       <c r="C498" s="3" t="n"/>
       <c r="D498" s="4" t="n"/>
@@ -8619,10 +7289,7 @@
       <c r="J498" s="4" t="n"/>
     </row>
     <row r="499" ht="22" customHeight="1">
-      <c r="A499" s="3">
-        <f>IF(C499="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A499" s="3" t="n"/>
       <c r="B499" s="3" t="n"/>
       <c r="C499" s="3" t="n"/>
       <c r="D499" s="4" t="n"/>
@@ -8634,10 +7301,7 @@
       <c r="J499" s="4" t="n"/>
     </row>
     <row r="500" ht="22" customHeight="1">
-      <c r="A500" s="3">
-        <f>IF(C500="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A500" s="3" t="n"/>
       <c r="B500" s="3" t="n"/>
       <c r="C500" s="3" t="n"/>
       <c r="D500" s="4" t="n"/>
@@ -8649,10 +7313,7 @@
       <c r="J500" s="4" t="n"/>
     </row>
     <row r="501" ht="22" customHeight="1">
-      <c r="A501" s="3">
-        <f>IF(C501="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A501" s="3" t="n"/>
       <c r="B501" s="3" t="n"/>
       <c r="C501" s="3" t="n"/>
       <c r="D501" s="4" t="n"/>
@@ -8664,10 +7325,7 @@
       <c r="J501" s="4" t="n"/>
     </row>
     <row r="502" ht="22" customHeight="1">
-      <c r="A502" s="3">
-        <f>IF(C502="","",ROW()-2)</f>
-        <v/>
-      </c>
+      <c r="A502" s="3" t="n"/>
       <c r="B502" s="3" t="n"/>
       <c r="C502" s="3" t="n"/>
       <c r="D502" s="4" t="n"/>
@@ -8692,14 +7350,11 @@
         <f>COUNTA(C3:C502) &amp; " 笔订单"</f>
         <v/>
       </c>
-      <c r="I504" s="13" t="n"/>
-      <c r="J504" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A504:F504"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H504:J504"/>
+  <mergeCells count="2">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8711,7 +7366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8770,21 +7425,17 @@
           <t>01月</t>
         </is>
       </c>
-      <c r="C3" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,2,1))</f>
-        <v/>
-      </c>
-      <c r="D3" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,2,1))</f>
-        <v/>
-      </c>
-      <c r="E3" s="6">
-        <f>IF(C3=0,0,D3/C3)</f>
-        <v/>
-      </c>
-      <c r="F3" s="11">
-        <f>IF(D3=0,0,D3/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -8796,21 +7447,17 @@
           <t>02月</t>
         </is>
       </c>
-      <c r="C4" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,2,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,3,1))</f>
-        <v/>
-      </c>
-      <c r="D4" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,2,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,3,1))</f>
-        <v/>
-      </c>
-      <c r="E4" s="6">
-        <f>IF(C4=0,0,D4/C4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="11">
-        <f>IF(D4=0,0,D4/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -8822,21 +7469,17 @@
           <t>03月</t>
         </is>
       </c>
-      <c r="C5" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,3,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,4,1))</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,3,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,4,1))</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
-        <f>IF(C5=0,0,D5/C5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>IF(D5=0,0,D5/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -8848,21 +7491,17 @@
           <t>04月</t>
         </is>
       </c>
-      <c r="C6" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,4,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,5,1))</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,4,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,5,1))</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
-        <f>IF(C6=0,0,D6/C6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>IF(D6=0,0,D6/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -8874,21 +7513,17 @@
           <t>05月</t>
         </is>
       </c>
-      <c r="C7" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,5,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,5,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,6,1))</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>IF(C7=0,0,D7/C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>IF(D7=0,0,D7/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -8900,21 +7535,17 @@
           <t>06月</t>
         </is>
       </c>
-      <c r="C8" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,6,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,6,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,7,1))</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>IF(C8=0,0,D8/C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>IF(D8=0,0,D8/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -8926,21 +7557,17 @@
           <t>07月</t>
         </is>
       </c>
-      <c r="C9" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,7,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,7,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,8,1))</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IF(C9=0,0,D9/C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>IF(D9=0,0,D9/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -8952,21 +7579,17 @@
           <t>08月</t>
         </is>
       </c>
-      <c r="C10" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,8,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,9,1))</f>
-        <v/>
-      </c>
-      <c r="D10" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,8,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,9,1))</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>IF(C10=0,0,D10/C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>IF(D10=0,0,D10/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -8978,21 +7601,17 @@
           <t>09月</t>
         </is>
       </c>
-      <c r="C11" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,9,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,10,1))</f>
-        <v/>
-      </c>
-      <c r="D11" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,9,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,10,1))</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>IF(C11=0,0,D11/C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>IF(D11=0,0,D11/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -9004,21 +7623,17 @@
           <t>10月</t>
         </is>
       </c>
-      <c r="C12" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,10,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,11,1))</f>
-        <v/>
-      </c>
-      <c r="D12" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,10,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,11,1))</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>IF(C12=0,0,D12/C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11">
-        <f>IF(D12=0,0,D12/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -9030,21 +7645,17 @@
           <t>11月</t>
         </is>
       </c>
-      <c r="C13" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,11,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,12,1))</f>
-        <v/>
-      </c>
-      <c r="D13" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,11,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,12,1))</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>IF(C13=0,0,D13/C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="11">
-        <f>IF(D13=0,0,D13/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -9056,21 +7667,17 @@
           <t>12月</t>
         </is>
       </c>
-      <c r="C14" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,12,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,1,1)+365)</f>
-        <v/>
-      </c>
-      <c r="D14" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,12,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2026,1,1)+365)</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>IF(C14=0,0,D14/C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>IF(D14=0,0,D14/SUM($D$3:$D$14))</f>
-        <v/>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -9079,28 +7686,26 @@
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="10">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="9">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="9">
-        <f>IF(C15=0,0,D15/C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="1">
     <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9114,7 +7719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9162,25 +7767,26 @@
       <c r="A3" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B3" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C3" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D3" s="6">
-        <f>IF(B3=0,0,C3/B3)</f>
-        <v/>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9190,7 +7796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9234,176 +7840,168 @@
           <t>抖音</t>
         </is>
       </c>
-      <c r="B3" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"抖音",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C3" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"抖音",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D3" s="11">
-        <f>IF(C3=0,0,C3/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>抖音商城</t>
         </is>
       </c>
-      <c r="B4" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"1688",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C4" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"1688",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D4" s="11">
-        <f>IF(C4=0,0,C4/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0.6609</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>1688</t>
         </is>
       </c>
-      <c r="B5" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"淘宝",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"淘宝",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
-        <f>IF(C5=0,0,C5/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0.3391</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>淘宝</t>
         </is>
       </c>
-      <c r="B6" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"京东",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"京东",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>IF(C6=0,0,C6/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>京东</t>
         </is>
       </c>
-      <c r="B7" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"拼多多",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C7" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"拼多多",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D7" s="11">
-        <f>IF(C7=0,0,C7/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>天猫</t>
+          <t>拼多多</t>
         </is>
       </c>
-      <c r="B8" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"天猫",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C8" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"天猫",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>IF(C8=0,0,C8/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>苏宁</t>
+          <t>天猫</t>
         </is>
       </c>
-      <c r="B9" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"苏宁",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"苏宁",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D9" s="11">
-        <f>IF(C9=0,0,C9/SUM($C$3:$C$10))</f>
-        <v/>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>苏宁</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B10" s="3">
-        <f>COUNTIFS('🛒购买记录明细'!B3:B502,"其他",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="C10" s="6">
-        <f>SUMIFS('🛒购买记录明细'!G3:G502,'🛒购买记录明细'!B3:B502,"其他",'🛒购买记录明细'!C3:C502,"&gt;="&amp;DATE(2026,1,1),'🛒购买记录明细'!C3:C502,"&lt;"&amp;DATE(2027,1,1))</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
-        <f>IF(C10=0,0,C10/SUM($C$3:$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="B11" s="10">
-        <f>SUM(B3:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>截图</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
           <t>3311879379799327755</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n"/>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1347,7 +1347,7 @@
           <t>6928046994516508348</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n"/>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -1381,8 +1381,7 @@
           <t>2 笔订单</t>
         </is>
       </c>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="n"/>
@@ -7354,7 +7353,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet name="📊月度统计" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="📈年度统计" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="🏪平台分布" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="📦出货记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,6 +210,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1264,12 +1270,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>购买订单号</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>关联出货单</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -1381,7 +1387,8 @@
           <t>2 笔订单</t>
         </is>
       </c>
-      <c r="I6" s="14" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="14" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="n"/>
@@ -7353,7 +7360,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8004,4 +8011,731 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N502"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📦 出货记录表 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>出货平台</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>订购日期</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>销售价</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>税金</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>出货订单号</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>关联购买记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>46214</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>6E-4EHX-JF04</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>312</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>1714</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>503-95444475-5097463</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>3311879379799327755</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>46221</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>琥珀色</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>LK-RN2M-G3YX</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>312</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1714</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>249-6387958-2579060</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>6928046994516508348</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>总销售额: ¥3,428.00</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2 笔出货</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -157,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -212,7 +211,10 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1317,7 +1319,11 @@
           <t>3311879379799327755</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>503-95444475-5097463</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1353,7 +1359,11 @@
           <t>6928046994516508348</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>249-6387958-2579060</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -8110,10 +8120,10 @@
           <t>Amazon日本站</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="21" t="n">
         <v>46214</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="21" t="n">
         <v>46217</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -8166,10 +8176,10 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>46221</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="21" t="n">
         <v>46224</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -8228,11 +8238,15 @@
           <t>总销售额: ¥3,428.00</t>
         </is>
       </c>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="14" t="n"/>
       <c r="M6" s="10" t="inlineStr">
         <is>
           <t>2 笔出货</t>
         </is>
       </c>
+      <c r="N6" s="14" t="n"/>
     </row>
     <row r="7"/>
     <row r="8"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1319,7 +1319,7 @@
           <t>3311879379799327755</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>503-95444475-5097463</t>
         </is>
@@ -1359,7 +1359,7 @@
           <t>6928046994516508348</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>249-6387958-2579060</t>
         </is>
@@ -7372,6 +7372,10 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8161,7 +8165,7 @@
           <t>503-95444475-5097463</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>3311879379799327755</t>
         </is>
@@ -8217,7 +8221,7 @@
           <t>249-6387958-2579060</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>6928046994516508348</t>
         </is>
@@ -8750,6 +8754,10 @@
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="🛒购买记录明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📊月度统计" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="📈年度统计" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="🏪平台分布" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="📦出货记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="📦出货记录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="📊月度统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="📈年度统计" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="🏪平台分布" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7386,653 +7386,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📊 月度购买统计 (2026年)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>购买笔数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>总金额(元)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>平均单价(元)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>01月</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>02月</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>03月</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>04月</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>05月</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>06月</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>07月</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>08月</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>09月</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>📊 合计</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:B15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📈 年度购买统计 (2026年)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>购买笔数</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总金额(元)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>平均单价(元)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🏪 购买平台分布 (2026年)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>购买平台</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>购买笔数</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总金额(元)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>抖音</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>抖音商城</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>0.6609</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>1688</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0.3391</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>淘宝</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>京东</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>拼多多</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>苏宁</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>📊 合计</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:N502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -8760,4 +8113,651 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📊 月度购买统计 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>购买笔数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>总金额(元)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>平均单价(元)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>01月</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>06月</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>07月</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>08月</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>09月</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📈 年度购买统计 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>购买笔数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>总金额(元)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>平均单价(元)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🏪 购买平台分布 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>购买平台</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>购买笔数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>总金额(元)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>抖音商城</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0.6609</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0.3391</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>淘宝</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>拼多多</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>苏宁</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1215,22 +1215,22 @@
   <dimension ref="A1:J504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🛒 购买记录明细表  (2026年)</t>
+          <t>🛒 购买记录明细表 (2026年)</t>
         </is>
       </c>
     </row>
@@ -7368,13 +7368,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
+    <hyperlink ref="I3" location="'📦出货记录'!A3" display="503-95444475-5097463"/>
+    <hyperlink ref="I4" location="'📦出货记录'!A4" display="249-6387958-2579060"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7388,6 +7389,22 @@
   </sheetPr>
   <dimension ref="A1:N502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
@@ -8102,14 +8119,15 @@
     <row r="501"/>
     <row r="502"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="I6:L6"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I6:L6"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
+    <hyperlink ref="N3" location="'🛒购买记录明细'!A3" display="3311879379799327755"/>
+    <hyperlink ref="N4" location="'🛒购买记录明细'!A4" display="6928046994516508348"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -156,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +216,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7398,10 +7402,10 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
@@ -7456,22 +7460,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>销售价</t>
+          <t>销售价(日元)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>税金</t>
+          <t>税金(日元)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>手续费</t>
+          <t>手续费(日元)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售额(日元)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -7518,16 +7522,16 @@
       <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="22" t="n">
         <v>2026</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="22" t="n">
         <v>184</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="22" t="n">
         <v>312</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="22" t="n">
         <v>1714</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -7574,16 +7578,16 @@
       <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="22" t="n">
         <v>2026</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="22" t="n">
         <v>184</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="22" t="n">
         <v>312</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="22" t="n">
         <v>1714</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -7609,7 +7613,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>总销售额: ¥3,428.00</t>
+          <t>总销售额: JPY 3,428</t>
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
@@ -8120,9 +8124,9 @@
     <row r="502"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I6:L6"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:N6"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1222,11 +1223,11 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1371,50 +1372,71 @@
       <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>拼多多</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>46221.59108796297</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>260718-641864876461684</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>249-6387958-2579060</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>2 笔订单</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="14" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>3 笔订单</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="14" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="n"/>
@@ -7373,13 +7395,14 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" location="'📦出货记录'!A3" display="503-95444475-5097463"/>
     <hyperlink ref="I4" location="'📦出货记录'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="I5" location="'📦出货记录'!A4" display="249-6387958-2579060"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8335,13 +8358,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>17.4</v>
+        <v>37.4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>12.47</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -8465,13 +8488,13 @@
       </c>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>17.4</v>
+        <v>37.4</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>12.47</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>1</v>
@@ -8545,13 +8568,13 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>17.4</v>
+        <v>37.4</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>12.47</v>
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
@@ -8640,7 +8663,7 @@
         <v>11.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.6609</v>
+        <v>0.3075</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -8656,7 +8679,7 @@
         <v>5.9</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.3391</v>
+        <v>0.1578</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -8698,13 +8721,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0</v>
+        <v>0.5348000000000001</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -8762,10 +8785,10 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>17.4</v>
+        <v>37.4</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>1</v>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1221,7 +1220,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
@@ -1337,31 +1336,31 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>抖音商城</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C4" s="15" t="n">
-        <v>46221.42550925926</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>500ml琥珀圆形大力神杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>6928046994516508348</t>
+          <t>260718-641864876461684</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -1372,71 +1371,43 @@
       <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>拼多多</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>46221.59108796297</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>260718-641864876461684</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>249-6387958-2579060</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="10" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10" t="n"/>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>2 笔订单</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="14" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>📊 合计</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="9" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>3 笔订单</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="14" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="n"/>
@@ -7395,9 +7366,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" location="'📦出货记录'!A3" display="503-95444475-5097463"/>
@@ -7430,7 +7401,7 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7620,7 +7591,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>6928046994516508348</t>
+          <t>260718-641864876461684</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8125,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N3" location="'🛒购买记录明细'!A3" display="3311879379799327755"/>
-    <hyperlink ref="N4" location="'🛒购买记录明细'!A4" display="6928046994516508348"/>
+    <hyperlink ref="N4" location="'🛒购买记录明细'!A4" display="260718-641864876461684"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8358,13 +8329,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>37.4</v>
+        <v>25.9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>12.47</v>
+        <v>12.95</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -8488,13 +8459,13 @@
       </c>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>37.4</v>
+        <v>25.9</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>12.47</v>
+        <v>12.95</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>1</v>
@@ -8568,13 +8539,13 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>37.4</v>
+        <v>25.9</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>12.47</v>
+        <v>12.95</v>
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
@@ -8657,13 +8628,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.3075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -8679,7 +8650,7 @@
         <v>5.9</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.1578</v>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -8727,7 +8698,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.7722</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -8785,10 +8756,10 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>37.4</v>
+        <v>25.9</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>1</v>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1216,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J504"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1229,6 +1230,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1266,7 +1269,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>购买数量</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1285,6 +1288,16 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>出货数量</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1328,7 +1341,13 @@
           <t>503-95444475-5097463</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -1368,46 +1387,98 @@
           <t>249-6387958-2579060</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>46224.4587962963</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>玻璃修复膏玻璃表面专业抛光</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>50g+海绵</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>3313191614834136171</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>249-4866874-7926210</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>最低起订2个，卖出1个，库存1个</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>2 笔订单</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="14" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="10" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="9" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>3 笔订单</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>库存合计</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="n"/>
@@ -7366,14 +7437,14 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" location="'📦出货记录'!A3" display="503-95444475-5097463"/>
     <hyperlink ref="I4" location="'📦出货记录'!A4" display="249-6387958-2579060"/>
-    <hyperlink ref="I5" location="'📦出货记录'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="I5" location="'📦出货记录'!A5" display="249-4866874-7926210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7595,32 +7666,88 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1X-GB0W-BY30</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>1122</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>117</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>249-4866874-7926210</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>3313191614834136171</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="8" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 3,428</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>2 笔出货</t>
-        </is>
-      </c>
-      <c r="N6" s="14" t="n"/>
-    </row>
-    <row r="7"/>
+      <c r="H7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 4,433</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>3 笔出货</t>
+        </is>
+      </c>
+    </row>
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>
@@ -8118,14 +8245,15 @@
     <row r="502"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="I7:L7"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N3" location="'🛒购买记录明细'!A3" display="3311879379799327755"/>
     <hyperlink ref="N4" location="'🛒购买记录明细'!A4" display="260718-641864876461684"/>
+    <hyperlink ref="N5" location="'🛒购买记录明细'!A5" display="3313191614834136171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8329,13 +8457,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>25.9</v>
+        <v>37.79</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>12.95</v>
+        <v>12.6</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -8459,13 +8587,13 @@
       </c>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>25.9</v>
+        <v>37.79</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>12.95</v>
+        <v>12.6</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>1</v>
@@ -8539,13 +8667,13 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>25.9</v>
+        <v>37.79</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>12.95</v>
+        <v>12.6</v>
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
@@ -8644,13 +8772,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5.9</v>
+        <v>17.79</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.2278</v>
+        <v>0.4708</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -8698,7 +8826,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.7722</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -8756,10 +8884,10 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>25.9</v>
+        <v>37.79</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>1</v>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1342,7 +1341,7 @@
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>0</v>
@@ -1388,7 +1387,7 @@
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
@@ -7438,8 +7437,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" location="'📦出货记录'!A3" display="503-95444475-5097463"/>
@@ -7742,11 +7741,15 @@
           <t>总销售额: JPY 4,433</t>
         </is>
       </c>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="14" t="n"/>
       <c r="M7" s="10" t="inlineStr">
         <is>
           <t>3 笔出货</t>
         </is>
       </c>
+      <c r="N7" s="14" t="n"/>
     </row>
     <row r="8"/>
     <row r="9"/>
@@ -8245,8 +8248,8 @@
     <row r="502"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="M7:N7"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -109,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -188,6 +188,50 @@
       <bottom style="thin">
         <color rgb="00D9E1F2"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E1F2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E1F2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E1F2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E1F2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E1F2"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1632,27 +1676,27 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46224.4587962963</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1706,22 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G4" s="25" t="n"/>
       <c r="H4" s="27" t="inlineStr">
@@ -1692,136 +1736,51 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>玻璃修复膏玻璃表面专业抛光</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>20</v>
+        <v>5.95</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46221.59108796297</v>
-      </c>
-      <c r="G5" s="25" t="n"/>
+        <v>46224.4587962963</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <v>46223</v>
+      </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
           <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>透明</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="33" t="n">
-        <v>46214</v>
-      </c>
-      <c r="H6" s="27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
+    <row r="6"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>📊 库存合计</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>3 种商品</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>琥珀色</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="25" t="n"/>
-      <c r="G7" s="33" t="n">
-        <v>46221</v>
-      </c>
-      <c r="H7" s="27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>玻璃修复膏 50g 车用</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>50g</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="25" t="n"/>
-      <c r="G8" s="33" t="n">
-        <v>46223</v>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>📊 库存合计</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>6 种商品</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -2016,8 +1975,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E7:H7"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2042,8 +2001,8 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2138,19 +2097,19 @@
         <v>2</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="29" t="n">
         <v>11.89</v>
       </c>
       <c r="J3" s="34" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="K3" s="34" t="n">
-        <v>-237.8</v>
+        <v>767.2</v>
       </c>
     </row>
     <row r="4"/>
@@ -2164,10 +2123,10 @@
         <v>11.89</v>
       </c>
       <c r="J5" s="35" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="K5" s="35" t="n">
-        <v>-237</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -339,6 +339,9 @@
     </xf>
     <xf numFmtId="167" fontId="2" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1994,15 +1997,15 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2073,12 +2076,12 @@
       <c r="A3" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>3313191614834136171</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>249-4866874-7926210</t>
         </is>
@@ -2112,25 +2115,109 @@
         <v>767.2</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>📊 合计</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="J5" s="35" t="n">
-        <v>1005</v>
-      </c>
-      <c r="K5" s="35" t="n">
-        <v>767</v>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>503-95444475-5097463</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="34" t="n">
+        <v>1714</v>
+      </c>
+      <c r="K4" s="34" t="n">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>249-6387958-2579060</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>琥珀色</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <v>1714</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>1714</v>
       </c>
     </row>
     <row r="6"/>
-    <row r="7"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>4433</v>
+      </c>
+      <c r="K7" s="35" t="n">
+        <v>4195</v>
+      </c>
+    </row>
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>
@@ -2329,8 +2416,14 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" location="'📥进货表'!A5" display="3313191614834136171"/>
+    <hyperlink ref="C3" location="'📤销售表'!A5" display="249-4866874-7926210"/>
+    <hyperlink ref="C4" location="'📤销售表'!A3" display="503-95444475-5097463"/>
+    <hyperlink ref="C5" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1996,10 +1996,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
@@ -2078,127 +2078,127 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>3313191614834136171</t>
+          <t>3311879379799327755</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>249-4866874-7926210</t>
+          <t>503-95444475-5097463</t>
         </is>
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>11.89</v>
+        <v>5.9</v>
       </c>
       <c r="J3" s="34" t="n">
-        <v>1005</v>
+        <v>1714</v>
       </c>
       <c r="K3" s="34" t="n">
-        <v>767.2</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>260718-641864876461684</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>503-95444475-5097463</t>
+          <t>249-6387958-2579060</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>透明</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="F4" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J4" s="34" t="n">
         <v>1714</v>
       </c>
       <c r="K4" s="34" t="n">
-        <v>1714</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>3313191614834136171</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>249-6387958-2579060</t>
+          <t>249-4866874-7926210</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+          <t>玻璃修复膏玻璃表面专业抛光</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>琥珀色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>0</v>
+        <v>11.89</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>1714</v>
+        <v>1005</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>1714</v>
+        <v>767.2</v>
       </c>
     </row>
     <row r="6"/>
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="I7" s="31" t="n">
-        <v>11.89</v>
+        <v>37.79</v>
       </c>
       <c r="J7" s="35" t="n">
         <v>4433</v>
       </c>
       <c r="K7" s="35" t="n">
-        <v>4195</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="8"/>
@@ -2419,10 +2419,12 @@
     <mergeCell ref="A7:E7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" location="'📥进货表'!A5" display="3313191614834136171"/>
-    <hyperlink ref="C3" location="'📤销售表'!A5" display="249-4866874-7926210"/>
-    <hyperlink ref="C4" location="'📤销售表'!A3" display="503-95444475-5097463"/>
-    <hyperlink ref="C5" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
+    <hyperlink ref="C3" location="'📤销售表'!A3" display="503-95444475-5097463"/>
+    <hyperlink ref="B4" location="'📥进货表'!A4" display="260718-641864876461684"/>
+    <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="B5" location="'📥进货表'!A5" display="3313191614834136171"/>
+    <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1679,24 +1679,26 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>玻璃修复膏玻璃表面专业抛光</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46215.5080787037</v>
-      </c>
-      <c r="G3" s="25" t="n"/>
+        <v>46224.4587962963</v>
+      </c>
+      <c r="G3" s="33" t="n">
+        <v>46223</v>
+      </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
           <t>库存充足 (1个)</t>
@@ -1709,27 +1711,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46221.59108796297</v>
-      </c>
-      <c r="G4" s="25" t="n"/>
+        <v>46215.5080787037</v>
+      </c>
+      <c r="G4" s="33" t="n">
+        <v>46214</v>
+      </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -1739,29 +1743,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.95</v>
+        <v>20</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46224.4587962963</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46223</v>
+        <v>46221</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1777,7 @@
         </is>
       </c>
       <c r="D7" s="32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -720,7 +720,7 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -868,11 +868,11 @@
         </is>
       </c>
       <c r="C5" s="26" t="n">
-        <v>46224.4587962963</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="F5" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>11.89</v>
+        <v>18</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>3313191614834136171</t>
+          <t>3314711712867008960</t>
         </is>
       </c>
       <c r="I5" s="29" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
-          <t>最低起订2个</t>
+          <t>原订单3313191614834136171退货后重新下单</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="G7" s="31" t="n">
-        <v>37.79</v>
+        <v>43.9</v>
       </c>
       <c r="H7" s="32" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
@@ -1688,20 +1688,20 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46224.4587962963</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G3" s="33" t="n">
         <v>46223</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="D7" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>3313191614834136171</t>
+          <t>3314711712867008960</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏玻璃表面专业抛光</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
@@ -2187,22 +2187,22 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>11.89</v>
+        <v>18</v>
       </c>
       <c r="J5" s="34" t="n">
         <v>1005</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>767.2</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6"/>
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="I7" s="31" t="n">
-        <v>37.79</v>
+        <v>43.9</v>
       </c>
       <c r="J7" s="35" t="n">
         <v>4433</v>
       </c>
       <c r="K7" s="35" t="n">
-        <v>3677</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="8"/>
@@ -2427,7 +2427,7 @@
     <hyperlink ref="C3" location="'📤销售表'!A3" display="503-95444475-5097463"/>
     <hyperlink ref="B4" location="'📥进货表'!A4" display="260718-641864876461684"/>
     <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
-    <hyperlink ref="B5" location="'📥进货表'!A5" display="3313191614834136171"/>
+    <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -900,23 +900,60 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>46230.61077546296</v>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G7" s="31" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="H7" s="32" t="inlineStr">
-        <is>
-          <t>3 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="G8" s="31" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>4 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
@@ -1113,9 +1150,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1381,25 +1418,76 @@
       </c>
       <c r="N5" s="27" t="n"/>
     </row>
-    <row r="6"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J6" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K6" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L6" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>250-31255524-9007023</t>
+        </is>
+      </c>
+      <c r="N6" s="27" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 4,433</t>
-        </is>
-      </c>
-      <c r="M7" s="32" t="inlineStr">
-        <is>
-          <t>3 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="I8" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 5,362</t>
+        </is>
+      </c>
+      <c r="M8" s="32" t="inlineStr">
+        <is>
+          <t>4 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
@@ -1596,9 +1684,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1711,29 +1799,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46230.61077546296</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46214</v>
+        <v>46230</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -1743,49 +1831,80 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>46215.5080787037</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F6" s="33" t="n">
         <v>46221.59108796297</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G6" s="33" t="n">
         <v>46221</v>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D7" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>3 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="D8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>4 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
@@ -1982,8 +2101,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:H8"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2205,24 +2324,66 @@
         <v>645</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>250-31255524-9007023</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="K6" s="34" t="n">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I7" s="31" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>4433</v>
-      </c>
-      <c r="K7" s="35" t="n">
-        <v>3555</v>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="I8" s="31" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>5362</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>4360</v>
+      </c>
+    </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
@@ -2420,7 +2581,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2429,6 +2590,8 @@
     <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
     <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
+    <hyperlink ref="B6" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C6" location="'📤销售表'!A6" display="250-31255524-9007023"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1470,25 +1470,76 @@
       </c>
       <c r="N6" s="27" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L7" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>249-3150938-6827810</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 5,362</t>
-        </is>
-      </c>
-      <c r="M8" s="32" t="inlineStr">
-        <is>
-          <t>4 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 6,291</t>
+        </is>
+      </c>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>5 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -1684,9 +1735,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I9:L9"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1799,29 +1850,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46230.61077546296</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46230</v>
+        <v>46214</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1882,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -1863,25 +1914,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>3.1</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46230.61077546296</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46232</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -1897,7 +1948,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2352,39 +2403,81 @@
         <v>2</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="29" t="n">
         <v>6.2</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>929</v>
+        <v>1858</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>249-3150938-6827810</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <v>1858</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I8" s="31" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J8" s="35" t="n">
-        <v>5362</v>
-      </c>
-      <c r="K8" s="35" t="n">
-        <v>4360</v>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="I9" s="31" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>8149</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>7023</v>
+      </c>
+    </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -2581,7 +2674,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2592,6 +2685,8 @@
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
     <hyperlink ref="B6" location="'📥进货表'!A6" display="3314150547079044970"/>
     <hyperlink ref="C6" location="'📤销售表'!A6" display="250-31255524-9007023"/>
+    <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C7" location="'📤销售表'!A7" display="249-3150938-6827810"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1428,44 +1428,44 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>切蒜器带透明收纳容器</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>ba0010</t>
+          <t>1X-GB0W-BY30</t>
         </is>
       </c>
       <c r="H6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>699</v>
+        <v>1122</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="L6" s="34" t="n">
-        <v>929</v>
+        <v>1005</v>
       </c>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>250-31255524-9007023</t>
+          <t>503-2823993-6428631</t>
         </is>
       </c>
       <c r="N6" s="27" t="n"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D7" s="33" t="n">
         <v>46232</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>46234</v>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
@@ -1517,30 +1517,81 @@
       </c>
       <c r="M7" s="25" t="inlineStr">
         <is>
+          <t>250-31255524-9007023</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J8" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K8" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L8" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
           <t>249-3150938-6827810</t>
         </is>
       </c>
-      <c r="N7" s="27" t="n"/>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="N8" s="27" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 6,291</t>
-        </is>
-      </c>
-      <c r="M9" s="32" t="inlineStr">
-        <is>
-          <t>5 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 7,296</t>
+        </is>
+      </c>
+      <c r="M10" s="32" t="inlineStr">
+        <is>
+          <t>6 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -1735,9 +1786,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I10:L10"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1827,7 +1878,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>6</v>
@@ -1836,11 +1887,11 @@
         <v>46230.48587962963</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1999,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2178,7 +2229,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -2360,19 +2411,19 @@
         <v>3</v>
       </c>
       <c r="G5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="25" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" s="25" t="n">
-        <v>2</v>
       </c>
       <c r="I5" s="29" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>1005</v>
+        <v>2010</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>645</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2381,41 +2432,41 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
+          <t>3314711712867008960</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>250-31255524-9007023</t>
+          <t>503-2823993-6428631</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>1858</v>
+        <v>2010</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>1734</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2429,7 +2480,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>249-3150938-6827810</t>
+          <t>250-31255524-9007023</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
@@ -2461,24 +2512,66 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>249-3150938-6827810</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" s="34" t="n">
+        <v>1858</v>
+      </c>
+      <c r="K8" s="34" t="n">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I9" s="31" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="J9" s="35" t="n">
-        <v>8149</v>
-      </c>
-      <c r="K9" s="35" t="n">
-        <v>7023</v>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="I10" s="31" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>11164</v>
+      </c>
+      <c r="K10" s="35" t="n">
+        <v>9678</v>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -2674,7 +2767,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2683,10 +2776,12 @@
     <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
     <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
-    <hyperlink ref="B6" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C6" location="'📤销售表'!A6" display="250-31255524-9007023"/>
+    <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
+    <hyperlink ref="C6" location="'📤销售表'!A6" display="503-2823993-6428631"/>
     <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C7" location="'📤销售表'!A7" display="249-3150938-6827810"/>
+    <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
+    <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -938,23 +938,64 @@
       </c>
       <c r="J6" s="27" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>46233.89283564815</v>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>补货</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G8" s="31" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="H8" s="32" t="inlineStr">
-        <is>
-          <t>4 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="G9" s="31" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>5 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -1150,9 +1191,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H8:J8"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="H9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1574,25 +1615,76 @@
       </c>
       <c r="N8" s="27" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J9" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L9" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t>250-5095218-9791066</t>
+        </is>
+      </c>
+      <c r="N9" s="27" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 7,296</t>
-        </is>
-      </c>
-      <c r="M10" s="32" t="inlineStr">
-        <is>
-          <t>6 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 8,225</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>7 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
@@ -1786,9 +1878,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1869,29 +1961,27 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46230.48587962963</v>
-      </c>
-      <c r="G3" s="33" t="n">
-        <v>46232</v>
-      </c>
+        <v>46233.89283564815</v>
+      </c>
+      <c r="G3" s="25" t="n"/>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -1901,29 +1991,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46214</v>
+        <v>46232</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -1933,25 +2023,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -1965,49 +2055,80 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>3.1</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
+        <v>46221.59108796297</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <v>46221</v>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F7" s="33" t="n">
         <v>46230.61077546296</v>
       </c>
-      <c r="G6" s="33" t="n">
-        <v>46232</v>
-      </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="G7" s="33" t="n">
+        <v>46233</v>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>4 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="D9" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>5 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -2203,8 +2324,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E9:H9"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2230,7 +2351,7 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2497,19 +2618,19 @@
         <v>2</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I7" s="29" t="n">
         <v>6.2</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>1858</v>
+        <v>2787</v>
       </c>
       <c r="K7" s="34" t="n">
-        <v>1734</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2540,39 +2661,81 @@
         <v>2</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I8" s="29" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>1858</v>
+        <v>2787</v>
       </c>
       <c r="K8" s="34" t="n">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>250-5095218-9791066</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J9" s="34" t="n">
+        <v>2787</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I10" s="31" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="J10" s="35" t="n">
-        <v>11164</v>
-      </c>
-      <c r="K10" s="35" t="n">
-        <v>9678</v>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="I11" s="31" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>15809</v>
+      </c>
+      <c r="K11" s="35" t="n">
+        <v>14199</v>
+      </c>
+    </row>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
@@ -2766,8 +2929,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2782,6 +2945,8 @@
     <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
     <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
     <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
+    <hyperlink ref="B9" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1961,27 +1961,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.85</v>
+        <v>6</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46233.89283564815</v>
-      </c>
-      <c r="G3" s="25" t="n"/>
+        <v>46230.48587962963</v>
+      </c>
+      <c r="G3" s="33" t="n">
+        <v>46232</v>
+      </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -1991,25 +1993,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46233.89283564815</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -2081,54 +2083,23 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>多功能不锈钢压蒜器</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>按压式2个装 绿色</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>46230.61077546296</v>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>46233</v>
-      </c>
-      <c r="H7" s="27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>5 种商品</t>
-        </is>
-      </c>
-    </row>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>4 种商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -2324,8 +2295,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:H8"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2618,19 +2589,19 @@
         <v>2</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="29" t="n">
         <v>6.2</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>2787</v>
+        <v>1858</v>
       </c>
       <c r="K7" s="34" t="n">
-        <v>2663</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2661,19 +2632,19 @@
         <v>2</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="29" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>2787</v>
+        <v>1858</v>
       </c>
       <c r="K8" s="34" t="n">
-        <v>2663</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2682,7 +2653,7 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
+          <t>3315532944810035788</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
@@ -2704,19 +2675,19 @@
         <v>2</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>6.2</v>
+        <v>19.4</v>
       </c>
       <c r="J9" s="34" t="n">
-        <v>2787</v>
+        <v>929</v>
       </c>
       <c r="K9" s="34" t="n">
-        <v>2663</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10"/>
@@ -2727,13 +2698,13 @@
         </is>
       </c>
       <c r="I11" s="31" t="n">
-        <v>80.5</v>
+        <v>93.7</v>
       </c>
       <c r="J11" s="35" t="n">
-        <v>15809</v>
+        <v>12093</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>14199</v>
+        <v>10219</v>
       </c>
     </row>
     <row r="12"/>
@@ -2945,7 +2916,7 @@
     <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
     <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
     <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
-    <hyperlink ref="B9" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
     <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="F7" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="29" t="n">
         <v>19.4</v>
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="I7" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="J7" s="27" t="inlineStr">
         <is>
-          <t>补货</t>
+          <t>补货 买2件每件2个</t>
         </is>
       </c>
     </row>
@@ -1961,29 +1961,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>6</v>
+        <v>4.27</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46233.89283564815</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -1993,25 +1993,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46233.89283564815</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="F9" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="29" t="n">
         <v>19.4</v>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1667,25 +1667,76 @@
       </c>
       <c r="N9" s="27" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J10" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K10" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L10" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>249-0534083-8865426</t>
+        </is>
+      </c>
+      <c r="N10" s="27" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 8,225</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t>7 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="I12" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 9,154</t>
+        </is>
+      </c>
+      <c r="M12" s="32" t="inlineStr">
+        <is>
+          <t>8 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -1878,9 +1929,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1970,7 +2021,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.27</v>
@@ -1983,7 +2034,7 @@
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2142,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2675,39 +2726,81 @@
         <v>4</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="29" t="n">
         <v>19.4</v>
       </c>
       <c r="J9" s="34" t="n">
-        <v>929</v>
+        <v>1858</v>
       </c>
       <c r="K9" s="34" t="n">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>249-0534083-8865426</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J10" s="34" t="n">
+        <v>1858</v>
+      </c>
+      <c r="K10" s="34" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I11" s="31" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="J11" s="35" t="n">
-        <v>12093</v>
-      </c>
-      <c r="K11" s="35" t="n">
-        <v>10219</v>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="I12" s="31" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>14880</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>12618</v>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -2900,8 +2993,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2918,6 +3011,8 @@
     <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
     <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
     <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
+    <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2365,15 +2365,15 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2535,9 +2535,9 @@
           <t>3314711712867008960</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>249-4866874-7926210</t>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>249-4866874-7926210, 503-2823993-6428631</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -2575,41 +2575,41 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>3314711712867008960</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>503-2823993-6428631</t>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>250-31255524-9007023, 249-3150938-6827810</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>2010</v>
+        <v>1858</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>1650</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>250-31255524-9007023</t>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>250-5095218-9791066, 249-0534083-8865426</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
@@ -2637,170 +2637,44 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="25" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>6.2</v>
+        <v>19.4</v>
       </c>
       <c r="J7" s="34" t="n">
         <v>1858</v>
       </c>
       <c r="K7" s="34" t="n">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>3314150547079044970</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>249-3150938-6827810</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>多功能不锈钢压蒜器</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>按压式2个装 绿色</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J8" s="34" t="n">
-        <v>1858</v>
-      </c>
-      <c r="K8" s="34" t="n">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>3315532944810035788</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>250-5095218-9791066</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>多功能不锈钢压蒜器</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>按压式2个装 绿色</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J9" s="34" t="n">
-        <v>1858</v>
-      </c>
-      <c r="K9" s="34" t="n">
         <v>1470</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="36" t="inlineStr">
-        <is>
-          <t>3315532944810035788</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>249-0534083-8865426</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>多功能不锈钢压蒜器</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>按压式2个装 绿色</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J10" s="34" t="n">
-        <v>1858</v>
-      </c>
-      <c r="K10" s="34" t="n">
-        <v>1470</v>
-      </c>
-    </row>
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>📊 合计</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>9154</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>7764</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>📊 合计</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="J12" s="35" t="n">
-        <v>14880</v>
-      </c>
-      <c r="K12" s="35" t="n">
-        <v>12618</v>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -2994,7 +2868,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -3002,17 +2876,8 @@
     <hyperlink ref="B4" location="'📥进货表'!A4" display="260718-641864876461684"/>
     <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
     <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
-    <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
-    <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
-    <hyperlink ref="C6" location="'📤销售表'!A6" display="503-2823993-6428631"/>
-    <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
-    <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
-    <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
-    <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
+    <hyperlink ref="B6" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="B7" location="'📥进货表'!A7" display="3315532944810035788"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2365,7 +2365,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -2535,9 +2535,9 @@
           <t>3314711712867008960</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>249-4866874-7926210, 503-2823993-6428631</t>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>249-4866874-7926210</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -2554,19 +2554,19 @@
         <v>3</v>
       </c>
       <c r="G5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="25" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" s="25" t="n">
-        <v>1</v>
       </c>
       <c r="I5" s="29" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>2010</v>
+        <v>1005</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>1650</v>
+        <v>885</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2575,41 +2575,41 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>250-31255524-9007023, 249-3150938-6827810</t>
+          <t>3314711712867008960</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>503-2823993-6428631</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>1858</v>
+        <v>1005</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>1734</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2618,63 +2618,189 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>250-31255524-9007023</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>3314150547079044970</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>249-3150938-6827810</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="K8" s="34" t="n">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
           <t>3315532944810035788</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>250-5095218-9791066, 249-0534083-8865426</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>250-5095218-9791066</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>按压式2个装 绿色</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J9" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>249-0534083-8865426</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="I10" s="29" t="n">
         <v>19.4</v>
       </c>
-      <c r="J7" s="34" t="n">
-        <v>1858</v>
-      </c>
-      <c r="K7" s="34" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="J10" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="K10" s="34" t="n">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I9" s="31" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="J9" s="35" t="n">
+      <c r="I12" s="31" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="J12" s="35" t="n">
         <v>9154</v>
       </c>
-      <c r="K9" s="35" t="n">
-        <v>7764</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
+      <c r="K12" s="35" t="n">
+        <v>8078</v>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -2868,7 +2994,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2876,8 +3002,17 @@
     <hyperlink ref="B4" location="'📥进货表'!A4" display="260718-641864876461684"/>
     <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
     <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
-    <hyperlink ref="B6" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="B7" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
+    <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
+    <hyperlink ref="C6" location="'📤销售表'!A6" display="503-2823993-6428631"/>
+    <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
+    <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
+    <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
+    <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2360,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K202"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2369,11 +2369,9 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2411,30 +2409,20 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>采购数量</t>
+          <t>销售数量</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>销售数量</t>
+          <t>采购金额(元)</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>销售金额(日元)</t>
         </is>
       </c>
       <c r="I2" s="24" t="inlineStr">
-        <is>
-          <t>采购金额(元)</t>
-        </is>
-      </c>
-      <c r="J2" s="24" t="inlineStr">
-        <is>
-          <t>销售金额(日元)</t>
-        </is>
-      </c>
-      <c r="K2" s="24" t="inlineStr">
         <is>
           <t>利润(日元)</t>
         </is>
@@ -2467,19 +2455,13 @@
       <c r="F3" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="29" t="n">
+      <c r="G3" s="29" t="n">
         <v>5.9</v>
       </c>
-      <c r="J3" s="34" t="n">
+      <c r="H3" s="34" t="n">
         <v>1714</v>
       </c>
-      <c r="K3" s="34" t="n">
+      <c r="I3" s="34" t="n">
         <v>1596</v>
       </c>
     </row>
@@ -2510,19 +2492,13 @@
       <c r="F4" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="29" t="n">
+      <c r="G4" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="J4" s="34" t="n">
+      <c r="H4" s="34" t="n">
         <v>1714</v>
       </c>
-      <c r="K4" s="34" t="n">
+      <c r="I4" s="34" t="n">
         <v>1314</v>
       </c>
     </row>
@@ -2551,21 +2527,15 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="29" t="n">
+      <c r="G5" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="J5" s="34" t="n">
+      <c r="H5" s="34" t="n">
         <v>1005</v>
       </c>
-      <c r="K5" s="34" t="n">
+      <c r="I5" s="34" t="n">
         <v>885</v>
       </c>
     </row>
@@ -2594,21 +2564,15 @@
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="29" t="n">
+      <c r="G6" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="J6" s="34" t="n">
+      <c r="H6" s="34" t="n">
         <v>1005</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="I6" s="34" t="n">
         <v>885</v>
       </c>
     </row>
@@ -2637,21 +2601,15 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="G7" s="29" t="n">
         <v>6.2</v>
       </c>
-      <c r="J7" s="34" t="n">
+      <c r="H7" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="K7" s="34" t="n">
+      <c r="I7" s="34" t="n">
         <v>867</v>
       </c>
     </row>
@@ -2680,21 +2638,15 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="29" t="n">
+      <c r="G8" s="29" t="n">
         <v>6.2</v>
       </c>
-      <c r="J8" s="34" t="n">
+      <c r="H8" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="K8" s="34" t="n">
+      <c r="I8" s="34" t="n">
         <v>867</v>
       </c>
     </row>
@@ -2723,21 +2675,15 @@
         </is>
       </c>
       <c r="F9" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="29" t="n">
+      <c r="G9" s="29" t="n">
         <v>19.4</v>
       </c>
-      <c r="J9" s="34" t="n">
+      <c r="H9" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="K9" s="34" t="n">
+      <c r="I9" s="34" t="n">
         <v>832</v>
       </c>
     </row>
@@ -2766,21 +2712,15 @@
         </is>
       </c>
       <c r="F10" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="29" t="n">
+      <c r="G10" s="29" t="n">
         <v>19.4</v>
       </c>
-      <c r="J10" s="34" t="n">
+      <c r="H10" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="K10" s="34" t="n">
+      <c r="I10" s="34" t="n">
         <v>832</v>
       </c>
     </row>
@@ -2791,13 +2731,13 @@
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I12" s="31" t="n">
+      <c r="G12" s="31" t="n">
         <v>113.1</v>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="H12" s="35" t="n">
         <v>9154</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="I12" s="35" t="n">
         <v>8078</v>
       </c>
     </row>
@@ -2993,7 +2933,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1216,7 +1216,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -1719,25 +1719,76 @@
       </c>
       <c r="N10" s="27" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J11" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K11" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L11" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>249-1510675-8261403</t>
+        </is>
+      </c>
+      <c r="N11" s="27" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 9,154</t>
-        </is>
-      </c>
-      <c r="M12" s="32" t="inlineStr">
-        <is>
-          <t>8 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 10,083</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>9 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
@@ -1929,9 +1980,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2012,29 +2063,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46233.89283564815</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2044,25 +2095,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6</v>
+        <v>4.27</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46233.89283564815</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -2142,7 +2193,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2724,24 +2775,60 @@
         <v>832</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>249-1510675-8261403</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="I11" s="34" t="n">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G12" s="31" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <v>9154</v>
-      </c>
-      <c r="I12" s="35" t="n">
-        <v>8078</v>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="G13" s="31" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>10083</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>8910</v>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
@@ -2934,7 +3021,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -2953,6 +3040,8 @@
     <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
     <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
     <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
+    <hyperlink ref="B11" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C11" location="'📤销售表'!A11" display="249-1510675-8261403"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1771,25 +1771,76 @@
       </c>
       <c r="N11" s="27" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J12" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K12" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L12" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>250-5527153-7956617</t>
+        </is>
+      </c>
+      <c r="N12" s="27" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 10,083</t>
-        </is>
-      </c>
-      <c r="M13" s="32" t="inlineStr">
-        <is>
-          <t>9 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 11,012</t>
+        </is>
+      </c>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>10 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
@@ -1980,9 +2031,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2095,29 +2146,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>4.27</v>
+        <v>5.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46233.89283564815</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46233</v>
+        <v>46214</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2178,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -2159,25 +2210,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>4.27</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46233.89283564815</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46234</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -2193,7 +2244,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2812,24 +2863,60 @@
         <v>832</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>3315532944810035788</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>250-5527153-7956617</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G13" s="31" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>10083</v>
-      </c>
-      <c r="I13" s="35" t="n">
-        <v>8910</v>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="G14" s="31" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>11012</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>9742</v>
+      </c>
+    </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
@@ -3021,7 +3108,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -3042,6 +3129,8 @@
     <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
     <hyperlink ref="B11" location="'📥进货表'!A7" display="3315532944810035788"/>
     <hyperlink ref="C11" location="'📤销售表'!A11" display="249-1510675-8261403"/>
+    <hyperlink ref="B12" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C12" location="'📤销售表'!A12" display="250-5527153-7956617"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -717,7 +717,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="41" customWidth="1" min="10" max="10"/>
@@ -980,23 +980,64 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>46236.88541666666</v>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>补货 10个装</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G9" s="31" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="H9" s="32" t="inlineStr">
-        <is>
-          <t>5 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="G10" s="31" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>6 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -1192,8 +1233,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="H10:J10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1823,25 +1864,76 @@
       </c>
       <c r="N12" s="27" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J13" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K13" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L13" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>503-5593381-1019045</t>
+        </is>
+      </c>
+      <c r="N13" s="27" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 11,012</t>
-        </is>
-      </c>
-      <c r="M14" s="32" t="inlineStr">
-        <is>
-          <t>10 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 11,941</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>11 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
@@ -2031,9 +2123,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="I15:L15"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2114,29 +2206,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>6</v>
+        <v>4.46</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (9个)</t>
         </is>
       </c>
     </row>
@@ -2146,29 +2238,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46214</v>
+        <v>46232</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2178,25 +2270,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -2210,25 +2302,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>4.27</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46233.89283564815</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46234</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -2244,7 +2336,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2473,7 +2565,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2900,24 +2992,60 @@
         <v>832</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>503-5593381-1019045</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>837.6</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G14" s="31" t="n">
-        <v>151.9</v>
-      </c>
-      <c r="H14" s="35" t="n">
-        <v>11012</v>
-      </c>
-      <c r="I14" s="35" t="n">
-        <v>9742</v>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="G15" s="31" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>11941</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>10579</v>
+      </c>
+    </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
@@ -3108,7 +3236,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -3131,6 +3259,8 @@
     <hyperlink ref="C11" location="'📤销售表'!A11" display="249-1510675-8261403"/>
     <hyperlink ref="B12" location="'📥进货表'!A7" display="3315532944810035788"/>
     <hyperlink ref="C12" location="'📤销售表'!A12" display="250-5527153-7956617"/>
+    <hyperlink ref="B13" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C13" location="'📤销售表'!A13" display="503-5593381-1019045"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1916,25 +1916,76 @@
       </c>
       <c r="N13" s="27" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J14" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K14" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L14" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>249-4191194-8245444</t>
+        </is>
+      </c>
+      <c r="N14" s="27" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 11,941</t>
-        </is>
-      </c>
-      <c r="M15" s="32" t="inlineStr">
-        <is>
-          <t>11 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 12,870</t>
+        </is>
+      </c>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>12 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
@@ -2123,9 +2174,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2215,7 +2266,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2224,11 +2275,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (9个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2387,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -2554,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2565,7 +2616,6 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2616,11 +2666,6 @@
           <t>销售金额(日元)</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
-        <is>
-          <t>利润(日元)</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="n">
@@ -2655,9 +2700,6 @@
       <c r="H3" s="34" t="n">
         <v>1714</v>
       </c>
-      <c r="I3" s="34" t="n">
-        <v>1596</v>
-      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="25" t="n">
@@ -2692,9 +2734,6 @@
       <c r="H4" s="34" t="n">
         <v>1714</v>
       </c>
-      <c r="I4" s="34" t="n">
-        <v>1314</v>
-      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="25" t="n">
@@ -2729,9 +2768,6 @@
       <c r="H5" s="34" t="n">
         <v>1005</v>
       </c>
-      <c r="I5" s="34" t="n">
-        <v>885</v>
-      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="25" t="n">
@@ -2766,9 +2802,6 @@
       <c r="H6" s="34" t="n">
         <v>1005</v>
       </c>
-      <c r="I6" s="34" t="n">
-        <v>885</v>
-      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="25" t="n">
@@ -2803,9 +2836,6 @@
       <c r="H7" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I7" s="34" t="n">
-        <v>867</v>
-      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="25" t="n">
@@ -2840,9 +2870,6 @@
       <c r="H8" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I8" s="34" t="n">
-        <v>867</v>
-      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="25" t="n">
@@ -2877,9 +2904,6 @@
       <c r="H9" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I9" s="34" t="n">
-        <v>832</v>
-      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="25" t="n">
@@ -2914,9 +2938,6 @@
       <c r="H10" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I10" s="34" t="n">
-        <v>832</v>
-      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="25" t="n">
@@ -2951,9 +2972,6 @@
       <c r="H11" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I11" s="34" t="n">
-        <v>832</v>
-      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="25" t="n">
@@ -2988,9 +3006,6 @@
       <c r="H12" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I12" s="34" t="n">
-        <v>832</v>
-      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="25" t="n">
@@ -3025,28 +3040,55 @@
       <c r="H13" s="34" t="n">
         <v>929</v>
       </c>
-      <c r="I13" s="34" t="n">
-        <v>837.6</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>249-4191194-8245444</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢压蒜器</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>按压式2个装 绿色</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G15" s="31" t="n">
-        <v>197.6</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>11941</v>
-      </c>
-      <c r="I15" s="35" t="n">
-        <v>10579</v>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="G16" s="31" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>12870</v>
+      </c>
+    </row>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
@@ -3235,8 +3277,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
@@ -3261,6 +3303,8 @@
     <hyperlink ref="C12" location="'📤销售表'!A12" display="250-5527153-7956617"/>
     <hyperlink ref="B13" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C13" location="'📤销售表'!A13" display="503-5593381-1019045"/>
+    <hyperlink ref="B14" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C14" location="'📤销售表'!A14" display="249-4191194-8245444"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2611,8 +2611,8 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>透明</t>
         </is>
       </c>
       <c r="F3" s="25" t="n">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>琥珀色</t>
         </is>
       </c>
       <c r="F4" s="25" t="n">
@@ -2751,19 +2751,19 @@
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H5" s="34" t="n">
         <v>1005</v>
@@ -2785,19 +2785,19 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H6" s="34" t="n">
         <v>1005</v>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="H7" s="34" t="n">
         <v>929</v>
@@ -2853,19 +2853,19 @@
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="H8" s="34" t="n">
         <v>929</v>
@@ -2887,19 +2887,19 @@
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19.4</v>
+        <v>4.85</v>
       </c>
       <c r="H9" s="34" t="n">
         <v>929</v>
@@ -2921,19 +2921,19 @@
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>19.4</v>
+        <v>4.85</v>
       </c>
       <c r="H10" s="34" t="n">
         <v>929</v>
@@ -2955,19 +2955,19 @@
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>19.4</v>
+        <v>4.85</v>
       </c>
       <c r="H11" s="34" t="n">
         <v>929</v>
@@ -2989,19 +2989,19 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>19.4</v>
+        <v>4.85</v>
       </c>
       <c r="H12" s="34" t="n">
         <v>929</v>
@@ -3023,19 +3023,19 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>45.7</v>
+        <v>4.57</v>
       </c>
       <c r="H13" s="34" t="n">
         <v>929</v>
@@ -3057,19 +3057,19 @@
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>45.7</v>
+        <v>4.57</v>
       </c>
       <c r="H14" s="34" t="n">
         <v>929</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="G16" s="31" t="n">
-        <v>243.3</v>
+        <v>72.64</v>
       </c>
       <c r="H16" s="35" t="n">
         <v>12870</v>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1968,25 +1968,76 @@
       </c>
       <c r="N14" s="27" t="n"/>
     </row>
-    <row r="15"/>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J15" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K15" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L15" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M15" s="25" t="inlineStr">
+        <is>
+          <t>249-3982035-2006207</t>
+        </is>
+      </c>
+      <c r="N15" s="27" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 12,870</t>
-        </is>
-      </c>
-      <c r="M16" s="32" t="inlineStr">
-        <is>
-          <t>12 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 13,799</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>13 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -2174,9 +2225,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="I17:L17"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2266,7 +2317,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2275,11 +2326,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (8个)</t>
+          <t>库存充足 (7个)</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2438,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -3075,21 +3126,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>249-3982035-2006207</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G16" s="31" t="n">
-        <v>72.64</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>12870</v>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="G17" s="31" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>13799</v>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -3277,7 +3361,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3305,6 +3389,8 @@
     <hyperlink ref="C13" location="'📤销售表'!A13" display="503-5593381-1019045"/>
     <hyperlink ref="B14" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C14" location="'📤销售表'!A14" display="249-4191194-8245444"/>
+    <hyperlink ref="B15" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C15" location="'📤销售表'!A15" display="249-3982035-2006207"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2020,25 +2020,76 @@
       </c>
       <c r="N15" s="27" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J16" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K16" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L16" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>250-0207357-6815003</t>
+        </is>
+      </c>
+      <c r="N16" s="27" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 13,799</t>
-        </is>
-      </c>
-      <c r="M17" s="32" t="inlineStr">
-        <is>
-          <t>13 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 14,728</t>
+        </is>
+      </c>
+      <c r="M18" s="32" t="inlineStr">
+        <is>
+          <t>14 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -2225,9 +2276,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="I18:L18"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2317,7 +2368,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2326,11 +2377,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (7个)</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2489,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -3160,21 +3211,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>250-0207357-6815003</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G17" s="31" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>13799</v>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="G18" s="31" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>14728</v>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -3361,7 +3445,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3391,6 +3475,8 @@
     <hyperlink ref="C14" location="'📤销售表'!A14" display="249-4191194-8245444"/>
     <hyperlink ref="B15" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C15" location="'📤销售表'!A15" display="249-3982035-2006207"/>
+    <hyperlink ref="B16" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C16" location="'📤销售表'!A16" display="250-0207357-6815003"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2072,25 +2072,76 @@
       </c>
       <c r="N16" s="27" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J17" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K17" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L17" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t>250-6902845-9205438</t>
+        </is>
+      </c>
+      <c r="N17" s="27" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 14,728</t>
-        </is>
-      </c>
-      <c r="M18" s="32" t="inlineStr">
-        <is>
-          <t>14 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 15,657</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>15 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
@@ -2276,9 +2327,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2368,7 +2419,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2377,11 +2428,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2540,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -3245,21 +3296,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>250-6902845-9205438</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G18" s="31" t="n">
-        <v>81.78</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>14728</v>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="G19" s="31" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>15657</v>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
@@ -3445,7 +3529,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3477,6 +3561,8 @@
     <hyperlink ref="C15" location="'📤销售表'!A15" display="249-3982035-2006207"/>
     <hyperlink ref="B16" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C16" location="'📤销售表'!A16" display="250-0207357-6815003"/>
+    <hyperlink ref="B17" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2124,25 +2124,76 @@
       </c>
       <c r="N17" s="27" t="n"/>
     </row>
-    <row r="18"/>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J18" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K18" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L18" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M18" s="25" t="inlineStr">
+        <is>
+          <t>250-3154848-2935021</t>
+        </is>
+      </c>
+      <c r="N18" s="27" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I19" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 15,657</t>
-        </is>
-      </c>
-      <c r="M19" s="32" t="inlineStr">
-        <is>
-          <t>15 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 16,586</t>
+        </is>
+      </c>
+      <c r="M20" s="32" t="inlineStr">
+        <is>
+          <t>16 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
@@ -2327,9 +2378,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2419,7 +2470,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2428,11 +2479,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (4个)</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2591,7 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
@@ -3330,21 +3381,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>250-3154848-2935021</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G19" s="31" t="n">
-        <v>86.34999999999999</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>15657</v>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="G20" s="31" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>16586</v>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
@@ -3529,7 +3613,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3563,6 +3647,8 @@
     <hyperlink ref="C16" location="'📤销售表'!A16" display="250-0207357-6815003"/>
     <hyperlink ref="B17" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
+    <hyperlink ref="B18" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1022,23 +1022,60 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>46244.33587962963</v>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX塑料除黄剂</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>100ml+毛巾</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G10" s="31" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="H10" s="32" t="inlineStr">
-        <is>
-          <t>6 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="G11" s="31" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>7 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
@@ -1232,9 +1269,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2176,25 +2213,76 @@
       </c>
       <c r="N18" s="27" t="n"/>
     </row>
-    <row r="19"/>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J19" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K19" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L19" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M19" s="25" t="inlineStr">
+        <is>
+          <t>249-8279106-7397442</t>
+        </is>
+      </c>
+      <c r="N19" s="27" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I20" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 16,586</t>
-        </is>
-      </c>
-      <c r="M20" s="32" t="inlineStr">
-        <is>
-          <t>16 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 18,259</t>
+        </is>
+      </c>
+      <c r="M21" s="32" t="inlineStr">
+        <is>
+          <t>17 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -2378,9 +2466,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2493,29 +2581,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46232</v>
+        <v>46242</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -2525,29 +2613,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46232</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2557,49 +2645,80 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>46215.5080787037</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F7" s="33" t="n">
         <v>46221.59108796297</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G7" s="33" t="n">
         <v>46221</v>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>4 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="D9" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>5 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -2795,8 +2914,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E9:H9"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3415,21 +3534,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>249-8279106-7397442</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G20" s="31" t="n">
-        <v>90.92</v>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>16586</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="G21" s="31" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>18259</v>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -3613,7 +3765,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3649,6 +3801,8 @@
     <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
     <hyperlink ref="B18" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
+    <hyperlink ref="B19" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C19" location="'📤销售表'!A19" display="249-8279106-7397442"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2265,25 +2265,76 @@
       </c>
       <c r="N19" s="27" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J20" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K20" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L20" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M20" s="25" t="inlineStr">
+        <is>
+          <t>503-5134375-2874203</t>
+        </is>
+      </c>
+      <c r="N20" s="27" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 18,259</t>
-        </is>
-      </c>
-      <c r="M21" s="32" t="inlineStr">
-        <is>
-          <t>17 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 19,932</t>
+        </is>
+      </c>
+      <c r="M22" s="32" t="inlineStr">
+        <is>
+          <t>18 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
@@ -2466,9 +2517,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2581,29 +2632,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46242</v>
+        <v>46232</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2613,25 +2664,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -2711,7 +2762,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3568,21 +3619,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>503-5134375-2874203</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G21" s="31" t="n">
-        <v>97.59</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>18259</v>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="G22" s="31" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>19932</v>
+      </c>
+    </row>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
@@ -3765,7 +3849,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3803,6 +3887,8 @@
     <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
     <hyperlink ref="B19" location="'📥进货表'!A9" display="3316792152573008960"/>
     <hyperlink ref="C19" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B20" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C20" location="'📤销售表'!A20" display="503-5134375-2874203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2317,26 +2317,128 @@
       </c>
       <c r="N20" s="27" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J21" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K21" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L21" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M21" s="25" t="inlineStr">
+        <is>
+          <t>250-1961123-9212663</t>
+        </is>
+      </c>
+      <c r="N21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J22" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K22" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L22" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>503-2776046-0470254</t>
+        </is>
+      </c>
+      <c r="N22" s="27" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I22" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 19,932</t>
-        </is>
-      </c>
-      <c r="M22" s="32" t="inlineStr">
-        <is>
-          <t>18 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 21,790</t>
+        </is>
+      </c>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>20 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -2517,9 +2619,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="I24:L24"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2609,7 +2711,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.46</v>
@@ -2618,11 +2720,11 @@
         <v>46236.88541666666</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (4个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2864,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3591,32 +3693,32 @@
       </c>
       <c r="B19" s="36" t="inlineStr">
         <is>
-          <t>3316792152573008960</t>
+          <t>3315760069697054152</t>
         </is>
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>249-8279106-7397442</t>
+          <t>250-1961123-9212663</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="29" t="n">
-        <v>6.67</v>
+        <v>4.57</v>
       </c>
       <c r="H19" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -3625,50 +3727,116 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
+          <t>3315760069697054152</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>503-2776046-0470254</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
           <t>3316792152573008960</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>249-8279106-7397442</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>503-5134375-2874203</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F20" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="29" t="n">
+      <c r="F22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="29" t="n">
         <v>6.67</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H22" s="34" t="n">
         <v>1673</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G22" s="31" t="n">
-        <v>104.26</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>19932</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
+      <c r="G24" s="31" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>21790</v>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -3849,7 +4017,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -3885,10 +4053,14 @@
     <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
     <hyperlink ref="B18" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
-    <hyperlink ref="B19" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C19" location="'📤销售表'!A19" display="249-8279106-7397442"/>
-    <hyperlink ref="B20" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C20" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="B19" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C19" location="'📤销售表'!A21" display="250-1961123-9212663"/>
+    <hyperlink ref="B20" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C20" location="'📤销售表'!A22" display="503-2776046-0470254"/>
+    <hyperlink ref="B21" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C21" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B22" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C22" location="'📤销售表'!A20" display="503-5134375-2874203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1060,23 +1060,64 @@
       </c>
       <c r="J9" s="27" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢按压式压蒜器</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>按压压蒜器1个 绿色</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>331637642022008960</t>
+        </is>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>补货10个</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G11" s="31" t="n">
-        <v>135.2</v>
-      </c>
-      <c r="H11" s="32" t="inlineStr">
-        <is>
-          <t>7 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="G12" s="31" t="n">
+        <v>184</v>
+      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>8 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -1269,9 +1310,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="H12:J12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2421,25 +2462,76 @@
       </c>
       <c r="N22" s="27" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J23" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K23" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L23" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M23" s="25" t="inlineStr">
+        <is>
+          <t>250-5218699-2591031</t>
+        </is>
+      </c>
+      <c r="N23" s="27" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I24" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 21,790</t>
-        </is>
-      </c>
-      <c r="M24" s="32" t="inlineStr">
-        <is>
-          <t>20 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 22,719</t>
+        </is>
+      </c>
+      <c r="M25" s="32" t="inlineStr">
+        <is>
+          <t>21 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -2619,9 +2711,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="I25:L25"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2644,7 +2736,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2702,29 +2794,27 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>多功能不锈钢按压式压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>按压压蒜器1个 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.46</v>
+        <v>4.88</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46236.88541666666</v>
-      </c>
-      <c r="G3" s="33" t="n">
-        <v>46246</v>
-      </c>
+        <v>46247</v>
+      </c>
+      <c r="G3" s="25" t="n"/>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (10个)</t>
         </is>
       </c>
     </row>
@@ -2766,25 +2856,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.67</v>
+        <v>4.46</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46236.88541666666</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -2798,29 +2888,29 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>6.67</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46244</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2830,49 +2920,80 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>46215.5080787037</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F8" s="33" t="n">
         <v>46221.59108796297</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G8" s="33" t="n">
         <v>46221</v>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="9"/>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D9" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>5 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="D10" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>6 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -3067,8 +3188,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:H10"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3761,32 +3882,32 @@
       </c>
       <c r="B21" s="36" t="inlineStr">
         <is>
-          <t>3316792152573008960</t>
+          <t>3315760069697054152</t>
         </is>
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>249-8279106-7397442</t>
+          <t>250-5218699-2591031</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="29" t="n">
-        <v>6.67</v>
+        <v>4.57</v>
       </c>
       <c r="H21" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -3800,7 +3921,7 @@
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>503-5134375-2874203</t>
+          <t>249-8279106-7397442</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -3823,21 +3944,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>503-5134375-2874203</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G24" s="31" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>21790</v>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="G25" s="31" t="n">
+        <v>117.97</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>22719</v>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -4017,7 +4171,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4057,10 +4211,12 @@
     <hyperlink ref="C19" location="'📤销售表'!A21" display="250-1961123-9212663"/>
     <hyperlink ref="B20" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C20" location="'📤销售表'!A22" display="503-2776046-0470254"/>
-    <hyperlink ref="B21" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C21" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B21" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C21" location="'📤销售表'!A23" display="250-5218699-2591031"/>
     <hyperlink ref="B22" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C22" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="C22" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B23" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C23" location="'📤销售表'!A20" display="503-5134375-2874203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2794,27 +2794,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢按压式压蒜器</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压压蒜器1个 绿色</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.88</v>
+        <v>4.62</v>
       </c>
       <c r="F3" s="33" t="n">
         <v>46247</v>
       </c>
-      <c r="G3" s="25" t="n"/>
+      <c r="G3" s="33" t="n">
+        <v>46246</v>
+      </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (10个)</t>
+          <t>库存充足 (11个)</t>
         </is>
       </c>
     </row>
@@ -2856,25 +2858,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>4.46</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46236.88541666666</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -2888,29 +2890,29 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>6.67</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46244</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -2920,25 +2922,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -2946,54 +2948,23 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>46221.59108796297</v>
-      </c>
-      <c r="G8" s="33" t="n">
-        <v>46221</v>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="8"/>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D9" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>6 种商品</t>
-        </is>
-      </c>
-    </row>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>5 种商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -3188,8 +3159,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E9:H9"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2514,25 +2514,76 @@
       </c>
       <c r="N23" s="27" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="34" t="n">
+        <v>1397</v>
+      </c>
+      <c r="J24" s="34" t="n">
+        <v>127</v>
+      </c>
+      <c r="K24" s="34" t="n">
+        <v>338</v>
+      </c>
+      <c r="L24" s="34" t="n">
+        <v>1857</v>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>250-8757664-8770260</t>
+        </is>
+      </c>
+      <c r="N24" s="27" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I25" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 22,719</t>
-        </is>
-      </c>
-      <c r="M25" s="32" t="inlineStr">
-        <is>
-          <t>21 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 24,576</t>
+        </is>
+      </c>
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>22 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
@@ -2711,9 +2762,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="I26:L26"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2736,7 +2787,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2803,7 +2854,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -2812,11 +2863,11 @@
         <v>46247</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (11个)</t>
+          <t>库存充足 (9个)</t>
         </is>
       </c>
     </row>
@@ -2956,7 +3007,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3887,32 +3938,32 @@
       </c>
       <c r="B22" s="36" t="inlineStr">
         <is>
-          <t>3316792152573008960</t>
+          <t>3315760069697054152</t>
         </is>
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>249-8279106-7397442</t>
+          <t>250-8757664-8770260</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F22" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>1673</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -3926,7 +3977,7 @@
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>503-5134375-2874203</t>
+          <t>249-8279106-7397442</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -3949,21 +4000,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>503-5134375-2874203</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G25" s="31" t="n">
-        <v>117.97</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>22719</v>
-      </c>
-    </row>
-    <row r="26"/>
+      <c r="G26" s="31" t="n">
+        <v>127.11</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>24576</v>
+      </c>
+    </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
@@ -4142,7 +4226,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4184,10 +4268,12 @@
     <hyperlink ref="C20" location="'📤销售表'!A22" display="503-2776046-0470254"/>
     <hyperlink ref="B21" location="'📥进货表'!A8" display="3315760069697054152"/>
     <hyperlink ref="C21" location="'📤销售表'!A23" display="250-5218699-2591031"/>
-    <hyperlink ref="B22" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C22" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B22" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C22" location="'📤销售表'!A24" display="250-8757664-8770260"/>
     <hyperlink ref="B23" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C23" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="C23" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B24" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2566,25 +2566,76 @@
       </c>
       <c r="N24" s="27" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>1X-GB0W-BY30</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="34" t="n">
+        <v>1122</v>
+      </c>
+      <c r="J25" s="34" t="n">
+        <v>102</v>
+      </c>
+      <c r="K25" s="34" t="n">
+        <v>117</v>
+      </c>
+      <c r="L25" s="34" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M25" s="25" t="inlineStr">
+        <is>
+          <t>249-9105063-4908645</t>
+        </is>
+      </c>
+      <c r="N25" s="27" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I26" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 24,576</t>
-        </is>
-      </c>
-      <c r="M26" s="32" t="inlineStr">
-        <is>
-          <t>22 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 25,581</t>
+        </is>
+      </c>
+      <c r="M27" s="32" t="inlineStr">
+        <is>
+          <t>23 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
@@ -2762,9 +2813,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="I27:L27"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2877,25 +2928,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -2909,29 +2960,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.67</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46244</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -2941,25 +2992,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -2973,25 +3024,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46230.48587962963</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46221</v>
+        <v>46249</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3007,7 +3058,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3428,32 +3479,32 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
+          <t>3314711712867008960</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>250-31255524-9007023</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>切蒜器带透明收纳容器</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H7" s="34" t="n">
-        <v>929</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -3467,7 +3518,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>249-3150938-6827810</t>
+          <t>250-31255524-9007023</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
@@ -3496,12 +3547,12 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>3315532944810035788</t>
+          <t>3314150547079044970</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>250-5095218-9791066</t>
+          <t>249-3150938-6827810</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
@@ -3518,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>4.85</v>
+        <v>3.1</v>
       </c>
       <c r="H9" s="34" t="n">
         <v>929</v>
@@ -3535,7 +3586,7 @@
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>249-0534083-8865426</t>
+          <t>250-5095218-9791066</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
@@ -3569,7 +3620,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>249-1510675-8261403</t>
+          <t>249-0534083-8865426</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
@@ -3603,7 +3654,7 @@
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>250-5527153-7956617</t>
+          <t>249-1510675-8261403</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
@@ -3632,12 +3683,12 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>3315760069697054152</t>
+          <t>3315532944810035788</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>503-5593381-1019045</t>
+          <t>250-5527153-7956617</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
@@ -3654,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>4.57</v>
+        <v>4.85</v>
       </c>
       <c r="H13" s="34" t="n">
         <v>929</v>
@@ -3671,7 +3722,7 @@
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>249-4191194-8245444</t>
+          <t>503-5593381-1019045</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -3705,7 +3756,7 @@
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>249-3982035-2006207</t>
+          <t>249-4191194-8245444</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
@@ -3739,7 +3790,7 @@
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>250-0207357-6815003</t>
+          <t>249-3982035-2006207</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -3773,7 +3824,7 @@
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>250-6902845-9205438</t>
+          <t>250-0207357-6815003</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -3807,7 +3858,7 @@
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>250-3154848-2935021</t>
+          <t>250-6902845-9205438</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -3841,7 +3892,7 @@
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>250-1961123-9212663</t>
+          <t>250-3154848-2935021</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -3875,7 +3926,7 @@
       </c>
       <c r="C20" s="36" t="inlineStr">
         <is>
-          <t>503-2776046-0470254</t>
+          <t>250-1961123-9212663</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -3909,7 +3960,7 @@
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>250-5218699-2591031</t>
+          <t>503-2776046-0470254</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
@@ -3943,7 +3994,7 @@
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>250-8757664-8770260</t>
+          <t>250-5218699-2591031</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -3957,13 +4008,13 @@
         </is>
       </c>
       <c r="F22" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>9.140000000000001</v>
+        <v>4.57</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>1857</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -3972,32 +4023,32 @@
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>3316792152573008960</t>
+          <t>3315760069697054152</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>249-8279106-7397442</t>
+          <t>250-8757664-8770260</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F23" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="29" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H23" s="34" t="n">
-        <v>1673</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -4011,7 +4062,7 @@
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>503-5134375-2874203</t>
+          <t>249-8279106-7397442</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -4034,21 +4085,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>503-5134375-2874203</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G26" s="31" t="n">
-        <v>127.11</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>24576</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="G27" s="31" t="n">
+        <v>133.11</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>25581</v>
+      </c>
+    </row>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
@@ -4226,7 +4310,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4238,42 +4322,44 @@
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
     <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C6" location="'📤销售表'!A6" display="503-2823993-6428631"/>
-    <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
+    <hyperlink ref="B7" location="'📥进货表'!A5" display="3314711712867008960"/>
+    <hyperlink ref="C7" location="'📤销售表'!A25" display="249-9105063-4908645"/>
     <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
-    <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
+    <hyperlink ref="C8" location="'📤销售表'!A7" display="250-31255524-9007023"/>
+    <hyperlink ref="B9" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C9" location="'📤销售表'!A8" display="249-3150938-6827810"/>
     <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
+    <hyperlink ref="C10" location="'📤销售表'!A9" display="250-5095218-9791066"/>
     <hyperlink ref="B11" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C11" location="'📤销售表'!A11" display="249-1510675-8261403"/>
+    <hyperlink ref="C11" location="'📤销售表'!A10" display="249-0534083-8865426"/>
     <hyperlink ref="B12" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C12" location="'📤销售表'!A12" display="250-5527153-7956617"/>
-    <hyperlink ref="B13" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C13" location="'📤销售表'!A13" display="503-5593381-1019045"/>
+    <hyperlink ref="C12" location="'📤销售表'!A11" display="249-1510675-8261403"/>
+    <hyperlink ref="B13" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C13" location="'📤销售表'!A12" display="250-5527153-7956617"/>
     <hyperlink ref="B14" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C14" location="'📤销售表'!A14" display="249-4191194-8245444"/>
+    <hyperlink ref="C14" location="'📤销售表'!A13" display="503-5593381-1019045"/>
     <hyperlink ref="B15" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C15" location="'📤销售表'!A15" display="249-3982035-2006207"/>
+    <hyperlink ref="C15" location="'📤销售表'!A14" display="249-4191194-8245444"/>
     <hyperlink ref="B16" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C16" location="'📤销售表'!A16" display="250-0207357-6815003"/>
+    <hyperlink ref="C16" location="'📤销售表'!A15" display="249-3982035-2006207"/>
     <hyperlink ref="B17" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
+    <hyperlink ref="C17" location="'📤销售表'!A16" display="250-0207357-6815003"/>
     <hyperlink ref="B18" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
+    <hyperlink ref="C18" location="'📤销售表'!A17" display="250-6902845-9205438"/>
     <hyperlink ref="B19" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C19" location="'📤销售表'!A21" display="250-1961123-9212663"/>
+    <hyperlink ref="C19" location="'📤销售表'!A18" display="250-3154848-2935021"/>
     <hyperlink ref="B20" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C20" location="'📤销售表'!A22" display="503-2776046-0470254"/>
+    <hyperlink ref="C20" location="'📤销售表'!A21" display="250-1961123-9212663"/>
     <hyperlink ref="B21" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C21" location="'📤销售表'!A23" display="250-5218699-2591031"/>
+    <hyperlink ref="C21" location="'📤销售表'!A22" display="503-2776046-0470254"/>
     <hyperlink ref="B22" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C22" location="'📤销售表'!A24" display="250-8757664-8770260"/>
-    <hyperlink ref="B23" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C23" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="C22" location="'📤销售表'!A23" display="250-5218699-2591031"/>
+    <hyperlink ref="B23" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C23" location="'📤销售表'!A24" display="250-8757664-8770260"/>
     <hyperlink ref="B24" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="C24" location="'📤销售表'!A19" display="249-8279106-7397442"/>
+    <hyperlink ref="B25" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C25" location="'📤销售表'!A20" display="503-5134375-2874203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -10,7 +10,8 @@
     <sheet name="📥进货表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="📤销售表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="📦库存表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="🔗关联视图" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="❌库存遗失表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="🔗关联视图" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,23 +1103,64 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>46251.90046296296</v>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX玻璃修复膏</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>50g+海绵</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>3316979100148008960</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>补货3个（旧批次库存遗失补货）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G12" s="31" t="n">
-        <v>184</v>
-      </c>
-      <c r="H12" s="32" t="inlineStr">
-        <is>
-          <t>8 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="G13" s="31" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>9 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
@@ -1311,8 +1353,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2928,29 +2970,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.67</v>
+        <v>6.08</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -2960,29 +3002,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46244</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -2992,25 +3034,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -3024,25 +3066,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46230.48587962963</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46249</v>
+        <v>46221</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3058,7 +3100,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3275,6 +3317,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I202"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>❌ 库存遗失表 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>遗失数量</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>遗失时间</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>关联采购订单号</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>关联销售订单号</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>遗失原因</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX玻璃修复膏</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>50g+海绵</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>3314878984043005675</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>249-9105063-4908645</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>库存遗失，无法发货</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>已重新采购3个（3316979100148008960），销售订单转关联新批次</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>📊 遗失合计</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>1 笔遗失记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="A5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3479,32 +3859,32 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>3314711712867008960</t>
+          <t>3314150547079044970</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-31255524-9007023</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="H7" s="34" t="n">
-        <v>1005</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -3518,7 +3898,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>250-31255524-9007023</t>
+          <t>249-3150938-6827810</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
@@ -3547,12 +3927,12 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>3314150547079044970</t>
+          <t>3315532944810035788</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>249-3150938-6827810</t>
+          <t>250-5095218-9791066</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
@@ -3569,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="H9" s="34" t="n">
         <v>929</v>
@@ -3586,7 +3966,7 @@
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>250-5095218-9791066</t>
+          <t>249-0534083-8865426</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
@@ -3620,7 +4000,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>249-0534083-8865426</t>
+          <t>249-1510675-8261403</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
@@ -3654,7 +4034,7 @@
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>249-1510675-8261403</t>
+          <t>250-5527153-7956617</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
@@ -3683,12 +4063,12 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>3315532944810035788</t>
+          <t>3315760069697054152</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>250-5527153-7956617</t>
+          <t>503-5593381-1019045</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
@@ -3705,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>4.85</v>
+        <v>4.57</v>
       </c>
       <c r="H13" s="34" t="n">
         <v>929</v>
@@ -3722,7 +4102,7 @@
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>503-5593381-1019045</t>
+          <t>249-4191194-8245444</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -3756,7 +4136,7 @@
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>249-4191194-8245444</t>
+          <t>249-3982035-2006207</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
@@ -3790,7 +4170,7 @@
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>249-3982035-2006207</t>
+          <t>250-0207357-6815003</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -3824,7 +4204,7 @@
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>250-0207357-6815003</t>
+          <t>250-6902845-9205438</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -3858,7 +4238,7 @@
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>250-6902845-9205438</t>
+          <t>250-3154848-2935021</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -3892,7 +4272,7 @@
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>250-3154848-2935021</t>
+          <t>250-1961123-9212663</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -3926,7 +4306,7 @@
       </c>
       <c r="C20" s="36" t="inlineStr">
         <is>
-          <t>250-1961123-9212663</t>
+          <t>503-2776046-0470254</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -3960,7 +4340,7 @@
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>503-2776046-0470254</t>
+          <t>250-5218699-2591031</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
@@ -3994,7 +4374,7 @@
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>250-5218699-2591031</t>
+          <t>250-8757664-8770260</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -4008,13 +4388,13 @@
         </is>
       </c>
       <c r="F22" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>4.57</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>929</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -4023,32 +4403,32 @@
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>3315760069697054152</t>
+          <t>3316792152573008960</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>250-8757664-8770260</t>
+          <t>249-8279106-7397442</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>切蒜器带透明收纳容器</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F23" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="29" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="H23" s="34" t="n">
-        <v>1857</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -4062,7 +4442,7 @@
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>249-8279106-7397442</t>
+          <t>503-5134375-2874203</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -4091,32 +4471,32 @@
       </c>
       <c r="B25" s="36" t="inlineStr">
         <is>
-          <t>3316792152573008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
-          <t>503-5134375-2874203</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>6.67</v>
+        <v>6.17</v>
       </c>
       <c r="H25" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="26"/>
@@ -4127,7 +4507,7 @@
         </is>
       </c>
       <c r="G27" s="31" t="n">
-        <v>133.11</v>
+        <v>133.28</v>
       </c>
       <c r="H27" s="35" t="n">
         <v>25581</v>
@@ -4322,44 +4702,44 @@
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
     <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C6" location="'📤销售表'!A6" display="503-2823993-6428631"/>
-    <hyperlink ref="B7" location="'📥进货表'!A5" display="3314711712867008960"/>
-    <hyperlink ref="C7" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="B7" location="'📥进货表'!A6" display="3314150547079044970"/>
+    <hyperlink ref="C7" location="'📤销售表'!A7" display="250-31255524-9007023"/>
     <hyperlink ref="B8" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C8" location="'📤销售表'!A7" display="250-31255524-9007023"/>
-    <hyperlink ref="B9" location="'📥进货表'!A6" display="3314150547079044970"/>
-    <hyperlink ref="C9" location="'📤销售表'!A8" display="249-3150938-6827810"/>
+    <hyperlink ref="C8" location="'📤销售表'!A8" display="249-3150938-6827810"/>
+    <hyperlink ref="B9" location="'📥进货表'!A7" display="3315532944810035788"/>
+    <hyperlink ref="C9" location="'📤销售表'!A9" display="250-5095218-9791066"/>
     <hyperlink ref="B10" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C10" location="'📤销售表'!A9" display="250-5095218-9791066"/>
+    <hyperlink ref="C10" location="'📤销售表'!A10" display="249-0534083-8865426"/>
     <hyperlink ref="B11" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C11" location="'📤销售表'!A10" display="249-0534083-8865426"/>
+    <hyperlink ref="C11" location="'📤销售表'!A11" display="249-1510675-8261403"/>
     <hyperlink ref="B12" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C12" location="'📤销售表'!A11" display="249-1510675-8261403"/>
-    <hyperlink ref="B13" location="'📥进货表'!A7" display="3315532944810035788"/>
-    <hyperlink ref="C13" location="'📤销售表'!A12" display="250-5527153-7956617"/>
+    <hyperlink ref="C12" location="'📤销售表'!A12" display="250-5527153-7956617"/>
+    <hyperlink ref="B13" location="'📥进货表'!A8" display="3315760069697054152"/>
+    <hyperlink ref="C13" location="'📤销售表'!A13" display="503-5593381-1019045"/>
     <hyperlink ref="B14" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C14" location="'📤销售表'!A13" display="503-5593381-1019045"/>
+    <hyperlink ref="C14" location="'📤销售表'!A14" display="249-4191194-8245444"/>
     <hyperlink ref="B15" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C15" location="'📤销售表'!A14" display="249-4191194-8245444"/>
+    <hyperlink ref="C15" location="'📤销售表'!A15" display="249-3982035-2006207"/>
     <hyperlink ref="B16" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C16" location="'📤销售表'!A15" display="249-3982035-2006207"/>
+    <hyperlink ref="C16" location="'📤销售表'!A16" display="250-0207357-6815003"/>
     <hyperlink ref="B17" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C17" location="'📤销售表'!A16" display="250-0207357-6815003"/>
+    <hyperlink ref="C17" location="'📤销售表'!A17" display="250-6902845-9205438"/>
     <hyperlink ref="B18" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C18" location="'📤销售表'!A17" display="250-6902845-9205438"/>
+    <hyperlink ref="C18" location="'📤销售表'!A18" display="250-3154848-2935021"/>
     <hyperlink ref="B19" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C19" location="'📤销售表'!A18" display="250-3154848-2935021"/>
+    <hyperlink ref="C19" location="'📤销售表'!A21" display="250-1961123-9212663"/>
     <hyperlink ref="B20" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C20" location="'📤销售表'!A21" display="250-1961123-9212663"/>
+    <hyperlink ref="C20" location="'📤销售表'!A22" display="503-2776046-0470254"/>
     <hyperlink ref="B21" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C21" location="'📤销售表'!A22" display="503-2776046-0470254"/>
+    <hyperlink ref="C21" location="'📤销售表'!A23" display="250-5218699-2591031"/>
     <hyperlink ref="B22" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C22" location="'📤销售表'!A23" display="250-5218699-2591031"/>
-    <hyperlink ref="B23" location="'📥进货表'!A8" display="3315760069697054152"/>
-    <hyperlink ref="C23" location="'📤销售表'!A24" display="250-8757664-8770260"/>
+    <hyperlink ref="C22" location="'📤销售表'!A24" display="250-8757664-8770260"/>
+    <hyperlink ref="B23" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C23" location="'📤销售表'!A19" display="249-8279106-7397442"/>
     <hyperlink ref="B24" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C24" location="'📤销售表'!A19" display="249-8279106-7397442"/>
-    <hyperlink ref="B25" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C25" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
+    <hyperlink ref="B25" location="'📥进货表'!A11" display="3316979100148008960"/>
+    <hyperlink ref="C25" location="'📤销售表'!A25" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3317,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3326,9 +3326,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3371,15 +3370,10 @@
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>关联销售订单号</t>
+          <t>遗失原因</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
-        <is>
-          <t>遗失原因</t>
-        </is>
-      </c>
-      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -3412,15 +3406,10 @@
       </c>
       <c r="G3" s="27" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>库存遗失，无法发货</t>
         </is>
       </c>
       <c r="H3" s="27" t="inlineStr">
-        <is>
-          <t>库存遗失，无法发货</t>
-        </is>
-      </c>
-      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>已重新采购3个（3316979100148008960），销售订单转关联新批次</t>
         </is>
@@ -3641,9 +3630,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="E5:I5"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2660,25 +2660,76 @@
       </c>
       <c r="N25" s="27" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="30" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J26" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K26" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L26" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>249-2682748-9036611</t>
+        </is>
+      </c>
+      <c r="N26" s="27" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 25,581</t>
-        </is>
-      </c>
-      <c r="M27" s="32" t="inlineStr">
-        <is>
-          <t>23 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 27,254</t>
+        </is>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>24 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
@@ -2855,9 +2906,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="M28:N28"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3002,29 +3053,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.67</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46244</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -3034,25 +3085,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -3066,25 +3117,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>20</v>
+        <v>6.67</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46244.33587962963</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46221</v>
+        <v>46252</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3100,7 +3151,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4460,49 +4511,82 @@
       </c>
       <c r="B25" s="36" t="inlineStr">
         <is>
+          <t>3316792152573008960</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>249-2682748-9036611</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F25" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="29" t="n">
+      <c r="F26" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H25" s="34" t="n">
+      <c r="H26" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="30" t="inlineStr">
+    <row r="27"/>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G27" s="31" t="n">
-        <v>133.28</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>25581</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="G28" s="31" t="n">
+        <v>139.95</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>27254</v>
+      </c>
+    </row>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
@@ -4679,7 +4763,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4727,8 +4811,10 @@
     <hyperlink ref="C23" location="'📤销售表'!A19" display="249-8279106-7397442"/>
     <hyperlink ref="B24" location="'📥进货表'!A9" display="3316792152573008960"/>
     <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
-    <hyperlink ref="B25" location="'📥进货表'!A11" display="3316979100148008960"/>
-    <hyperlink ref="C25" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="B25" location="'📥进货表'!A9" display="3316792152573008960"/>
+    <hyperlink ref="C25" location="'📤销售表'!A26" display="249-2682748-9036611"/>
+    <hyperlink ref="B26" location="'📥进货表'!A11" display="3316979100148008960"/>
+    <hyperlink ref="C26" location="'📤销售表'!A25" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>6.08</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="F3" s="27" t="inlineStr">
         <is>
-          <t>3314878984043005675</t>
+          <t>3314711712867008960</t>
         </is>
       </c>
       <c r="G3" s="27" t="inlineStr">

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3450,7 +3450,7 @@
       <c r="E3" s="33" t="n">
         <v>46251</v>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>3314711712867008960</t>
         </is>
@@ -3685,6 +3685,9 @@
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F3" location="'📥进货表'!A5" display="3314711712867008960"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3368,17 +3368,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3411,20 +3412,25 @@
       </c>
       <c r="E2" s="24" t="inlineStr">
         <is>
+          <t>遗失成本(元)</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
           <t>遗失时间</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>关联采购订单号</t>
         </is>
       </c>
-      <c r="G2" s="24" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>遗失原因</t>
         </is>
       </c>
-      <c r="H2" s="24" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -3447,20 +3453,23 @@
       <c r="D3" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="33" t="n">
+      <c r="E3" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="33" t="n">
         <v>46251</v>
       </c>
-      <c r="F3" s="36" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>3314711712867008960</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>库存遗失，无法发货</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>已重新采购3个（3316979100148008960），销售订单转关联新批次</t>
         </is>
@@ -3476,7 +3485,10 @@
       <c r="D5" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>1 笔遗失记录</t>
         </is>
@@ -3681,12 +3693,12 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F5:I5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F3" location="'📥进货表'!A5" display="3314711712867008960"/>
+    <hyperlink ref="G3" location="'📥进货表'!A5" display="3314711712867008960"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2712,25 +2712,76 @@
       </c>
       <c r="N26" s="27" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J27" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K27" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L27" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>250-3702632-4431839</t>
+        </is>
+      </c>
+      <c r="N27" s="27" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I28" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 27,254</t>
-        </is>
-      </c>
-      <c r="M28" s="32" t="inlineStr">
-        <is>
-          <t>24 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 28,927</t>
+        </is>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>25 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
@@ -2906,9 +2957,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="I29:L29"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4588,21 +4639,54 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>250-3702632-4431839</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G28" s="31" t="n">
+      <c r="G29" s="31" t="n">
         <v>139.95</v>
       </c>
-      <c r="H28" s="35" t="n">
-        <v>27254</v>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="H29" s="35" t="n">
+        <v>28927</v>
+      </c>
+    </row>
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
@@ -4778,7 +4862,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4830,6 +4914,7 @@
     <hyperlink ref="C25" location="'📤销售表'!A26" display="249-2682748-9036611"/>
     <hyperlink ref="B26" location="'📥进货表'!A11" display="3316979100148008960"/>
     <hyperlink ref="C26" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="C27" location="'📤销售表'!A27" display="250-3702632-4431839"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>6.08</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1113,55 +1113,96 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>46251.90046296296</v>
+        <v>46252.65864583333</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="F11" s="28" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>缺货补货（订单250-3702632-4431839待发）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>46251.90046296296</v>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX玻璃修复膏</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>50g+海绵</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="29" t="n">
         <v>18.5</v>
       </c>
-      <c r="H11" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="I11" s="29" t="n">
+      <c r="I12" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>补货3个（旧批次库存遗失补货）</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G13" s="31" t="n">
-        <v>202.5</v>
-      </c>
-      <c r="H13" s="32" t="inlineStr">
-        <is>
-          <t>9 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="G14" s="31" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>10 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
@@ -1352,9 +1393,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="H14:J14"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3104,29 +3145,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46252.65864583333</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46252</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -3136,25 +3177,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -3168,25 +3209,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>6.67</v>
+        <v>20</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46244.33587962963</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46252</v>
+        <v>46221</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3202,7 +3243,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4611,66 +4652,66 @@
       </c>
       <c r="B26" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C26" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H26" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="H27" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28"/>
@@ -4681,7 +4722,7 @@
         </is>
       </c>
       <c r="G29" s="31" t="n">
-        <v>139.95</v>
+        <v>146.28</v>
       </c>
       <c r="H29" s="35" t="n">
         <v>28927</v>
@@ -4912,9 +4953,10 @@
     <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
     <hyperlink ref="B25" location="'📥进货表'!A9" display="3316792152573008960"/>
     <hyperlink ref="C25" location="'📤销售表'!A26" display="249-2682748-9036611"/>
-    <hyperlink ref="B26" location="'📥进货表'!A11" display="3316979100148008960"/>
-    <hyperlink ref="C26" location="'📤销售表'!A25" display="249-9105063-4908645"/>
-    <hyperlink ref="C27" location="'📤销售表'!A27" display="250-3702632-4431839"/>
+    <hyperlink ref="B26" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C26" location="'📤销售表'!A27" display="250-3702632-4431839"/>
+    <hyperlink ref="B27" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C27" location="'📤销售表'!A25" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2805,25 +2805,76 @@
       </c>
       <c r="N27" s="27" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J28" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K28" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L28" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>250-9517256-2524664</t>
+        </is>
+      </c>
+      <c r="N28" s="27" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 28,927</t>
-        </is>
-      </c>
-      <c r="M29" s="32" t="inlineStr">
-        <is>
-          <t>25 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 30,600</t>
+        </is>
+      </c>
+      <c r="M30" s="32" t="inlineStr">
+        <is>
+          <t>26 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="31"/>
     <row r="32"/>
     <row r="33"/>
@@ -2998,9 +3049,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3154,7 +3205,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>6.5</v>
@@ -3163,11 +3214,11 @@
         <v>46252.65864583333</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3294,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4686,49 +4737,82 @@
       </c>
       <c r="B27" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>250-9517256-2524664</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F27" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="29" t="n">
+      <c r="F28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H27" s="34" t="n">
+      <c r="H28" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="29"/>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G29" s="31" t="n">
-        <v>146.28</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>28927</v>
-      </c>
-    </row>
-    <row r="30"/>
+      <c r="G30" s="31" t="n">
+        <v>152.61</v>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>30600</v>
+      </c>
+    </row>
     <row r="31"/>
     <row r="32"/>
     <row r="33"/>
@@ -4903,7 +4987,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -4955,8 +5039,10 @@
     <hyperlink ref="C25" location="'📤销售表'!A26" display="249-2682748-9036611"/>
     <hyperlink ref="B26" location="'📥进货表'!A11" display="3316370306219008960"/>
     <hyperlink ref="C26" location="'📤销售表'!A27" display="250-3702632-4431839"/>
-    <hyperlink ref="B27" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C27" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="B27" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C27" location="'📤销售表'!A28" display="250-9517256-2524664"/>
+    <hyperlink ref="B28" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C28" location="'📤销售表'!A25" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2857,25 +2857,76 @@
       </c>
       <c r="N28" s="27" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J29" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K29" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L29" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="N29" s="27" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I30" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 30,600</t>
-        </is>
-      </c>
-      <c r="M30" s="32" t="inlineStr">
-        <is>
-          <t>26 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 32,273</t>
+        </is>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>27 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="32"/>
     <row r="33"/>
     <row r="34"/>
@@ -3049,9 +3100,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3196,29 +3247,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46252.65864583333</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46253</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -3228,25 +3279,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -3260,25 +3311,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>20</v>
+        <v>6.5</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46252.65864583333</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46221</v>
+        <v>46253</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3294,7 +3345,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4771,49 +4822,82 @@
       </c>
       <c r="B28" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C28" s="36" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="29" t="n">
+      <c r="F29" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H28" s="34" t="n">
+      <c r="H29" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="30"/>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G30" s="31" t="n">
-        <v>152.61</v>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>30600</v>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="G31" s="31" t="n">
+        <v>158.94</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>32273</v>
+      </c>
+    </row>
     <row r="32"/>
     <row r="33"/>
     <row r="34"/>
@@ -4987,7 +5071,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5041,8 +5125,10 @@
     <hyperlink ref="C26" location="'📤销售表'!A27" display="250-3702632-4431839"/>
     <hyperlink ref="B27" location="'📥进货表'!A11" display="3316370306219008960"/>
     <hyperlink ref="C27" location="'📤销售表'!A28" display="250-9517256-2524664"/>
-    <hyperlink ref="B28" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C28" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="B28" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C28" location="'📤销售表'!A29" display="250-1884634-9513463"/>
+    <hyperlink ref="B29" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C29" location="'📤销售表'!A25" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2659,44 +2659,44 @@
         </is>
       </c>
       <c r="C25" s="33" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="D25" s="33" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>1X-GB0W-BY30</t>
+          <t>ba0010</t>
         </is>
       </c>
       <c r="H25" s="28" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="34" t="n">
-        <v>1122</v>
+        <v>699</v>
       </c>
       <c r="J25" s="34" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="L25" s="34" t="n">
-        <v>1005</v>
+        <v>929</v>
       </c>
       <c r="M25" s="25" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>249-7625220-2616668</t>
         </is>
       </c>
       <c r="N25" s="27" t="n"/>
@@ -2711,44 +2711,44 @@
         </is>
       </c>
       <c r="C26" s="33" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D26" s="33" t="n">
         <v>46252</v>
       </c>
-      <c r="D26" s="33" t="n">
-        <v>46254</v>
-      </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>asd159</t>
+          <t>1X-GB0W-BY30</t>
         </is>
       </c>
       <c r="H26" s="28" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>1468</v>
+        <v>1122</v>
       </c>
       <c r="J26" s="34" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="L26" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
       <c r="M26" s="25" t="inlineStr">
         <is>
-          <t>249-2682748-9036611</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="N26" s="27" t="n"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M27" s="25" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>249-2682748-9036611</t>
         </is>
       </c>
       <c r="N27" s="27" t="n"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="C28" s="33" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="D28" s="33" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="M28" s="25" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="N28" s="27" t="n"/>
@@ -2904,30 +2904,81 @@
       </c>
       <c r="M29" s="25" t="inlineStr">
         <is>
+          <t>250-9517256-2524664</t>
+        </is>
+      </c>
+      <c r="N29" s="27" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H30" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J30" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K30" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L30" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
           <t>250-1884634-9513463</t>
         </is>
       </c>
-      <c r="N29" s="27" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="N30" s="27" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I31" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 32,273</t>
-        </is>
-      </c>
-      <c r="M31" s="32" t="inlineStr">
-        <is>
-          <t>27 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 33,202</t>
+        </is>
+      </c>
+      <c r="M32" s="32" t="inlineStr">
+        <is>
+          <t>28 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
@@ -3100,9 +3151,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="I32:L32"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3192,7 +3243,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3201,11 +3252,11 @@
         <v>46247</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (9个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3396,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4754,32 +4805,32 @@
       </c>
       <c r="B26" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C26" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>249-7625220-2616668</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H26" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -4793,7 +4844,7 @@
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -4827,7 +4878,7 @@
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -4856,49 +4907,82 @@
       </c>
       <c r="B29" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F29" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="29" t="n">
+      <c r="F30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H29" s="34" t="n">
+      <c r="H30" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G31" s="31" t="n">
-        <v>158.94</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>32273</v>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="G32" s="31" t="n">
+        <v>163.82</v>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>33202</v>
+      </c>
+    </row>
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
@@ -5071,7 +5155,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5120,15 +5204,17 @@
     <hyperlink ref="B24" location="'📥进货表'!A9" display="3316792152573008960"/>
     <hyperlink ref="C24" location="'📤销售表'!A20" display="503-5134375-2874203"/>
     <hyperlink ref="B25" location="'📥进货表'!A9" display="3316792152573008960"/>
-    <hyperlink ref="C25" location="'📤销售表'!A26" display="249-2682748-9036611"/>
-    <hyperlink ref="B26" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C26" location="'📤销售表'!A27" display="250-3702632-4431839"/>
+    <hyperlink ref="C25" location="'📤销售表'!A27" display="249-2682748-9036611"/>
+    <hyperlink ref="B26" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C26" location="'📤销售表'!A25" display="249-7625220-2616668"/>
     <hyperlink ref="B27" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C27" location="'📤销售表'!A28" display="250-9517256-2524664"/>
+    <hyperlink ref="C27" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B28" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C28" location="'📤销售表'!A29" display="250-1884634-9513463"/>
-    <hyperlink ref="B29" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C29" location="'📤销售表'!A25" display="249-9105063-4908645"/>
+    <hyperlink ref="C28" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B29" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C29" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B30" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C30" location="'📤销售表'!A26" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -2961,25 +2961,76 @@
       </c>
       <c r="N30" s="27" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J31" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K31" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L31" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>250-4176024-0609441</t>
+        </is>
+      </c>
+      <c r="N31" s="27" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I32" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 33,202</t>
-        </is>
-      </c>
-      <c r="M32" s="32" t="inlineStr">
-        <is>
-          <t>28 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 34,131</t>
+        </is>
+      </c>
+      <c r="M33" s="32" t="inlineStr">
+        <is>
+          <t>29 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
@@ -3151,9 +3202,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3243,7 +3294,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3256,7 +3307,7 @@
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (8个)</t>
+          <t>库存充足 (7个)</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3447,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4839,32 +4890,32 @@
       </c>
       <c r="B27" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>250-4176024-0609441</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H27" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -4878,7 +4929,7 @@
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -4912,7 +4963,7 @@
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
@@ -4941,49 +4992,82 @@
       </c>
       <c r="B30" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="29" t="n">
+      <c r="F31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H30" s="34" t="n">
+      <c r="H31" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+    <row r="32"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G32" s="31" t="n">
-        <v>163.82</v>
-      </c>
-      <c r="H32" s="35" t="n">
-        <v>33202</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="G33" s="31" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>34131</v>
+      </c>
+    </row>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
@@ -5155,7 +5239,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5207,14 +5291,16 @@
     <hyperlink ref="C25" location="'📤销售表'!A27" display="249-2682748-9036611"/>
     <hyperlink ref="B26" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C26" location="'📤销售表'!A25" display="249-7625220-2616668"/>
-    <hyperlink ref="B27" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C27" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B27" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C27" location="'📤销售表'!A31" display="250-4176024-0609441"/>
     <hyperlink ref="B28" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C28" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="C28" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B29" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C29" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B30" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C30" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="C29" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B30" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C30" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B31" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C31" location="'📤销售表'!A26" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3013,25 +3013,76 @@
       </c>
       <c r="N31" s="27" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D32" s="33" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J32" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K32" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L32" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M32" s="25" t="inlineStr">
+        <is>
+          <t>503-8642770-5227060</t>
+        </is>
+      </c>
+      <c r="N32" s="27" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I33" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 34,131</t>
-        </is>
-      </c>
-      <c r="M33" s="32" t="inlineStr">
-        <is>
-          <t>29 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
+      <c r="I34" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 35,060</t>
+        </is>
+      </c>
+      <c r="M34" s="32" t="inlineStr">
+        <is>
+          <t>30 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
@@ -3202,9 +3253,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="I34:L34"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3294,7 +3345,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3307,7 +3358,7 @@
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (7个)</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3498,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -4924,32 +4975,32 @@
       </c>
       <c r="B28" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>503-8642770-5227060</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -4963,7 +5014,7 @@
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
@@ -4997,7 +5048,7 @@
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -5026,49 +5077,82 @@
       </c>
       <c r="B31" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E31" s="27" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F31" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="29" t="n">
+      <c r="F32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H31" s="34" t="n">
+      <c r="H32" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
+    <row r="33"/>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G33" s="31" t="n">
-        <v>168.7</v>
-      </c>
-      <c r="H33" s="35" t="n">
-        <v>34131</v>
-      </c>
-    </row>
-    <row r="34"/>
+      <c r="G34" s="31" t="n">
+        <v>173.58</v>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>35060</v>
+      </c>
+    </row>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
@@ -5239,7 +5323,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5293,14 +5377,16 @@
     <hyperlink ref="C26" location="'📤销售表'!A25" display="249-7625220-2616668"/>
     <hyperlink ref="B27" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C27" location="'📤销售表'!A31" display="250-4176024-0609441"/>
-    <hyperlink ref="B28" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C28" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B28" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C28" location="'📤销售表'!A32" display="503-8642770-5227060"/>
     <hyperlink ref="B29" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C29" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="C29" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B30" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C30" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B31" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C31" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="C30" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B31" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C31" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B32" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C32" location="'📤销售表'!A26" display="249-9105063-4908645"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1187,23 +1187,64 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>46255.43991898148</v>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX塑料除黄剂</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>100ml+毛巾</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="27" t="inlineStr">
+        <is>
+          <t>除黄剂补货3个</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G14" s="31" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="H14" s="32" t="inlineStr">
-        <is>
-          <t>10 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="G15" s="31" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>11 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
@@ -1393,9 +1434,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H15:J15"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3065,26 +3106,128 @@
       </c>
       <c r="N32" s="27" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J33" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K33" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L33" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M33" s="25" t="inlineStr">
+        <is>
+          <t>250-3896584-8818260</t>
+        </is>
+      </c>
+      <c r="N33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H34" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J34" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K34" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L34" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M34" s="25" t="inlineStr">
+        <is>
+          <t>249-9065958-6465408</t>
+        </is>
+      </c>
+      <c r="N34" s="27" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I34" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 35,060</t>
-        </is>
-      </c>
-      <c r="M34" s="32" t="inlineStr">
-        <is>
-          <t>30 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
+      <c r="I36" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 37,662</t>
+        </is>
+      </c>
+      <c r="M36" s="32" t="inlineStr">
+        <is>
+          <t>32 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
@@ -3253,9 +3396,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3345,7 +3488,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3358,7 +3501,7 @@
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -3400,29 +3543,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46255.43991898148</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46254</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -3432,25 +3575,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -3464,25 +3607,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>6.5</v>
+        <v>20</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46252.65864583333</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46253</v>
+        <v>46221</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -3498,7 +3641,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -5009,32 +5152,32 @@
       </c>
       <c r="B29" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>249-9065958-6465408</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H29" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -5048,7 +5191,7 @@
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -5082,7 +5225,7 @@
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
@@ -5111,50 +5254,116 @@
       </c>
       <c r="B32" s="36" t="inlineStr">
         <is>
+          <t>3316370306219008960</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>250-1884634-9513463</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H32" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
           <t>3316979100148008960</t>
         </is>
       </c>
-      <c r="C32" s="36" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>249-9105063-4908645</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="29" t="n">
+      <c r="F33" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="29" t="n">
         <v>6.17</v>
       </c>
-      <c r="H32" s="34" t="n">
+      <c r="H33" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>250-3896584-8818260</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G34" s="31" t="n">
-        <v>173.58</v>
-      </c>
-      <c r="H34" s="35" t="n">
-        <v>35060</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
+      <c r="G36" s="31" t="n">
+        <v>185.46</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>37662</v>
+      </c>
+    </row>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
@@ -5323,7 +5532,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5379,14 +5588,18 @@
     <hyperlink ref="C27" location="'📤销售表'!A31" display="250-4176024-0609441"/>
     <hyperlink ref="B28" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C28" location="'📤销售表'!A32" display="503-8642770-5227060"/>
-    <hyperlink ref="B29" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C29" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B29" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C29" location="'📤销售表'!A34" display="249-9065958-6465408"/>
     <hyperlink ref="B30" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C30" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="C30" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B31" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C31" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B32" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C32" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="C31" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B32" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C32" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B33" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C33" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="B34" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C34" location="'📤销售表'!A33" display="250-3896584-8818260"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
